--- a/Översikt SURAHAMMAR.xlsx
+++ b/Översikt SURAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45470</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>45684</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 31280-2024</t>
+          <t>A 39697-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45504</v>
+        <v>45890</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,23 +964,23 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>6.9</v>
+        <v>25.7</v>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="K4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -992,21 +992,182 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="R4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
         <v>44</v>
       </c>
       <c r="T4" t="n">
+        <v>240</v>
+      </c>
+      <c r="U4" t="n">
+        <v>104</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Grönfink
+Knärot
+Bivråk
+Brunlångöra
+Dropptaggsvamp
+Fjällig taggsvamp s.str.
+Järnsparv
+Motaggsvamp
+Nordfladdermus
+Skarp dropptaggsvamp
+Skogshare
+Sotvaxskivling
+Sparvuggla
+Stornopping
+Talltita
+Älg
+Blodvaxing
+Gulgrön kantmusseron
+Honungsvaxing
+Luktvaxing
+Mindre märgborre
+Smal svampklubba
+Vedticka
+Gråspett
+Järpe
+Liljekonvalj
+Mattlummer
+Nattskärra
+Spillkråka
+Tjäder
+Tofsmes
+Dvärgpipistrell
+Gröngöling
+Kungsfågel
+Orre
+Slaguggla
+Större brunfladdermus
+Sångsvan
+Trana
+Trollpipistrell
+Vattenfladdermus
+Vanlig groda
+Fläcknycklar
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39697-2025 artfynd.xlsx", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39697-2025 karta.png", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39697-2025 georefererad karta.tif", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="Z4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 39697-2025 karta knärot.png", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39697-2025 FSC-klagomål.docx", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39697-2025 FSC-klagomål mail.docx", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39697-2025 tillsynsbegäran.docx", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39697-2025 tillsynsbegäran mail.docx", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39697-2025 prioriterade fågelarter.docx", "A 39697-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 31280-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45504</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K5" t="n">
+        <v>12</v>
+      </c>
+      <c r="L5" t="n">
+        <v>22</v>
+      </c>
+      <c r="M5" t="n">
+        <v>5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>27</v>
+      </c>
+      <c r="R5" t="n">
+        <v>5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>44</v>
+      </c>
+      <c r="T5" t="n">
         <v>93</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>91</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Gränsticka
 Knärot
@@ -1054,201 +1215,40 @@
 Lopplummer (aggregat)</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31280-2024 artfynd.xlsx", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31280-2024 karta.png", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31280-2024 georefererad karta.tif", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="Z4">
+      <c r="Z5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 31280-2024 karta knärot.png", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31280-2024 FSC-klagomål.docx", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31280-2024 FSC-klagomål mail.docx", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31280-2024 tillsynsbegäran.docx", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31280-2024 tillsynsbegäran mail.docx", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 31280-2024 prioriterade fågelarter.docx", "A 31280-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 39697-2025</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45890</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>28</v>
-      </c>
-      <c r="K5" t="n">
-        <v>7</v>
-      </c>
-      <c r="L5" t="n">
-        <v>14</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>16</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2</v>
-      </c>
-      <c r="S5" t="n">
-        <v>44</v>
-      </c>
-      <c r="T5" t="n">
-        <v>240</v>
-      </c>
-      <c r="U5" t="n">
-        <v>104</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Grönfink
-Knärot
-Bivråk
-Brunlångöra
-Dropptaggsvamp
-Fjällig taggsvamp s.str.
-Järnsparv
-Motaggsvamp
-Nordfladdermus
-Skarp dropptaggsvamp
-Skogshare
-Sotvaxskivling
-Sparvuggla
-Stornopping
-Talltita
-Älg
-Blodvaxing
-Gulgrön kantmusseron
-Honungsvaxing
-Luktvaxing
-Mindre märgborre
-Smal svampklubba
-Vedticka
-Gråspett
-Järpe
-Liljekonvalj
-Mattlummer
-Nattskärra
-Spillkråka
-Tjäder
-Tofsmes
-Dvärgpipistrell
-Gröngöling
-Kungsfågel
-Orre
-Slaguggla
-Större brunfladdermus
-Sångsvan
-Trana
-Trollpipistrell
-Vattenfladdermus
-Vanlig groda
-Fläcknycklar
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39697-2025 artfynd.xlsx", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39697-2025 karta.png", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39697-2025 georefererad karta.tif", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="Z5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 39697-2025 karta knärot.png", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39697-2025 FSC-klagomål.docx", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39697-2025 FSC-klagomål mail.docx", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39697-2025 tillsynsbegäran.docx", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39697-2025 tillsynsbegäran mail.docx", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39697-2025 prioriterade fågelarter.docx", "A 39697-2025")</f>
         <v/>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
         <v>45582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45169</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45139</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45782</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>45282</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>46216</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>46216</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>46237</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>44613</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>46085</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 20389-2024</t>
+          <t>A 31059-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45435</v>
+        <v>46215</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2596,23 +2596,28 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K16" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2621,7 +2626,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
@@ -2630,12 +2635,133 @@
         <v>13</v>
       </c>
       <c r="T16" t="n">
+        <v>26</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Bombmurkla
+Brunlångöra
+Dofttaggsvamp
+Nordfladdermus
+Talltita
+Vårärt
+Grönkulla
+Blåsippa
+Dvärgpipistrell
+Åkergroda
+Nattviol
+Lopplummer (aggregat)
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31059-2026 artfynd.xlsx", "A 31059-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31059-2026 karta.png", "A 31059-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31059-2026 georefererad karta.tif", "A 31059-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31059-2026 FSC-klagomål.docx", "A 31059-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31059-2026 FSC-klagomål mail.docx", "A 31059-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31059-2026 tillsynsbegäran.docx", "A 31059-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31059-2026 tillsynsbegäran mail.docx", "A 31059-2026")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 31059-2026 prioriterade fågelarter.docx", "A 31059-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 20389-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45435</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>7</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>13</v>
+      </c>
+      <c r="T17" t="n">
         <v>32</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>29</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Gropticka
@@ -2652,166 +2778,40 @@
 Havsörn</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 20389-2024 artfynd.xlsx", "A 20389-2024")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 20389-2024 karta.png", "A 20389-2024")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 20389-2024 georefererad karta.tif", "A 20389-2024")</f>
         <v/>
       </c>
-      <c r="Z16">
+      <c r="Z17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 20389-2024 karta knärot.png", "A 20389-2024")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 20389-2024 FSC-klagomål.docx", "A 20389-2024")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 20389-2024 FSC-klagomål mail.docx", "A 20389-2024")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 20389-2024 tillsynsbegäran.docx", "A 20389-2024")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 20389-2024 tillsynsbegäran mail.docx", "A 20389-2024")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 20389-2024 prioriterade fågelarter.docx", "A 20389-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 31059-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46215</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>11</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>5</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>6</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>13</v>
-      </c>
-      <c r="T17" t="n">
-        <v>26</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Bombmurkla
-Brunlångöra
-Dofttaggsvamp
-Nordfladdermus
-Talltita
-Vårärt
-Grönkulla
-Blåsippa
-Dvärgpipistrell
-Åkergroda
-Nattviol
-Lopplummer (aggregat)
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31059-2026 artfynd.xlsx", "A 31059-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31059-2026 karta.png", "A 31059-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31059-2026 georefererad karta.tif", "A 31059-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31059-2026 FSC-klagomål.docx", "A 31059-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31059-2026 FSC-klagomål mail.docx", "A 31059-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31059-2026 tillsynsbegäran.docx", "A 31059-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31059-2026 tillsynsbegäran mail.docx", "A 31059-2026")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 31059-2026 prioriterade fågelarter.docx", "A 31059-2026")</f>
         <v/>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
         <v>46111</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>45890</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>44832</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45523</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>45070</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 44798-2024</t>
+          <t>A 31060-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3451,10 +3451,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45574</v>
+        <v>46215</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3468,26 +3468,26 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3496,7 +3496,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
         <v>1</v>
@@ -3505,12 +3505,134 @@
         <v>9</v>
       </c>
       <c r="T23" t="n">
+        <v>9</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Bombmurkla
+Brunlångöra
+Nordfladdermus
+Springkorn
+Vedticka
+Spillkråka
+Dvärgpipistrell
+Åkergroda
+Vanlig groda</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31060-2026 artfynd.xlsx", "A 31060-2026")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31060-2026 karta.png", "A 31060-2026")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31060-2026 georefererad karta.tif", "A 31060-2026")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31060-2026 FSC-klagomål.docx", "A 31060-2026")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31060-2026 FSC-klagomål mail.docx", "A 31060-2026")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31060-2026 tillsynsbegäran.docx", "A 31060-2026")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31060-2026 tillsynsbegäran mail.docx", "A 31060-2026")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 31060-2026 prioriterade fågelarter.docx", "A 31060-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 44798-2024</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>45574</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>7</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>8</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>9</v>
+      </c>
+      <c r="T24" t="n">
         <v>26</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U24" t="n">
         <v>10</v>
       </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Rosetticka
 Brunklöver
@@ -3523,154 +3645,32 @@
 Brandticka</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 44798-2024 artfynd.xlsx", "A 44798-2024")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 44798-2024 karta.png", "A 44798-2024")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 44798-2024 georefererad karta.tif", "A 44798-2024")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 44798-2024 FSC-klagomål.docx", "A 44798-2024")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 44798-2024 FSC-klagomål mail.docx", "A 44798-2024")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 44798-2024 tillsynsbegäran.docx", "A 44798-2024")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 44798-2024 tillsynsbegäran mail.docx", "A 44798-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 31060-2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>46215</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J24" t="n">
-        <v>7</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2</v>
-      </c>
-      <c r="L24" t="n">
-        <v>2</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" t="n">
-        <v>9</v>
-      </c>
-      <c r="T24" t="n">
-        <v>9</v>
-      </c>
-      <c r="U24" t="n">
-        <v>3</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Bombmurkla
-Brunlångöra
-Nordfladdermus
-Springkorn
-Vedticka
-Spillkråka
-Dvärgpipistrell
-Åkergroda
-Vanlig groda</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31060-2026 artfynd.xlsx", "A 31060-2026")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31060-2026 karta.png", "A 31060-2026")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31060-2026 georefererad karta.tif", "A 31060-2026")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31060-2026 FSC-klagomål.docx", "A 31060-2026")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31060-2026 FSC-klagomål mail.docx", "A 31060-2026")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31060-2026 tillsynsbegäran.docx", "A 31060-2026")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31060-2026 tillsynsbegäran mail.docx", "A 31060-2026")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 31060-2026 prioriterade fågelarter.docx", "A 31060-2026")</f>
         <v/>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
         <v>45435</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>44518</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>44477</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>45203</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 22840-2023</t>
+          <t>A 36260-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45072</v>
+        <v>46268</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4186,21 +4186,26 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="J29" t="n">
+        <v>4</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
         <v>2</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
@@ -4211,21 +4216,136 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S29" t="n">
         <v>7</v>
       </c>
       <c r="T29" t="n">
+        <v>8</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare
+Silverblåvinge
+Enkelbeckasin
+Blodticka
+Nattskärra
+Vanlig snok
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 36260-2026 artfynd.xlsx", "A 36260-2026")</f>
+        <v/>
+      </c>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 36260-2026 karta.png", "A 36260-2026")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 36260-2026 georefererad karta.tif", "A 36260-2026")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 36260-2026 FSC-klagomål.docx", "A 36260-2026")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 36260-2026 FSC-klagomål mail.docx", "A 36260-2026")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 36260-2026 tillsynsbegäran.docx", "A 36260-2026")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 36260-2026 tillsynsbegäran mail.docx", "A 36260-2026")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 36260-2026 prioriterade fågelarter.docx", "A 36260-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A 22840-2023</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>45072</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>7</v>
+      </c>
+      <c r="T30" t="n">
         <v>10</v>
       </c>
-      <c r="U29" t="n">
+      <c r="U30" t="n">
         <v>9</v>
       </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>Hultbräken
 Kärrviol
@@ -4236,152 +4356,32 @@
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W29">
+      <c r="W30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 22840-2023 artfynd.xlsx", "A 22840-2023")</f>
         <v/>
       </c>
-      <c r="X29">
+      <c r="X30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 22840-2023 karta.png", "A 22840-2023")</f>
         <v/>
       </c>
-      <c r="Y29">
+      <c r="Y30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 22840-2023 georefererad karta.tif", "A 22840-2023")</f>
         <v/>
       </c>
-      <c r="AA29">
+      <c r="AA30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 22840-2023 FSC-klagomål.docx", "A 22840-2023")</f>
         <v/>
       </c>
-      <c r="AB29">
+      <c r="AB30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 22840-2023 FSC-klagomål mail.docx", "A 22840-2023")</f>
         <v/>
       </c>
-      <c r="AC29">
+      <c r="AC30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 22840-2023 tillsynsbegäran.docx", "A 22840-2023")</f>
         <v/>
       </c>
-      <c r="AD29">
+      <c r="AD30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 22840-2023 tillsynsbegäran mail.docx", "A 22840-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>A 36260-2026</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>46268</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J30" t="n">
-        <v>4</v>
-      </c>
-      <c r="K30" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" t="n">
-        <v>2</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3</v>
-      </c>
-      <c r="R30" t="n">
-        <v>2</v>
-      </c>
-      <c r="S30" t="n">
-        <v>7</v>
-      </c>
-      <c r="T30" t="n">
-        <v>8</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Mindre bastardsvärmare
-Silverblåvinge
-Enkelbeckasin
-Blodticka
-Nattskärra
-Vanlig snok
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 36260-2026 artfynd.xlsx", "A 36260-2026")</f>
-        <v/>
-      </c>
-      <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 36260-2026 karta.png", "A 36260-2026")</f>
-        <v/>
-      </c>
-      <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 36260-2026 georefererad karta.tif", "A 36260-2026")</f>
-        <v/>
-      </c>
-      <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 36260-2026 FSC-klagomål.docx", "A 36260-2026")</f>
-        <v/>
-      </c>
-      <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 36260-2026 FSC-klagomål mail.docx", "A 36260-2026")</f>
-        <v/>
-      </c>
-      <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 36260-2026 tillsynsbegäran.docx", "A 36260-2026")</f>
-        <v/>
-      </c>
-      <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 36260-2026 tillsynsbegäran mail.docx", "A 36260-2026")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 36260-2026 prioriterade fågelarter.docx", "A 36260-2026")</f>
         <v/>
       </c>
     </row>
@@ -4405,7 +4405,7 @@
         <v>45545</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>45945</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>44518</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10236-2026</t>
+          <t>A 63145-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4760,10 +4760,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46076</v>
+        <v>46009</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4777,23 +4777,23 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.8</v>
+        <v>40.5</v>
       </c>
       <c r="J34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
         <v>2</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -4805,10 +4805,10 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
         <v>6</v>
@@ -4820,6 +4820,125 @@
         <v>0</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril
+Mindre hackspett
+Talltita
+Svart trolldruva
+Kungsfågel
+Nattviol</t>
+        </is>
+      </c>
+      <c r="W34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63145-2025 artfynd.xlsx", "A 63145-2025")</f>
+        <v/>
+      </c>
+      <c r="X34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63145-2025 karta.png", "A 63145-2025")</f>
+        <v/>
+      </c>
+      <c r="Y34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63145-2025 georefererad karta.tif", "A 63145-2025")</f>
+        <v/>
+      </c>
+      <c r="AA34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63145-2025 FSC-klagomål.docx", "A 63145-2025")</f>
+        <v/>
+      </c>
+      <c r="AB34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63145-2025 FSC-klagomål mail.docx", "A 63145-2025")</f>
+        <v/>
+      </c>
+      <c r="AC34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63145-2025 tillsynsbegäran.docx", "A 63145-2025")</f>
+        <v/>
+      </c>
+      <c r="AD34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63145-2025 tillsynsbegäran mail.docx", "A 63145-2025")</f>
+        <v/>
+      </c>
+      <c r="AE34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 63145-2025 prioriterade fågelarter.docx", "A 63145-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>A 10236-2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>46076</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2</v>
+      </c>
+      <c r="L35" t="n">
+        <v>2</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>6</v>
+      </c>
+      <c r="T35" t="n">
+        <v>13</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>Gullpudra
 Vågticka
@@ -4829,151 +4948,32 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W34">
+      <c r="W35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 10236-2026 artfynd.xlsx", "A 10236-2026")</f>
         <v/>
       </c>
-      <c r="X34">
+      <c r="X35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 10236-2026 karta.png", "A 10236-2026")</f>
         <v/>
       </c>
-      <c r="Y34">
+      <c r="Y35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 10236-2026 georefererad karta.tif", "A 10236-2026")</f>
         <v/>
       </c>
-      <c r="AA34">
+      <c r="AA35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 10236-2026 FSC-klagomål.docx", "A 10236-2026")</f>
         <v/>
       </c>
-      <c r="AB34">
+      <c r="AB35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 10236-2026 FSC-klagomål mail.docx", "A 10236-2026")</f>
         <v/>
       </c>
-      <c r="AC34">
+      <c r="AC35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 10236-2026 tillsynsbegäran.docx", "A 10236-2026")</f>
         <v/>
       </c>
-      <c r="AD34">
+      <c r="AD35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 10236-2026 tillsynsbegäran mail.docx", "A 10236-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>A 63145-2025</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>46009</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="J35" t="n">
-        <v>5</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" t="n">
-        <v>2</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>3</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1</v>
-      </c>
-      <c r="S35" t="n">
-        <v>6</v>
-      </c>
-      <c r="T35" t="n">
-        <v>13</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>Väddnätfjäril
-Mindre hackspett
-Talltita
-Svart trolldruva
-Kungsfågel
-Nattviol</t>
-        </is>
-      </c>
-      <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63145-2025 artfynd.xlsx", "A 63145-2025")</f>
-        <v/>
-      </c>
-      <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63145-2025 karta.png", "A 63145-2025")</f>
-        <v/>
-      </c>
-      <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63145-2025 georefererad karta.tif", "A 63145-2025")</f>
-        <v/>
-      </c>
-      <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63145-2025 FSC-klagomål.docx", "A 63145-2025")</f>
-        <v/>
-      </c>
-      <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63145-2025 FSC-klagomål mail.docx", "A 63145-2025")</f>
-        <v/>
-      </c>
-      <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63145-2025 tillsynsbegäran.docx", "A 63145-2025")</f>
-        <v/>
-      </c>
-      <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63145-2025 tillsynsbegäran mail.docx", "A 63145-2025")</f>
-        <v/>
-      </c>
-      <c r="AE35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 63145-2025 prioriterade fågelarter.docx", "A 63145-2025")</f>
         <v/>
       </c>
     </row>
@@ -4997,7 +4997,7 @@
         <v>44832</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>44832</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>44565</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>45369</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>45503</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>45463</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>44518</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 69777-2021</t>
+          <t>A 63146-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5796,10 +5796,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44532</v>
+        <v>46009</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5811,8 +5811,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>2.3</v>
+        <v>10.2</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
@@ -5827,7 +5832,7 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5836,611 +5841,606 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
       </c>
       <c r="T43" t="n">
+        <v>12</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>Stor aspticka
+Svart trolldruva
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63146-2025 artfynd.xlsx", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="X43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63146-2025 karta.png", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="Y43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63146-2025 georefererad karta.tif", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="AA43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63146-2025 FSC-klagomål.docx", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="AB43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63146-2025 FSC-klagomål mail.docx", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="AC43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63146-2025 tillsynsbegäran.docx", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="AD43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63146-2025 tillsynsbegäran mail.docx", "A 63146-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>A 39694-2025</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="n">
+        <v>45890</v>
+      </c>
+      <c r="E44" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Mindre märgborre
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39694-2025 artfynd.xlsx", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="X44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39694-2025 karta.png", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="Y44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39694-2025 georefererad karta.tif", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="AA44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39694-2025 FSC-klagomål.docx", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="AB44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39694-2025 FSC-klagomål mail.docx", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="AC44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39694-2025 tillsynsbegäran.docx", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="AD44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39694-2025 tillsynsbegäran mail.docx", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="AE44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39694-2025 prioriterade fågelarter.docx", "A 39694-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>A 49718-2023</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>45212</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>2</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3</v>
+      </c>
+      <c r="T45" t="n">
+        <v>6</v>
+      </c>
+      <c r="U45" t="n">
+        <v>6</v>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Talltita
+Zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="W45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 49718-2023 artfynd.xlsx", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="X45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 49718-2023 karta.png", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="Y45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 49718-2023 georefererad karta.tif", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="AA45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 49718-2023 FSC-klagomål.docx", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="AB45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 49718-2023 FSC-klagomål mail.docx", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="AC45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 49718-2023 tillsynsbegäran.docx", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="AD45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 49718-2023 tillsynsbegäran mail.docx", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="AE45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 49718-2023 prioriterade fågelarter.docx", "A 49718-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>A 42765-2022</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v>44832</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>Krusfrö
+Barkticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 42765-2022 artfynd.xlsx", "A 42765-2022")</f>
+        <v/>
+      </c>
+      <c r="X46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 42765-2022 karta.png", "A 42765-2022")</f>
+        <v/>
+      </c>
+      <c r="Y46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 42765-2022 georefererad karta.tif", "A 42765-2022")</f>
+        <v/>
+      </c>
+      <c r="AA46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 42765-2022 FSC-klagomål.docx", "A 42765-2022")</f>
+        <v/>
+      </c>
+      <c r="AB46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 42765-2022 FSC-klagomål mail.docx", "A 42765-2022")</f>
+        <v/>
+      </c>
+      <c r="AC46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 42765-2022 tillsynsbegäran.docx", "A 42765-2022")</f>
+        <v/>
+      </c>
+      <c r="AD46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 42765-2022 tillsynsbegäran mail.docx", "A 42765-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>A 69777-2021</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>44532</v>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>2</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3</v>
+      </c>
+      <c r="T47" t="n">
         <v>5</v>
       </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
         <is>
           <t>Bombmurkla
 Rävticka
 Vedticka</t>
         </is>
       </c>
-      <c r="W43">
+      <c r="W47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 69777-2021 artfynd.xlsx", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="X43">
+      <c r="X47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 69777-2021 karta.png", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="Y43">
+      <c r="Y47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 69777-2021 georefererad karta.tif", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="AA43">
+      <c r="AA47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 69777-2021 FSC-klagomål.docx", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="AB43">
+      <c r="AB47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 69777-2021 FSC-klagomål mail.docx", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="AC43">
+      <c r="AC47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 69777-2021 tillsynsbegäran.docx", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="AD43">
+      <c r="AD47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 69777-2021 tillsynsbegäran mail.docx", "A 69777-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>A 49718-2023</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>A 4082-2025</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D44" s="1" t="n">
-        <v>45212</v>
-      </c>
-      <c r="E44" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F44" t="inlineStr">
+      <c r="D48" s="1" t="n">
+        <v>45684</v>
+      </c>
+      <c r="E48" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>VÄSTMANLANDS LÄN</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="I44" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J44" t="n">
-        <v>1</v>
-      </c>
-      <c r="K44" t="n">
-        <v>1</v>
-      </c>
-      <c r="L44" t="n">
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J48" t="n">
         <v>2</v>
       </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
+      <c r="K48" t="n">
         <v>2</v>
       </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
         <v>3</v>
       </c>
-      <c r="T44" t="n">
-        <v>6</v>
-      </c>
-      <c r="U44" t="n">
-        <v>6</v>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Talltita
-Zontaggsvamp</t>
-        </is>
-      </c>
-      <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 49718-2023 artfynd.xlsx", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 49718-2023 karta.png", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 49718-2023 georefererad karta.tif", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 49718-2023 FSC-klagomål.docx", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 49718-2023 FSC-klagomål mail.docx", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 49718-2023 tillsynsbegäran.docx", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 49718-2023 tillsynsbegäran mail.docx", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="AE44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 49718-2023 prioriterade fågelarter.docx", "A 49718-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>A 39694-2025</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="n">
-        <v>45890</v>
-      </c>
-      <c r="E45" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J45" t="n">
-        <v>1</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1</v>
-      </c>
-      <c r="L45" t="n">
-        <v>1</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>1</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
+      <c r="T48" t="n">
         <v>3</v>
       </c>
-      <c r="T45" t="n">
-        <v>3</v>
-      </c>
-      <c r="U45" t="n">
-        <v>2</v>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Mindre märgborre
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39694-2025 artfynd.xlsx", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39694-2025 karta.png", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39694-2025 georefererad karta.tif", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39694-2025 FSC-klagomål.docx", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39694-2025 FSC-klagomål mail.docx", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39694-2025 tillsynsbegäran.docx", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39694-2025 tillsynsbegäran mail.docx", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="AE45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39694-2025 prioriterade fågelarter.docx", "A 39694-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>A 63146-2025</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="n">
-        <v>46009</v>
-      </c>
-      <c r="E46" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="J46" t="n">
-        <v>1</v>
-      </c>
-      <c r="K46" t="n">
-        <v>2</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>3</v>
-      </c>
-      <c r="T46" t="n">
-        <v>12</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>Stor aspticka
-Svart trolldruva
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63146-2025 artfynd.xlsx", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63146-2025 karta.png", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63146-2025 georefererad karta.tif", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63146-2025 FSC-klagomål.docx", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63146-2025 FSC-klagomål mail.docx", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63146-2025 tillsynsbegäran.docx", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63146-2025 tillsynsbegäran mail.docx", "A 63146-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>A 4082-2025</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="n">
-        <v>45684</v>
-      </c>
-      <c r="E47" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="J47" t="n">
-        <v>2</v>
-      </c>
-      <c r="K47" t="n">
-        <v>2</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>3</v>
-      </c>
-      <c r="T47" t="n">
-        <v>3</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1</v>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
+      <c r="U48" t="n">
+        <v>1</v>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
         <is>
           <t>Grönpyrola
 Plattlummer
 Lopplummer (aggregat)</t>
         </is>
       </c>
-      <c r="W47">
+      <c r="W48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 4082-2025 artfynd.xlsx", "A 4082-2025")</f>
         <v/>
       </c>
-      <c r="X47">
+      <c r="X48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 4082-2025 karta.png", "A 4082-2025")</f>
         <v/>
       </c>
-      <c r="Y47">
+      <c r="Y48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 4082-2025 georefererad karta.tif", "A 4082-2025")</f>
         <v/>
       </c>
-      <c r="AA47">
+      <c r="AA48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 4082-2025 FSC-klagomål.docx", "A 4082-2025")</f>
         <v/>
       </c>
-      <c r="AB47">
+      <c r="AB48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 4082-2025 FSC-klagomål mail.docx", "A 4082-2025")</f>
         <v/>
       </c>
-      <c r="AC47">
+      <c r="AC48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 4082-2025 tillsynsbegäran.docx", "A 4082-2025")</f>
         <v/>
       </c>
-      <c r="AD47">
+      <c r="AD48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 4082-2025 tillsynsbegäran mail.docx", "A 4082-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>A 42765-2022</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="n">
-        <v>44832</v>
-      </c>
-      <c r="E48" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J48" t="n">
-        <v>1</v>
-      </c>
-      <c r="K48" t="n">
-        <v>1</v>
-      </c>
-      <c r="L48" t="n">
-        <v>1</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>1</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>3</v>
-      </c>
-      <c r="T48" t="n">
-        <v>4</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1</v>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>Krusfrö
-Barkticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 42765-2022 artfynd.xlsx", "A 42765-2022")</f>
-        <v/>
-      </c>
-      <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 42765-2022 karta.png", "A 42765-2022")</f>
-        <v/>
-      </c>
-      <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 42765-2022 georefererad karta.tif", "A 42765-2022")</f>
-        <v/>
-      </c>
-      <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 42765-2022 FSC-klagomål.docx", "A 42765-2022")</f>
-        <v/>
-      </c>
-      <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 42765-2022 FSC-klagomål mail.docx", "A 42765-2022")</f>
-        <v/>
-      </c>
-      <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 42765-2022 tillsynsbegäran.docx", "A 42765-2022")</f>
-        <v/>
-      </c>
-      <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 42765-2022 tillsynsbegäran mail.docx", "A 42765-2022")</f>
         <v/>
       </c>
     </row>
@@ -6464,7 +6464,7 @@
         <v>45205</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>46239</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>46248</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>46268</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>44635</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>45708</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>45708</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 56362-2023</t>
+          <t>A 30074-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7265,10 +7265,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45236</v>
+        <v>45110</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7282,11 +7282,11 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>15.2</v>
+        <v>1.1</v>
       </c>
       <c r="J56" t="n">
         <v>1</v>
@@ -7298,7 +7298,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
@@ -7310,10 +7310,10 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>2</v>
@@ -7322,47 +7322,47 @@
         <v>2</v>
       </c>
       <c r="U56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>Väddnätfjäril
-Grönpyrola</t>
+          <t>Grönpyrola
+Revlummer</t>
         </is>
       </c>
       <c r="W56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 56362-2023 artfynd.xlsx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 30074-2023 artfynd.xlsx", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="X56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 56362-2023 karta.png", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 30074-2023 karta.png", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="Y56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 56362-2023 georefererad karta.tif", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 30074-2023 georefererad karta.tif", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="AA56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 56362-2023 FSC-klagomål.docx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 30074-2023 FSC-klagomål.docx", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="AB56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 56362-2023 FSC-klagomål mail.docx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 30074-2023 FSC-klagomål mail.docx", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="AC56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 56362-2023 tillsynsbegäran.docx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 30074-2023 tillsynsbegäran.docx", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="AD56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 56362-2023 tillsynsbegäran mail.docx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 30074-2023 tillsynsbegäran mail.docx", "A 30074-2023")</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 14001-2023</t>
+          <t>A 13788-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45007</v>
+        <v>45737</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7391,16 +7391,11 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -7409,7 +7404,7 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
         <v>0</v>
@@ -7421,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>2</v>
@@ -7433,47 +7428,51 @@
         <v>2</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>Garnlav
-Motaggsvamp</t>
+          <t>Sparvuggla
+Nattskärra</t>
         </is>
       </c>
       <c r="W57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 14001-2023 artfynd.xlsx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 13788-2025 artfynd.xlsx", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="X57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 14001-2023 karta.png", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 13788-2025 karta.png", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="Y57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 14001-2023 georefererad karta.tif", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 13788-2025 georefererad karta.tif", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="AA57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 14001-2023 FSC-klagomål.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 13788-2025 FSC-klagomål.docx", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="AB57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 14001-2023 FSC-klagomål mail.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 13788-2025 FSC-klagomål mail.docx", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="AC57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 14001-2023 tillsynsbegäran.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 13788-2025 tillsynsbegäran.docx", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="AD57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 14001-2023 tillsynsbegäran mail.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 13788-2025 tillsynsbegäran mail.docx", "A 13788-2025")</f>
+        <v/>
+      </c>
+      <c r="AE57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 13788-2025 prioriterade fågelarter.docx", "A 13788-2025")</f>
         <v/>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 47453-2024</t>
+          <t>A 63138-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7487,10 +7486,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45587</v>
+        <v>46009</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7502,17 +7501,22 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>5.1</v>
+        <v>2.5</v>
       </c>
       <c r="J58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -7527,7 +7531,7 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -7536,47 +7540,47 @@
         <v>2</v>
       </c>
       <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
         <v>2</v>
       </c>
-      <c r="U58" t="n">
-        <v>1</v>
-      </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>Göktyta
-Gröngöling</t>
+          <t>Mindre märgborre
+Tjäder</t>
         </is>
       </c>
       <c r="W58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 47453-2024 artfynd.xlsx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63138-2025 artfynd.xlsx", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="X58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 47453-2024 karta.png", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63138-2025 karta.png", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="Y58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 47453-2024 georefererad karta.tif", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63138-2025 georefererad karta.tif", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="AA58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 47453-2024 FSC-klagomål.docx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63138-2025 FSC-klagomål.docx", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="AB58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 47453-2024 FSC-klagomål mail.docx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63138-2025 FSC-klagomål mail.docx", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="AC58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 47453-2024 tillsynsbegäran.docx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63138-2025 tillsynsbegäran.docx", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="AD58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 47453-2024 tillsynsbegäran mail.docx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63138-2025 tillsynsbegäran mail.docx", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="AE58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 47453-2024 prioriterade fågelarter.docx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 63138-2025 prioriterade fågelarter.docx", "A 63138-2025")</f>
         <v/>
       </c>
     </row>
@@ -7600,7 +7604,7 @@
         <v>45895</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7694,7 +7698,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 37013-2025</t>
+          <t>A 56362-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7708,10 +7712,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45874</v>
+        <v>45236</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7729,19 +7733,19 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>10.7</v>
+        <v>15.2</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N60" t="n">
         <v>0</v>
@@ -7753,10 +7757,10 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S60" t="n">
         <v>2</v>
@@ -7765,47 +7769,47 @@
         <v>2</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril
-Fältgentiana</t>
+          <t>Väddnätfjäril
+Grönpyrola</t>
         </is>
       </c>
       <c r="W60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37013-2025 artfynd.xlsx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 56362-2023 artfynd.xlsx", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="X60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37013-2025 karta.png", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 56362-2023 karta.png", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="Y60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37013-2025 georefererad karta.tif", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 56362-2023 georefererad karta.tif", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="AA60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37013-2025 FSC-klagomål.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 56362-2023 FSC-klagomål.docx", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="AB60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37013-2025 FSC-klagomål mail.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 56362-2023 FSC-klagomål mail.docx", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="AC60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37013-2025 tillsynsbegäran.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 56362-2023 tillsynsbegäran.docx", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="AD60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37013-2025 tillsynsbegäran mail.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 56362-2023 tillsynsbegäran mail.docx", "A 56362-2023")</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 11501-2023</t>
+          <t>A 47453-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7819,10 +7823,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44991</v>
+        <v>45587</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7834,22 +7838,17 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -7864,7 +7863,7 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -7876,47 +7875,51 @@
         <v>2</v>
       </c>
       <c r="U61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva
-Nattviol</t>
+          <t>Göktyta
+Gröngöling</t>
         </is>
       </c>
       <c r="W61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 11501-2023 artfynd.xlsx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 47453-2024 artfynd.xlsx", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="X61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 11501-2023 karta.png", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 47453-2024 karta.png", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="Y61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 11501-2023 georefererad karta.tif", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 47453-2024 georefererad karta.tif", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="AA61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 11501-2023 FSC-klagomål.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 47453-2024 FSC-klagomål.docx", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="AB61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 11501-2023 FSC-klagomål mail.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 47453-2024 FSC-klagomål mail.docx", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="AC61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 11501-2023 tillsynsbegäran.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 47453-2024 tillsynsbegäran.docx", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="AD61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 11501-2023 tillsynsbegäran mail.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 47453-2024 tillsynsbegäran mail.docx", "A 47453-2024")</f>
+        <v/>
+      </c>
+      <c r="AE61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 47453-2024 prioriterade fågelarter.docx", "A 47453-2024")</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 41204-2023</t>
+          <t>A 37013-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7930,10 +7933,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45174</v>
+        <v>45874</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7945,20 +7948,25 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>10.7</v>
       </c>
       <c r="J62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N62" t="n">
         <v>0</v>
@@ -7973,60 +7981,56 @@
         <v>2</v>
       </c>
       <c r="R62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S62" t="n">
         <v>2</v>
       </c>
       <c r="T62" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>Knärot
-Vedtrappmossa</t>
+          <t>Brunfläckig pärlemorfjäril
+Fältgentiana</t>
         </is>
       </c>
       <c r="W62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 41204-2023 artfynd.xlsx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37013-2025 artfynd.xlsx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="X62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 41204-2023 karta.png", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37013-2025 karta.png", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="Y62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 41204-2023 georefererad karta.tif", "A 41204-2023")</f>
-        <v/>
-      </c>
-      <c r="Z62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 41204-2023 karta knärot.png", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37013-2025 georefererad karta.tif", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AA62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 41204-2023 FSC-klagomål.docx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37013-2025 FSC-klagomål.docx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AB62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 41204-2023 FSC-klagomål mail.docx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37013-2025 FSC-klagomål mail.docx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AC62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 41204-2023 tillsynsbegäran.docx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37013-2025 tillsynsbegäran.docx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AD62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 41204-2023 tillsynsbegäran mail.docx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37013-2025 tillsynsbegäran mail.docx", "A 37013-2025")</f>
         <v/>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 30074-2023</t>
+          <t>A 36261-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -8040,10 +8044,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45110</v>
+        <v>46268</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8061,16 +8065,16 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>7.9</v>
       </c>
       <c r="J63" t="n">
         <v>1</v>
       </c>
       <c r="K63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
@@ -8085,7 +8089,7 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
@@ -8101,43 +8105,43 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola
+          <t>Krusfrö
 Revlummer</t>
         </is>
       </c>
       <c r="W63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 30074-2023 artfynd.xlsx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 36261-2026 artfynd.xlsx", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="X63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 30074-2023 karta.png", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 36261-2026 karta.png", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="Y63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 30074-2023 georefererad karta.tif", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 36261-2026 georefererad karta.tif", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="AA63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 30074-2023 FSC-klagomål.docx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 36261-2026 FSC-klagomål.docx", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="AB63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 30074-2023 FSC-klagomål mail.docx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 36261-2026 FSC-klagomål mail.docx", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="AC63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 30074-2023 tillsynsbegäran.docx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 36261-2026 tillsynsbegäran.docx", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="AD63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 30074-2023 tillsynsbegäran mail.docx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 36261-2026 tillsynsbegäran mail.docx", "A 36261-2026")</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 63138-2025</t>
+          <t>A 41204-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -8151,10 +8155,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46009</v>
+        <v>45174</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8166,25 +8170,20 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>1</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
@@ -8196,63 +8195,63 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S64" t="n">
         <v>2</v>
       </c>
       <c r="T64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>Mindre märgborre
-Tjäder</t>
+          <t>Knärot
+Vedtrappmossa</t>
         </is>
       </c>
       <c r="W64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63138-2025 artfynd.xlsx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 41204-2023 artfynd.xlsx", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="X64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63138-2025 karta.png", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 41204-2023 karta.png", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="Y64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63138-2025 georefererad karta.tif", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 41204-2023 georefererad karta.tif", "A 41204-2023")</f>
+        <v/>
+      </c>
+      <c r="Z64">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 41204-2023 karta knärot.png", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="AA64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63138-2025 FSC-klagomål.docx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 41204-2023 FSC-klagomål.docx", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="AB64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63138-2025 FSC-klagomål mail.docx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 41204-2023 FSC-klagomål mail.docx", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="AC64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63138-2025 tillsynsbegäran.docx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 41204-2023 tillsynsbegäran.docx", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="AD64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63138-2025 tillsynsbegäran mail.docx", "A 63138-2025")</f>
-        <v/>
-      </c>
-      <c r="AE64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 63138-2025 prioriterade fågelarter.docx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 41204-2023 tillsynsbegäran mail.docx", "A 41204-2023")</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 13971-2023</t>
+          <t>A 11501-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -8266,10 +8265,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45007</v>
+        <v>44991</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8287,13 +8286,13 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -8320,50 +8319,50 @@
         <v>2</v>
       </c>
       <c r="T65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>Dubbelnycklar
-Fläcknycklar</t>
+          <t>Svart trolldruva
+Nattviol</t>
         </is>
       </c>
       <c r="W65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 13971-2023 artfynd.xlsx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 11501-2023 artfynd.xlsx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="X65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 13971-2023 karta.png", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 11501-2023 karta.png", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="Y65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 13971-2023 georefererad karta.tif", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 11501-2023 georefererad karta.tif", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AA65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 13971-2023 FSC-klagomål.docx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 11501-2023 FSC-klagomål.docx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AB65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 13971-2023 FSC-klagomål mail.docx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 11501-2023 FSC-klagomål mail.docx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AC65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 13971-2023 tillsynsbegäran.docx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 11501-2023 tillsynsbegäran.docx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AD65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 13971-2023 tillsynsbegäran mail.docx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 11501-2023 tillsynsbegäran mail.docx", "A 11501-2023")</f>
         <v/>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 36261-2026</t>
+          <t>A 14001-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -8377,10 +8376,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46268</v>
+        <v>45007</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8394,14 +8393,14 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>7.9</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -8410,7 +8409,7 @@
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N66" t="n">
         <v>0</v>
@@ -8422,10 +8421,10 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S66" t="n">
         <v>2</v>
@@ -8438,43 +8437,43 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>Krusfrö
-Revlummer</t>
+          <t>Garnlav
+Motaggsvamp</t>
         </is>
       </c>
       <c r="W66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 36261-2026 artfynd.xlsx", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 14001-2023 artfynd.xlsx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="X66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 36261-2026 karta.png", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 14001-2023 karta.png", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="Y66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 36261-2026 georefererad karta.tif", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 14001-2023 georefererad karta.tif", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AA66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 36261-2026 FSC-klagomål.docx", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 14001-2023 FSC-klagomål.docx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AB66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 36261-2026 FSC-klagomål mail.docx", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 14001-2023 FSC-klagomål mail.docx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AC66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 36261-2026 tillsynsbegäran.docx", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 14001-2023 tillsynsbegäran.docx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AD66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 36261-2026 tillsynsbegäran mail.docx", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 14001-2023 tillsynsbegäran mail.docx", "A 14001-2023")</f>
         <v/>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 13788-2025</t>
+          <t>A 13971-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -8488,10 +8487,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45737</v>
+        <v>45007</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8503,8 +8502,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>9.699999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="J67" t="n">
         <v>2</v>
@@ -8513,7 +8517,7 @@
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
@@ -8528,7 +8532,7 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
@@ -8537,47 +8541,43 @@
         <v>2</v>
       </c>
       <c r="T67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>Sparvuggla
-Nattskärra</t>
+          <t>Dubbelnycklar
+Fläcknycklar</t>
         </is>
       </c>
       <c r="W67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 13788-2025 artfynd.xlsx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 13971-2023 artfynd.xlsx", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="X67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 13788-2025 karta.png", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 13971-2023 karta.png", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="Y67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 13788-2025 georefererad karta.tif", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 13971-2023 georefererad karta.tif", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="AA67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 13788-2025 FSC-klagomål.docx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 13971-2023 FSC-klagomål.docx", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="AB67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 13788-2025 FSC-klagomål mail.docx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 13971-2023 FSC-klagomål mail.docx", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="AC67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 13788-2025 tillsynsbegäran.docx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 13971-2023 tillsynsbegäran.docx", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="AD67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 13788-2025 tillsynsbegäran mail.docx", "A 13788-2025")</f>
-        <v/>
-      </c>
-      <c r="AE67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 13788-2025 prioriterade fågelarter.docx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 13971-2023 tillsynsbegäran mail.docx", "A 13971-2023")</f>
         <v/>
       </c>
     </row>
@@ -8601,7 +8601,7 @@
         <v>45720</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>44696</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>44739</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>44524</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>44696</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 39099-2022</t>
+          <t>A 30076-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -9149,10 +9149,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44817</v>
+        <v>45110</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9166,17 +9166,17 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>7.4</v>
+        <v>1.1</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -9206,39 +9206,39 @@
         <v>1</v>
       </c>
       <c r="U73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39099-2022 artfynd.xlsx", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 30076-2023 artfynd.xlsx", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="X73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39099-2022 karta.png", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 30076-2023 karta.png", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="Y73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39099-2022 georefererad karta.tif", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 30076-2023 georefererad karta.tif", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="AA73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39099-2022 FSC-klagomål.docx", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 30076-2023 FSC-klagomål.docx", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="AB73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39099-2022 FSC-klagomål mail.docx", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 30076-2023 FSC-klagomål mail.docx", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="AC73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39099-2022 tillsynsbegäran.docx", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 30076-2023 tillsynsbegäran.docx", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="AD73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39099-2022 tillsynsbegäran mail.docx", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 30076-2023 tillsynsbegäran mail.docx", "A 30076-2023")</f>
         <v/>
       </c>
     </row>
@@ -9262,7 +9262,7 @@
         <v>44977</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 34584-2025</t>
+          <t>A 37287-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -9369,10 +9369,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45846</v>
+        <v>45156</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9384,22 +9384,17 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -9414,7 +9409,7 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R75" t="n">
         <v>0</v>
@@ -9426,50 +9421,46 @@
         <v>1</v>
       </c>
       <c r="U75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="W75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34584-2025 artfynd.xlsx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37287-2023 artfynd.xlsx", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="X75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34584-2025 karta.png", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37287-2023 karta.png", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="Y75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34584-2025 georefererad karta.tif", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37287-2023 georefererad karta.tif", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="AA75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34584-2025 FSC-klagomål.docx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37287-2023 FSC-klagomål.docx", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="AB75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34584-2025 FSC-klagomål mail.docx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37287-2023 FSC-klagomål mail.docx", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="AC75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34584-2025 tillsynsbegäran.docx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37287-2023 tillsynsbegäran.docx", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="AD75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34584-2025 tillsynsbegäran mail.docx", "A 34584-2025")</f>
-        <v/>
-      </c>
-      <c r="AE75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 34584-2025 prioriterade fågelarter.docx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37287-2023 tillsynsbegäran mail.docx", "A 37287-2023")</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 16013-2023</t>
+          <t>A 34584-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -9483,10 +9474,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45026</v>
+        <v>45846</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9498,11 +9489,16 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -9511,7 +9507,7 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
         <v>0</v>
@@ -9523,10 +9519,10 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>1</v>
@@ -9535,46 +9531,50 @@
         <v>1</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 16013-2023 artfynd.xlsx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34584-2025 artfynd.xlsx", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="X76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 16013-2023 karta.png", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34584-2025 karta.png", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="Y76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 16013-2023 georefererad karta.tif", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34584-2025 georefererad karta.tif", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="AA76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 16013-2023 FSC-klagomål.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34584-2025 FSC-klagomål.docx", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="AB76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 16013-2023 FSC-klagomål mail.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34584-2025 FSC-klagomål mail.docx", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="AC76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 16013-2023 tillsynsbegäran.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34584-2025 tillsynsbegäran.docx", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="AD76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 16013-2023 tillsynsbegäran mail.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34584-2025 tillsynsbegäran mail.docx", "A 34584-2025")</f>
+        <v/>
+      </c>
+      <c r="AE76">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 34584-2025 prioriterade fågelarter.docx", "A 34584-2025")</f>
         <v/>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 34955-2022</t>
+          <t>A 39099-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -9588,10 +9588,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44796</v>
+        <v>44817</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9605,20 +9605,20 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -9633,7 +9633,7 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
         <v>0</v>
@@ -9649,42 +9649,42 @@
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="W77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34955-2022 artfynd.xlsx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39099-2022 artfynd.xlsx", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="X77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34955-2022 karta.png", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39099-2022 karta.png", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="Y77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34955-2022 georefererad karta.tif", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39099-2022 georefererad karta.tif", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="AA77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34955-2022 FSC-klagomål.docx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39099-2022 FSC-klagomål.docx", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="AB77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34955-2022 FSC-klagomål mail.docx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39099-2022 FSC-klagomål mail.docx", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="AC77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34955-2022 tillsynsbegäran.docx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39099-2022 tillsynsbegäran.docx", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="AD77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34955-2022 tillsynsbegäran mail.docx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39099-2022 tillsynsbegäran mail.docx", "A 39099-2022")</f>
         <v/>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 33231-2024</t>
+          <t>A 17632-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -9698,10 +9698,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45518</v>
+        <v>44680</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9713,19 +9713,14 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>5.2</v>
       </c>
       <c r="J78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -9755,46 +9750,46 @@
         <v>1</v>
       </c>
       <c r="U78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="W78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 33231-2024 artfynd.xlsx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 17632-2022 artfynd.xlsx", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="X78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 33231-2024 karta.png", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 17632-2022 karta.png", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="Y78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 33231-2024 georefererad karta.tif", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 17632-2022 georefererad karta.tif", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="AA78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 33231-2024 FSC-klagomål.docx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 17632-2022 FSC-klagomål.docx", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="AB78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 33231-2024 FSC-klagomål mail.docx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 17632-2022 FSC-klagomål mail.docx", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="AC78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 33231-2024 tillsynsbegäran.docx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 17632-2022 tillsynsbegäran.docx", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="AD78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 33231-2024 tillsynsbegäran mail.docx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 17632-2022 tillsynsbegäran mail.docx", "A 17632-2022")</f>
         <v/>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 30076-2023</t>
+          <t>A 34955-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -9808,10 +9803,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45110</v>
+        <v>44796</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9829,16 +9824,16 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -9853,7 +9848,7 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R79" t="n">
         <v>0</v>
@@ -9865,39 +9860,39 @@
         <v>1</v>
       </c>
       <c r="U79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 30076-2023 artfynd.xlsx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34955-2022 artfynd.xlsx", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="X79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 30076-2023 karta.png", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34955-2022 karta.png", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="Y79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 30076-2023 georefererad karta.tif", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34955-2022 georefererad karta.tif", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="AA79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 30076-2023 FSC-klagomål.docx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34955-2022 FSC-klagomål.docx", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="AB79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 30076-2023 FSC-klagomål mail.docx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34955-2022 FSC-klagomål mail.docx", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="AC79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 30076-2023 tillsynsbegäran.docx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34955-2022 tillsynsbegäran.docx", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="AD79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 30076-2023 tillsynsbegäran mail.docx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34955-2022 tillsynsbegäran mail.docx", "A 34955-2022")</f>
         <v/>
       </c>
     </row>
@@ -9921,7 +9916,7 @@
         <v>44991</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10018,7 +10013,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 24167-2024</t>
+          <t>A 31589-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -10028,14 +10023,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45456</v>
+        <v>46224</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10047,14 +10042,19 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>0.6</v>
+        <v>7</v>
       </c>
       <c r="J81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -10088,42 +10088,42 @@
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 24167-2024 artfynd.xlsx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31589-2026 artfynd.xlsx", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="X81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 24167-2024 karta.png", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31589-2026 karta.png", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="Y81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 24167-2024 georefererad karta.tif", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31589-2026 georefererad karta.tif", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="AA81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 24167-2024 FSC-klagomål.docx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31589-2026 FSC-klagomål.docx", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="AB81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 24167-2024 FSC-klagomål mail.docx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31589-2026 FSC-klagomål mail.docx", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="AC81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 24167-2024 tillsynsbegäran.docx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31589-2026 tillsynsbegäran.docx", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="AD81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 24167-2024 tillsynsbegäran mail.docx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31589-2026 tillsynsbegäran mail.docx", "A 31589-2026")</f>
         <v/>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 37287-2023</t>
+          <t>A 44356-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -10137,10 +10137,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45156</v>
+        <v>45573</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10152,17 +10152,22 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -10177,7 +10182,7 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
         <v>0</v>
@@ -10189,46 +10194,46 @@
         <v>1</v>
       </c>
       <c r="U82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>Mindre tåtelsmygare</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37287-2023 artfynd.xlsx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 44356-2024 artfynd.xlsx", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="X82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37287-2023 karta.png", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 44356-2024 karta.png", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="Y82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37287-2023 georefererad karta.tif", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 44356-2024 georefererad karta.tif", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="AA82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37287-2023 FSC-klagomål.docx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 44356-2024 FSC-klagomål.docx", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="AB82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37287-2023 FSC-klagomål mail.docx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 44356-2024 FSC-klagomål mail.docx", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="AC82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37287-2023 tillsynsbegäran.docx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 44356-2024 tillsynsbegäran.docx", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="AD82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37287-2023 tillsynsbegäran mail.docx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 44356-2024 tillsynsbegäran mail.docx", "A 44356-2024")</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 44356-2024</t>
+          <t>A 33231-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -10242,10 +10247,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45573</v>
+        <v>45518</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10259,11 +10264,11 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>1</v>
@@ -10303,42 +10308,42 @@
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="W83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 44356-2024 artfynd.xlsx", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 33231-2024 artfynd.xlsx", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="X83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 44356-2024 karta.png", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 33231-2024 karta.png", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="Y83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 44356-2024 georefererad karta.tif", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 33231-2024 georefererad karta.tif", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="AA83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 44356-2024 FSC-klagomål.docx", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 33231-2024 FSC-klagomål.docx", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="AB83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 44356-2024 FSC-klagomål mail.docx", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 33231-2024 FSC-klagomål mail.docx", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="AC83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 44356-2024 tillsynsbegäran.docx", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 33231-2024 tillsynsbegäran.docx", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="AD83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 44356-2024 tillsynsbegäran mail.docx", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 33231-2024 tillsynsbegäran mail.docx", "A 33231-2024")</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 17632-2022</t>
+          <t>A 24167-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -10348,14 +10353,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44680</v>
+        <v>45456</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10368,13 +10373,13 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>5.2</v>
+        <v>0.6</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -10408,42 +10413,42 @@
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 17632-2022 artfynd.xlsx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 24167-2024 artfynd.xlsx", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="X84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 17632-2022 karta.png", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 24167-2024 karta.png", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="Y84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 17632-2022 georefererad karta.tif", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 24167-2024 georefererad karta.tif", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="AA84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 17632-2022 FSC-klagomål.docx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 24167-2024 FSC-klagomål.docx", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="AB84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 17632-2022 FSC-klagomål mail.docx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 24167-2024 FSC-klagomål mail.docx", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="AC84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 17632-2022 tillsynsbegäran.docx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 24167-2024 tillsynsbegäran.docx", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="AD84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 17632-2022 tillsynsbegäran mail.docx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 24167-2024 tillsynsbegäran mail.docx", "A 24167-2024")</f>
         <v/>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 31589-2026</t>
+          <t>A 16013-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -10457,10 +10462,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46224</v>
+        <v>45026</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10472,25 +10477,20 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>7</v>
+        <v>3.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N85" t="n">
         <v>0</v>
@@ -10502,10 +10502,10 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S85" t="n">
         <v>1</v>
@@ -10518,35 +10518,35 @@
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="W85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31589-2026 artfynd.xlsx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 16013-2023 artfynd.xlsx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="X85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31589-2026 karta.png", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 16013-2023 karta.png", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="Y85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31589-2026 georefererad karta.tif", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 16013-2023 georefererad karta.tif", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AA85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31589-2026 FSC-klagomål.docx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 16013-2023 FSC-klagomål.docx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AB85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31589-2026 FSC-klagomål mail.docx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 16013-2023 FSC-klagomål mail.docx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AC85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31589-2026 tillsynsbegäran.docx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 16013-2023 tillsynsbegäran.docx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AD85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31589-2026 tillsynsbegäran mail.docx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 16013-2023 tillsynsbegäran mail.docx", "A 16013-2023")</f>
         <v/>
       </c>
     </row>
@@ -10570,7 +10570,7 @@
         <v>44509</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         <v>44696</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>44782</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>44550</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>44586</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>44582</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>44694</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>44518</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>44796</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 21509-2024</t>
+          <t>A 15637-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -11259,10 +11259,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45441</v>
+        <v>44662</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11274,13 +11274,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -11323,7 +11318,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 24158-2023</t>
+          <t>A 48205-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -11337,10 +11332,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45079</v>
+        <v>45205</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11354,11 +11349,11 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.1</v>
+        <v>7.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -11401,7 +11396,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 42832-2022</t>
+          <t>A 15743-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -11411,14 +11406,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44832</v>
+        <v>45021</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11431,7 +11426,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -11474,7 +11469,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 42841-2022</t>
+          <t>A 19786-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -11484,14 +11479,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44832</v>
+        <v>45050</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11503,8 +11498,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>1.8</v>
+        <v>8.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -11547,7 +11547,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 3818-2022</t>
+          <t>A 15739-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -11561,10 +11561,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44587</v>
+        <v>45021</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -11620,7 +11620,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 19782-2023</t>
+          <t>A 7787-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -11634,10 +11634,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45050</v>
+        <v>45348</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11649,13 +11649,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>5.2</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -11698,7 +11693,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 14626-2023</t>
+          <t>A 4724-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -11712,10 +11707,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45012</v>
+        <v>46048</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11727,13 +11722,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -11776,7 +11766,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 56378-2023</t>
+          <t>A 4734-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -11790,10 +11780,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45236</v>
+        <v>46048</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11805,13 +11795,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>4.6</v>
+        <v>0.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -11854,7 +11839,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 11728-2023</t>
+          <t>A 10249-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -11864,14 +11849,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44993</v>
+        <v>46076</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11885,11 +11870,11 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.4</v>
+        <v>4.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -11949,7 +11934,7 @@
         <v>46076</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12010,7 +11995,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 10249-2026</t>
+          <t>A 10562-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -12024,10 +12009,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12041,11 +12026,11 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -12088,7 +12073,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 10562-2026</t>
+          <t>A 37954-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -12102,10 +12087,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46077</v>
+        <v>45881</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12117,13 +12102,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>2.3</v>
+        <v>9.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -12166,7 +12146,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 37954-2025</t>
+          <t>A 72367-2021</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -12180,10 +12160,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45881</v>
+        <v>44545</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12196,7 +12176,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>9.5</v>
+        <v>2.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -12239,7 +12219,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 20904-2023</t>
+          <t>A 33931-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -12249,14 +12229,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45060</v>
+        <v>44790</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12268,13 +12248,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -12317,7 +12292,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 42829-2022</t>
+          <t>A 12841-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -12327,14 +12302,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44832</v>
+        <v>46091</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12346,8 +12321,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>1.6</v>
+        <v>4.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -12390,7 +12370,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 12841-2026</t>
+          <t>A 24158-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -12404,10 +12384,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46091</v>
+        <v>45079</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12421,11 +12401,11 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -12468,7 +12448,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 48205-2023</t>
+          <t>A 42714-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -12482,10 +12462,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45205</v>
+        <v>44832</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12497,13 +12477,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>7.6</v>
+        <v>1.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -12546,7 +12521,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 55873-2025</t>
+          <t>A 19246-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -12556,14 +12531,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45973</v>
+        <v>46132</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12581,7 +12556,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -12624,7 +12599,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 33931-2022</t>
+          <t>A 55873-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -12638,10 +12613,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44790</v>
+        <v>45973</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12653,8 +12628,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -12697,7 +12677,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 22662-2023</t>
+          <t>A 32808-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -12707,14 +12687,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45071</v>
+        <v>45516</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12728,11 +12708,11 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -12775,7 +12755,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 19246-2026</t>
+          <t>A 35682-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -12785,14 +12765,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46132</v>
+        <v>44799</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12853,7 +12833,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 4724-2026</t>
+          <t>A 11728-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -12863,14 +12843,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46048</v>
+        <v>44993</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12882,8 +12862,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -12926,7 +12911,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 4734-2026</t>
+          <t>A 5567-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -12940,10 +12925,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46048</v>
+        <v>44595</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12956,7 +12941,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -12999,7 +12984,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 25450-2024</t>
+          <t>A 42832-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -13009,14 +12994,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45463</v>
+        <v>44832</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13028,13 +13013,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -13094,7 +13074,7 @@
         <v>45084</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13150,7 +13130,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 32808-2024</t>
+          <t>A 42841-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -13160,14 +13140,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45516</v>
+        <v>44832</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13179,13 +13159,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -13228,7 +13203,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 20535-2026</t>
+          <t>A 42829-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -13242,10 +13217,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46140</v>
+        <v>44832</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13257,13 +13232,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -13323,7 +13293,7 @@
         <v>45594</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13384,7 +13354,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 72367-2021</t>
+          <t>A 20535-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -13394,14 +13364,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44545</v>
+        <v>46140</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13413,8 +13383,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -13457,7 +13432,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 42714-2022</t>
+          <t>A 2867-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -13471,10 +13446,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44832</v>
+        <v>45315</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13486,8 +13461,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -13530,7 +13510,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 19099-2022</t>
+          <t>A 3085-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -13544,10 +13524,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44691</v>
+        <v>44946</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13561,11 +13541,11 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>3.4</v>
+        <v>13</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -13608,7 +13588,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 25780-2023</t>
+          <t>A 24201-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -13622,10 +13602,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45090</v>
+        <v>46168</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13638,7 +13618,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -13681,7 +13661,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 24201-2026</t>
+          <t>A 32501-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -13691,14 +13671,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46168</v>
+        <v>46239</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13711,7 +13691,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -13754,7 +13734,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 35682-2022</t>
+          <t>A 22628-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -13768,10 +13748,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44799</v>
+        <v>46155</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13789,7 +13769,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -13832,7 +13812,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 2867-2024</t>
+          <t>A 33933-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -13846,10 +13826,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45315</v>
+        <v>46248</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13867,7 +13847,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -13910,7 +13890,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 2660-2024</t>
+          <t>A 20904-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -13920,14 +13900,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45310</v>
+        <v>45060</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13939,8 +13919,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -13983,7 +13968,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 5567-2022</t>
+          <t>A 31061-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -13997,10 +13982,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44595</v>
+        <v>46215</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14012,8 +13997,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -14056,7 +14046,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 32223-2026</t>
+          <t>A 2660-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -14070,10 +14060,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46237</v>
+        <v>45310</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14085,13 +14075,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>8.199999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -14134,7 +14119,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 32501-2026</t>
+          <t>A 32223-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -14144,14 +14129,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46239</v>
+        <v>46237</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14163,8 +14148,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>1.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -14207,7 +14197,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 22628-2026</t>
+          <t>A 14626-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -14221,10 +14211,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46155</v>
+        <v>45012</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14238,7 +14228,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I134" t="n">
@@ -14285,7 +14275,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 3085-2023</t>
+          <t>A 25450-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -14299,10 +14289,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44946</v>
+        <v>45463</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14316,11 +14306,11 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>13</v>
+        <v>2.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -14363,7 +14353,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 7848-2022</t>
+          <t>A 19782-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -14377,10 +14367,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44608</v>
+        <v>45050</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14392,8 +14382,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>2.1</v>
+        <v>5.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -14436,7 +14431,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 33933-2026</t>
+          <t>A 7848-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -14450,10 +14445,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46248</v>
+        <v>44608</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14465,13 +14460,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -14514,7 +14504,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 15743-2023</t>
+          <t>A 56378-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -14528,10 +14518,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45021</v>
+        <v>45236</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14543,8 +14533,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -14587,7 +14582,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 31061-2026</t>
+          <t>A 19099-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -14601,10 +14596,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46215</v>
+        <v>44691</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14618,11 +14613,11 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -14665,7 +14660,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 15637-2022</t>
+          <t>A 3818-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -14679,10 +14674,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44662</v>
+        <v>44587</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14695,7 +14690,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -14738,7 +14733,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 19786-2023</t>
+          <t>A 21509-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -14752,10 +14747,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45050</v>
+        <v>45441</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14773,7 +14768,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>8.1</v>
+        <v>3.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -14816,7 +14811,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 7787-2024</t>
+          <t>A 22662-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -14826,14 +14821,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45348</v>
+        <v>45071</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14845,8 +14840,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -14889,7 +14889,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 15739-2023</t>
+          <t>A 25780-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -14903,10 +14903,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45021</v>
+        <v>45090</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -14979,7 +14979,7 @@
         <v>44734</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
         <v>44734</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>46251</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>

--- a/Översikt SURAHAMMAR.xlsx
+++ b/Översikt SURAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45470</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>45684</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 31280-2024</t>
+          <t>A 39697-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45504</v>
+        <v>45890</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,23 +964,23 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>6.9</v>
+        <v>25.7</v>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="K4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -992,21 +992,182 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="R4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
         <v>44</v>
       </c>
       <c r="T4" t="n">
+        <v>242</v>
+      </c>
+      <c r="U4" t="n">
+        <v>106</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Grönfink
+Knärot
+Bivråk
+Brunlångöra
+Dropptaggsvamp
+Fjällig taggsvamp s.str.
+Järnsparv
+Motaggsvamp
+Nordfladdermus
+Skarp dropptaggsvamp
+Skogshare
+Sotvaxskivling
+Sparvuggla
+Stornopping
+Talltita
+Älg
+Blodvaxing
+Gulgrön kantmusseron
+Honungsvaxing
+Luktvaxing
+Mindre märgborre
+Smal svampklubba
+Vedticka
+Gråspett
+Järpe
+Liljekonvalj
+Mattlummer
+Nattskärra
+Spillkråka
+Tjäder
+Tofsmes
+Dvärgpipistrell
+Gröngöling
+Kungsfågel
+Orre
+Slaguggla
+Större brunfladdermus
+Sångsvan
+Trana
+Trollpipistrell
+Vattenfladdermus
+Vanlig groda
+Fläcknycklar
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39697-2025 artfynd.xlsx", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39697-2025 karta.png", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39697-2025 georefererad karta.tif", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="Z4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 39697-2025 karta knärot.png", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39697-2025 FSC-klagomål.docx", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39697-2025 FSC-klagomål mail.docx", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39697-2025 tillsynsbegäran.docx", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39697-2025 tillsynsbegäran mail.docx", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39697-2025 prioriterade fågelarter.docx", "A 39697-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 31280-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45504</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K5" t="n">
+        <v>12</v>
+      </c>
+      <c r="L5" t="n">
+        <v>22</v>
+      </c>
+      <c r="M5" t="n">
+        <v>5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>27</v>
+      </c>
+      <c r="R5" t="n">
+        <v>5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>44</v>
+      </c>
+      <c r="T5" t="n">
         <v>93</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>91</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Gränsticka
 Knärot
@@ -1054,201 +1215,40 @@
 Lopplummer (aggregat)</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31280-2024 artfynd.xlsx", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31280-2024 karta.png", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31280-2024 georefererad karta.tif", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="Z4">
+      <c r="Z5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 31280-2024 karta knärot.png", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31280-2024 FSC-klagomål.docx", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31280-2024 FSC-klagomål mail.docx", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31280-2024 tillsynsbegäran.docx", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31280-2024 tillsynsbegäran mail.docx", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 31280-2024 prioriterade fågelarter.docx", "A 31280-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 39697-2025</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45890</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>28</v>
-      </c>
-      <c r="K5" t="n">
-        <v>7</v>
-      </c>
-      <c r="L5" t="n">
-        <v>14</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>16</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2</v>
-      </c>
-      <c r="S5" t="n">
-        <v>44</v>
-      </c>
-      <c r="T5" t="n">
-        <v>240</v>
-      </c>
-      <c r="U5" t="n">
-        <v>104</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Grönfink
-Knärot
-Bivråk
-Brunlångöra
-Dropptaggsvamp
-Fjällig taggsvamp s.str.
-Järnsparv
-Motaggsvamp
-Nordfladdermus
-Skarp dropptaggsvamp
-Skogshare
-Sotvaxskivling
-Sparvuggla
-Stornopping
-Talltita
-Älg
-Blodvaxing
-Gulgrön kantmusseron
-Honungsvaxing
-Luktvaxing
-Mindre märgborre
-Smal svampklubba
-Vedticka
-Gråspett
-Järpe
-Liljekonvalj
-Mattlummer
-Nattskärra
-Spillkråka
-Tjäder
-Tofsmes
-Dvärgpipistrell
-Gröngöling
-Kungsfågel
-Orre
-Slaguggla
-Större brunfladdermus
-Sångsvan
-Trana
-Trollpipistrell
-Vattenfladdermus
-Vanlig groda
-Fläcknycklar
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39697-2025 artfynd.xlsx", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39697-2025 karta.png", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39697-2025 georefererad karta.tif", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="Z5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 39697-2025 karta knärot.png", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39697-2025 FSC-klagomål.docx", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39697-2025 FSC-klagomål mail.docx", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39697-2025 tillsynsbegäran.docx", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39697-2025 tillsynsbegäran mail.docx", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39697-2025 prioriterade fågelarter.docx", "A 39697-2025")</f>
         <v/>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
         <v>45582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45169</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45139</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45782</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>45282</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>46216</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>46216</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>46237</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>44613</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>46085</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>45435</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>46215</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>46111</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 42853-2022</t>
+          <t>A 39594-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2953,14 +2953,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44832</v>
+        <v>45890</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2972,23 +2972,28 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J19" t="n">
+        <v>6</v>
+      </c>
+      <c r="K19" t="n">
         <v>3</v>
       </c>
-      <c r="K19" t="n">
-        <v>7</v>
-      </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2997,21 +3002,140 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>11</v>
       </c>
       <c r="T19" t="n">
+        <v>14</v>
+      </c>
+      <c r="U19" t="n">
+        <v>10</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Brunlångöra
+Dropptaggsvamp
+Gropticka
+Nordfladdermus
+Talltita
+Bronshjon
+Gullgröppa
+Vedticka
+Järpe
+Tjäder
+Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39594-2025 artfynd.xlsx", "A 39594-2025")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39594-2025 karta.png", "A 39594-2025")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39594-2025 georefererad karta.tif", "A 39594-2025")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39594-2025 FSC-klagomål.docx", "A 39594-2025")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39594-2025 FSC-klagomål mail.docx", "A 39594-2025")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39594-2025 tillsynsbegäran.docx", "A 39594-2025")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39594-2025 tillsynsbegäran mail.docx", "A 39594-2025")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39594-2025 prioriterade fågelarter.docx", "A 39594-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 42853-2022</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>44832</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>7</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>11</v>
+      </c>
+      <c r="T20" t="n">
         <v>15</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U20" t="n">
         <v>2</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Ask
 Kandelabersvamp
@@ -3026,160 +3150,36 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 42853-2022 artfynd.xlsx", "A 42853-2022")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 42853-2022 karta.png", "A 42853-2022")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 42853-2022 georefererad karta.tif", "A 42853-2022")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 42853-2022 FSC-klagomål.docx", "A 42853-2022")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 42853-2022 FSC-klagomål mail.docx", "A 42853-2022")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 42853-2022 tillsynsbegäran.docx", "A 42853-2022")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 42853-2022 tillsynsbegäran mail.docx", "A 42853-2022")</f>
         <v/>
       </c>
-      <c r="AE19">
+      <c r="AE20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 42853-2022 prioriterade fågelarter.docx", "A 42853-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 39594-2025</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45890</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>7</v>
-      </c>
-      <c r="J20" t="n">
-        <v>6</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3</v>
-      </c>
-      <c r="L20" t="n">
-        <v>5</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>5</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>11</v>
-      </c>
-      <c r="T20" t="n">
-        <v>14</v>
-      </c>
-      <c r="U20" t="n">
-        <v>10</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Brunlångöra
-Dropptaggsvamp
-Gropticka
-Nordfladdermus
-Talltita
-Bronshjon
-Gullgröppa
-Vedticka
-Järpe
-Tjäder
-Dvärgpipistrell</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39594-2025 artfynd.xlsx", "A 39594-2025")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39594-2025 karta.png", "A 39594-2025")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39594-2025 georefererad karta.tif", "A 39594-2025")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39594-2025 FSC-klagomål.docx", "A 39594-2025")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39594-2025 FSC-klagomål mail.docx", "A 39594-2025")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39594-2025 tillsynsbegäran.docx", "A 39594-2025")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39594-2025 tillsynsbegäran mail.docx", "A 39594-2025")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39594-2025 prioriterade fågelarter.docx", "A 39594-2025")</f>
         <v/>
       </c>
     </row>
@@ -3203,7 +3203,7 @@
         <v>45523</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>45070</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>44565</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 44798-2024</t>
+          <t>A 31060-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45574</v>
+        <v>46215</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3591,26 +3591,26 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3619,7 +3619,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -3628,12 +3628,134 @@
         <v>9</v>
       </c>
       <c r="T24" t="n">
+        <v>9</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Bombmurkla
+Brunlångöra
+Nordfladdermus
+Springkorn
+Vedticka
+Spillkråka
+Dvärgpipistrell
+Åkergroda
+Vanlig groda</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31060-2026 artfynd.xlsx", "A 31060-2026")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31060-2026 karta.png", "A 31060-2026")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31060-2026 georefererad karta.tif", "A 31060-2026")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31060-2026 FSC-klagomål.docx", "A 31060-2026")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31060-2026 FSC-klagomål mail.docx", "A 31060-2026")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31060-2026 tillsynsbegäran.docx", "A 31060-2026")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31060-2026 tillsynsbegäran mail.docx", "A 31060-2026")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 31060-2026 prioriterade fågelarter.docx", "A 31060-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 44798-2024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>45574</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>7</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>8</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>9</v>
+      </c>
+      <c r="T25" t="n">
         <v>26</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U25" t="n">
         <v>10</v>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Rosetticka
 Brunklöver
@@ -3646,154 +3768,32 @@
 Brandticka</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 44798-2024 artfynd.xlsx", "A 44798-2024")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 44798-2024 karta.png", "A 44798-2024")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 44798-2024 georefererad karta.tif", "A 44798-2024")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 44798-2024 FSC-klagomål.docx", "A 44798-2024")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 44798-2024 FSC-klagomål mail.docx", "A 44798-2024")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 44798-2024 tillsynsbegäran.docx", "A 44798-2024")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 44798-2024 tillsynsbegäran mail.docx", "A 44798-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 31060-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>46215</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J25" t="n">
-        <v>7</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2</v>
-      </c>
-      <c r="L25" t="n">
-        <v>2</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S25" t="n">
-        <v>9</v>
-      </c>
-      <c r="T25" t="n">
-        <v>9</v>
-      </c>
-      <c r="U25" t="n">
-        <v>3</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Bombmurkla
-Brunlångöra
-Nordfladdermus
-Springkorn
-Vedticka
-Spillkråka
-Dvärgpipistrell
-Åkergroda
-Vanlig groda</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31060-2026 artfynd.xlsx", "A 31060-2026")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31060-2026 karta.png", "A 31060-2026")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31060-2026 georefererad karta.tif", "A 31060-2026")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31060-2026 FSC-klagomål.docx", "A 31060-2026")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31060-2026 FSC-klagomål mail.docx", "A 31060-2026")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31060-2026 tillsynsbegäran.docx", "A 31060-2026")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31060-2026 tillsynsbegäran mail.docx", "A 31060-2026")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 31060-2026 prioriterade fågelarter.docx", "A 31060-2026")</f>
         <v/>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
         <v>45435</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>44518</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>44477</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>45203</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>45072</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>46268</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>45545</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>45945</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>44518</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 63145-2025</t>
+          <t>A 10236-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46009</v>
+        <v>46076</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4900,23 +4900,23 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>40.5</v>
+        <v>2.8</v>
       </c>
       <c r="J35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L35" t="n">
         <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -4928,10 +4928,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>6</v>
@@ -4943,6 +4943,121 @@
         <v>0</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>Gullpudra
+Vågticka
+Brandticka
+Strutbräken
+Lopplummer (aggregat)
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 10236-2026 artfynd.xlsx", "A 10236-2026")</f>
+        <v/>
+      </c>
+      <c r="X35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 10236-2026 karta.png", "A 10236-2026")</f>
+        <v/>
+      </c>
+      <c r="Y35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 10236-2026 georefererad karta.tif", "A 10236-2026")</f>
+        <v/>
+      </c>
+      <c r="AA35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 10236-2026 FSC-klagomål.docx", "A 10236-2026")</f>
+        <v/>
+      </c>
+      <c r="AB35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 10236-2026 FSC-klagomål mail.docx", "A 10236-2026")</f>
+        <v/>
+      </c>
+      <c r="AC35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 10236-2026 tillsynsbegäran.docx", "A 10236-2026")</f>
+        <v/>
+      </c>
+      <c r="AD35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 10236-2026 tillsynsbegäran mail.docx", "A 10236-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>A 63145-2025</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>46009</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="J36" t="n">
+        <v>5</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" t="n">
+        <v>2</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" t="n">
+        <v>6</v>
+      </c>
+      <c r="T36" t="n">
+        <v>13</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>Väddnätfjäril
 Mindre hackspett
@@ -4952,151 +5067,36 @@
 Nattviol</t>
         </is>
       </c>
-      <c r="W35">
+      <c r="W36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63145-2025 artfynd.xlsx", "A 63145-2025")</f>
         <v/>
       </c>
-      <c r="X35">
+      <c r="X36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63145-2025 karta.png", "A 63145-2025")</f>
         <v/>
       </c>
-      <c r="Y35">
+      <c r="Y36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63145-2025 georefererad karta.tif", "A 63145-2025")</f>
         <v/>
       </c>
-      <c r="AA35">
+      <c r="AA36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63145-2025 FSC-klagomål.docx", "A 63145-2025")</f>
         <v/>
       </c>
-      <c r="AB35">
+      <c r="AB36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63145-2025 FSC-klagomål mail.docx", "A 63145-2025")</f>
         <v/>
       </c>
-      <c r="AC35">
+      <c r="AC36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63145-2025 tillsynsbegäran.docx", "A 63145-2025")</f>
         <v/>
       </c>
-      <c r="AD35">
+      <c r="AD36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63145-2025 tillsynsbegäran mail.docx", "A 63145-2025")</f>
         <v/>
       </c>
-      <c r="AE35">
+      <c r="AE36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 63145-2025 prioriterade fågelarter.docx", "A 63145-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>A 10236-2026</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="n">
-        <v>46076</v>
-      </c>
-      <c r="E36" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J36" t="n">
-        <v>2</v>
-      </c>
-      <c r="K36" t="n">
-        <v>2</v>
-      </c>
-      <c r="L36" t="n">
-        <v>2</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>2</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>6</v>
-      </c>
-      <c r="T36" t="n">
-        <v>13</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>Gullpudra
-Vågticka
-Brandticka
-Strutbräken
-Lopplummer (aggregat)
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 10236-2026 artfynd.xlsx", "A 10236-2026")</f>
-        <v/>
-      </c>
-      <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 10236-2026 karta.png", "A 10236-2026")</f>
-        <v/>
-      </c>
-      <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 10236-2026 georefererad karta.tif", "A 10236-2026")</f>
-        <v/>
-      </c>
-      <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 10236-2026 FSC-klagomål.docx", "A 10236-2026")</f>
-        <v/>
-      </c>
-      <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 10236-2026 FSC-klagomål mail.docx", "A 10236-2026")</f>
-        <v/>
-      </c>
-      <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 10236-2026 tillsynsbegäran.docx", "A 10236-2026")</f>
-        <v/>
-      </c>
-      <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 10236-2026 tillsynsbegäran mail.docx", "A 10236-2026")</f>
         <v/>
       </c>
     </row>
@@ -5120,7 +5120,7 @@
         <v>44832</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>44832</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>45369</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>45503</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>45463</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>44518</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>45890</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 69777-2021</t>
+          <t>A 49718-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44532</v>
+        <v>45212</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5933,22 +5933,22 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
       </c>
       <c r="K44" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" t="n">
         <v>2</v>
       </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5957,947 +5957,947 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
       </c>
       <c r="T44" t="n">
+        <v>6</v>
+      </c>
+      <c r="U44" t="n">
+        <v>6</v>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Talltita
+Zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="W44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 49718-2023 artfynd.xlsx", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="X44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 49718-2023 karta.png", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="Y44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 49718-2023 georefererad karta.tif", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="AA44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 49718-2023 FSC-klagomål.docx", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="AB44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 49718-2023 FSC-klagomål mail.docx", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="AC44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 49718-2023 tillsynsbegäran.docx", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="AD44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 49718-2023 tillsynsbegäran mail.docx", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="AE44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 49718-2023 prioriterade fågelarter.docx", "A 49718-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>A 42765-2022</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>44832</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>Krusfrö
+Barkticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 42765-2022 artfynd.xlsx", "A 42765-2022")</f>
+        <v/>
+      </c>
+      <c r="X45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 42765-2022 karta.png", "A 42765-2022")</f>
+        <v/>
+      </c>
+      <c r="Y45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 42765-2022 georefererad karta.tif", "A 42765-2022")</f>
+        <v/>
+      </c>
+      <c r="AA45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 42765-2022 FSC-klagomål.docx", "A 42765-2022")</f>
+        <v/>
+      </c>
+      <c r="AB45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 42765-2022 FSC-klagomål mail.docx", "A 42765-2022")</f>
+        <v/>
+      </c>
+      <c r="AC45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 42765-2022 tillsynsbegäran.docx", "A 42765-2022")</f>
+        <v/>
+      </c>
+      <c r="AD45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 42765-2022 tillsynsbegäran mail.docx", "A 42765-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>A 63146-2025</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v>46009</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3</v>
+      </c>
+      <c r="T46" t="n">
+        <v>12</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>Stor aspticka
+Svart trolldruva
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63146-2025 artfynd.xlsx", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="X46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63146-2025 karta.png", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="Y46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63146-2025 georefererad karta.tif", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="AA46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63146-2025 FSC-klagomål.docx", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="AB46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63146-2025 FSC-klagomål mail.docx", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="AC46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63146-2025 tillsynsbegäran.docx", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="AD46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63146-2025 tillsynsbegäran mail.docx", "A 63146-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>A 69777-2021</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>44532</v>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>2</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3</v>
+      </c>
+      <c r="T47" t="n">
         <v>5</v>
       </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
         <is>
           <t>Bombmurkla
 Rävticka
 Vedticka</t>
         </is>
       </c>
-      <c r="W44">
+      <c r="W47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 69777-2021 artfynd.xlsx", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="X44">
+      <c r="X47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 69777-2021 karta.png", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="Y44">
+      <c r="Y47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 69777-2021 georefererad karta.tif", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="AA44">
+      <c r="AA47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 69777-2021 FSC-klagomål.docx", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="AB44">
+      <c r="AB47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 69777-2021 FSC-klagomål mail.docx", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="AC44">
+      <c r="AC47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 69777-2021 tillsynsbegäran.docx", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="AD44">
+      <c r="AD47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 69777-2021 tillsynsbegäran mail.docx", "A 69777-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>A 49718-2023</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>A 4082-2025</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D45" s="1" t="n">
-        <v>45212</v>
-      </c>
-      <c r="E45" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F45" t="inlineStr">
+      <c r="D48" s="1" t="n">
+        <v>45684</v>
+      </c>
+      <c r="E48" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>VÄSTMANLANDS LÄN</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="I45" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J45" t="n">
-        <v>1</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1</v>
-      </c>
-      <c r="L45" t="n">
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J48" t="n">
         <v>2</v>
       </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
+      <c r="K48" t="n">
         <v>2</v>
       </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
         <v>3</v>
       </c>
-      <c r="T45" t="n">
-        <v>6</v>
-      </c>
-      <c r="U45" t="n">
-        <v>6</v>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Talltita
-Zontaggsvamp</t>
-        </is>
-      </c>
-      <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 49718-2023 artfynd.xlsx", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 49718-2023 karta.png", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 49718-2023 georefererad karta.tif", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 49718-2023 FSC-klagomål.docx", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 49718-2023 FSC-klagomål mail.docx", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 49718-2023 tillsynsbegäran.docx", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 49718-2023 tillsynsbegäran mail.docx", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="AE45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 49718-2023 prioriterade fågelarter.docx", "A 49718-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>A 4082-2025</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="n">
-        <v>45684</v>
-      </c>
-      <c r="E46" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="J46" t="n">
-        <v>2</v>
-      </c>
-      <c r="K46" t="n">
-        <v>2</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
+      <c r="T48" t="n">
         <v>3</v>
       </c>
-      <c r="T46" t="n">
-        <v>3</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1</v>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
+      <c r="U48" t="n">
+        <v>1</v>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
         <is>
           <t>Grönpyrola
 Plattlummer
 Lopplummer (aggregat)</t>
         </is>
       </c>
-      <c r="W46">
+      <c r="W48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 4082-2025 artfynd.xlsx", "A 4082-2025")</f>
         <v/>
       </c>
-      <c r="X46">
+      <c r="X48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 4082-2025 karta.png", "A 4082-2025")</f>
         <v/>
       </c>
-      <c r="Y46">
+      <c r="Y48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 4082-2025 georefererad karta.tif", "A 4082-2025")</f>
         <v/>
       </c>
-      <c r="AA46">
+      <c r="AA48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 4082-2025 FSC-klagomål.docx", "A 4082-2025")</f>
         <v/>
       </c>
-      <c r="AB46">
+      <c r="AB48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 4082-2025 FSC-klagomål mail.docx", "A 4082-2025")</f>
         <v/>
       </c>
-      <c r="AC46">
+      <c r="AC48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 4082-2025 tillsynsbegäran.docx", "A 4082-2025")</f>
         <v/>
       </c>
-      <c r="AD46">
+      <c r="AD48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 4082-2025 tillsynsbegäran mail.docx", "A 4082-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>A 48128-2023</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D47" s="1" t="n">
+      <c r="D49" s="1" t="n">
         <v>45205</v>
       </c>
-      <c r="E47" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F47" t="inlineStr">
+      <c r="E49" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>VÄSTMANLANDS LÄN</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
-      <c r="I47" t="n">
+      <c r="I49" t="n">
         <v>11.8</v>
       </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
-        <v>1</v>
-      </c>
-      <c r="L47" t="n">
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" t="n">
         <v>2</v>
       </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
         <v>2</v>
       </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
         <v>3</v>
       </c>
-      <c r="T47" t="n">
+      <c r="T49" t="n">
         <v>3</v>
       </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
         <is>
           <t>Jungfrulin
 Svinrot
 Vedticka</t>
         </is>
       </c>
-      <c r="W47">
+      <c r="W49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 48128-2023 artfynd.xlsx", "A 48128-2023")</f>
         <v/>
       </c>
-      <c r="X47">
+      <c r="X49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 48128-2023 karta.png", "A 48128-2023")</f>
         <v/>
       </c>
-      <c r="Y47">
+      <c r="Y49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 48128-2023 georefererad karta.tif", "A 48128-2023")</f>
         <v/>
       </c>
-      <c r="AA47">
+      <c r="AA49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 48128-2023 FSC-klagomål.docx", "A 48128-2023")</f>
         <v/>
       </c>
-      <c r="AB47">
+      <c r="AB49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 48128-2023 FSC-klagomål mail.docx", "A 48128-2023")</f>
         <v/>
       </c>
-      <c r="AC47">
+      <c r="AC49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 48128-2023 tillsynsbegäran.docx", "A 48128-2023")</f>
         <v/>
       </c>
-      <c r="AD47">
+      <c r="AD49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 48128-2023 tillsynsbegäran mail.docx", "A 48128-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>A 63146-2025</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>A 33935-2026</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D48" s="1" t="n">
-        <v>46009</v>
-      </c>
-      <c r="E48" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F48" t="inlineStr">
+      <c r="D50" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E50" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>VÄSTMANLANDS LÄN</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I48" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="J48" t="n">
-        <v>1</v>
-      </c>
-      <c r="K48" t="n">
+      <c r="I50" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J50" t="n">
         <v>2</v>
       </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
+      <c r="K50" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
         <v>3</v>
       </c>
-      <c r="T48" t="n">
-        <v>12</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>Stor aspticka
-Svart trolldruva
+      <c r="T50" t="n">
+        <v>5</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Mindre märgborre
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 33935-2026 artfynd.xlsx", "A 33935-2026")</f>
+        <v/>
+      </c>
+      <c r="X50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 33935-2026 karta.png", "A 33935-2026")</f>
+        <v/>
+      </c>
+      <c r="Y50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 33935-2026 georefererad karta.tif", "A 33935-2026")</f>
+        <v/>
+      </c>
+      <c r="AA50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 33935-2026 FSC-klagomål.docx", "A 33935-2026")</f>
+        <v/>
+      </c>
+      <c r="AB50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 33935-2026 FSC-klagomål mail.docx", "A 33935-2026")</f>
+        <v/>
+      </c>
+      <c r="AC50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 33935-2026 tillsynsbegäran.docx", "A 33935-2026")</f>
+        <v/>
+      </c>
+      <c r="AD50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 33935-2026 tillsynsbegäran mail.docx", "A 33935-2026")</f>
+        <v/>
+      </c>
+      <c r="AE50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 33935-2026 prioriterade fågelarter.docx", "A 33935-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>A 36264-2026</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="E51" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>2</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1</v>
+      </c>
+      <c r="S51" t="n">
+        <v>3</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>Grangråticka
+Fjällig taggsvamp s.str.
 Blåsippa</t>
         </is>
       </c>
-      <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63146-2025 artfynd.xlsx", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63146-2025 karta.png", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63146-2025 georefererad karta.tif", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63146-2025 FSC-klagomål.docx", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63146-2025 FSC-klagomål mail.docx", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63146-2025 tillsynsbegäran.docx", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63146-2025 tillsynsbegäran mail.docx", "A 63146-2025")</f>
+      <c r="W51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 36264-2026 artfynd.xlsx", "A 36264-2026")</f>
+        <v/>
+      </c>
+      <c r="X51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 36264-2026 karta.png", "A 36264-2026")</f>
+        <v/>
+      </c>
+      <c r="Y51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 36264-2026 georefererad karta.tif", "A 36264-2026")</f>
+        <v/>
+      </c>
+      <c r="AA51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 36264-2026 FSC-klagomål.docx", "A 36264-2026")</f>
+        <v/>
+      </c>
+      <c r="AB51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 36264-2026 FSC-klagomål mail.docx", "A 36264-2026")</f>
+        <v/>
+      </c>
+      <c r="AC51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 36264-2026 tillsynsbegäran.docx", "A 36264-2026")</f>
+        <v/>
+      </c>
+      <c r="AD51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 36264-2026 tillsynsbegäran mail.docx", "A 36264-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>A 32443-2026</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D49" s="1" t="n">
+      <c r="D52" s="1" t="n">
         <v>46239</v>
       </c>
-      <c r="E49" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F49" t="inlineStr">
+      <c r="E52" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>VÄSTMANLANDS LÄN</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
-      <c r="I49" t="n">
+      <c r="I52" t="n">
         <v>9.5</v>
       </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
         <v>3</v>
       </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
         <v>3</v>
       </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
         <v>3</v>
       </c>
-      <c r="T49" t="n">
+      <c r="T52" t="n">
         <v>5</v>
       </c>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" s="2" t="inlineStr">
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Tallticka
 Ullticka</t>
         </is>
       </c>
-      <c r="W49">
+      <c r="W52">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 32443-2026 artfynd.xlsx", "A 32443-2026")</f>
         <v/>
       </c>
-      <c r="X49">
+      <c r="X52">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 32443-2026 karta.png", "A 32443-2026")</f>
         <v/>
       </c>
-      <c r="Y49">
+      <c r="Y52">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 32443-2026 georefererad karta.tif", "A 32443-2026")</f>
         <v/>
       </c>
-      <c r="AA49">
+      <c r="AA52">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 32443-2026 FSC-klagomål.docx", "A 32443-2026")</f>
         <v/>
       </c>
-      <c r="AB49">
+      <c r="AB52">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 32443-2026 FSC-klagomål mail.docx", "A 32443-2026")</f>
         <v/>
       </c>
-      <c r="AC49">
+      <c r="AC52">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 32443-2026 tillsynsbegäran.docx", "A 32443-2026")</f>
         <v/>
       </c>
-      <c r="AD49">
+      <c r="AD52">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 32443-2026 tillsynsbegäran mail.docx", "A 32443-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="15" customHeight="1">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>A 42765-2022</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="n">
-        <v>44832</v>
-      </c>
-      <c r="E50" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1</v>
-      </c>
-      <c r="K50" t="n">
-        <v>1</v>
-      </c>
-      <c r="L50" t="n">
-        <v>1</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>1</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>3</v>
-      </c>
-      <c r="T50" t="n">
-        <v>4</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1</v>
-      </c>
-      <c r="V50" s="2" t="inlineStr">
-        <is>
-          <t>Krusfrö
-Barkticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 42765-2022 artfynd.xlsx", "A 42765-2022")</f>
-        <v/>
-      </c>
-      <c r="X50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 42765-2022 karta.png", "A 42765-2022")</f>
-        <v/>
-      </c>
-      <c r="Y50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 42765-2022 georefererad karta.tif", "A 42765-2022")</f>
-        <v/>
-      </c>
-      <c r="AA50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 42765-2022 FSC-klagomål.docx", "A 42765-2022")</f>
-        <v/>
-      </c>
-      <c r="AB50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 42765-2022 FSC-klagomål mail.docx", "A 42765-2022")</f>
-        <v/>
-      </c>
-      <c r="AC50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 42765-2022 tillsynsbegäran.docx", "A 42765-2022")</f>
-        <v/>
-      </c>
-      <c r="AD50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 42765-2022 tillsynsbegäran mail.docx", "A 42765-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>A 33935-2026</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="n">
-        <v>46248</v>
-      </c>
-      <c r="E51" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J51" t="n">
-        <v>2</v>
-      </c>
-      <c r="K51" t="n">
-        <v>1</v>
-      </c>
-      <c r="L51" t="n">
-        <v>1</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>1</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>3</v>
-      </c>
-      <c r="T51" t="n">
-        <v>5</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Mindre märgborre
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 33935-2026 artfynd.xlsx", "A 33935-2026")</f>
-        <v/>
-      </c>
-      <c r="X51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 33935-2026 karta.png", "A 33935-2026")</f>
-        <v/>
-      </c>
-      <c r="Y51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 33935-2026 georefererad karta.tif", "A 33935-2026")</f>
-        <v/>
-      </c>
-      <c r="AA51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 33935-2026 FSC-klagomål.docx", "A 33935-2026")</f>
-        <v/>
-      </c>
-      <c r="AB51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 33935-2026 FSC-klagomål mail.docx", "A 33935-2026")</f>
-        <v/>
-      </c>
-      <c r="AC51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 33935-2026 tillsynsbegäran.docx", "A 33935-2026")</f>
-        <v/>
-      </c>
-      <c r="AD51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 33935-2026 tillsynsbegäran mail.docx", "A 33935-2026")</f>
-        <v/>
-      </c>
-      <c r="AE51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 33935-2026 prioriterade fågelarter.docx", "A 33935-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="15" customHeight="1">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>A 36264-2026</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D52" s="1" t="n">
-        <v>46268</v>
-      </c>
-      <c r="E52" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I52" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J52" t="n">
-        <v>1</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
-        <v>1</v>
-      </c>
-      <c r="M52" t="n">
-        <v>1</v>
-      </c>
-      <c r="N52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>2</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1</v>
-      </c>
-      <c r="S52" t="n">
-        <v>3</v>
-      </c>
-      <c r="T52" t="n">
-        <v>3</v>
-      </c>
-      <c r="U52" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" s="2" t="inlineStr">
-        <is>
-          <t>Grangråticka
-Fjällig taggsvamp s.str.
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 36264-2026 artfynd.xlsx", "A 36264-2026")</f>
-        <v/>
-      </c>
-      <c r="X52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 36264-2026 karta.png", "A 36264-2026")</f>
-        <v/>
-      </c>
-      <c r="Y52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 36264-2026 georefererad karta.tif", "A 36264-2026")</f>
-        <v/>
-      </c>
-      <c r="AA52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 36264-2026 FSC-klagomål.docx", "A 36264-2026")</f>
-        <v/>
-      </c>
-      <c r="AB52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 36264-2026 FSC-klagomål mail.docx", "A 36264-2026")</f>
-        <v/>
-      </c>
-      <c r="AC52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 36264-2026 tillsynsbegäran.docx", "A 36264-2026")</f>
-        <v/>
-      </c>
-      <c r="AD52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 36264-2026 tillsynsbegäran mail.docx", "A 36264-2026")</f>
         <v/>
       </c>
     </row>
@@ -6921,7 +6921,7 @@
         <v>44635</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>45708</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>45708</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 56362-2023</t>
+          <t>A 30074-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7270,10 +7270,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45236</v>
+        <v>45110</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7287,11 +7287,11 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>15.2</v>
+        <v>1.1</v>
       </c>
       <c r="J56" t="n">
         <v>1</v>
@@ -7303,7 +7303,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
@@ -7315,10 +7315,10 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>2</v>
@@ -7327,47 +7327,47 @@
         <v>2</v>
       </c>
       <c r="U56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>Väddnätfjäril
-Grönpyrola</t>
+          <t>Grönpyrola
+Revlummer</t>
         </is>
       </c>
       <c r="W56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 56362-2023 artfynd.xlsx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 30074-2023 artfynd.xlsx", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="X56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 56362-2023 karta.png", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 30074-2023 karta.png", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="Y56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 56362-2023 georefererad karta.tif", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 30074-2023 georefererad karta.tif", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="AA56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 56362-2023 FSC-klagomål.docx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 30074-2023 FSC-klagomål.docx", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="AB56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 56362-2023 FSC-klagomål mail.docx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 30074-2023 FSC-klagomål mail.docx", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="AC56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 56362-2023 tillsynsbegäran.docx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 30074-2023 tillsynsbegäran.docx", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="AD56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 56362-2023 tillsynsbegäran mail.docx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 30074-2023 tillsynsbegäran mail.docx", "A 30074-2023")</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 40403-2025</t>
+          <t>A 13788-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45895</v>
+        <v>45737</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7396,25 +7396,20 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>3.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
         <v>0</v>
@@ -7429,56 +7424,60 @@
         <v>1</v>
       </c>
       <c r="R57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>2</v>
       </c>
       <c r="T57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>Igelkott
-Gröngöling</t>
+          <t>Sparvuggla
+Nattskärra</t>
         </is>
       </c>
       <c r="W57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 40403-2025 artfynd.xlsx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 13788-2025 artfynd.xlsx", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="X57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 40403-2025 karta.png", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 13788-2025 karta.png", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="Y57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 40403-2025 georefererad karta.tif", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 13788-2025 georefererad karta.tif", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="AA57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 40403-2025 FSC-klagomål.docx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 13788-2025 FSC-klagomål.docx", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="AB57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 40403-2025 FSC-klagomål mail.docx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 13788-2025 FSC-klagomål mail.docx", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="AC57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 40403-2025 tillsynsbegäran.docx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 13788-2025 tillsynsbegäran.docx", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="AD57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 40403-2025 tillsynsbegäran mail.docx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 13788-2025 tillsynsbegäran mail.docx", "A 13788-2025")</f>
+        <v/>
+      </c>
+      <c r="AE57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 13788-2025 prioriterade fågelarter.docx", "A 13788-2025")</f>
         <v/>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 14001-2023</t>
+          <t>A 56362-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7492,10 +7491,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45007</v>
+        <v>45236</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7513,16 +7512,16 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>15.2</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
         <v>1</v>
@@ -7537,7 +7536,7 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R58" t="n">
         <v>1</v>
@@ -7549,40 +7548,40 @@
         <v>2</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>Garnlav
-Motaggsvamp</t>
+          <t>Väddnätfjäril
+Grönpyrola</t>
         </is>
       </c>
       <c r="W58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 14001-2023 artfynd.xlsx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 56362-2023 artfynd.xlsx", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="X58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 14001-2023 karta.png", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 56362-2023 karta.png", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="Y58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 14001-2023 georefererad karta.tif", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 56362-2023 georefererad karta.tif", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="AA58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 14001-2023 FSC-klagomål.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 56362-2023 FSC-klagomål.docx", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="AB58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 14001-2023 FSC-klagomål mail.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 56362-2023 FSC-klagomål mail.docx", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="AC58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 14001-2023 tillsynsbegäran.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 56362-2023 tillsynsbegäran.docx", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="AD58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 14001-2023 tillsynsbegäran mail.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 56362-2023 tillsynsbegäran mail.docx", "A 56362-2023")</f>
         <v/>
       </c>
     </row>
@@ -7606,7 +7605,7 @@
         <v>45587</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7699,7 +7698,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 11501-2023</t>
+          <t>A 40403-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7713,10 +7712,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44991</v>
+        <v>45895</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7730,23 +7729,23 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J60" t="n">
         <v>1</v>
       </c>
       <c r="K60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N60" t="n">
         <v>0</v>
@@ -7758,59 +7757,59 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S60" t="n">
         <v>2</v>
       </c>
       <c r="T60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva
-Nattviol</t>
+          <t>Igelkott
+Gröngöling</t>
         </is>
       </c>
       <c r="W60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 11501-2023 artfynd.xlsx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 40403-2025 artfynd.xlsx", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="X60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 11501-2023 karta.png", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 40403-2025 karta.png", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="Y60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 11501-2023 georefererad karta.tif", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 40403-2025 georefererad karta.tif", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="AA60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 11501-2023 FSC-klagomål.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 40403-2025 FSC-klagomål.docx", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="AB60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 11501-2023 FSC-klagomål mail.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 40403-2025 FSC-klagomål mail.docx", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="AC60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 11501-2023 tillsynsbegäran.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 40403-2025 tillsynsbegäran.docx", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="AD60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 11501-2023 tillsynsbegäran mail.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 40403-2025 tillsynsbegäran mail.docx", "A 40403-2025")</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 41204-2023</t>
+          <t>A 37013-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7824,10 +7823,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45174</v>
+        <v>45874</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7839,20 +7838,25 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>10.7</v>
       </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
@@ -7867,53 +7871,49 @@
         <v>2</v>
       </c>
       <c r="R61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S61" t="n">
         <v>2</v>
       </c>
       <c r="T61" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U61" t="n">
         <v>0</v>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>Knärot
-Vedtrappmossa</t>
+          <t>Brunfläckig pärlemorfjäril
+Fältgentiana</t>
         </is>
       </c>
       <c r="W61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 41204-2023 artfynd.xlsx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37013-2025 artfynd.xlsx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="X61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 41204-2023 karta.png", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37013-2025 karta.png", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="Y61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 41204-2023 georefererad karta.tif", "A 41204-2023")</f>
-        <v/>
-      </c>
-      <c r="Z61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 41204-2023 karta knärot.png", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37013-2025 georefererad karta.tif", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AA61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 41204-2023 FSC-klagomål.docx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37013-2025 FSC-klagomål.docx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AB61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 41204-2023 FSC-klagomål mail.docx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37013-2025 FSC-klagomål mail.docx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AC61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 41204-2023 tillsynsbegäran.docx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37013-2025 tillsynsbegäran.docx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AD61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 41204-2023 tillsynsbegäran mail.docx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37013-2025 tillsynsbegäran mail.docx", "A 37013-2025")</f>
         <v/>
       </c>
     </row>
@@ -7937,7 +7937,7 @@
         <v>46009</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 30074-2023</t>
+          <t>A 41204-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -8049,10 +8049,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45110</v>
+        <v>45174</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8064,25 +8064,20 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>1</v>
       </c>
       <c r="K63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
@@ -8094,59 +8089,63 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S63" t="n">
         <v>2</v>
       </c>
       <c r="T63" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola
-Revlummer</t>
+          <t>Knärot
+Vedtrappmossa</t>
         </is>
       </c>
       <c r="W63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 30074-2023 artfynd.xlsx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 41204-2023 artfynd.xlsx", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="X63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 30074-2023 karta.png", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 41204-2023 karta.png", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="Y63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 30074-2023 georefererad karta.tif", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 41204-2023 georefererad karta.tif", "A 41204-2023")</f>
+        <v/>
+      </c>
+      <c r="Z63">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 41204-2023 karta knärot.png", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="AA63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 30074-2023 FSC-klagomål.docx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 41204-2023 FSC-klagomål.docx", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="AB63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 30074-2023 FSC-klagomål mail.docx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 41204-2023 FSC-klagomål mail.docx", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="AC63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 30074-2023 tillsynsbegäran.docx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 41204-2023 tillsynsbegäran.docx", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="AD63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 30074-2023 tillsynsbegäran mail.docx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 41204-2023 tillsynsbegäran mail.docx", "A 41204-2023")</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 13971-2023</t>
+          <t>A 11501-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -8160,10 +8159,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45007</v>
+        <v>44991</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8181,13 +8180,13 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -8214,50 +8213,50 @@
         <v>2</v>
       </c>
       <c r="T64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>Dubbelnycklar
-Fläcknycklar</t>
+          <t>Svart trolldruva
+Nattviol</t>
         </is>
       </c>
       <c r="W64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 13971-2023 artfynd.xlsx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 11501-2023 artfynd.xlsx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="X64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 13971-2023 karta.png", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 11501-2023 karta.png", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="Y64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 13971-2023 georefererad karta.tif", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 11501-2023 georefererad karta.tif", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AA64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 13971-2023 FSC-klagomål.docx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 11501-2023 FSC-klagomål.docx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AB64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 13971-2023 FSC-klagomål mail.docx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 11501-2023 FSC-klagomål mail.docx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AC64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 13971-2023 tillsynsbegäran.docx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 11501-2023 tillsynsbegäran.docx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AD64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 13971-2023 tillsynsbegäran mail.docx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 11501-2023 tillsynsbegäran mail.docx", "A 11501-2023")</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 36261-2026</t>
+          <t>A 14001-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -8271,10 +8270,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46268</v>
+        <v>45007</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8288,14 +8287,14 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>7.9</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -8304,7 +8303,7 @@
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
@@ -8316,10 +8315,10 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S65" t="n">
         <v>2</v>
@@ -8332,43 +8331,43 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>Krusfrö
-Revlummer</t>
+          <t>Garnlav
+Motaggsvamp</t>
         </is>
       </c>
       <c r="W65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 36261-2026 artfynd.xlsx", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 14001-2023 artfynd.xlsx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="X65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 36261-2026 karta.png", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 14001-2023 karta.png", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="Y65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 36261-2026 georefererad karta.tif", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 14001-2023 georefererad karta.tif", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AA65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 36261-2026 FSC-klagomål.docx", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 14001-2023 FSC-klagomål.docx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AB65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 36261-2026 FSC-klagomål mail.docx", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 14001-2023 FSC-klagomål mail.docx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AC65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 36261-2026 tillsynsbegäran.docx", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 14001-2023 tillsynsbegäran.docx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AD65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 36261-2026 tillsynsbegäran mail.docx", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 14001-2023 tillsynsbegäran mail.docx", "A 14001-2023")</f>
         <v/>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 13788-2025</t>
+          <t>A 13971-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -8382,10 +8381,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45737</v>
+        <v>45007</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8397,8 +8396,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>9.699999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="J66" t="n">
         <v>2</v>
@@ -8407,7 +8411,7 @@
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -8422,7 +8426,7 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
@@ -8431,54 +8435,50 @@
         <v>2</v>
       </c>
       <c r="T66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>Sparvuggla
-Nattskärra</t>
+          <t>Dubbelnycklar
+Fläcknycklar</t>
         </is>
       </c>
       <c r="W66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 13788-2025 artfynd.xlsx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 13971-2023 artfynd.xlsx", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="X66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 13788-2025 karta.png", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 13971-2023 karta.png", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="Y66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 13788-2025 georefererad karta.tif", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 13971-2023 georefererad karta.tif", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="AA66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 13788-2025 FSC-klagomål.docx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 13971-2023 FSC-klagomål.docx", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="AB66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 13788-2025 FSC-klagomål mail.docx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 13971-2023 FSC-klagomål mail.docx", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="AC66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 13788-2025 tillsynsbegäran.docx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 13971-2023 tillsynsbegäran.docx", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="AD66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 13788-2025 tillsynsbegäran mail.docx", "A 13788-2025")</f>
-        <v/>
-      </c>
-      <c r="AE66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 13788-2025 prioriterade fågelarter.docx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 13971-2023 tillsynsbegäran mail.docx", "A 13971-2023")</f>
         <v/>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 37013-2025</t>
+          <t>A 36261-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -8492,10 +8492,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45874</v>
+        <v>46268</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8509,23 +8509,23 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>10.7</v>
+        <v>7.9</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
         <v>0</v>
@@ -8537,10 +8537,10 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>2</v>
@@ -8553,36 +8553,36 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril
-Fältgentiana</t>
+          <t>Krusfrö
+Revlummer</t>
         </is>
       </c>
       <c r="W67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37013-2025 artfynd.xlsx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 36261-2026 artfynd.xlsx", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="X67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37013-2025 karta.png", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 36261-2026 karta.png", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="Y67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37013-2025 georefererad karta.tif", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 36261-2026 georefererad karta.tif", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="AA67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37013-2025 FSC-klagomål.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 36261-2026 FSC-klagomål.docx", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="AB67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37013-2025 FSC-klagomål mail.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 36261-2026 FSC-klagomål mail.docx", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="AC67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37013-2025 tillsynsbegäran.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 36261-2026 tillsynsbegäran.docx", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="AD67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37013-2025 tillsynsbegäran mail.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 36261-2026 tillsynsbegäran mail.docx", "A 36261-2026")</f>
         <v/>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
         <v>45720</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8717,7 +8717,7 @@
         <v>44696</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>44739</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>44524</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>44696</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 39099-2022</t>
+          <t>A 30076-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -9154,10 +9154,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44817</v>
+        <v>45110</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9171,17 +9171,17 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>7.4</v>
+        <v>1.1</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -9211,46 +9211,46 @@
         <v>1</v>
       </c>
       <c r="U73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39099-2022 artfynd.xlsx", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 30076-2023 artfynd.xlsx", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="X73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39099-2022 karta.png", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 30076-2023 karta.png", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="Y73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39099-2022 georefererad karta.tif", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 30076-2023 georefererad karta.tif", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="AA73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39099-2022 FSC-klagomål.docx", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 30076-2023 FSC-klagomål.docx", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="AB73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39099-2022 FSC-klagomål mail.docx", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 30076-2023 FSC-klagomål mail.docx", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="AC73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39099-2022 tillsynsbegäran.docx", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 30076-2023 tillsynsbegäran.docx", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="AD73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39099-2022 tillsynsbegäran mail.docx", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 30076-2023 tillsynsbegäran mail.docx", "A 30076-2023")</f>
         <v/>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 17632-2022</t>
+          <t>A 8553-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -9260,14 +9260,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44680</v>
+        <v>44977</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9279,20 +9279,25 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>5.2</v>
+        <v>1.5</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N74" t="n">
         <v>0</v>
@@ -9304,10 +9309,10 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S74" t="n">
         <v>1</v>
@@ -9320,42 +9325,42 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="W74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 17632-2022 artfynd.xlsx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 8553-2023 artfynd.xlsx", "A 8553-2023")</f>
         <v/>
       </c>
       <c r="X74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 17632-2022 karta.png", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 8553-2023 karta.png", "A 8553-2023")</f>
         <v/>
       </c>
       <c r="Y74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 17632-2022 georefererad karta.tif", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 8553-2023 georefererad karta.tif", "A 8553-2023")</f>
         <v/>
       </c>
       <c r="AA74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 17632-2022 FSC-klagomål.docx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 8553-2023 FSC-klagomål.docx", "A 8553-2023")</f>
         <v/>
       </c>
       <c r="AB74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 17632-2022 FSC-klagomål mail.docx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 8553-2023 FSC-klagomål mail.docx", "A 8553-2023")</f>
         <v/>
       </c>
       <c r="AC74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 17632-2022 tillsynsbegäran.docx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 8553-2023 tillsynsbegäran.docx", "A 8553-2023")</f>
         <v/>
       </c>
       <c r="AD74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 17632-2022 tillsynsbegäran mail.docx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 8553-2023 tillsynsbegäran mail.docx", "A 8553-2023")</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 8553-2023</t>
+          <t>A 37287-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -9365,14 +9370,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44977</v>
+        <v>45156</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9384,25 +9389,20 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
         <v>0</v>
@@ -9417,7 +9417,7 @@
         <v>1</v>
       </c>
       <c r="R75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>1</v>
@@ -9430,42 +9430,42 @@
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>Väddnätfjäril</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="W75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 8553-2023 artfynd.xlsx", "A 8553-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37287-2023 artfynd.xlsx", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="X75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 8553-2023 karta.png", "A 8553-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37287-2023 karta.png", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="Y75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 8553-2023 georefererad karta.tif", "A 8553-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37287-2023 georefererad karta.tif", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="AA75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 8553-2023 FSC-klagomål.docx", "A 8553-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37287-2023 FSC-klagomål.docx", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="AB75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 8553-2023 FSC-klagomål mail.docx", "A 8553-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37287-2023 FSC-klagomål mail.docx", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="AC75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 8553-2023 tillsynsbegäran.docx", "A 8553-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37287-2023 tillsynsbegäran.docx", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="AD75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 8553-2023 tillsynsbegäran mail.docx", "A 8553-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37287-2023 tillsynsbegäran mail.docx", "A 37287-2023")</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 16013-2023</t>
+          <t>A 34584-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -9479,10 +9479,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45026</v>
+        <v>45846</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9494,11 +9494,16 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -9507,7 +9512,7 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
         <v>0</v>
@@ -9519,10 +9524,10 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>1</v>
@@ -9531,46 +9536,50 @@
         <v>1</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 16013-2023 artfynd.xlsx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34584-2025 artfynd.xlsx", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="X76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 16013-2023 karta.png", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34584-2025 karta.png", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="Y76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 16013-2023 georefererad karta.tif", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34584-2025 georefererad karta.tif", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="AA76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 16013-2023 FSC-klagomål.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34584-2025 FSC-klagomål.docx", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="AB76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 16013-2023 FSC-klagomål mail.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34584-2025 FSC-klagomål mail.docx", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="AC76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 16013-2023 tillsynsbegäran.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34584-2025 tillsynsbegäran.docx", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="AD76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 16013-2023 tillsynsbegäran mail.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34584-2025 tillsynsbegäran mail.docx", "A 34584-2025")</f>
+        <v/>
+      </c>
+      <c r="AE76">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 34584-2025 prioriterade fågelarter.docx", "A 34584-2025")</f>
         <v/>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 34955-2022</t>
+          <t>A 39099-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -9584,10 +9593,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44796</v>
+        <v>44817</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9601,20 +9610,20 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -9629,7 +9638,7 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
         <v>0</v>
@@ -9645,42 +9654,42 @@
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="W77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34955-2022 artfynd.xlsx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39099-2022 artfynd.xlsx", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="X77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34955-2022 karta.png", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39099-2022 karta.png", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="Y77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34955-2022 georefererad karta.tif", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39099-2022 georefererad karta.tif", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="AA77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34955-2022 FSC-klagomål.docx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39099-2022 FSC-klagomål.docx", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="AB77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34955-2022 FSC-klagomål mail.docx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39099-2022 FSC-klagomål mail.docx", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="AC77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34955-2022 tillsynsbegäran.docx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39099-2022 tillsynsbegäran.docx", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="AD77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34955-2022 tillsynsbegäran mail.docx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39099-2022 tillsynsbegäran mail.docx", "A 39099-2022")</f>
         <v/>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 33231-2024</t>
+          <t>A 17632-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -9694,10 +9703,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45518</v>
+        <v>44680</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9709,19 +9718,14 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>5.2</v>
       </c>
       <c r="J78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -9751,46 +9755,46 @@
         <v>1</v>
       </c>
       <c r="U78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="W78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 33231-2024 artfynd.xlsx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 17632-2022 artfynd.xlsx", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="X78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 33231-2024 karta.png", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 17632-2022 karta.png", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="Y78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 33231-2024 georefererad karta.tif", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 17632-2022 georefererad karta.tif", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="AA78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 33231-2024 FSC-klagomål.docx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 17632-2022 FSC-klagomål.docx", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="AB78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 33231-2024 FSC-klagomål mail.docx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 17632-2022 FSC-klagomål mail.docx", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="AC78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 33231-2024 tillsynsbegäran.docx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 17632-2022 tillsynsbegäran.docx", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="AD78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 33231-2024 tillsynsbegäran mail.docx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 17632-2022 tillsynsbegäran mail.docx", "A 17632-2022")</f>
         <v/>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 30076-2023</t>
+          <t>A 34955-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -9804,10 +9808,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45110</v>
+        <v>44796</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9825,16 +9829,16 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -9849,7 +9853,7 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R79" t="n">
         <v>0</v>
@@ -9861,39 +9865,39 @@
         <v>1</v>
       </c>
       <c r="U79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 30076-2023 artfynd.xlsx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34955-2022 artfynd.xlsx", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="X79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 30076-2023 karta.png", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34955-2022 karta.png", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="Y79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 30076-2023 georefererad karta.tif", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34955-2022 georefererad karta.tif", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="AA79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 30076-2023 FSC-klagomål.docx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34955-2022 FSC-klagomål.docx", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="AB79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 30076-2023 FSC-klagomål mail.docx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34955-2022 FSC-klagomål mail.docx", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="AC79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 30076-2023 tillsynsbegäran.docx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34955-2022 tillsynsbegäran.docx", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="AD79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 30076-2023 tillsynsbegäran mail.docx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34955-2022 tillsynsbegäran mail.docx", "A 34955-2022")</f>
         <v/>
       </c>
     </row>
@@ -9917,7 +9921,7 @@
         <v>44991</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10014,7 +10018,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 24167-2024</t>
+          <t>A 44356-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -10024,14 +10028,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45456</v>
+        <v>45573</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10043,8 +10047,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>1</v>
@@ -10080,46 +10089,46 @@
         <v>1</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 24167-2024 artfynd.xlsx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 44356-2024 artfynd.xlsx", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="X81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 24167-2024 karta.png", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 44356-2024 karta.png", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="Y81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 24167-2024 georefererad karta.tif", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 44356-2024 georefererad karta.tif", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="AA81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 24167-2024 FSC-klagomål.docx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 44356-2024 FSC-klagomål.docx", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="AB81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 24167-2024 FSC-klagomål mail.docx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 44356-2024 FSC-klagomål mail.docx", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="AC81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 24167-2024 tillsynsbegäran.docx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 44356-2024 tillsynsbegäran.docx", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="AD81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 24167-2024 tillsynsbegäran mail.docx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 44356-2024 tillsynsbegäran mail.docx", "A 44356-2024")</f>
         <v/>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 37287-2023</t>
+          <t>A 33231-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -10133,10 +10142,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45156</v>
+        <v>45518</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10148,17 +10157,22 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -10173,7 +10187,7 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
         <v>0</v>
@@ -10185,46 +10199,46 @@
         <v>1</v>
       </c>
       <c r="U82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>Mindre tåtelsmygare</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="W82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37287-2023 artfynd.xlsx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 33231-2024 artfynd.xlsx", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="X82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37287-2023 karta.png", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 33231-2024 karta.png", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="Y82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37287-2023 georefererad karta.tif", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 33231-2024 georefererad karta.tif", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="AA82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37287-2023 FSC-klagomål.docx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 33231-2024 FSC-klagomål.docx", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="AB82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37287-2023 FSC-klagomål mail.docx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 33231-2024 FSC-klagomål mail.docx", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="AC82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37287-2023 tillsynsbegäran.docx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 33231-2024 tillsynsbegäran.docx", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="AD82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37287-2023 tillsynsbegäran mail.docx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 33231-2024 tillsynsbegäran mail.docx", "A 33231-2024")</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 44356-2024</t>
+          <t>A 24167-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -10234,14 +10248,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45573</v>
+        <v>45456</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10253,13 +10267,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J83" t="n">
         <v>1</v>
@@ -10295,39 +10304,39 @@
         <v>1</v>
       </c>
       <c r="U83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 44356-2024 artfynd.xlsx", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 24167-2024 artfynd.xlsx", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="X83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 44356-2024 karta.png", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 24167-2024 karta.png", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="Y83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 44356-2024 georefererad karta.tif", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 24167-2024 georefererad karta.tif", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="AA83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 44356-2024 FSC-klagomål.docx", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 24167-2024 FSC-klagomål.docx", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="AB83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 44356-2024 FSC-klagomål mail.docx", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 24167-2024 FSC-klagomål mail.docx", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="AC83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 44356-2024 tillsynsbegäran.docx", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 24167-2024 tillsynsbegäran.docx", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="AD83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 44356-2024 tillsynsbegäran mail.docx", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 24167-2024 tillsynsbegäran mail.docx", "A 24167-2024")</f>
         <v/>
       </c>
     </row>
@@ -10351,7 +10360,7 @@
         <v>46224</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10444,7 +10453,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 34584-2025</t>
+          <t>A 16013-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -10458,10 +10467,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45846</v>
+        <v>45026</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10473,16 +10482,11 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="J85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -10491,7 +10495,7 @@
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N85" t="n">
         <v>0</v>
@@ -10503,10 +10507,10 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S85" t="n">
         <v>1</v>
@@ -10515,43 +10519,39 @@
         <v>1</v>
       </c>
       <c r="U85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="W85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34584-2025 artfynd.xlsx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 16013-2023 artfynd.xlsx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="X85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34584-2025 karta.png", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 16013-2023 karta.png", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="Y85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34584-2025 georefererad karta.tif", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 16013-2023 georefererad karta.tif", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AA85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34584-2025 FSC-klagomål.docx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 16013-2023 FSC-klagomål.docx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AB85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34584-2025 FSC-klagomål mail.docx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 16013-2023 FSC-klagomål mail.docx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AC85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34584-2025 tillsynsbegäran.docx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 16013-2023 tillsynsbegäran.docx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AD85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34584-2025 tillsynsbegäran mail.docx", "A 34584-2025")</f>
-        <v/>
-      </c>
-      <c r="AE85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 34584-2025 prioriterade fågelarter.docx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 16013-2023 tillsynsbegäran mail.docx", "A 16013-2023")</f>
         <v/>
       </c>
     </row>
@@ -10575,7 +10575,7 @@
         <v>44509</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>44696</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>44782</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         <v>44550</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>44586</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>44582</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>44694</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 35682-2022</t>
+          <t>A 66342-2021</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44799</v>
+        <v>44518</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -11189,7 +11189,7 @@
         <v>44796</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 66342-2021</t>
+          <t>A 48205-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -11264,10 +11264,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44518</v>
+        <v>45205</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11281,11 +11281,11 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.4</v>
+        <v>7.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -11328,7 +11328,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 21509-2024</t>
+          <t>A 15743-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -11342,10 +11342,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45441</v>
+        <v>45021</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11357,13 +11357,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -11406,7 +11401,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 42832-2022</t>
+          <t>A 15637-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -11416,14 +11411,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44832</v>
+        <v>44662</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11436,7 +11431,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -11479,7 +11474,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 42841-2022</t>
+          <t>A 19786-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -11489,14 +11484,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44832</v>
+        <v>45050</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11508,8 +11503,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>1.8</v>
+        <v>8.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -11552,7 +11552,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 24158-2023</t>
+          <t>A 7787-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -11566,10 +11566,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45079</v>
+        <v>45348</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11581,13 +11581,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -11630,7 +11625,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 37954-2025</t>
+          <t>A 72367-2021</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -11644,10 +11639,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45881</v>
+        <v>44545</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11660,7 +11655,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>9.5</v>
+        <v>2.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -11703,7 +11698,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 2867-2024</t>
+          <t>A 33931-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -11717,10 +11712,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45315</v>
+        <v>44790</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11732,13 +11727,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -11781,7 +11771,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 2660-2024</t>
+          <t>A 37954-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -11795,10 +11785,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45310</v>
+        <v>45881</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11811,7 +11801,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.1</v>
+        <v>9.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -11854,7 +11844,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 5567-2022</t>
+          <t>A 4724-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -11868,10 +11858,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44595</v>
+        <v>46048</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11884,7 +11874,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -11927,7 +11917,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 12841-2026</t>
+          <t>A 4734-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -11941,10 +11931,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46091</v>
+        <v>46048</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11956,13 +11946,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -12005,7 +11990,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 3818-2022</t>
+          <t>A 24158-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -12019,10 +12004,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44587</v>
+        <v>45079</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12034,8 +12019,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -12078,7 +12068,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 19782-2023</t>
+          <t>A 42714-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -12092,10 +12082,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45050</v>
+        <v>44832</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12107,13 +12097,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -12156,7 +12141,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 19246-2026</t>
+          <t>A 55873-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -12166,14 +12151,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46132</v>
+        <v>45973</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12191,7 +12176,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -12234,7 +12219,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 14626-2023</t>
+          <t>A 35682-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -12248,10 +12233,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45012</v>
+        <v>44799</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12265,11 +12250,11 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -12312,7 +12297,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 56378-2023</t>
+          <t>A 11728-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -12322,14 +12307,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45236</v>
+        <v>44993</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12347,7 +12332,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>4.6</v>
+        <v>0.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -12390,7 +12375,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 11728-2023</t>
+          <t>A 5567-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -12400,14 +12385,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44993</v>
+        <v>44595</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12419,13 +12404,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -12468,7 +12448,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 55873-2025</t>
+          <t>A 10249-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -12482,10 +12462,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45973</v>
+        <v>46076</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12499,11 +12479,11 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -12546,7 +12526,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 3085-2023</t>
+          <t>A 42832-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -12556,14 +12536,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44946</v>
+        <v>44832</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12575,13 +12555,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>13</v>
+        <v>1.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -12624,7 +12599,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 20904-2023</t>
+          <t>A 10244-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -12634,14 +12609,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45060</v>
+        <v>46076</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12655,11 +12630,11 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -12702,7 +12677,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 32808-2024</t>
+          <t>A 10562-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -12716,10 +12691,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45516</v>
+        <v>46077</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12737,7 +12712,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -12780,7 +12755,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 42829-2022</t>
+          <t>A 24665-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -12790,14 +12765,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44832</v>
+        <v>45084</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12810,7 +12785,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -12853,7 +12828,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 20535-2026</t>
+          <t>A 42841-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -12867,10 +12842,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46140</v>
+        <v>44832</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12882,13 +12857,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -12931,7 +12901,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 7848-2022</t>
+          <t>A 42829-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -12941,14 +12911,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44608</v>
+        <v>44832</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12961,7 +12931,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -13004,7 +12974,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 49058-2024</t>
+          <t>A 12841-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -13018,10 +12988,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45594</v>
+        <v>46091</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13035,11 +13005,11 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>11.4</v>
+        <v>4.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -13082,7 +13052,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 48205-2023</t>
+          <t>A 2867-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -13096,10 +13066,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45205</v>
+        <v>45315</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13113,11 +13083,11 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>7.6</v>
+        <v>1.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -13160,7 +13130,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 33931-2022</t>
+          <t>A 3085-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -13174,10 +13144,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44790</v>
+        <v>44946</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13189,8 +13159,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>2.2</v>
+        <v>13</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -13233,7 +13208,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 22662-2023</t>
+          <t>A 19246-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -13243,14 +13218,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45071</v>
+        <v>46132</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13268,7 +13243,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -13311,7 +13286,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 24201-2026</t>
+          <t>A 32808-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -13325,10 +13300,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46168</v>
+        <v>45516</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13340,8 +13315,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -13384,7 +13364,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 4724-2026</t>
+          <t>A 20904-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -13394,14 +13374,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46048</v>
+        <v>45060</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13411,6 +13391,11 @@
       <c r="G123" t="inlineStr">
         <is>
           <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I123" t="n">
@@ -13457,7 +13442,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 4734-2026</t>
+          <t>A 2660-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -13471,10 +13456,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46048</v>
+        <v>45310</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13487,7 +13472,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -13530,7 +13515,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 15743-2023</t>
+          <t>A 49058-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -13544,10 +13529,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45021</v>
+        <v>45594</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13559,8 +13544,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>0.5</v>
+        <v>11.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -13603,7 +13593,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 10244-2026</t>
+          <t>A 20535-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -13613,14 +13603,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46076</v>
+        <v>46140</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13634,11 +13624,11 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>8.699999999999999</v>
+        <v>2.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -13681,7 +13671,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 10249-2026</t>
+          <t>A 14626-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -13695,10 +13685,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46076</v>
+        <v>45012</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13712,11 +13702,11 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -13759,7 +13749,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 10562-2026</t>
+          <t>A 25450-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -13773,10 +13763,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46077</v>
+        <v>45463</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13790,11 +13780,11 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -13837,7 +13827,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 25450-2024</t>
+          <t>A 24201-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -13851,10 +13841,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45463</v>
+        <v>46168</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13866,13 +13856,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -13915,7 +13900,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 32501-2026</t>
+          <t>A 19782-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -13925,14 +13910,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46239</v>
+        <v>45050</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13944,8 +13929,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>1.5</v>
+        <v>5.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -13988,7 +13978,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 22628-2026</t>
+          <t>A 7848-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -14002,10 +13992,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46155</v>
+        <v>44608</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14017,13 +14007,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -14066,7 +14051,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 24665-2023</t>
+          <t>A 56378-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -14080,10 +14065,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45084</v>
+        <v>45236</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14095,8 +14080,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>0.9</v>
+        <v>4.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -14139,7 +14129,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 72367-2021</t>
+          <t>A 19099-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -14153,10 +14143,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44545</v>
+        <v>44691</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14168,8 +14158,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -14212,7 +14207,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 42714-2022</t>
+          <t>A 22628-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -14226,10 +14221,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44832</v>
+        <v>46155</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14241,8 +14236,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -14285,7 +14285,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 15637-2022</t>
+          <t>A 3818-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -14299,10 +14299,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44662</v>
+        <v>44587</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14315,7 +14315,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -14375,7 +14375,7 @@
         <v>46248</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 19786-2023</t>
+          <t>A 31061-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -14450,10 +14450,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45050</v>
+        <v>46215</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14467,11 +14467,11 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>8.1</v>
+        <v>4.4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -14514,7 +14514,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 19099-2022</t>
+          <t>A 21509-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -14528,10 +14528,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44691</v>
+        <v>45441</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14545,11 +14545,11 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -14592,7 +14592,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 31061-2026</t>
+          <t>A 22662-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -14602,14 +14602,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46215</v>
+        <v>45071</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -14687,7 +14687,7 @@
         <v>45090</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 7787-2024</t>
+          <t>A 32501-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -14753,14 +14753,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45348</v>
+        <v>46239</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -14833,7 +14833,7 @@
         <v>46237</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>45021</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>44734</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>44734</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>46251</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>

--- a/Översikt SURAHAMMAR.xlsx
+++ b/Översikt SURAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45470</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>45684</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 39697-2025</t>
+          <t>A 31280-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45890</v>
+        <v>45504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,23 +964,23 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>25.7</v>
+        <v>6.9</v>
       </c>
       <c r="J4" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -992,21 +992,182 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S4" t="n">
         <v>44</v>
       </c>
       <c r="T4" t="n">
+        <v>93</v>
+      </c>
+      <c r="U4" t="n">
+        <v>91</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Gränsticka
+Knärot
+Liten hornflikmossa
+Spadskinn
+Torrmusseron
+Apelsinticka
+Fjällig taggsvamp s.str.
+Grantaggsvamp
+Gropticka
+Kattfotslav
+Knölspindel
+Kötticka
+Mjölsvärting
+Nordfladdermus
+Nordtagging
+Persiljespindling
+Rynkskinn
+Skarp dropptaggsvamp
+Svartvit taggsvamp
+Tallkötticka
+Tallticka
+Talltita
+Ullticka
+Vaddporing
+Vedskivlav
+Vedtrappmossa
+Vågticka
+Bollvitmossa
+Bronshjon
+Flagellkvastmossa
+Grönpyrola
+Kornknutmossa
+Mindre märgborre
+Rostfläck
+Rödgul trumpetsvamp
+Smal svampklubba
+Thomsons trägnagare
+Vedticka
+Vågbandad barkbock
+Blåsippa
+Kungsfågel
+Mindre vattensalamander
+Fläcknycklar
+Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31280-2024 artfynd.xlsx", "A 31280-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31280-2024 karta.png", "A 31280-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31280-2024 georefererad karta.tif", "A 31280-2024")</f>
+        <v/>
+      </c>
+      <c r="Z4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 31280-2024 karta knärot.png", "A 31280-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31280-2024 FSC-klagomål.docx", "A 31280-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31280-2024 FSC-klagomål mail.docx", "A 31280-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31280-2024 tillsynsbegäran.docx", "A 31280-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31280-2024 tillsynsbegäran mail.docx", "A 31280-2024")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 31280-2024 prioriterade fågelarter.docx", "A 31280-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 39697-2025</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45890</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>28</v>
+      </c>
+      <c r="K5" t="n">
+        <v>7</v>
+      </c>
+      <c r="L5" t="n">
+        <v>14</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>16</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>44</v>
+      </c>
+      <c r="T5" t="n">
         <v>242</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>106</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Grönfink
 Knärot
@@ -1054,201 +1215,40 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39697-2025 artfynd.xlsx", "A 39697-2025")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39697-2025 karta.png", "A 39697-2025")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39697-2025 georefererad karta.tif", "A 39697-2025")</f>
         <v/>
       </c>
-      <c r="Z4">
+      <c r="Z5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 39697-2025 karta knärot.png", "A 39697-2025")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39697-2025 FSC-klagomål.docx", "A 39697-2025")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39697-2025 FSC-klagomål mail.docx", "A 39697-2025")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39697-2025 tillsynsbegäran.docx", "A 39697-2025")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39697-2025 tillsynsbegäran mail.docx", "A 39697-2025")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39697-2025 prioriterade fågelarter.docx", "A 39697-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 31280-2024</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45504</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J5" t="n">
-        <v>8</v>
-      </c>
-      <c r="K5" t="n">
-        <v>12</v>
-      </c>
-      <c r="L5" t="n">
-        <v>22</v>
-      </c>
-      <c r="M5" t="n">
-        <v>5</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>27</v>
-      </c>
-      <c r="R5" t="n">
-        <v>5</v>
-      </c>
-      <c r="S5" t="n">
-        <v>44</v>
-      </c>
-      <c r="T5" t="n">
-        <v>93</v>
-      </c>
-      <c r="U5" t="n">
-        <v>91</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Gränsticka
-Knärot
-Liten hornflikmossa
-Spadskinn
-Torrmusseron
-Apelsinticka
-Fjällig taggsvamp s.str.
-Grantaggsvamp
-Gropticka
-Kattfotslav
-Knölspindel
-Kötticka
-Mjölsvärting
-Nordfladdermus
-Nordtagging
-Persiljespindling
-Rynkskinn
-Skarp dropptaggsvamp
-Svartvit taggsvamp
-Tallkötticka
-Tallticka
-Talltita
-Ullticka
-Vaddporing
-Vedskivlav
-Vedtrappmossa
-Vågticka
-Bollvitmossa
-Bronshjon
-Flagellkvastmossa
-Grönpyrola
-Kornknutmossa
-Mindre märgborre
-Rostfläck
-Rödgul trumpetsvamp
-Smal svampklubba
-Thomsons trägnagare
-Vedticka
-Vågbandad barkbock
-Blåsippa
-Kungsfågel
-Mindre vattensalamander
-Fläcknycklar
-Lopplummer (aggregat)</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31280-2024 artfynd.xlsx", "A 31280-2024")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31280-2024 karta.png", "A 31280-2024")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31280-2024 georefererad karta.tif", "A 31280-2024")</f>
-        <v/>
-      </c>
-      <c r="Z5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 31280-2024 karta knärot.png", "A 31280-2024")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31280-2024 FSC-klagomål.docx", "A 31280-2024")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31280-2024 FSC-klagomål mail.docx", "A 31280-2024")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31280-2024 tillsynsbegäran.docx", "A 31280-2024")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31280-2024 tillsynsbegäran mail.docx", "A 31280-2024")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 31280-2024 prioriterade fågelarter.docx", "A 31280-2024")</f>
         <v/>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
         <v>45582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45169</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45139</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45782</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>45282</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>46216</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>46216</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>46237</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>44613</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>46085</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>45435</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>46215</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>46111</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 39594-2025</t>
+          <t>A 42853-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2953,14 +2953,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45890</v>
+        <v>44832</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2972,51 +2972,170 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" t="n">
         <v>7</v>
       </c>
-      <c r="J19" t="n">
-        <v>6</v>
-      </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>3</v>
       </c>
-      <c r="L19" t="n">
-        <v>5</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>5</v>
-      </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>11</v>
       </c>
       <c r="T19" t="n">
+        <v>15</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Kandelabersvamp
+Mindre hackspett
+Blodvaxing
+Gulvaxing
+Luktvaxing
+Tvåblad
+Vitvaxing agg.
+Ängsfingersvamp
+Ängsvaxing agg.
+Skogsduva</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 42853-2022 artfynd.xlsx", "A 42853-2022")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 42853-2022 karta.png", "A 42853-2022")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 42853-2022 georefererad karta.tif", "A 42853-2022")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 42853-2022 FSC-klagomål.docx", "A 42853-2022")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 42853-2022 FSC-klagomål mail.docx", "A 42853-2022")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 42853-2022 tillsynsbegäran.docx", "A 42853-2022")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 42853-2022 tillsynsbegäran mail.docx", "A 42853-2022")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 42853-2022 prioriterade fågelarter.docx", "A 42853-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 39594-2025</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45890</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>5</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>5</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>11</v>
+      </c>
+      <c r="T20" t="n">
         <v>14</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U20" t="n">
         <v>10</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Brunlångöra
 Dropptaggsvamp
@@ -3031,155 +3150,36 @@
 Dvärgpipistrell</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39594-2025 artfynd.xlsx", "A 39594-2025")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39594-2025 karta.png", "A 39594-2025")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39594-2025 georefererad karta.tif", "A 39594-2025")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39594-2025 FSC-klagomål.docx", "A 39594-2025")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39594-2025 FSC-klagomål mail.docx", "A 39594-2025")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39594-2025 tillsynsbegäran.docx", "A 39594-2025")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39594-2025 tillsynsbegäran mail.docx", "A 39594-2025")</f>
         <v/>
       </c>
-      <c r="AE19">
+      <c r="AE20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39594-2025 prioriterade fågelarter.docx", "A 39594-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 42853-2022</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>44832</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3</v>
-      </c>
-      <c r="K20" t="n">
-        <v>7</v>
-      </c>
-      <c r="L20" t="n">
-        <v>2</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>11</v>
-      </c>
-      <c r="T20" t="n">
-        <v>15</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Kandelabersvamp
-Mindre hackspett
-Blodvaxing
-Gulvaxing
-Luktvaxing
-Tvåblad
-Vitvaxing agg.
-Ängsfingersvamp
-Ängsvaxing agg.
-Skogsduva</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 42853-2022 artfynd.xlsx", "A 42853-2022")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 42853-2022 karta.png", "A 42853-2022")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 42853-2022 georefererad karta.tif", "A 42853-2022")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 42853-2022 FSC-klagomål.docx", "A 42853-2022")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 42853-2022 FSC-klagomål mail.docx", "A 42853-2022")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 42853-2022 tillsynsbegäran.docx", "A 42853-2022")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 42853-2022 tillsynsbegäran mail.docx", "A 42853-2022")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 42853-2022 prioriterade fågelarter.docx", "A 42853-2022")</f>
         <v/>
       </c>
     </row>
@@ -3203,7 +3203,7 @@
         <v>45523</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>45070</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>44565</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>46215</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>45574</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>45435</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>44518</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>44477</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>45203</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 22840-2023</t>
+          <t>A 36260-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4294,10 +4294,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45072</v>
+        <v>46268</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4309,21 +4309,26 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="J30" t="n">
+        <v>4</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
         <v>2</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
@@ -4334,21 +4339,136 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S30" t="n">
         <v>7</v>
       </c>
       <c r="T30" t="n">
+        <v>8</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare
+Silverblåvinge
+Enkelbeckasin
+Blodticka
+Nattskärra
+Vanlig snok
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 36260-2026 artfynd.xlsx", "A 36260-2026")</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 36260-2026 karta.png", "A 36260-2026")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 36260-2026 georefererad karta.tif", "A 36260-2026")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 36260-2026 FSC-klagomål.docx", "A 36260-2026")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 36260-2026 FSC-klagomål mail.docx", "A 36260-2026")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 36260-2026 tillsynsbegäran.docx", "A 36260-2026")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 36260-2026 tillsynsbegäran mail.docx", "A 36260-2026")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 36260-2026 prioriterade fågelarter.docx", "A 36260-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A 22840-2023</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>45072</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>7</v>
+      </c>
+      <c r="T31" t="n">
         <v>10</v>
       </c>
-      <c r="U30" t="n">
+      <c r="U31" t="n">
         <v>9</v>
       </c>
-      <c r="V30" s="2" t="inlineStr">
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>Hultbräken
 Kärrviol
@@ -4359,152 +4479,32 @@
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W30">
+      <c r="W31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 22840-2023 artfynd.xlsx", "A 22840-2023")</f>
         <v/>
       </c>
-      <c r="X30">
+      <c r="X31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 22840-2023 karta.png", "A 22840-2023")</f>
         <v/>
       </c>
-      <c r="Y30">
+      <c r="Y31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 22840-2023 georefererad karta.tif", "A 22840-2023")</f>
         <v/>
       </c>
-      <c r="AA30">
+      <c r="AA31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 22840-2023 FSC-klagomål.docx", "A 22840-2023")</f>
         <v/>
       </c>
-      <c r="AB30">
+      <c r="AB31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 22840-2023 FSC-klagomål mail.docx", "A 22840-2023")</f>
         <v/>
       </c>
-      <c r="AC30">
+      <c r="AC31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 22840-2023 tillsynsbegäran.docx", "A 22840-2023")</f>
         <v/>
       </c>
-      <c r="AD30">
+      <c r="AD31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 22840-2023 tillsynsbegäran mail.docx", "A 22840-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A 36260-2026</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>46268</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J31" t="n">
-        <v>4</v>
-      </c>
-      <c r="K31" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M31" t="n">
-        <v>2</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3</v>
-      </c>
-      <c r="R31" t="n">
-        <v>2</v>
-      </c>
-      <c r="S31" t="n">
-        <v>7</v>
-      </c>
-      <c r="T31" t="n">
-        <v>8</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Mindre bastardsvärmare
-Silverblåvinge
-Enkelbeckasin
-Blodticka
-Nattskärra
-Vanlig snok
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 36260-2026 artfynd.xlsx", "A 36260-2026")</f>
-        <v/>
-      </c>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 36260-2026 karta.png", "A 36260-2026")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 36260-2026 georefererad karta.tif", "A 36260-2026")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 36260-2026 FSC-klagomål.docx", "A 36260-2026")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 36260-2026 FSC-klagomål mail.docx", "A 36260-2026")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 36260-2026 tillsynsbegäran.docx", "A 36260-2026")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 36260-2026 tillsynsbegäran mail.docx", "A 36260-2026")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 36260-2026 prioriterade fågelarter.docx", "A 36260-2026")</f>
         <v/>
       </c>
     </row>
@@ -4528,7 +4528,7 @@
         <v>45545</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>45945</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>44518</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>46076</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>46009</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>44832</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>44832</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>45369</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>45503</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>45463</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>44518</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 39694-2025</t>
+          <t>A 69777-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5801,10 +5801,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45890</v>
+        <v>44532</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5816,28 +5816,23 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5849,943 +5844,948 @@
         <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
       </c>
       <c r="T43" t="n">
+        <v>5</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>Bombmurkla
+Rävticka
+Vedticka</t>
+        </is>
+      </c>
+      <c r="W43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 69777-2021 artfynd.xlsx", "A 69777-2021")</f>
+        <v/>
+      </c>
+      <c r="X43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 69777-2021 karta.png", "A 69777-2021")</f>
+        <v/>
+      </c>
+      <c r="Y43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 69777-2021 georefererad karta.tif", "A 69777-2021")</f>
+        <v/>
+      </c>
+      <c r="AA43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 69777-2021 FSC-klagomål.docx", "A 69777-2021")</f>
+        <v/>
+      </c>
+      <c r="AB43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 69777-2021 FSC-klagomål mail.docx", "A 69777-2021")</f>
+        <v/>
+      </c>
+      <c r="AC43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 69777-2021 tillsynsbegäran.docx", "A 69777-2021")</f>
+        <v/>
+      </c>
+      <c r="AD43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 69777-2021 tillsynsbegäran mail.docx", "A 69777-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>A 49718-2023</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="n">
+        <v>45212</v>
+      </c>
+      <c r="E44" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" t="n">
+        <v>2</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
         <v>3</v>
       </c>
-      <c r="U43" t="n">
+      <c r="T44" t="n">
+        <v>6</v>
+      </c>
+      <c r="U44" t="n">
+        <v>6</v>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Talltita
+Zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="W44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 49718-2023 artfynd.xlsx", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="X44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 49718-2023 karta.png", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="Y44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 49718-2023 georefererad karta.tif", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="AA44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 49718-2023 FSC-klagomål.docx", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="AB44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 49718-2023 FSC-klagomål mail.docx", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="AC44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 49718-2023 tillsynsbegäran.docx", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="AD44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 49718-2023 tillsynsbegäran mail.docx", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="AE44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 49718-2023 prioriterade fågelarter.docx", "A 49718-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>A 39694-2025</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>45890</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
         <v>2</v>
       </c>
-      <c r="V43" s="2" t="inlineStr">
+      <c r="V45" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Mindre märgborre
 Tjäder</t>
         </is>
       </c>
-      <c r="W43">
+      <c r="W45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39694-2025 artfynd.xlsx", "A 39694-2025")</f>
         <v/>
       </c>
-      <c r="X43">
+      <c r="X45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39694-2025 karta.png", "A 39694-2025")</f>
         <v/>
       </c>
-      <c r="Y43">
+      <c r="Y45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39694-2025 georefererad karta.tif", "A 39694-2025")</f>
         <v/>
       </c>
-      <c r="AA43">
+      <c r="AA45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39694-2025 FSC-klagomål.docx", "A 39694-2025")</f>
         <v/>
       </c>
-      <c r="AB43">
+      <c r="AB45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39694-2025 FSC-klagomål mail.docx", "A 39694-2025")</f>
         <v/>
       </c>
-      <c r="AC43">
+      <c r="AC45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39694-2025 tillsynsbegäran.docx", "A 39694-2025")</f>
         <v/>
       </c>
-      <c r="AD43">
+      <c r="AD45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39694-2025 tillsynsbegäran mail.docx", "A 39694-2025")</f>
         <v/>
       </c>
-      <c r="AE43">
+      <c r="AE45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39694-2025 prioriterade fågelarter.docx", "A 39694-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>A 49718-2023</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>A 4082-2025</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D44" s="1" t="n">
-        <v>45212</v>
-      </c>
-      <c r="E44" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F44" t="inlineStr">
+      <c r="D46" s="1" t="n">
+        <v>45684</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>VÄSTMANLANDS LÄN</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="I44" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J44" t="n">
-        <v>1</v>
-      </c>
-      <c r="K44" t="n">
-        <v>1</v>
-      </c>
-      <c r="L44" t="n">
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J46" t="n">
         <v>2</v>
       </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
+      <c r="K46" t="n">
         <v>2</v>
       </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
         <v>3</v>
       </c>
-      <c r="T44" t="n">
-        <v>6</v>
-      </c>
-      <c r="U44" t="n">
-        <v>6</v>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Talltita
-Zontaggsvamp</t>
-        </is>
-      </c>
-      <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 49718-2023 artfynd.xlsx", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 49718-2023 karta.png", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 49718-2023 georefererad karta.tif", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 49718-2023 FSC-klagomål.docx", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 49718-2023 FSC-klagomål mail.docx", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 49718-2023 tillsynsbegäran.docx", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 49718-2023 tillsynsbegäran mail.docx", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="AE44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 49718-2023 prioriterade fågelarter.docx", "A 49718-2023")</f>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>Grönpyrola
+Plattlummer
+Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="W46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 4082-2025 artfynd.xlsx", "A 4082-2025")</f>
+        <v/>
+      </c>
+      <c r="X46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 4082-2025 karta.png", "A 4082-2025")</f>
+        <v/>
+      </c>
+      <c r="Y46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 4082-2025 georefererad karta.tif", "A 4082-2025")</f>
+        <v/>
+      </c>
+      <c r="AA46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 4082-2025 FSC-klagomål.docx", "A 4082-2025")</f>
+        <v/>
+      </c>
+      <c r="AB46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 4082-2025 FSC-klagomål mail.docx", "A 4082-2025")</f>
+        <v/>
+      </c>
+      <c r="AC46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 4082-2025 tillsynsbegäran.docx", "A 4082-2025")</f>
+        <v/>
+      </c>
+      <c r="AD46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 4082-2025 tillsynsbegäran mail.docx", "A 4082-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>A 48128-2023</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>45205</v>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" t="n">
+        <v>2</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>2</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>Jungfrulin
+Svinrot
+Vedticka</t>
+        </is>
+      </c>
+      <c r="W47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 48128-2023 artfynd.xlsx", "A 48128-2023")</f>
+        <v/>
+      </c>
+      <c r="X47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 48128-2023 karta.png", "A 48128-2023")</f>
+        <v/>
+      </c>
+      <c r="Y47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 48128-2023 georefererad karta.tif", "A 48128-2023")</f>
+        <v/>
+      </c>
+      <c r="AA47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 48128-2023 FSC-klagomål.docx", "A 48128-2023")</f>
+        <v/>
+      </c>
+      <c r="AB47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 48128-2023 FSC-klagomål mail.docx", "A 48128-2023")</f>
+        <v/>
+      </c>
+      <c r="AC47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 48128-2023 tillsynsbegäran.docx", "A 48128-2023")</f>
+        <v/>
+      </c>
+      <c r="AD47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 48128-2023 tillsynsbegäran mail.docx", "A 48128-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>A 42765-2022</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D45" s="1" t="n">
+      <c r="D48" s="1" t="n">
         <v>44832</v>
       </c>
-      <c r="E45" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F45" t="inlineStr">
+      <c r="E48" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>VÄSTMANLANDS LÄN</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="I45" t="n">
+      <c r="I48" t="n">
         <v>1.8</v>
       </c>
-      <c r="J45" t="n">
-        <v>1</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1</v>
-      </c>
-      <c r="L45" t="n">
-        <v>1</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>1</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
         <v>3</v>
       </c>
-      <c r="T45" t="n">
+      <c r="T48" t="n">
         <v>4</v>
       </c>
-      <c r="U45" t="n">
-        <v>1</v>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
+      <c r="U48" t="n">
+        <v>1</v>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
         <is>
           <t>Krusfrö
 Barkticka
 Blåsippa</t>
         </is>
       </c>
-      <c r="W45">
+      <c r="W48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 42765-2022 artfynd.xlsx", "A 42765-2022")</f>
         <v/>
       </c>
-      <c r="X45">
+      <c r="X48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 42765-2022 karta.png", "A 42765-2022")</f>
         <v/>
       </c>
-      <c r="Y45">
+      <c r="Y48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 42765-2022 georefererad karta.tif", "A 42765-2022")</f>
         <v/>
       </c>
-      <c r="AA45">
+      <c r="AA48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 42765-2022 FSC-klagomål.docx", "A 42765-2022")</f>
         <v/>
       </c>
-      <c r="AB45">
+      <c r="AB48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 42765-2022 FSC-klagomål mail.docx", "A 42765-2022")</f>
         <v/>
       </c>
-      <c r="AC45">
+      <c r="AC48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 42765-2022 tillsynsbegäran.docx", "A 42765-2022")</f>
         <v/>
       </c>
-      <c r="AD45">
+      <c r="AD48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 42765-2022 tillsynsbegäran mail.docx", "A 42765-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>A 33935-2026</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D49" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E49" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J49" t="n">
+        <v>2</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>3</v>
+      </c>
+      <c r="T49" t="n">
+        <v>5</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Mindre märgborre
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 33935-2026 artfynd.xlsx", "A 33935-2026")</f>
+        <v/>
+      </c>
+      <c r="X49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 33935-2026 karta.png", "A 33935-2026")</f>
+        <v/>
+      </c>
+      <c r="Y49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 33935-2026 georefererad karta.tif", "A 33935-2026")</f>
+        <v/>
+      </c>
+      <c r="AA49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 33935-2026 FSC-klagomål.docx", "A 33935-2026")</f>
+        <v/>
+      </c>
+      <c r="AB49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 33935-2026 FSC-klagomål mail.docx", "A 33935-2026")</f>
+        <v/>
+      </c>
+      <c r="AC49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 33935-2026 tillsynsbegäran.docx", "A 33935-2026")</f>
+        <v/>
+      </c>
+      <c r="AD49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 33935-2026 tillsynsbegäran mail.docx", "A 33935-2026")</f>
+        <v/>
+      </c>
+      <c r="AE49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 33935-2026 prioriterade fågelarter.docx", "A 33935-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>A 36264-2026</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D50" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="E50" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>2</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1</v>
+      </c>
+      <c r="S50" t="n">
+        <v>3</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>Grangråticka
+Fjällig taggsvamp s.str.
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 36264-2026 artfynd.xlsx", "A 36264-2026")</f>
+        <v/>
+      </c>
+      <c r="X50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 36264-2026 karta.png", "A 36264-2026")</f>
+        <v/>
+      </c>
+      <c r="Y50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 36264-2026 georefererad karta.tif", "A 36264-2026")</f>
+        <v/>
+      </c>
+      <c r="AA50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 36264-2026 FSC-klagomål.docx", "A 36264-2026")</f>
+        <v/>
+      </c>
+      <c r="AB50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 36264-2026 FSC-klagomål mail.docx", "A 36264-2026")</f>
+        <v/>
+      </c>
+      <c r="AC50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 36264-2026 tillsynsbegäran.docx", "A 36264-2026")</f>
+        <v/>
+      </c>
+      <c r="AD50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 36264-2026 tillsynsbegäran mail.docx", "A 36264-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>A 63146-2025</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D46" s="1" t="n">
+      <c r="D51" s="1" t="n">
         <v>46009</v>
       </c>
-      <c r="E46" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F46" t="inlineStr">
+      <c r="E51" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>VÄSTMANLANDS LÄN</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I46" t="n">
+      <c r="I51" t="n">
         <v>10.2</v>
       </c>
-      <c r="J46" t="n">
-        <v>1</v>
-      </c>
-      <c r="K46" t="n">
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
         <v>2</v>
       </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
         <v>3</v>
       </c>
-      <c r="T46" t="n">
+      <c r="T51" t="n">
         <v>12</v>
       </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
         <is>
           <t>Stor aspticka
 Svart trolldruva
 Blåsippa</t>
         </is>
       </c>
-      <c r="W46">
+      <c r="W51">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63146-2025 artfynd.xlsx", "A 63146-2025")</f>
         <v/>
       </c>
-      <c r="X46">
+      <c r="X51">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63146-2025 karta.png", "A 63146-2025")</f>
         <v/>
       </c>
-      <c r="Y46">
+      <c r="Y51">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63146-2025 georefererad karta.tif", "A 63146-2025")</f>
         <v/>
       </c>
-      <c r="AA46">
+      <c r="AA51">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63146-2025 FSC-klagomål.docx", "A 63146-2025")</f>
         <v/>
       </c>
-      <c r="AB46">
+      <c r="AB51">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63146-2025 FSC-klagomål mail.docx", "A 63146-2025")</f>
         <v/>
       </c>
-      <c r="AC46">
+      <c r="AC51">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63146-2025 tillsynsbegäran.docx", "A 63146-2025")</f>
         <v/>
       </c>
-      <c r="AD46">
+      <c r="AD51">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63146-2025 tillsynsbegäran mail.docx", "A 63146-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>A 69777-2021</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="n">
-        <v>44532</v>
-      </c>
-      <c r="E47" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J47" t="n">
-        <v>1</v>
-      </c>
-      <c r="K47" t="n">
-        <v>2</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>1</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>1</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1</v>
-      </c>
-      <c r="S47" t="n">
-        <v>3</v>
-      </c>
-      <c r="T47" t="n">
-        <v>5</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>Bombmurkla
-Rävticka
-Vedticka</t>
-        </is>
-      </c>
-      <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 69777-2021 artfynd.xlsx", "A 69777-2021")</f>
-        <v/>
-      </c>
-      <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 69777-2021 karta.png", "A 69777-2021")</f>
-        <v/>
-      </c>
-      <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 69777-2021 georefererad karta.tif", "A 69777-2021")</f>
-        <v/>
-      </c>
-      <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 69777-2021 FSC-klagomål.docx", "A 69777-2021")</f>
-        <v/>
-      </c>
-      <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 69777-2021 FSC-klagomål mail.docx", "A 69777-2021")</f>
-        <v/>
-      </c>
-      <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 69777-2021 tillsynsbegäran.docx", "A 69777-2021")</f>
-        <v/>
-      </c>
-      <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 69777-2021 tillsynsbegäran mail.docx", "A 69777-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>A 4082-2025</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="n">
-        <v>45684</v>
-      </c>
-      <c r="E48" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="J48" t="n">
-        <v>2</v>
-      </c>
-      <c r="K48" t="n">
-        <v>2</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>3</v>
-      </c>
-      <c r="T48" t="n">
-        <v>3</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1</v>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>Grönpyrola
-Plattlummer
-Lopplummer (aggregat)</t>
-        </is>
-      </c>
-      <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 4082-2025 artfynd.xlsx", "A 4082-2025")</f>
-        <v/>
-      </c>
-      <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 4082-2025 karta.png", "A 4082-2025")</f>
-        <v/>
-      </c>
-      <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 4082-2025 georefererad karta.tif", "A 4082-2025")</f>
-        <v/>
-      </c>
-      <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 4082-2025 FSC-klagomål.docx", "A 4082-2025")</f>
-        <v/>
-      </c>
-      <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 4082-2025 FSC-klagomål mail.docx", "A 4082-2025")</f>
-        <v/>
-      </c>
-      <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 4082-2025 tillsynsbegäran.docx", "A 4082-2025")</f>
-        <v/>
-      </c>
-      <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 4082-2025 tillsynsbegäran mail.docx", "A 4082-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="15" customHeight="1">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>A 48128-2023</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D49" s="1" t="n">
-        <v>45205</v>
-      </c>
-      <c r="E49" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
-        <v>1</v>
-      </c>
-      <c r="L49" t="n">
-        <v>2</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>2</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>3</v>
-      </c>
-      <c r="T49" t="n">
-        <v>3</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" s="2" t="inlineStr">
-        <is>
-          <t>Jungfrulin
-Svinrot
-Vedticka</t>
-        </is>
-      </c>
-      <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 48128-2023 artfynd.xlsx", "A 48128-2023")</f>
-        <v/>
-      </c>
-      <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 48128-2023 karta.png", "A 48128-2023")</f>
-        <v/>
-      </c>
-      <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 48128-2023 georefererad karta.tif", "A 48128-2023")</f>
-        <v/>
-      </c>
-      <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 48128-2023 FSC-klagomål.docx", "A 48128-2023")</f>
-        <v/>
-      </c>
-      <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 48128-2023 FSC-klagomål mail.docx", "A 48128-2023")</f>
-        <v/>
-      </c>
-      <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 48128-2023 tillsynsbegäran.docx", "A 48128-2023")</f>
-        <v/>
-      </c>
-      <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 48128-2023 tillsynsbegäran mail.docx", "A 48128-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="15" customHeight="1">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>A 33935-2026</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="n">
-        <v>46248</v>
-      </c>
-      <c r="E50" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J50" t="n">
-        <v>2</v>
-      </c>
-      <c r="K50" t="n">
-        <v>1</v>
-      </c>
-      <c r="L50" t="n">
-        <v>1</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>1</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>3</v>
-      </c>
-      <c r="T50" t="n">
-        <v>5</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Mindre märgborre
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 33935-2026 artfynd.xlsx", "A 33935-2026")</f>
-        <v/>
-      </c>
-      <c r="X50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 33935-2026 karta.png", "A 33935-2026")</f>
-        <v/>
-      </c>
-      <c r="Y50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 33935-2026 georefererad karta.tif", "A 33935-2026")</f>
-        <v/>
-      </c>
-      <c r="AA50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 33935-2026 FSC-klagomål.docx", "A 33935-2026")</f>
-        <v/>
-      </c>
-      <c r="AB50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 33935-2026 FSC-klagomål mail.docx", "A 33935-2026")</f>
-        <v/>
-      </c>
-      <c r="AC50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 33935-2026 tillsynsbegäran.docx", "A 33935-2026")</f>
-        <v/>
-      </c>
-      <c r="AD50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 33935-2026 tillsynsbegäran mail.docx", "A 33935-2026")</f>
-        <v/>
-      </c>
-      <c r="AE50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 33935-2026 prioriterade fågelarter.docx", "A 33935-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>A 36264-2026</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="n">
-        <v>46268</v>
-      </c>
-      <c r="E51" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J51" t="n">
-        <v>1</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>1</v>
-      </c>
-      <c r="M51" t="n">
-        <v>1</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>2</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1</v>
-      </c>
-      <c r="S51" t="n">
-        <v>3</v>
-      </c>
-      <c r="T51" t="n">
-        <v>3</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" s="2" t="inlineStr">
-        <is>
-          <t>Grangråticka
-Fjällig taggsvamp s.str.
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 36264-2026 artfynd.xlsx", "A 36264-2026")</f>
-        <v/>
-      </c>
-      <c r="X51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 36264-2026 karta.png", "A 36264-2026")</f>
-        <v/>
-      </c>
-      <c r="Y51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 36264-2026 georefererad karta.tif", "A 36264-2026")</f>
-        <v/>
-      </c>
-      <c r="AA51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 36264-2026 FSC-klagomål.docx", "A 36264-2026")</f>
-        <v/>
-      </c>
-      <c r="AB51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 36264-2026 FSC-klagomål mail.docx", "A 36264-2026")</f>
-        <v/>
-      </c>
-      <c r="AC51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 36264-2026 tillsynsbegäran.docx", "A 36264-2026")</f>
-        <v/>
-      </c>
-      <c r="AD51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 36264-2026 tillsynsbegäran mail.docx", "A 36264-2026")</f>
         <v/>
       </c>
     </row>
@@ -6809,7 +6809,7 @@
         <v>46239</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>44635</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>45708</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>45708</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 30074-2023</t>
+          <t>A 56362-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7270,10 +7270,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45110</v>
+        <v>45236</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7287,11 +7287,11 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.1</v>
+        <v>15.2</v>
       </c>
       <c r="J56" t="n">
         <v>1</v>
@@ -7303,7 +7303,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
@@ -7315,10 +7315,10 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S56" t="n">
         <v>2</v>
@@ -7327,47 +7327,47 @@
         <v>2</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola
-Revlummer</t>
+          <t>Väddnätfjäril
+Grönpyrola</t>
         </is>
       </c>
       <c r="W56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 30074-2023 artfynd.xlsx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 56362-2023 artfynd.xlsx", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="X56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 30074-2023 karta.png", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 56362-2023 karta.png", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="Y56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 30074-2023 georefererad karta.tif", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 56362-2023 georefererad karta.tif", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="AA56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 30074-2023 FSC-klagomål.docx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 56362-2023 FSC-klagomål.docx", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="AB56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 30074-2023 FSC-klagomål mail.docx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 56362-2023 FSC-klagomål mail.docx", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="AC56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 30074-2023 tillsynsbegäran.docx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 56362-2023 tillsynsbegäran.docx", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="AD56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 30074-2023 tillsynsbegäran mail.docx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 56362-2023 tillsynsbegäran mail.docx", "A 56362-2023")</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 13788-2025</t>
+          <t>A 14001-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45737</v>
+        <v>45007</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7396,35 +7396,40 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>9.699999999999999</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
         <v>2</v>
       </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>1</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>1</v>
-      </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S57" t="n">
         <v>2</v>
@@ -7433,51 +7438,47 @@
         <v>2</v>
       </c>
       <c r="U57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>Sparvuggla
-Nattskärra</t>
+          <t>Garnlav
+Motaggsvamp</t>
         </is>
       </c>
       <c r="W57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 13788-2025 artfynd.xlsx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 14001-2023 artfynd.xlsx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="X57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 13788-2025 karta.png", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 14001-2023 karta.png", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="Y57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 13788-2025 georefererad karta.tif", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 14001-2023 georefererad karta.tif", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AA57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 13788-2025 FSC-klagomål.docx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 14001-2023 FSC-klagomål.docx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AB57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 13788-2025 FSC-klagomål mail.docx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 14001-2023 FSC-klagomål mail.docx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AC57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 13788-2025 tillsynsbegäran.docx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 14001-2023 tillsynsbegäran.docx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AD57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 13788-2025 tillsynsbegäran mail.docx", "A 13788-2025")</f>
-        <v/>
-      </c>
-      <c r="AE57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 13788-2025 prioriterade fågelarter.docx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 14001-2023 tillsynsbegäran mail.docx", "A 14001-2023")</f>
         <v/>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 56362-2023</t>
+          <t>A 47453-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7491,10 +7492,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45236</v>
+        <v>45587</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7506,25 +7507,20 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>15.2</v>
+        <v>5.1</v>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
         <v>0</v>
@@ -7539,7 +7535,7 @@
         <v>1</v>
       </c>
       <c r="R58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>2</v>
@@ -7552,43 +7548,47 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>Väddnätfjäril
-Grönpyrola</t>
+          <t>Göktyta
+Gröngöling</t>
         </is>
       </c>
       <c r="W58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 56362-2023 artfynd.xlsx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 47453-2024 artfynd.xlsx", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="X58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 56362-2023 karta.png", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 47453-2024 karta.png", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="Y58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 56362-2023 georefererad karta.tif", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 47453-2024 georefererad karta.tif", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="AA58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 56362-2023 FSC-klagomål.docx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 47453-2024 FSC-klagomål.docx", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="AB58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 56362-2023 FSC-klagomål mail.docx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 47453-2024 FSC-klagomål mail.docx", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="AC58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 56362-2023 tillsynsbegäran.docx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 47453-2024 tillsynsbegäran.docx", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="AD58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 56362-2023 tillsynsbegäran mail.docx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 47453-2024 tillsynsbegäran mail.docx", "A 47453-2024")</f>
+        <v/>
+      </c>
+      <c r="AE58">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 47453-2024 prioriterade fågelarter.docx", "A 47453-2024")</f>
         <v/>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 47453-2024</t>
+          <t>A 11501-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45587</v>
+        <v>44991</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7617,17 +7617,22 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -7642,7 +7647,7 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -7654,51 +7659,47 @@
         <v>2</v>
       </c>
       <c r="U59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>Göktyta
-Gröngöling</t>
+          <t>Svart trolldruva
+Nattviol</t>
         </is>
       </c>
       <c r="W59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 47453-2024 artfynd.xlsx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 11501-2023 artfynd.xlsx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="X59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 47453-2024 karta.png", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 11501-2023 karta.png", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="Y59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 47453-2024 georefererad karta.tif", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 11501-2023 georefererad karta.tif", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AA59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 47453-2024 FSC-klagomål.docx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 11501-2023 FSC-klagomål.docx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AB59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 47453-2024 FSC-klagomål mail.docx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 11501-2023 FSC-klagomål mail.docx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AC59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 47453-2024 tillsynsbegäran.docx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 11501-2023 tillsynsbegäran.docx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AD59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 47453-2024 tillsynsbegäran mail.docx", "A 47453-2024")</f>
-        <v/>
-      </c>
-      <c r="AE59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 47453-2024 prioriterade fågelarter.docx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 11501-2023 tillsynsbegäran mail.docx", "A 11501-2023")</f>
         <v/>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 40403-2025</t>
+          <t>A 37013-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7712,10 +7713,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45895</v>
+        <v>45874</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7729,14 +7730,14 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.9</v>
+        <v>10.7</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -7745,7 +7746,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N60" t="n">
         <v>0</v>
@@ -7757,59 +7758,59 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S60" t="n">
         <v>2</v>
       </c>
       <c r="T60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>Igelkott
-Gröngöling</t>
+          <t>Brunfläckig pärlemorfjäril
+Fältgentiana</t>
         </is>
       </c>
       <c r="W60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 40403-2025 artfynd.xlsx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37013-2025 artfynd.xlsx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="X60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 40403-2025 karta.png", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37013-2025 karta.png", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="Y60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 40403-2025 georefererad karta.tif", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37013-2025 georefererad karta.tif", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AA60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 40403-2025 FSC-klagomål.docx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37013-2025 FSC-klagomål.docx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AB60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 40403-2025 FSC-klagomål mail.docx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37013-2025 FSC-klagomål mail.docx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AC60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 40403-2025 tillsynsbegäran.docx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37013-2025 tillsynsbegäran.docx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AD60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 40403-2025 tillsynsbegäran mail.docx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37013-2025 tillsynsbegäran mail.docx", "A 37013-2025")</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 37013-2025</t>
+          <t>A 40403-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7823,10 +7824,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45874</v>
+        <v>45895</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7840,14 +7841,14 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>10.7</v>
+        <v>3.9</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -7856,7 +7857,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
@@ -7868,59 +7869,59 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S61" t="n">
         <v>2</v>
       </c>
       <c r="T61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril
-Fältgentiana</t>
+          <t>Igelkott
+Gröngöling</t>
         </is>
       </c>
       <c r="W61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37013-2025 artfynd.xlsx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 40403-2025 artfynd.xlsx", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="X61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37013-2025 karta.png", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 40403-2025 karta.png", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="Y61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37013-2025 georefererad karta.tif", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 40403-2025 georefererad karta.tif", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="AA61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37013-2025 FSC-klagomål.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 40403-2025 FSC-klagomål.docx", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="AB61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37013-2025 FSC-klagomål mail.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 40403-2025 FSC-klagomål mail.docx", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="AC61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37013-2025 tillsynsbegäran.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 40403-2025 tillsynsbegäran.docx", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="AD61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37013-2025 tillsynsbegäran mail.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 40403-2025 tillsynsbegäran mail.docx", "A 40403-2025")</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 63138-2025</t>
+          <t>A 41204-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7934,10 +7935,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46009</v>
+        <v>45174</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7949,25 +7950,20 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>1</v>
       </c>
       <c r="K62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N62" t="n">
         <v>0</v>
@@ -7979,63 +7975,63 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S62" t="n">
         <v>2</v>
       </c>
       <c r="T62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>Mindre märgborre
-Tjäder</t>
+          <t>Knärot
+Vedtrappmossa</t>
         </is>
       </c>
       <c r="W62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63138-2025 artfynd.xlsx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 41204-2023 artfynd.xlsx", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="X62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63138-2025 karta.png", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 41204-2023 karta.png", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="Y62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63138-2025 georefererad karta.tif", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 41204-2023 georefererad karta.tif", "A 41204-2023")</f>
+        <v/>
+      </c>
+      <c r="Z62">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 41204-2023 karta knärot.png", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="AA62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63138-2025 FSC-klagomål.docx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 41204-2023 FSC-klagomål.docx", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="AB62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63138-2025 FSC-klagomål mail.docx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 41204-2023 FSC-klagomål mail.docx", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="AC62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63138-2025 tillsynsbegäran.docx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 41204-2023 tillsynsbegäran.docx", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="AD62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63138-2025 tillsynsbegäran mail.docx", "A 63138-2025")</f>
-        <v/>
-      </c>
-      <c r="AE62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 63138-2025 prioriterade fågelarter.docx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 41204-2023 tillsynsbegäran mail.docx", "A 41204-2023")</f>
         <v/>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 41204-2023</t>
+          <t>A 30074-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -8049,10 +8045,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45174</v>
+        <v>45110</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8064,20 +8060,25 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>1</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
@@ -8089,63 +8090,59 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>2</v>
       </c>
       <c r="T63" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>Knärot
-Vedtrappmossa</t>
+          <t>Grönpyrola
+Revlummer</t>
         </is>
       </c>
       <c r="W63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 41204-2023 artfynd.xlsx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 30074-2023 artfynd.xlsx", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="X63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 41204-2023 karta.png", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 30074-2023 karta.png", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="Y63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 41204-2023 georefererad karta.tif", "A 41204-2023")</f>
-        <v/>
-      </c>
-      <c r="Z63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 41204-2023 karta knärot.png", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 30074-2023 georefererad karta.tif", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="AA63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 41204-2023 FSC-klagomål.docx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 30074-2023 FSC-klagomål.docx", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="AB63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 41204-2023 FSC-klagomål mail.docx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 30074-2023 FSC-klagomål mail.docx", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="AC63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 41204-2023 tillsynsbegäran.docx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 30074-2023 tillsynsbegäran.docx", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="AD63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 41204-2023 tillsynsbegäran mail.docx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 30074-2023 tillsynsbegäran mail.docx", "A 30074-2023")</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 11501-2023</t>
+          <t>A 13971-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -8159,10 +8156,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44991</v>
+        <v>45007</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8180,13 +8177,13 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -8213,50 +8210,50 @@
         <v>2</v>
       </c>
       <c r="T64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva
-Nattviol</t>
+          <t>Dubbelnycklar
+Fläcknycklar</t>
         </is>
       </c>
       <c r="W64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 11501-2023 artfynd.xlsx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 13971-2023 artfynd.xlsx", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="X64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 11501-2023 karta.png", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 13971-2023 karta.png", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="Y64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 11501-2023 georefererad karta.tif", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 13971-2023 georefererad karta.tif", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="AA64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 11501-2023 FSC-klagomål.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 13971-2023 FSC-klagomål.docx", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="AB64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 11501-2023 FSC-klagomål mail.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 13971-2023 FSC-klagomål mail.docx", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="AC64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 11501-2023 tillsynsbegäran.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 13971-2023 tillsynsbegäran.docx", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="AD64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 11501-2023 tillsynsbegäran mail.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 13971-2023 tillsynsbegäran mail.docx", "A 13971-2023")</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 14001-2023</t>
+          <t>A 36261-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -8270,10 +8267,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45007</v>
+        <v>46268</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8287,14 +8284,14 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>7.9</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -8303,7 +8300,7 @@
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
@@ -8315,10 +8312,10 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>2</v>
@@ -8331,43 +8328,43 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>Garnlav
-Motaggsvamp</t>
+          <t>Krusfrö
+Revlummer</t>
         </is>
       </c>
       <c r="W65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 14001-2023 artfynd.xlsx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 36261-2026 artfynd.xlsx", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="X65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 14001-2023 karta.png", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 36261-2026 karta.png", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="Y65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 14001-2023 georefererad karta.tif", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 36261-2026 georefererad karta.tif", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="AA65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 14001-2023 FSC-klagomål.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 36261-2026 FSC-klagomål.docx", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="AB65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 14001-2023 FSC-klagomål mail.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 36261-2026 FSC-klagomål mail.docx", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="AC65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 14001-2023 tillsynsbegäran.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 36261-2026 tillsynsbegäran.docx", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="AD65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 14001-2023 tillsynsbegäran mail.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 36261-2026 tillsynsbegäran mail.docx", "A 36261-2026")</f>
         <v/>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 13971-2023</t>
+          <t>A 63138-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -8381,10 +8378,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45007</v>
+        <v>46009</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8402,13 +8399,13 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -8438,47 +8435,51 @@
         <v>3</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>Dubbelnycklar
-Fläcknycklar</t>
+          <t>Mindre märgborre
+Tjäder</t>
         </is>
       </c>
       <c r="W66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 13971-2023 artfynd.xlsx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63138-2025 artfynd.xlsx", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="X66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 13971-2023 karta.png", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63138-2025 karta.png", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="Y66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 13971-2023 georefererad karta.tif", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63138-2025 georefererad karta.tif", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="AA66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 13971-2023 FSC-klagomål.docx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63138-2025 FSC-klagomål.docx", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="AB66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 13971-2023 FSC-klagomål mail.docx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63138-2025 FSC-klagomål mail.docx", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="AC66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 13971-2023 tillsynsbegäran.docx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63138-2025 tillsynsbegäran.docx", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="AD66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 13971-2023 tillsynsbegäran mail.docx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63138-2025 tillsynsbegäran mail.docx", "A 63138-2025")</f>
+        <v/>
+      </c>
+      <c r="AE66">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 63138-2025 prioriterade fågelarter.docx", "A 63138-2025")</f>
         <v/>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 36261-2026</t>
+          <t>A 13788-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -8492,10 +8493,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46268</v>
+        <v>45737</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8507,16 +8508,11 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>7.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -8549,40 +8545,44 @@
         <v>2</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>Krusfrö
-Revlummer</t>
+          <t>Sparvuggla
+Nattskärra</t>
         </is>
       </c>
       <c r="W67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 36261-2026 artfynd.xlsx", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 13788-2025 artfynd.xlsx", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="X67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 36261-2026 karta.png", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 13788-2025 karta.png", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="Y67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 36261-2026 georefererad karta.tif", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 13788-2025 georefererad karta.tif", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="AA67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 36261-2026 FSC-klagomål.docx", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 13788-2025 FSC-klagomål.docx", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="AB67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 36261-2026 FSC-klagomål mail.docx", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 13788-2025 FSC-klagomål mail.docx", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="AC67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 36261-2026 tillsynsbegäran.docx", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 13788-2025 tillsynsbegäran.docx", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="AD67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 36261-2026 tillsynsbegäran mail.docx", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 13788-2025 tillsynsbegäran mail.docx", "A 13788-2025")</f>
+        <v/>
+      </c>
+      <c r="AE67">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 13788-2025 prioriterade fågelarter.docx", "A 13788-2025")</f>
         <v/>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
         <v>45720</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8717,7 +8717,7 @@
         <v>44696</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>44739</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>44524</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>44696</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 30076-2023</t>
+          <t>A 39099-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -9154,10 +9154,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45110</v>
+        <v>44817</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9171,17 +9171,17 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.1</v>
+        <v>7.4</v>
       </c>
       <c r="J73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -9211,39 +9211,39 @@
         <v>1</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="W73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 30076-2023 artfynd.xlsx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39099-2022 artfynd.xlsx", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="X73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 30076-2023 karta.png", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39099-2022 karta.png", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="Y73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 30076-2023 georefererad karta.tif", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39099-2022 georefererad karta.tif", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="AA73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 30076-2023 FSC-klagomål.docx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39099-2022 FSC-klagomål.docx", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="AB73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 30076-2023 FSC-klagomål mail.docx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39099-2022 FSC-klagomål mail.docx", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="AC73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 30076-2023 tillsynsbegäran.docx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39099-2022 tillsynsbegäran.docx", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="AD73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 30076-2023 tillsynsbegäran mail.docx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39099-2022 tillsynsbegäran mail.docx", "A 39099-2022")</f>
         <v/>
       </c>
     </row>
@@ -9267,7 +9267,7 @@
         <v>44977</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 37287-2023</t>
+          <t>A 34584-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -9374,10 +9374,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45156</v>
+        <v>45846</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9389,17 +9389,22 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -9414,7 +9419,7 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
         <v>0</v>
@@ -9426,46 +9431,50 @@
         <v>1</v>
       </c>
       <c r="U75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>Mindre tåtelsmygare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37287-2023 artfynd.xlsx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34584-2025 artfynd.xlsx", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="X75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37287-2023 karta.png", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34584-2025 karta.png", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="Y75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37287-2023 georefererad karta.tif", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34584-2025 georefererad karta.tif", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="AA75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37287-2023 FSC-klagomål.docx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34584-2025 FSC-klagomål.docx", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="AB75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37287-2023 FSC-klagomål mail.docx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34584-2025 FSC-klagomål mail.docx", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="AC75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37287-2023 tillsynsbegäran.docx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34584-2025 tillsynsbegäran.docx", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="AD75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37287-2023 tillsynsbegäran mail.docx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34584-2025 tillsynsbegäran mail.docx", "A 34584-2025")</f>
+        <v/>
+      </c>
+      <c r="AE75">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 34584-2025 prioriterade fågelarter.docx", "A 34584-2025")</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 34584-2025</t>
+          <t>A 16013-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -9479,10 +9488,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45846</v>
+        <v>45026</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9494,16 +9503,11 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="J76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -9512,7 +9516,7 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N76" t="n">
         <v>0</v>
@@ -9524,10 +9528,10 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S76" t="n">
         <v>1</v>
@@ -9536,50 +9540,46 @@
         <v>1</v>
       </c>
       <c r="U76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="W76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34584-2025 artfynd.xlsx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 16013-2023 artfynd.xlsx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="X76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34584-2025 karta.png", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 16013-2023 karta.png", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="Y76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34584-2025 georefererad karta.tif", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 16013-2023 georefererad karta.tif", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AA76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34584-2025 FSC-klagomål.docx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 16013-2023 FSC-klagomål.docx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AB76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34584-2025 FSC-klagomål mail.docx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 16013-2023 FSC-klagomål mail.docx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AC76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34584-2025 tillsynsbegäran.docx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 16013-2023 tillsynsbegäran.docx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AD76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34584-2025 tillsynsbegäran mail.docx", "A 34584-2025")</f>
-        <v/>
-      </c>
-      <c r="AE76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 34584-2025 prioriterade fågelarter.docx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 16013-2023 tillsynsbegäran mail.docx", "A 16013-2023")</f>
         <v/>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 39099-2022</t>
+          <t>A 34955-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -9593,10 +9593,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44817</v>
+        <v>44796</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9610,20 +9610,20 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -9638,7 +9638,7 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R77" t="n">
         <v>0</v>
@@ -9654,42 +9654,42 @@
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39099-2022 artfynd.xlsx", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34955-2022 artfynd.xlsx", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="X77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39099-2022 karta.png", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34955-2022 karta.png", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="Y77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39099-2022 georefererad karta.tif", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34955-2022 georefererad karta.tif", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="AA77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39099-2022 FSC-klagomål.docx", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34955-2022 FSC-klagomål.docx", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="AB77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39099-2022 FSC-klagomål mail.docx", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34955-2022 FSC-klagomål mail.docx", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="AC77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39099-2022 tillsynsbegäran.docx", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34955-2022 tillsynsbegäran.docx", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="AD77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39099-2022 tillsynsbegäran mail.docx", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34955-2022 tillsynsbegäran mail.docx", "A 34955-2022")</f>
         <v/>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 17632-2022</t>
+          <t>A 33231-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -9703,10 +9703,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44680</v>
+        <v>45518</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9718,14 +9718,19 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>5.2</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -9755,46 +9760,46 @@
         <v>1</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="W78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 17632-2022 artfynd.xlsx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 33231-2024 artfynd.xlsx", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="X78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 17632-2022 karta.png", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 33231-2024 karta.png", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="Y78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 17632-2022 georefererad karta.tif", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 33231-2024 georefererad karta.tif", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="AA78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 17632-2022 FSC-klagomål.docx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 33231-2024 FSC-klagomål.docx", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="AB78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 17632-2022 FSC-klagomål mail.docx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 33231-2024 FSC-klagomål mail.docx", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="AC78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 17632-2022 tillsynsbegäran.docx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 33231-2024 tillsynsbegäran.docx", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="AD78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 17632-2022 tillsynsbegäran mail.docx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 33231-2024 tillsynsbegäran mail.docx", "A 33231-2024")</f>
         <v/>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 34955-2022</t>
+          <t>A 30076-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -9808,10 +9813,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44796</v>
+        <v>45110</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9829,16 +9834,16 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -9853,7 +9858,7 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
         <v>0</v>
@@ -9865,39 +9870,39 @@
         <v>1</v>
       </c>
       <c r="U79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34955-2022 artfynd.xlsx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 30076-2023 artfynd.xlsx", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="X79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34955-2022 karta.png", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 30076-2023 karta.png", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="Y79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34955-2022 georefererad karta.tif", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 30076-2023 georefererad karta.tif", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="AA79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34955-2022 FSC-klagomål.docx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 30076-2023 FSC-klagomål.docx", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="AB79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34955-2022 FSC-klagomål mail.docx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 30076-2023 FSC-klagomål mail.docx", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="AC79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34955-2022 tillsynsbegäran.docx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 30076-2023 tillsynsbegäran.docx", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="AD79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34955-2022 tillsynsbegäran mail.docx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 30076-2023 tillsynsbegäran mail.docx", "A 30076-2023")</f>
         <v/>
       </c>
     </row>
@@ -9921,7 +9926,7 @@
         <v>44991</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10018,7 +10023,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 44356-2024</t>
+          <t>A 24167-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -10028,14 +10033,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45573</v>
+        <v>45456</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10047,13 +10052,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J81" t="n">
         <v>1</v>
@@ -10089,46 +10089,46 @@
         <v>1</v>
       </c>
       <c r="U81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 44356-2024 artfynd.xlsx", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 24167-2024 artfynd.xlsx", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="X81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 44356-2024 karta.png", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 24167-2024 karta.png", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="Y81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 44356-2024 georefererad karta.tif", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 24167-2024 georefererad karta.tif", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="AA81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 44356-2024 FSC-klagomål.docx", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 24167-2024 FSC-klagomål.docx", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="AB81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 44356-2024 FSC-klagomål mail.docx", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 24167-2024 FSC-klagomål mail.docx", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="AC81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 44356-2024 tillsynsbegäran.docx", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 24167-2024 tillsynsbegäran.docx", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="AD81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 44356-2024 tillsynsbegäran mail.docx", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 24167-2024 tillsynsbegäran mail.docx", "A 24167-2024")</f>
         <v/>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 33231-2024</t>
+          <t>A 37287-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -10142,10 +10142,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45518</v>
+        <v>45156</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10157,22 +10157,17 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -10187,7 +10182,7 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R82" t="n">
         <v>0</v>
@@ -10199,46 +10194,46 @@
         <v>1</v>
       </c>
       <c r="U82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="W82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 33231-2024 artfynd.xlsx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37287-2023 artfynd.xlsx", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="X82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 33231-2024 karta.png", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37287-2023 karta.png", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="Y82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 33231-2024 georefererad karta.tif", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37287-2023 georefererad karta.tif", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="AA82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 33231-2024 FSC-klagomål.docx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37287-2023 FSC-klagomål.docx", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="AB82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 33231-2024 FSC-klagomål mail.docx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37287-2023 FSC-klagomål mail.docx", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="AC82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 33231-2024 tillsynsbegäran.docx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37287-2023 tillsynsbegäran.docx", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="AD82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 33231-2024 tillsynsbegäran mail.docx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37287-2023 tillsynsbegäran mail.docx", "A 37287-2023")</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 24167-2024</t>
+          <t>A 44356-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -10248,14 +10243,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45456</v>
+        <v>45573</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10267,8 +10262,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J83" t="n">
         <v>1</v>
@@ -10304,46 +10304,46 @@
         <v>1</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 24167-2024 artfynd.xlsx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 44356-2024 artfynd.xlsx", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="X83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 24167-2024 karta.png", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 44356-2024 karta.png", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="Y83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 24167-2024 georefererad karta.tif", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 44356-2024 georefererad karta.tif", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="AA83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 24167-2024 FSC-klagomål.docx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 44356-2024 FSC-klagomål.docx", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="AB83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 24167-2024 FSC-klagomål mail.docx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 44356-2024 FSC-klagomål mail.docx", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="AC83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 24167-2024 tillsynsbegäran.docx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 44356-2024 tillsynsbegäran.docx", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="AD83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 24167-2024 tillsynsbegäran mail.docx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 44356-2024 tillsynsbegäran mail.docx", "A 44356-2024")</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 31589-2026</t>
+          <t>A 17632-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -10357,10 +10357,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46224</v>
+        <v>44680</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10372,13 +10372,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -10418,42 +10413,42 @@
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="W84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31589-2026 artfynd.xlsx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 17632-2022 artfynd.xlsx", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="X84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31589-2026 karta.png", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 17632-2022 karta.png", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="Y84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31589-2026 georefererad karta.tif", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 17632-2022 georefererad karta.tif", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="AA84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31589-2026 FSC-klagomål.docx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 17632-2022 FSC-klagomål.docx", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="AB84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31589-2026 FSC-klagomål mail.docx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 17632-2022 FSC-klagomål mail.docx", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="AC84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31589-2026 tillsynsbegäran.docx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 17632-2022 tillsynsbegäran.docx", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="AD84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31589-2026 tillsynsbegäran mail.docx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 17632-2022 tillsynsbegäran mail.docx", "A 17632-2022")</f>
         <v/>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 16013-2023</t>
+          <t>A 31589-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -10467,10 +10462,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45026</v>
+        <v>46224</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10482,20 +10477,25 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
         <v>0</v>
@@ -10507,10 +10507,10 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>1</v>
@@ -10523,35 +10523,35 @@
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 16013-2023 artfynd.xlsx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31589-2026 artfynd.xlsx", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="X85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 16013-2023 karta.png", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31589-2026 karta.png", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="Y85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 16013-2023 georefererad karta.tif", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31589-2026 georefererad karta.tif", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="AA85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 16013-2023 FSC-klagomål.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31589-2026 FSC-klagomål.docx", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="AB85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 16013-2023 FSC-klagomål mail.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31589-2026 FSC-klagomål mail.docx", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="AC85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 16013-2023 tillsynsbegäran.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31589-2026 tillsynsbegäran.docx", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="AD85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 16013-2023 tillsynsbegäran mail.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31589-2026 tillsynsbegäran mail.docx", "A 31589-2026")</f>
         <v/>
       </c>
     </row>
@@ -10575,7 +10575,7 @@
         <v>44509</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>44696</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>44782</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         <v>44550</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>44586</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>44582</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>44694</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>44518</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>44796</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 48205-2023</t>
+          <t>A 21509-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -11264,10 +11264,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45205</v>
+        <v>45441</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11281,11 +11281,11 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>7.6</v>
+        <v>3.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -11328,7 +11328,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 15743-2023</t>
+          <t>A 42832-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -11338,14 +11338,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45021</v>
+        <v>44832</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -11401,7 +11401,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 15637-2022</t>
+          <t>A 42841-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -11411,14 +11411,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44662</v>
+        <v>44832</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -11474,7 +11474,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 19786-2023</t>
+          <t>A 24158-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -11488,10 +11488,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45050</v>
+        <v>45079</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11505,11 +11505,11 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>8.1</v>
+        <v>1.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -11552,7 +11552,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 7787-2024</t>
+          <t>A 3818-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -11566,10 +11566,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45348</v>
+        <v>44587</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -11625,7 +11625,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 72367-2021</t>
+          <t>A 19782-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -11639,10 +11639,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44545</v>
+        <v>45050</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11654,8 +11654,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>2.5</v>
+        <v>5.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -11698,7 +11703,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 33931-2022</t>
+          <t>A 10244-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -11712,10 +11717,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44790</v>
+        <v>46076</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11727,8 +11732,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>2.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -11771,7 +11781,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 37954-2025</t>
+          <t>A 10249-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -11785,10 +11795,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45881</v>
+        <v>46076</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11800,8 +11810,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>9.5</v>
+        <v>4.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -11844,7 +11859,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 4724-2026</t>
+          <t>A 10562-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -11858,10 +11873,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46048</v>
+        <v>46077</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11873,8 +11888,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -11917,7 +11937,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 4734-2026</t>
+          <t>A 14626-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -11931,10 +11951,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46048</v>
+        <v>45012</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11946,8 +11966,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -11990,7 +12015,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 24158-2023</t>
+          <t>A 56378-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -12004,10 +12029,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45079</v>
+        <v>45236</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12021,11 +12046,11 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -12068,7 +12093,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 42714-2022</t>
+          <t>A 12841-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -12082,10 +12107,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44832</v>
+        <v>46091</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12097,8 +12122,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -12141,7 +12171,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 55873-2025</t>
+          <t>A 11728-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -12151,14 +12181,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45973</v>
+        <v>44993</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12172,11 +12202,11 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -12219,7 +12249,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 35682-2022</t>
+          <t>A 20904-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -12229,14 +12259,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44799</v>
+        <v>45060</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12254,7 +12284,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -12297,7 +12327,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 11728-2023</t>
+          <t>A 42829-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -12307,14 +12337,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44993</v>
+        <v>44832</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12326,13 +12356,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -12375,7 +12400,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 5567-2022</t>
+          <t>A 37954-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -12389,10 +12414,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44595</v>
+        <v>45881</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12405,7 +12430,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.3</v>
+        <v>9.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -12448,7 +12473,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 10249-2026</t>
+          <t>A 19246-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -12458,14 +12483,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46076</v>
+        <v>46132</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12479,11 +12504,11 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>4.8</v>
+        <v>1.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -12526,7 +12551,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 42832-2022</t>
+          <t>A 48205-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -12536,14 +12561,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44832</v>
+        <v>45205</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12555,8 +12580,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>1.1</v>
+        <v>7.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -12599,7 +12629,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 10244-2026</t>
+          <t>A 33931-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -12613,10 +12643,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46076</v>
+        <v>44790</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12628,13 +12658,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>8.699999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -12677,7 +12702,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 10562-2026</t>
+          <t>A 22662-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -12687,14 +12712,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46077</v>
+        <v>45071</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12708,11 +12733,11 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -12755,7 +12780,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 24665-2023</t>
+          <t>A 32808-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -12769,10 +12794,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45084</v>
+        <v>45516</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12784,8 +12809,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -12828,7 +12858,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 42841-2022</t>
+          <t>A 20535-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -12842,10 +12872,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44832</v>
+        <v>46140</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12857,8 +12887,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -12901,7 +12936,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 42829-2022</t>
+          <t>A 49058-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -12911,14 +12946,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44832</v>
+        <v>45594</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12930,8 +12965,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>1.6</v>
+        <v>11.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -12974,7 +13014,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 12841-2026</t>
+          <t>A 25450-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -12988,10 +13028,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46091</v>
+        <v>45463</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13009,7 +13049,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4.3</v>
+        <v>2.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -13052,7 +13092,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 2867-2024</t>
+          <t>A 24201-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -13066,10 +13106,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45315</v>
+        <v>46168</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13081,13 +13121,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -13130,7 +13165,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 3085-2023</t>
+          <t>A 24665-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -13144,10 +13179,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44946</v>
+        <v>45084</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13159,13 +13194,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>13</v>
+        <v>0.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -13208,7 +13238,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 19246-2026</t>
+          <t>A 72367-2021</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -13218,14 +13248,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46132</v>
+        <v>44545</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13237,13 +13267,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -13286,7 +13311,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 32808-2024</t>
+          <t>A 42714-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -13300,10 +13325,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45516</v>
+        <v>44832</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13315,13 +13340,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -13364,7 +13384,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 20904-2023</t>
+          <t>A 22628-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -13374,14 +13394,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45060</v>
+        <v>46155</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13399,7 +13419,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -13442,7 +13462,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 2660-2024</t>
+          <t>A 19099-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -13456,10 +13476,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45310</v>
+        <v>44691</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13471,8 +13491,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -13515,7 +13540,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 49058-2024</t>
+          <t>A 55873-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -13529,10 +13554,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45594</v>
+        <v>45973</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13550,7 +13575,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>11.4</v>
+        <v>0.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -13593,7 +13618,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 20535-2026</t>
+          <t>A 25780-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -13603,14 +13628,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46140</v>
+        <v>45090</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13622,13 +13647,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -13671,7 +13691,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 14626-2023</t>
+          <t>A 33933-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -13685,10 +13705,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45012</v>
+        <v>46248</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13706,7 +13726,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -13749,7 +13769,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 25450-2024</t>
+          <t>A 35682-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -13763,10 +13783,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45463</v>
+        <v>44799</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13780,11 +13800,11 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -13827,7 +13847,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 24201-2026</t>
+          <t>A 2867-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -13841,10 +13861,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46168</v>
+        <v>45315</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13856,8 +13876,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -13900,7 +13925,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 19782-2023</t>
+          <t>A 2660-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -13914,10 +13939,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45050</v>
+        <v>45310</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13929,13 +13954,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>5.2</v>
+        <v>2.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -13978,7 +13998,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 7848-2022</t>
+          <t>A 31061-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -13992,10 +14012,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44608</v>
+        <v>46215</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14007,8 +14027,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>2.1</v>
+        <v>4.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -14051,7 +14076,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 56378-2023</t>
+          <t>A 5567-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -14065,10 +14090,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45236</v>
+        <v>44595</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14080,13 +14105,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -14129,7 +14149,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 19099-2022</t>
+          <t>A 3085-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -14143,10 +14163,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44691</v>
+        <v>44946</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14160,11 +14180,11 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.4</v>
+        <v>13</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -14207,7 +14227,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 22628-2026</t>
+          <t>A 32223-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -14221,10 +14241,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46155</v>
+        <v>46237</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14238,11 +14258,11 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -14285,7 +14305,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 3818-2022</t>
+          <t>A 32501-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -14295,14 +14315,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44587</v>
+        <v>46239</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14315,7 +14335,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -14358,7 +14378,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 33933-2026</t>
+          <t>A 7848-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -14372,10 +14392,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46248</v>
+        <v>44608</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14387,13 +14407,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -14436,7 +14451,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 31061-2026</t>
+          <t>A 15743-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -14450,10 +14465,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46215</v>
+        <v>45021</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14465,13 +14480,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>4.4</v>
+        <v>0.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -14514,7 +14524,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 21509-2024</t>
+          <t>A 4724-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -14528,10 +14538,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45441</v>
+        <v>46048</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14543,13 +14553,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -14592,7 +14597,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 22662-2023</t>
+          <t>A 4734-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -14602,14 +14607,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45071</v>
+        <v>46048</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14621,13 +14626,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -14670,7 +14670,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 25780-2023</t>
+          <t>A 15637-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -14684,10 +14684,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45090</v>
+        <v>44662</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -14743,7 +14743,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 32501-2026</t>
+          <t>A 19786-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -14753,14 +14753,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46239</v>
+        <v>45050</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14772,8 +14772,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>1.5</v>
+        <v>8.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -14816,7 +14821,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 32223-2026</t>
+          <t>A 7787-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -14830,10 +14835,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46237</v>
+        <v>45348</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14845,13 +14850,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>8.199999999999999</v>
+        <v>1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -14911,7 +14911,7 @@
         <v>45021</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>44734</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>44734</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>46251</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>

--- a/Översikt SURAHAMMAR.xlsx
+++ b/Översikt SURAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45470</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>45684</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 31280-2024</t>
+          <t>A 39697-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45504</v>
+        <v>45890</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,23 +964,23 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>6.9</v>
+        <v>25.7</v>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="K4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -992,21 +992,182 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="R4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
         <v>44</v>
       </c>
       <c r="T4" t="n">
+        <v>242</v>
+      </c>
+      <c r="U4" t="n">
+        <v>106</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Grönfink
+Knärot
+Bivråk
+Brunlångöra
+Dropptaggsvamp
+Fjällig taggsvamp s.str.
+Järnsparv
+Motaggsvamp
+Nordfladdermus
+Skarp dropptaggsvamp
+Skogshare
+Sotvaxskivling
+Sparvuggla
+Stornopping
+Talltita
+Älg
+Blodvaxing
+Gulgrön kantmusseron
+Honungsvaxing
+Luktvaxing
+Mindre märgborre
+Smal svampklubba
+Vedticka
+Gråspett
+Järpe
+Liljekonvalj
+Mattlummer
+Nattskärra
+Spillkråka
+Tjäder
+Tofsmes
+Dvärgpipistrell
+Gröngöling
+Kungsfågel
+Orre
+Slaguggla
+Större brunfladdermus
+Sångsvan
+Trana
+Trollpipistrell
+Vattenfladdermus
+Vanlig groda
+Fläcknycklar
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39697-2025 artfynd.xlsx", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39697-2025 karta.png", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39697-2025 georefererad karta.tif", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="Z4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 39697-2025 karta knärot.png", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39697-2025 FSC-klagomål.docx", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39697-2025 FSC-klagomål mail.docx", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39697-2025 tillsynsbegäran.docx", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39697-2025 tillsynsbegäran mail.docx", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39697-2025 prioriterade fågelarter.docx", "A 39697-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 31280-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45504</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K5" t="n">
+        <v>12</v>
+      </c>
+      <c r="L5" t="n">
+        <v>22</v>
+      </c>
+      <c r="M5" t="n">
+        <v>5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>27</v>
+      </c>
+      <c r="R5" t="n">
+        <v>5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>44</v>
+      </c>
+      <c r="T5" t="n">
         <v>93</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>91</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Gränsticka
 Knärot
@@ -1054,201 +1215,40 @@
 Lopplummer (aggregat)</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31280-2024 artfynd.xlsx", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31280-2024 karta.png", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31280-2024 georefererad karta.tif", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="Z4">
+      <c r="Z5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 31280-2024 karta knärot.png", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31280-2024 FSC-klagomål.docx", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31280-2024 FSC-klagomål mail.docx", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31280-2024 tillsynsbegäran.docx", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31280-2024 tillsynsbegäran mail.docx", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 31280-2024 prioriterade fågelarter.docx", "A 31280-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 39697-2025</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45890</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>28</v>
-      </c>
-      <c r="K5" t="n">
-        <v>7</v>
-      </c>
-      <c r="L5" t="n">
-        <v>14</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>16</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2</v>
-      </c>
-      <c r="S5" t="n">
-        <v>44</v>
-      </c>
-      <c r="T5" t="n">
-        <v>242</v>
-      </c>
-      <c r="U5" t="n">
-        <v>106</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Grönfink
-Knärot
-Bivråk
-Brunlångöra
-Dropptaggsvamp
-Fjällig taggsvamp s.str.
-Järnsparv
-Motaggsvamp
-Nordfladdermus
-Skarp dropptaggsvamp
-Skogshare
-Sotvaxskivling
-Sparvuggla
-Stornopping
-Talltita
-Älg
-Blodvaxing
-Gulgrön kantmusseron
-Honungsvaxing
-Luktvaxing
-Mindre märgborre
-Smal svampklubba
-Vedticka
-Gråspett
-Järpe
-Liljekonvalj
-Mattlummer
-Nattskärra
-Spillkråka
-Tjäder
-Tofsmes
-Dvärgpipistrell
-Gröngöling
-Kungsfågel
-Orre
-Slaguggla
-Större brunfladdermus
-Sångsvan
-Trana
-Trollpipistrell
-Vattenfladdermus
-Vanlig groda
-Fläcknycklar
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39697-2025 artfynd.xlsx", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39697-2025 karta.png", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39697-2025 georefererad karta.tif", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="Z5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 39697-2025 karta knärot.png", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39697-2025 FSC-klagomål.docx", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39697-2025 FSC-klagomål mail.docx", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39697-2025 tillsynsbegäran.docx", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39697-2025 tillsynsbegäran mail.docx", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39697-2025 prioriterade fågelarter.docx", "A 39697-2025")</f>
         <v/>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
         <v>45582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45169</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45139</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45782</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>45282</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>46216</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>46216</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>46237</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>44613</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>46085</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>45435</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>46215</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>46111</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>44832</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>45890</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45523</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>45070</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>44565</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31060-2026</t>
+          <t>A 44798-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46215</v>
+        <v>45574</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3591,26 +3591,26 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>7.8</v>
+        <v>4.4</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
         <v>7</v>
       </c>
-      <c r="K24" t="n">
-        <v>2</v>
-      </c>
-      <c r="L24" t="n">
-        <v>2</v>
-      </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3619,7 +3619,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -3628,12 +3628,130 @@
         <v>9</v>
       </c>
       <c r="T24" t="n">
+        <v>26</v>
+      </c>
+      <c r="U24" t="n">
+        <v>10</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Rosetticka
+Brunklöver
+Gropticka
+Persiljespindling
+Scharlakansvaxing
+Svinrot
+Ullticka
+Vågticka
+Brandticka</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 44798-2024 artfynd.xlsx", "A 44798-2024")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 44798-2024 karta.png", "A 44798-2024")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 44798-2024 georefererad karta.tif", "A 44798-2024")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 44798-2024 FSC-klagomål.docx", "A 44798-2024")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 44798-2024 FSC-klagomål mail.docx", "A 44798-2024")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 44798-2024 tillsynsbegäran.docx", "A 44798-2024")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 44798-2024 tillsynsbegäran mail.docx", "A 44798-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 31060-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J25" t="n">
+        <v>7</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
         <v>9</v>
       </c>
-      <c r="U24" t="n">
+      <c r="T25" t="n">
+        <v>9</v>
+      </c>
+      <c r="U25" t="n">
         <v>3</v>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Bombmurkla
 Brunlångöra
@@ -3646,154 +3764,36 @@
 Vanlig groda</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31060-2026 artfynd.xlsx", "A 31060-2026")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31060-2026 karta.png", "A 31060-2026")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31060-2026 georefererad karta.tif", "A 31060-2026")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31060-2026 FSC-klagomål.docx", "A 31060-2026")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31060-2026 FSC-klagomål mail.docx", "A 31060-2026")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31060-2026 tillsynsbegäran.docx", "A 31060-2026")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31060-2026 tillsynsbegäran mail.docx", "A 31060-2026")</f>
         <v/>
       </c>
-      <c r="AE24">
+      <c r="AE25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 31060-2026 prioriterade fågelarter.docx", "A 31060-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 44798-2024</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>45574</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" t="n">
-        <v>7</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>8</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S25" t="n">
-        <v>9</v>
-      </c>
-      <c r="T25" t="n">
-        <v>26</v>
-      </c>
-      <c r="U25" t="n">
-        <v>10</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Rosetticka
-Brunklöver
-Gropticka
-Persiljespindling
-Scharlakansvaxing
-Svinrot
-Ullticka
-Vågticka
-Brandticka</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 44798-2024 artfynd.xlsx", "A 44798-2024")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 44798-2024 karta.png", "A 44798-2024")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 44798-2024 georefererad karta.tif", "A 44798-2024")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 44798-2024 FSC-klagomål.docx", "A 44798-2024")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 44798-2024 FSC-klagomål mail.docx", "A 44798-2024")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 44798-2024 tillsynsbegäran.docx", "A 44798-2024")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 44798-2024 tillsynsbegäran mail.docx", "A 44798-2024")</f>
         <v/>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
         <v>45435</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>44518</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>44477</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>45203</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 36260-2026</t>
+          <t>A 22840-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4294,10 +4294,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46268</v>
+        <v>45072</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4309,25 +4309,20 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="J30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -4339,21 +4334,137 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>7</v>
       </c>
       <c r="T30" t="n">
+        <v>10</v>
+      </c>
+      <c r="U30" t="n">
+        <v>9</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Hultbräken
+Kärrviol
+Mattlummer
+Skogsstjärna
+Stjärnstarr
+Vitsippa
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 22840-2023 artfynd.xlsx", "A 22840-2023")</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 22840-2023 karta.png", "A 22840-2023")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 22840-2023 georefererad karta.tif", "A 22840-2023")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 22840-2023 FSC-klagomål.docx", "A 22840-2023")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 22840-2023 FSC-klagomål mail.docx", "A 22840-2023")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 22840-2023 tillsynsbegäran.docx", "A 22840-2023")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 22840-2023 tillsynsbegäran mail.docx", "A 22840-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A 36260-2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J31" t="n">
+        <v>4</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="n">
+        <v>2</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2</v>
+      </c>
+      <c r="S31" t="n">
+        <v>7</v>
+      </c>
+      <c r="T31" t="n">
         <v>8</v>
       </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>Mindre bastardsvärmare
 Silverblåvinge
@@ -4364,147 +4475,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W30">
+      <c r="W31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 36260-2026 artfynd.xlsx", "A 36260-2026")</f>
         <v/>
       </c>
-      <c r="X30">
+      <c r="X31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 36260-2026 karta.png", "A 36260-2026")</f>
         <v/>
       </c>
-      <c r="Y30">
+      <c r="Y31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 36260-2026 georefererad karta.tif", "A 36260-2026")</f>
         <v/>
       </c>
-      <c r="AA30">
+      <c r="AA31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 36260-2026 FSC-klagomål.docx", "A 36260-2026")</f>
         <v/>
       </c>
-      <c r="AB30">
+      <c r="AB31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 36260-2026 FSC-klagomål mail.docx", "A 36260-2026")</f>
         <v/>
       </c>
-      <c r="AC30">
+      <c r="AC31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 36260-2026 tillsynsbegäran.docx", "A 36260-2026")</f>
         <v/>
       </c>
-      <c r="AD30">
+      <c r="AD31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 36260-2026 tillsynsbegäran mail.docx", "A 36260-2026")</f>
         <v/>
       </c>
-      <c r="AE30">
+      <c r="AE31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 36260-2026 prioriterade fågelarter.docx", "A 36260-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A 22840-2023</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>45072</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>7</v>
-      </c>
-      <c r="T31" t="n">
-        <v>10</v>
-      </c>
-      <c r="U31" t="n">
-        <v>9</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Hultbräken
-Kärrviol
-Mattlummer
-Skogsstjärna
-Stjärnstarr
-Vitsippa
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 22840-2023 artfynd.xlsx", "A 22840-2023")</f>
-        <v/>
-      </c>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 22840-2023 karta.png", "A 22840-2023")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 22840-2023 georefererad karta.tif", "A 22840-2023")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 22840-2023 FSC-klagomål.docx", "A 22840-2023")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 22840-2023 FSC-klagomål mail.docx", "A 22840-2023")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 22840-2023 tillsynsbegäran.docx", "A 22840-2023")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 22840-2023 tillsynsbegäran mail.docx", "A 22840-2023")</f>
         <v/>
       </c>
     </row>
@@ -4528,7 +4528,7 @@
         <v>45545</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>45945</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>44518</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10236-2026</t>
+          <t>A 63145-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46076</v>
+        <v>46009</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4900,23 +4900,23 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.8</v>
+        <v>40.5</v>
       </c>
       <c r="J35" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
         <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -4928,10 +4928,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
         <v>6</v>
@@ -4943,6 +4943,125 @@
         <v>0</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril
+Mindre hackspett
+Talltita
+Svart trolldruva
+Kungsfågel
+Nattviol</t>
+        </is>
+      </c>
+      <c r="W35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63145-2025 artfynd.xlsx", "A 63145-2025")</f>
+        <v/>
+      </c>
+      <c r="X35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63145-2025 karta.png", "A 63145-2025")</f>
+        <v/>
+      </c>
+      <c r="Y35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63145-2025 georefererad karta.tif", "A 63145-2025")</f>
+        <v/>
+      </c>
+      <c r="AA35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63145-2025 FSC-klagomål.docx", "A 63145-2025")</f>
+        <v/>
+      </c>
+      <c r="AB35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63145-2025 FSC-klagomål mail.docx", "A 63145-2025")</f>
+        <v/>
+      </c>
+      <c r="AC35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63145-2025 tillsynsbegäran.docx", "A 63145-2025")</f>
+        <v/>
+      </c>
+      <c r="AD35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63145-2025 tillsynsbegäran mail.docx", "A 63145-2025")</f>
+        <v/>
+      </c>
+      <c r="AE35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 63145-2025 prioriterade fågelarter.docx", "A 63145-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>A 10236-2026</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>46076</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2</v>
+      </c>
+      <c r="L36" t="n">
+        <v>2</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>6</v>
+      </c>
+      <c r="T36" t="n">
+        <v>13</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>Gullpudra
 Vågticka
@@ -4952,151 +5071,32 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W35">
+      <c r="W36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 10236-2026 artfynd.xlsx", "A 10236-2026")</f>
         <v/>
       </c>
-      <c r="X35">
+      <c r="X36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 10236-2026 karta.png", "A 10236-2026")</f>
         <v/>
       </c>
-      <c r="Y35">
+      <c r="Y36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 10236-2026 georefererad karta.tif", "A 10236-2026")</f>
         <v/>
       </c>
-      <c r="AA35">
+      <c r="AA36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 10236-2026 FSC-klagomål.docx", "A 10236-2026")</f>
         <v/>
       </c>
-      <c r="AB35">
+      <c r="AB36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 10236-2026 FSC-klagomål mail.docx", "A 10236-2026")</f>
         <v/>
       </c>
-      <c r="AC35">
+      <c r="AC36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 10236-2026 tillsynsbegäran.docx", "A 10236-2026")</f>
         <v/>
       </c>
-      <c r="AD35">
+      <c r="AD36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 10236-2026 tillsynsbegäran mail.docx", "A 10236-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>A 63145-2025</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="n">
-        <v>46009</v>
-      </c>
-      <c r="E36" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="J36" t="n">
-        <v>5</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" t="n">
-        <v>2</v>
-      </c>
-      <c r="M36" t="n">
-        <v>1</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>3</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1</v>
-      </c>
-      <c r="S36" t="n">
-        <v>6</v>
-      </c>
-      <c r="T36" t="n">
-        <v>13</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>Väddnätfjäril
-Mindre hackspett
-Talltita
-Svart trolldruva
-Kungsfågel
-Nattviol</t>
-        </is>
-      </c>
-      <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63145-2025 artfynd.xlsx", "A 63145-2025")</f>
-        <v/>
-      </c>
-      <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63145-2025 karta.png", "A 63145-2025")</f>
-        <v/>
-      </c>
-      <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63145-2025 georefererad karta.tif", "A 63145-2025")</f>
-        <v/>
-      </c>
-      <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63145-2025 FSC-klagomål.docx", "A 63145-2025")</f>
-        <v/>
-      </c>
-      <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63145-2025 FSC-klagomål mail.docx", "A 63145-2025")</f>
-        <v/>
-      </c>
-      <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63145-2025 tillsynsbegäran.docx", "A 63145-2025")</f>
-        <v/>
-      </c>
-      <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63145-2025 tillsynsbegäran mail.docx", "A 63145-2025")</f>
-        <v/>
-      </c>
-      <c r="AE36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 63145-2025 prioriterade fågelarter.docx", "A 63145-2025")</f>
         <v/>
       </c>
     </row>
@@ -5120,7 +5120,7 @@
         <v>44832</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>44832</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>45369</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>45503</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>45463</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>44518</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 69777-2021</t>
+          <t>A 49718-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5801,10 +5801,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44532</v>
+        <v>45212</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5817,22 +5817,22 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
       </c>
       <c r="K43" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" t="n">
         <v>2</v>
       </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5841,618 +5841,618 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
       </c>
       <c r="T43" t="n">
+        <v>6</v>
+      </c>
+      <c r="U43" t="n">
+        <v>6</v>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Talltita
+Zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="W43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 49718-2023 artfynd.xlsx", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="X43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 49718-2023 karta.png", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="Y43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 49718-2023 georefererad karta.tif", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="AA43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 49718-2023 FSC-klagomål.docx", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="AB43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 49718-2023 FSC-klagomål mail.docx", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="AC43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 49718-2023 tillsynsbegäran.docx", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="AD43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 49718-2023 tillsynsbegäran mail.docx", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="AE43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 49718-2023 prioriterade fågelarter.docx", "A 49718-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>A 42765-2022</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="n">
+        <v>44832</v>
+      </c>
+      <c r="E44" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3</v>
+      </c>
+      <c r="T44" t="n">
+        <v>4</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>Krusfrö
+Barkticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 42765-2022 artfynd.xlsx", "A 42765-2022")</f>
+        <v/>
+      </c>
+      <c r="X44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 42765-2022 karta.png", "A 42765-2022")</f>
+        <v/>
+      </c>
+      <c r="Y44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 42765-2022 georefererad karta.tif", "A 42765-2022")</f>
+        <v/>
+      </c>
+      <c r="AA44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 42765-2022 FSC-klagomål.docx", "A 42765-2022")</f>
+        <v/>
+      </c>
+      <c r="AB44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 42765-2022 FSC-klagomål mail.docx", "A 42765-2022")</f>
+        <v/>
+      </c>
+      <c r="AC44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 42765-2022 tillsynsbegäran.docx", "A 42765-2022")</f>
+        <v/>
+      </c>
+      <c r="AD44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 42765-2022 tillsynsbegäran mail.docx", "A 42765-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>A 39694-2025</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>45890</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Mindre märgborre
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39694-2025 artfynd.xlsx", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="X45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39694-2025 karta.png", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="Y45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39694-2025 georefererad karta.tif", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="AA45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39694-2025 FSC-klagomål.docx", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="AB45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39694-2025 FSC-klagomål mail.docx", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="AC45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39694-2025 tillsynsbegäran.docx", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="AD45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39694-2025 tillsynsbegäran mail.docx", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="AE45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39694-2025 prioriterade fågelarter.docx", "A 39694-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>A 69777-2021</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v>44532</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3</v>
+      </c>
+      <c r="T46" t="n">
         <v>5</v>
       </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
         <is>
           <t>Bombmurkla
 Rävticka
 Vedticka</t>
         </is>
       </c>
-      <c r="W43">
+      <c r="W46">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 69777-2021 artfynd.xlsx", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="X43">
+      <c r="X46">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 69777-2021 karta.png", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="Y43">
+      <c r="Y46">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 69777-2021 georefererad karta.tif", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="AA43">
+      <c r="AA46">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 69777-2021 FSC-klagomål.docx", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="AB43">
+      <c r="AB46">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 69777-2021 FSC-klagomål mail.docx", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="AC43">
+      <c r="AC46">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 69777-2021 tillsynsbegäran.docx", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="AD43">
+      <c r="AD46">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 69777-2021 tillsynsbegäran mail.docx", "A 69777-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>A 49718-2023</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>A 4082-2025</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D44" s="1" t="n">
-        <v>45212</v>
-      </c>
-      <c r="E44" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F44" t="inlineStr">
+      <c r="D47" s="1" t="n">
+        <v>45684</v>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>VÄSTMANLANDS LÄN</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="I44" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J44" t="n">
-        <v>1</v>
-      </c>
-      <c r="K44" t="n">
-        <v>1</v>
-      </c>
-      <c r="L44" t="n">
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J47" t="n">
         <v>2</v>
       </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
+      <c r="K47" t="n">
         <v>2</v>
       </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
         <v>3</v>
       </c>
-      <c r="T44" t="n">
-        <v>6</v>
-      </c>
-      <c r="U44" t="n">
-        <v>6</v>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Talltita
-Zontaggsvamp</t>
-        </is>
-      </c>
-      <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 49718-2023 artfynd.xlsx", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 49718-2023 karta.png", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 49718-2023 georefererad karta.tif", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 49718-2023 FSC-klagomål.docx", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 49718-2023 FSC-klagomål mail.docx", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 49718-2023 tillsynsbegäran.docx", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 49718-2023 tillsynsbegäran mail.docx", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="AE44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 49718-2023 prioriterade fågelarter.docx", "A 49718-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>A 39694-2025</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="n">
-        <v>45890</v>
-      </c>
-      <c r="E45" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J45" t="n">
-        <v>1</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1</v>
-      </c>
-      <c r="L45" t="n">
-        <v>1</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>1</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
+      <c r="T47" t="n">
         <v>3</v>
       </c>
-      <c r="T45" t="n">
-        <v>3</v>
-      </c>
-      <c r="U45" t="n">
-        <v>2</v>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Mindre märgborre
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39694-2025 artfynd.xlsx", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39694-2025 karta.png", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39694-2025 georefererad karta.tif", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39694-2025 FSC-klagomål.docx", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39694-2025 FSC-klagomål mail.docx", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39694-2025 tillsynsbegäran.docx", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39694-2025 tillsynsbegäran mail.docx", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="AE45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39694-2025 prioriterade fågelarter.docx", "A 39694-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>A 4082-2025</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="n">
-        <v>45684</v>
-      </c>
-      <c r="E46" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="J46" t="n">
-        <v>2</v>
-      </c>
-      <c r="K46" t="n">
-        <v>2</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>3</v>
-      </c>
-      <c r="T46" t="n">
-        <v>3</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1</v>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
+      <c r="U47" t="n">
+        <v>1</v>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
         <is>
           <t>Grönpyrola
 Plattlummer
 Lopplummer (aggregat)</t>
         </is>
       </c>
-      <c r="W46">
+      <c r="W47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 4082-2025 artfynd.xlsx", "A 4082-2025")</f>
         <v/>
       </c>
-      <c r="X46">
+      <c r="X47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 4082-2025 karta.png", "A 4082-2025")</f>
         <v/>
       </c>
-      <c r="Y46">
+      <c r="Y47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 4082-2025 georefererad karta.tif", "A 4082-2025")</f>
         <v/>
       </c>
-      <c r="AA46">
+      <c r="AA47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 4082-2025 FSC-klagomål.docx", "A 4082-2025")</f>
         <v/>
       </c>
-      <c r="AB46">
+      <c r="AB47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 4082-2025 FSC-klagomål mail.docx", "A 4082-2025")</f>
         <v/>
       </c>
-      <c r="AC46">
+      <c r="AC47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 4082-2025 tillsynsbegäran.docx", "A 4082-2025")</f>
         <v/>
       </c>
-      <c r="AD46">
+      <c r="AD47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 4082-2025 tillsynsbegäran mail.docx", "A 4082-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>A 48128-2023</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D47" s="1" t="n">
+      <c r="D48" s="1" t="n">
         <v>45205</v>
       </c>
-      <c r="E47" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F47" t="inlineStr">
+      <c r="E48" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>VÄSTMANLANDS LÄN</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
-      <c r="I47" t="n">
+      <c r="I48" t="n">
         <v>11.8</v>
       </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
-        <v>1</v>
-      </c>
-      <c r="L47" t="n">
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" t="n">
         <v>2</v>
       </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
         <v>2</v>
       </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
         <v>3</v>
       </c>
-      <c r="T47" t="n">
+      <c r="T48" t="n">
         <v>3</v>
       </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
         <is>
           <t>Jungfrulin
 Svinrot
 Vedticka</t>
         </is>
       </c>
-      <c r="W47">
+      <c r="W48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 48128-2023 artfynd.xlsx", "A 48128-2023")</f>
         <v/>
       </c>
-      <c r="X47">
+      <c r="X48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 48128-2023 karta.png", "A 48128-2023")</f>
         <v/>
       </c>
-      <c r="Y47">
+      <c r="Y48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 48128-2023 georefererad karta.tif", "A 48128-2023")</f>
         <v/>
       </c>
-      <c r="AA47">
+      <c r="AA48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 48128-2023 FSC-klagomål.docx", "A 48128-2023")</f>
         <v/>
       </c>
-      <c r="AB47">
+      <c r="AB48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 48128-2023 FSC-klagomål mail.docx", "A 48128-2023")</f>
         <v/>
       </c>
-      <c r="AC47">
+      <c r="AC48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 48128-2023 tillsynsbegäran.docx", "A 48128-2023")</f>
         <v/>
       </c>
-      <c r="AD47">
+      <c r="AD48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 48128-2023 tillsynsbegäran mail.docx", "A 48128-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>A 42765-2022</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="n">
-        <v>44832</v>
-      </c>
-      <c r="E48" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J48" t="n">
-        <v>1</v>
-      </c>
-      <c r="K48" t="n">
-        <v>1</v>
-      </c>
-      <c r="L48" t="n">
-        <v>1</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>1</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>3</v>
-      </c>
-      <c r="T48" t="n">
-        <v>4</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1</v>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>Krusfrö
-Barkticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 42765-2022 artfynd.xlsx", "A 42765-2022")</f>
-        <v/>
-      </c>
-      <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 42765-2022 karta.png", "A 42765-2022")</f>
-        <v/>
-      </c>
-      <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 42765-2022 georefererad karta.tif", "A 42765-2022")</f>
-        <v/>
-      </c>
-      <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 42765-2022 FSC-klagomål.docx", "A 42765-2022")</f>
-        <v/>
-      </c>
-      <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 42765-2022 FSC-klagomål mail.docx", "A 42765-2022")</f>
-        <v/>
-      </c>
-      <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 42765-2022 tillsynsbegäran.docx", "A 42765-2022")</f>
-        <v/>
-      </c>
-      <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 42765-2022 tillsynsbegäran mail.docx", "A 42765-2022")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 33935-2026</t>
+          <t>A 63146-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6466,10 +6466,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46248</v>
+        <v>46009</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6487,16 +6487,16 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.6</v>
+        <v>10.2</v>
       </c>
       <c r="J49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
         <v>2</v>
       </c>
-      <c r="K49" t="n">
-        <v>1</v>
-      </c>
       <c r="L49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -6511,7 +6511,7 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
@@ -6520,272 +6520,272 @@
         <v>3</v>
       </c>
       <c r="T49" t="n">
+        <v>12</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>Stor aspticka
+Svart trolldruva
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63146-2025 artfynd.xlsx", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="X49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63146-2025 karta.png", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="Y49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63146-2025 georefererad karta.tif", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="AA49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63146-2025 FSC-klagomål.docx", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="AB49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63146-2025 FSC-klagomål mail.docx", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="AC49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63146-2025 tillsynsbegäran.docx", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="AD49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63146-2025 tillsynsbegäran mail.docx", "A 63146-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>A 33935-2026</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D50" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E50" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J50" t="n">
+        <v>2</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>3</v>
+      </c>
+      <c r="T50" t="n">
         <v>5</v>
       </c>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" s="2" t="inlineStr">
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Mindre märgborre
 Spillkråka</t>
         </is>
       </c>
-      <c r="W49">
+      <c r="W50">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 33935-2026 artfynd.xlsx", "A 33935-2026")</f>
         <v/>
       </c>
-      <c r="X49">
+      <c r="X50">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 33935-2026 karta.png", "A 33935-2026")</f>
         <v/>
       </c>
-      <c r="Y49">
+      <c r="Y50">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 33935-2026 georefererad karta.tif", "A 33935-2026")</f>
         <v/>
       </c>
-      <c r="AA49">
+      <c r="AA50">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 33935-2026 FSC-klagomål.docx", "A 33935-2026")</f>
         <v/>
       </c>
-      <c r="AB49">
+      <c r="AB50">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 33935-2026 FSC-klagomål mail.docx", "A 33935-2026")</f>
         <v/>
       </c>
-      <c r="AC49">
+      <c r="AC50">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 33935-2026 tillsynsbegäran.docx", "A 33935-2026")</f>
         <v/>
       </c>
-      <c r="AD49">
+      <c r="AD50">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 33935-2026 tillsynsbegäran mail.docx", "A 33935-2026")</f>
         <v/>
       </c>
-      <c r="AE49">
+      <c r="AE50">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 33935-2026 prioriterade fågelarter.docx", "A 33935-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="50" ht="15" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>A 36264-2026</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D50" s="1" t="n">
+      <c r="D51" s="1" t="n">
         <v>46268</v>
       </c>
-      <c r="E50" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F50" t="inlineStr">
+      <c r="E51" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>VÄSTMANLANDS LÄN</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I50" t="n">
+      <c r="I51" t="n">
         <v>2.4</v>
       </c>
-      <c r="J50" t="n">
-        <v>1</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>1</v>
-      </c>
-      <c r="M50" t="n">
-        <v>1</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
         <v>2</v>
       </c>
-      <c r="R50" t="n">
-        <v>1</v>
-      </c>
-      <c r="S50" t="n">
+      <c r="R51" t="n">
+        <v>1</v>
+      </c>
+      <c r="S51" t="n">
         <v>3</v>
       </c>
-      <c r="T50" t="n">
+      <c r="T51" t="n">
         <v>3</v>
       </c>
-      <c r="U50" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" s="2" t="inlineStr">
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
         <is>
           <t>Grangråticka
 Fjällig taggsvamp s.str.
 Blåsippa</t>
         </is>
       </c>
-      <c r="W50">
+      <c r="W51">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 36264-2026 artfynd.xlsx", "A 36264-2026")</f>
         <v/>
       </c>
-      <c r="X50">
+      <c r="X51">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 36264-2026 karta.png", "A 36264-2026")</f>
         <v/>
       </c>
-      <c r="Y50">
+      <c r="Y51">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 36264-2026 georefererad karta.tif", "A 36264-2026")</f>
         <v/>
       </c>
-      <c r="AA50">
+      <c r="AA51">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 36264-2026 FSC-klagomål.docx", "A 36264-2026")</f>
         <v/>
       </c>
-      <c r="AB50">
+      <c r="AB51">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 36264-2026 FSC-klagomål mail.docx", "A 36264-2026")</f>
         <v/>
       </c>
-      <c r="AC50">
+      <c r="AC51">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 36264-2026 tillsynsbegäran.docx", "A 36264-2026")</f>
         <v/>
       </c>
-      <c r="AD50">
+      <c r="AD51">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 36264-2026 tillsynsbegäran mail.docx", "A 36264-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>A 63146-2025</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="n">
-        <v>46009</v>
-      </c>
-      <c r="E51" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="J51" t="n">
-        <v>1</v>
-      </c>
-      <c r="K51" t="n">
-        <v>2</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>3</v>
-      </c>
-      <c r="T51" t="n">
-        <v>12</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" s="2" t="inlineStr">
-        <is>
-          <t>Stor aspticka
-Svart trolldruva
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63146-2025 artfynd.xlsx", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="X51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63146-2025 karta.png", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="Y51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63146-2025 georefererad karta.tif", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="AA51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63146-2025 FSC-klagomål.docx", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="AB51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63146-2025 FSC-klagomål mail.docx", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="AC51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63146-2025 tillsynsbegäran.docx", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="AD51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63146-2025 tillsynsbegäran mail.docx", "A 63146-2025")</f>
         <v/>
       </c>
     </row>
@@ -6809,7 +6809,7 @@
         <v>46239</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>44635</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>45708</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>45708</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 56362-2023</t>
+          <t>A 30074-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7270,10 +7270,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45236</v>
+        <v>45110</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7287,11 +7287,11 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>15.2</v>
+        <v>1.1</v>
       </c>
       <c r="J56" t="n">
         <v>1</v>
@@ -7303,7 +7303,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
@@ -7315,10 +7315,10 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>2</v>
@@ -7327,47 +7327,47 @@
         <v>2</v>
       </c>
       <c r="U56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>Väddnätfjäril
-Grönpyrola</t>
+          <t>Grönpyrola
+Revlummer</t>
         </is>
       </c>
       <c r="W56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 56362-2023 artfynd.xlsx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 30074-2023 artfynd.xlsx", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="X56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 56362-2023 karta.png", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 30074-2023 karta.png", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="Y56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 56362-2023 georefererad karta.tif", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 30074-2023 georefererad karta.tif", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="AA56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 56362-2023 FSC-klagomål.docx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 30074-2023 FSC-klagomål.docx", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="AB56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 56362-2023 FSC-klagomål mail.docx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 30074-2023 FSC-klagomål mail.docx", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="AC56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 56362-2023 tillsynsbegäran.docx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 30074-2023 tillsynsbegäran.docx", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="AD56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 56362-2023 tillsynsbegäran mail.docx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 30074-2023 tillsynsbegäran mail.docx", "A 30074-2023")</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 14001-2023</t>
+          <t>A 56362-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45007</v>
+        <v>45236</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7402,16 +7402,16 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>15.2</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
         <v>1</v>
@@ -7426,7 +7426,7 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R57" t="n">
         <v>1</v>
@@ -7438,40 +7438,40 @@
         <v>2</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>Garnlav
-Motaggsvamp</t>
+          <t>Väddnätfjäril
+Grönpyrola</t>
         </is>
       </c>
       <c r="W57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 14001-2023 artfynd.xlsx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 56362-2023 artfynd.xlsx", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="X57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 14001-2023 karta.png", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 56362-2023 karta.png", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="Y57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 14001-2023 georefererad karta.tif", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 56362-2023 georefererad karta.tif", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="AA57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 14001-2023 FSC-klagomål.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 56362-2023 FSC-klagomål.docx", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="AB57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 14001-2023 FSC-klagomål mail.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 56362-2023 FSC-klagomål mail.docx", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="AC57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 14001-2023 tillsynsbegäran.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 56362-2023 tillsynsbegäran.docx", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="AD57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 14001-2023 tillsynsbegäran mail.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 56362-2023 tillsynsbegäran mail.docx", "A 56362-2023")</f>
         <v/>
       </c>
     </row>
@@ -7495,7 +7495,7 @@
         <v>45587</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 11501-2023</t>
+          <t>A 40403-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44991</v>
+        <v>45895</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7619,23 +7619,23 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J59" t="n">
         <v>1</v>
       </c>
       <c r="K59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
@@ -7647,59 +7647,59 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S59" t="n">
         <v>2</v>
       </c>
       <c r="T59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva
-Nattviol</t>
+          <t>Igelkott
+Gröngöling</t>
         </is>
       </c>
       <c r="W59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 11501-2023 artfynd.xlsx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 40403-2025 artfynd.xlsx", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="X59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 11501-2023 karta.png", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 40403-2025 karta.png", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="Y59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 11501-2023 georefererad karta.tif", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 40403-2025 georefererad karta.tif", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="AA59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 11501-2023 FSC-klagomål.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 40403-2025 FSC-klagomål.docx", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="AB59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 11501-2023 FSC-klagomål mail.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 40403-2025 FSC-klagomål mail.docx", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="AC59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 11501-2023 tillsynsbegäran.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 40403-2025 tillsynsbegäran.docx", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="AD59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 11501-2023 tillsynsbegäran mail.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 40403-2025 tillsynsbegäran mail.docx", "A 40403-2025")</f>
         <v/>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 37013-2025</t>
+          <t>A 63138-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7713,10 +7713,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45874</v>
+        <v>46009</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7734,19 +7734,19 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>10.7</v>
+        <v>2.5</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
         <v>0</v>
@@ -7758,59 +7758,63 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>2</v>
       </c>
       <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
         <v>2</v>
       </c>
-      <c r="U60" t="n">
-        <v>0</v>
-      </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril
-Fältgentiana</t>
+          <t>Mindre märgborre
+Tjäder</t>
         </is>
       </c>
       <c r="W60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37013-2025 artfynd.xlsx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63138-2025 artfynd.xlsx", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="X60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37013-2025 karta.png", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63138-2025 karta.png", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="Y60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37013-2025 georefererad karta.tif", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63138-2025 georefererad karta.tif", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="AA60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37013-2025 FSC-klagomål.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63138-2025 FSC-klagomål.docx", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="AB60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37013-2025 FSC-klagomål mail.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63138-2025 FSC-klagomål mail.docx", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="AC60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37013-2025 tillsynsbegäran.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63138-2025 tillsynsbegäran.docx", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="AD60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37013-2025 tillsynsbegäran mail.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63138-2025 tillsynsbegäran mail.docx", "A 63138-2025")</f>
+        <v/>
+      </c>
+      <c r="AE60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 63138-2025 prioriterade fågelarter.docx", "A 63138-2025")</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 40403-2025</t>
+          <t>A 41204-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7824,10 +7828,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45895</v>
+        <v>45174</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7839,13 +7843,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>1</v>
@@ -7854,7 +7853,7 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" t="n">
         <v>1</v>
@@ -7869,7 +7868,7 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R61" t="n">
         <v>1</v>
@@ -7878,50 +7877,54 @@
         <v>2</v>
       </c>
       <c r="T61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>Igelkott
-Gröngöling</t>
+          <t>Knärot
+Vedtrappmossa</t>
         </is>
       </c>
       <c r="W61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 40403-2025 artfynd.xlsx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 41204-2023 artfynd.xlsx", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="X61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 40403-2025 karta.png", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 41204-2023 karta.png", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="Y61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 40403-2025 georefererad karta.tif", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 41204-2023 georefererad karta.tif", "A 41204-2023")</f>
+        <v/>
+      </c>
+      <c r="Z61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 41204-2023 karta knärot.png", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="AA61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 40403-2025 FSC-klagomål.docx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 41204-2023 FSC-klagomål.docx", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="AB61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 40403-2025 FSC-klagomål mail.docx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 41204-2023 FSC-klagomål mail.docx", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="AC61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 40403-2025 tillsynsbegäran.docx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 41204-2023 tillsynsbegäran.docx", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="AD61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 40403-2025 tillsynsbegäran mail.docx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 41204-2023 tillsynsbegäran mail.docx", "A 41204-2023")</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 41204-2023</t>
+          <t>A 11501-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7935,10 +7938,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45174</v>
+        <v>44991</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7950,20 +7953,25 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J62" t="n">
         <v>1</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
         <v>0</v>
@@ -7975,63 +7983,59 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>2</v>
       </c>
       <c r="T62" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>Knärot
-Vedtrappmossa</t>
+          <t>Svart trolldruva
+Nattviol</t>
         </is>
       </c>
       <c r="W62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 41204-2023 artfynd.xlsx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 11501-2023 artfynd.xlsx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="X62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 41204-2023 karta.png", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 11501-2023 karta.png", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="Y62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 41204-2023 georefererad karta.tif", "A 41204-2023")</f>
-        <v/>
-      </c>
-      <c r="Z62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 41204-2023 karta knärot.png", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 11501-2023 georefererad karta.tif", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AA62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 41204-2023 FSC-klagomål.docx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 11501-2023 FSC-klagomål.docx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AB62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 41204-2023 FSC-klagomål mail.docx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 11501-2023 FSC-klagomål mail.docx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AC62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 41204-2023 tillsynsbegäran.docx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 11501-2023 tillsynsbegäran.docx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AD62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 41204-2023 tillsynsbegäran mail.docx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 11501-2023 tillsynsbegäran mail.docx", "A 11501-2023")</f>
         <v/>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 30074-2023</t>
+          <t>A 14001-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -8045,10 +8049,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45110</v>
+        <v>45007</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8062,23 +8066,23 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
@@ -8090,10 +8094,10 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S63" t="n">
         <v>2</v>
@@ -8106,36 +8110,36 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola
-Revlummer</t>
+          <t>Garnlav
+Motaggsvamp</t>
         </is>
       </c>
       <c r="W63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 30074-2023 artfynd.xlsx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 14001-2023 artfynd.xlsx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="X63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 30074-2023 karta.png", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 14001-2023 karta.png", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="Y63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 30074-2023 georefererad karta.tif", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 14001-2023 georefererad karta.tif", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AA63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 30074-2023 FSC-klagomål.docx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 14001-2023 FSC-klagomål.docx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AB63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 30074-2023 FSC-klagomål mail.docx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 14001-2023 FSC-klagomål mail.docx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AC63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 30074-2023 tillsynsbegäran.docx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 14001-2023 tillsynsbegäran.docx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AD63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 30074-2023 tillsynsbegäran mail.docx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 14001-2023 tillsynsbegäran mail.docx", "A 14001-2023")</f>
         <v/>
       </c>
     </row>
@@ -8159,7 +8163,7 @@
         <v>45007</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8270,7 +8274,7 @@
         <v>46268</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8364,7 +8368,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 63138-2025</t>
+          <t>A 13788-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -8378,10 +8382,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46009</v>
+        <v>45737</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8393,22 +8397,17 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>2.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -8423,7 +8422,7 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
@@ -8432,54 +8431,54 @@
         <v>2</v>
       </c>
       <c r="T66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U66" t="n">
         <v>2</v>
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>Mindre märgborre
-Tjäder</t>
+          <t>Sparvuggla
+Nattskärra</t>
         </is>
       </c>
       <c r="W66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63138-2025 artfynd.xlsx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 13788-2025 artfynd.xlsx", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="X66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63138-2025 karta.png", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 13788-2025 karta.png", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="Y66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63138-2025 georefererad karta.tif", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 13788-2025 georefererad karta.tif", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="AA66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63138-2025 FSC-klagomål.docx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 13788-2025 FSC-klagomål.docx", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="AB66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63138-2025 FSC-klagomål mail.docx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 13788-2025 FSC-klagomål mail.docx", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="AC66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63138-2025 tillsynsbegäran.docx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 13788-2025 tillsynsbegäran.docx", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="AD66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63138-2025 tillsynsbegäran mail.docx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 13788-2025 tillsynsbegäran mail.docx", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="AE66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 63138-2025 prioriterade fågelarter.docx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 13788-2025 prioriterade fågelarter.docx", "A 13788-2025")</f>
         <v/>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 13788-2025</t>
+          <t>A 37013-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -8493,10 +8492,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45737</v>
+        <v>45874</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8508,21 +8507,26 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>9.699999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
         <v>2</v>
       </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="n">
-        <v>1</v>
-      </c>
-      <c r="M67" t="n">
-        <v>0</v>
-      </c>
       <c r="N67" t="n">
         <v>0</v>
       </c>
@@ -8533,10 +8537,10 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S67" t="n">
         <v>2</v>
@@ -8545,44 +8549,40 @@
         <v>2</v>
       </c>
       <c r="U67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>Sparvuggla
-Nattskärra</t>
+          <t>Brunfläckig pärlemorfjäril
+Fältgentiana</t>
         </is>
       </c>
       <c r="W67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 13788-2025 artfynd.xlsx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37013-2025 artfynd.xlsx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="X67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 13788-2025 karta.png", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37013-2025 karta.png", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="Y67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 13788-2025 georefererad karta.tif", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37013-2025 georefererad karta.tif", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AA67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 13788-2025 FSC-klagomål.docx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37013-2025 FSC-klagomål.docx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AB67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 13788-2025 FSC-klagomål mail.docx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37013-2025 FSC-klagomål mail.docx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AC67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 13788-2025 tillsynsbegäran.docx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37013-2025 tillsynsbegäran.docx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AD67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 13788-2025 tillsynsbegäran mail.docx", "A 13788-2025")</f>
-        <v/>
-      </c>
-      <c r="AE67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 13788-2025 prioriterade fågelarter.docx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37013-2025 tillsynsbegäran mail.docx", "A 37013-2025")</f>
         <v/>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
         <v>45720</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8717,7 +8717,7 @@
         <v>44696</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>44739</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>44524</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>44696</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 39099-2022</t>
+          <t>A 30076-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -9154,10 +9154,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44817</v>
+        <v>45110</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9171,17 +9171,17 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>7.4</v>
+        <v>1.1</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -9211,39 +9211,39 @@
         <v>1</v>
       </c>
       <c r="U73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39099-2022 artfynd.xlsx", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 30076-2023 artfynd.xlsx", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="X73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39099-2022 karta.png", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 30076-2023 karta.png", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="Y73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39099-2022 georefererad karta.tif", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 30076-2023 georefererad karta.tif", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="AA73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39099-2022 FSC-klagomål.docx", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 30076-2023 FSC-klagomål.docx", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="AB73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39099-2022 FSC-klagomål mail.docx", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 30076-2023 FSC-klagomål mail.docx", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="AC73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39099-2022 tillsynsbegäran.docx", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 30076-2023 tillsynsbegäran.docx", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="AD73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39099-2022 tillsynsbegäran mail.docx", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 30076-2023 tillsynsbegäran mail.docx", "A 30076-2023")</f>
         <v/>
       </c>
     </row>
@@ -9267,7 +9267,7 @@
         <v>44977</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 34584-2025</t>
+          <t>A 37287-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -9374,10 +9374,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45846</v>
+        <v>45156</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9389,22 +9389,17 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -9419,7 +9414,7 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R75" t="n">
         <v>0</v>
@@ -9431,50 +9426,46 @@
         <v>1</v>
       </c>
       <c r="U75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="W75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34584-2025 artfynd.xlsx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37287-2023 artfynd.xlsx", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="X75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34584-2025 karta.png", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37287-2023 karta.png", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="Y75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34584-2025 georefererad karta.tif", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37287-2023 georefererad karta.tif", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="AA75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34584-2025 FSC-klagomål.docx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37287-2023 FSC-klagomål.docx", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="AB75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34584-2025 FSC-klagomål mail.docx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37287-2023 FSC-klagomål mail.docx", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="AC75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34584-2025 tillsynsbegäran.docx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37287-2023 tillsynsbegäran.docx", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="AD75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34584-2025 tillsynsbegäran mail.docx", "A 34584-2025")</f>
-        <v/>
-      </c>
-      <c r="AE75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 34584-2025 prioriterade fågelarter.docx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37287-2023 tillsynsbegäran mail.docx", "A 37287-2023")</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 16013-2023</t>
+          <t>A 39099-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -9488,10 +9479,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45026</v>
+        <v>44817</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9503,20 +9494,25 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>3.9</v>
+        <v>7.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
         <v>0</v>
@@ -9528,10 +9524,10 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>1</v>
@@ -9540,46 +9536,46 @@
         <v>1</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="W76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 16013-2023 artfynd.xlsx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39099-2022 artfynd.xlsx", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="X76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 16013-2023 karta.png", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39099-2022 karta.png", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="Y76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 16013-2023 georefererad karta.tif", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39099-2022 georefererad karta.tif", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="AA76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 16013-2023 FSC-klagomål.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39099-2022 FSC-klagomål.docx", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="AB76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 16013-2023 FSC-klagomål mail.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39099-2022 FSC-klagomål mail.docx", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="AC76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 16013-2023 tillsynsbegäran.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39099-2022 tillsynsbegäran.docx", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="AD76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 16013-2023 tillsynsbegäran mail.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39099-2022 tillsynsbegäran mail.docx", "A 39099-2022")</f>
         <v/>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 34955-2022</t>
+          <t>A 17632-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -9593,10 +9589,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44796</v>
+        <v>44680</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9608,22 +9604,17 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -9638,7 +9629,7 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
         <v>0</v>
@@ -9650,46 +9641,46 @@
         <v>1</v>
       </c>
       <c r="U77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="W77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34955-2022 artfynd.xlsx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 17632-2022 artfynd.xlsx", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="X77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34955-2022 karta.png", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 17632-2022 karta.png", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="Y77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34955-2022 georefererad karta.tif", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 17632-2022 georefererad karta.tif", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="AA77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34955-2022 FSC-klagomål.docx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 17632-2022 FSC-klagomål.docx", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="AB77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34955-2022 FSC-klagomål mail.docx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 17632-2022 FSC-klagomål mail.docx", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="AC77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34955-2022 tillsynsbegäran.docx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 17632-2022 tillsynsbegäran.docx", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="AD77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34955-2022 tillsynsbegäran mail.docx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 17632-2022 tillsynsbegäran mail.docx", "A 17632-2022")</f>
         <v/>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 33231-2024</t>
+          <t>A 34955-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -9703,10 +9694,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45518</v>
+        <v>44796</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9720,20 +9711,20 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>4.6</v>
       </c>
       <c r="J78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
@@ -9748,7 +9739,7 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R78" t="n">
         <v>0</v>
@@ -9764,42 +9755,42 @@
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 33231-2024 artfynd.xlsx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34955-2022 artfynd.xlsx", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="X78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 33231-2024 karta.png", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34955-2022 karta.png", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="Y78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 33231-2024 georefererad karta.tif", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34955-2022 georefererad karta.tif", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="AA78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 33231-2024 FSC-klagomål.docx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34955-2022 FSC-klagomål.docx", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="AB78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 33231-2024 FSC-klagomål mail.docx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34955-2022 FSC-klagomål mail.docx", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="AC78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 33231-2024 tillsynsbegäran.docx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34955-2022 tillsynsbegäran.docx", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="AD78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 33231-2024 tillsynsbegäran mail.docx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34955-2022 tillsynsbegäran mail.docx", "A 34955-2022")</f>
         <v/>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 30076-2023</t>
+          <t>A 10883-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -9813,10 +9804,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45110</v>
+        <v>44991</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9830,11 +9821,11 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>12.5</v>
       </c>
       <c r="J79" t="n">
         <v>1</v>
@@ -9843,7 +9834,7 @@
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -9858,7 +9849,7 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R79" t="n">
         <v>0</v>
@@ -9870,46 +9861,50 @@
         <v>1</v>
       </c>
       <c r="U79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="W79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 30076-2023 artfynd.xlsx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 10883-2023 artfynd.xlsx", "A 10883-2023")</f>
         <v/>
       </c>
       <c r="X79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 30076-2023 karta.png", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 10883-2023 karta.png", "A 10883-2023")</f>
         <v/>
       </c>
       <c r="Y79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 30076-2023 georefererad karta.tif", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 10883-2023 georefererad karta.tif", "A 10883-2023")</f>
         <v/>
       </c>
       <c r="AA79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 30076-2023 FSC-klagomål.docx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 10883-2023 FSC-klagomål.docx", "A 10883-2023")</f>
         <v/>
       </c>
       <c r="AB79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 30076-2023 FSC-klagomål mail.docx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 10883-2023 FSC-klagomål mail.docx", "A 10883-2023")</f>
         <v/>
       </c>
       <c r="AC79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 30076-2023 tillsynsbegäran.docx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 10883-2023 tillsynsbegäran.docx", "A 10883-2023")</f>
         <v/>
       </c>
       <c r="AD79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 30076-2023 tillsynsbegäran mail.docx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 10883-2023 tillsynsbegäran mail.docx", "A 10883-2023")</f>
+        <v/>
+      </c>
+      <c r="AE79">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 10883-2023 prioriterade fågelarter.docx", "A 10883-2023")</f>
         <v/>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 10883-2023</t>
+          <t>A 44356-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -9923,10 +9918,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44991</v>
+        <v>45573</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9940,11 +9935,11 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>12.5</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>1</v>
@@ -9953,7 +9948,7 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -9968,7 +9963,7 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
         <v>0</v>
@@ -9984,46 +9979,42 @@
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 10883-2023 artfynd.xlsx", "A 10883-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 44356-2024 artfynd.xlsx", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="X80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 10883-2023 karta.png", "A 10883-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 44356-2024 karta.png", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="Y80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 10883-2023 georefererad karta.tif", "A 10883-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 44356-2024 georefererad karta.tif", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="AA80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 10883-2023 FSC-klagomål.docx", "A 10883-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 44356-2024 FSC-klagomål.docx", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="AB80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 10883-2023 FSC-klagomål mail.docx", "A 10883-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 44356-2024 FSC-klagomål mail.docx", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="AC80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 10883-2023 tillsynsbegäran.docx", "A 10883-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 44356-2024 tillsynsbegäran.docx", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="AD80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 10883-2023 tillsynsbegäran mail.docx", "A 10883-2023")</f>
-        <v/>
-      </c>
-      <c r="AE80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 10883-2023 prioriterade fågelarter.docx", "A 10883-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 44356-2024 tillsynsbegäran mail.docx", "A 44356-2024")</f>
         <v/>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 24167-2024</t>
+          <t>A 33231-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -10033,14 +10024,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45456</v>
+        <v>45518</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10052,8 +10043,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J81" t="n">
         <v>1</v>
@@ -10089,46 +10085,46 @@
         <v>1</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="W81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 24167-2024 artfynd.xlsx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 33231-2024 artfynd.xlsx", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="X81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 24167-2024 karta.png", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 33231-2024 karta.png", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="Y81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 24167-2024 georefererad karta.tif", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 33231-2024 georefererad karta.tif", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="AA81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 24167-2024 FSC-klagomål.docx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 33231-2024 FSC-klagomål.docx", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="AB81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 24167-2024 FSC-klagomål mail.docx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 33231-2024 FSC-klagomål mail.docx", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="AC81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 24167-2024 tillsynsbegäran.docx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 33231-2024 tillsynsbegäran.docx", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="AD81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 24167-2024 tillsynsbegäran mail.docx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 33231-2024 tillsynsbegäran mail.docx", "A 33231-2024")</f>
         <v/>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 37287-2023</t>
+          <t>A 24167-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -10138,14 +10134,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45156</v>
+        <v>45456</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10161,13 +10157,13 @@
         <v>0.6</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -10182,7 +10178,7 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
         <v>0</v>
@@ -10198,42 +10194,42 @@
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>Mindre tåtelsmygare</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37287-2023 artfynd.xlsx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 24167-2024 artfynd.xlsx", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="X82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37287-2023 karta.png", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 24167-2024 karta.png", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="Y82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37287-2023 georefererad karta.tif", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 24167-2024 georefererad karta.tif", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="AA82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37287-2023 FSC-klagomål.docx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 24167-2024 FSC-klagomål.docx", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="AB82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37287-2023 FSC-klagomål mail.docx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 24167-2024 FSC-klagomål mail.docx", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="AC82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37287-2023 tillsynsbegäran.docx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 24167-2024 tillsynsbegäran.docx", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="AD82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37287-2023 tillsynsbegäran mail.docx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 24167-2024 tillsynsbegäran mail.docx", "A 24167-2024")</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 44356-2024</t>
+          <t>A 16013-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -10247,10 +10243,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45573</v>
+        <v>45026</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10262,16 +10258,11 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -10280,7 +10271,7 @@
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N83" t="n">
         <v>0</v>
@@ -10292,10 +10283,10 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S83" t="n">
         <v>1</v>
@@ -10304,46 +10295,46 @@
         <v>1</v>
       </c>
       <c r="U83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="W83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 44356-2024 artfynd.xlsx", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 16013-2023 artfynd.xlsx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="X83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 44356-2024 karta.png", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 16013-2023 karta.png", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="Y83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 44356-2024 georefererad karta.tif", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 16013-2023 georefererad karta.tif", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AA83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 44356-2024 FSC-klagomål.docx", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 16013-2023 FSC-klagomål.docx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AB83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 44356-2024 FSC-klagomål mail.docx", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 16013-2023 FSC-klagomål mail.docx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AC83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 44356-2024 tillsynsbegäran.docx", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 16013-2023 tillsynsbegäran.docx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AD83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 44356-2024 tillsynsbegäran mail.docx", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 16013-2023 tillsynsbegäran mail.docx", "A 16013-2023")</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 17632-2022</t>
+          <t>A 31589-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -10357,10 +10348,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44680</v>
+        <v>46224</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10372,8 +10363,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -10413,42 +10409,42 @@
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 17632-2022 artfynd.xlsx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31589-2026 artfynd.xlsx", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="X84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 17632-2022 karta.png", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31589-2026 karta.png", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="Y84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 17632-2022 georefererad karta.tif", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31589-2026 georefererad karta.tif", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="AA84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 17632-2022 FSC-klagomål.docx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31589-2026 FSC-klagomål.docx", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="AB84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 17632-2022 FSC-klagomål mail.docx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31589-2026 FSC-klagomål mail.docx", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="AC84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 17632-2022 tillsynsbegäran.docx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31589-2026 tillsynsbegäran.docx", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="AD84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 17632-2022 tillsynsbegäran mail.docx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31589-2026 tillsynsbegäran mail.docx", "A 31589-2026")</f>
         <v/>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 31589-2026</t>
+          <t>A 34584-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -10462,10 +10458,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46224</v>
+        <v>45846</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10479,17 +10475,17 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>7</v>
+        <v>2.7</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -10519,39 +10515,43 @@
         <v>1</v>
       </c>
       <c r="U85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31589-2026 artfynd.xlsx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34584-2025 artfynd.xlsx", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="X85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31589-2026 karta.png", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34584-2025 karta.png", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="Y85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31589-2026 georefererad karta.tif", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34584-2025 georefererad karta.tif", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="AA85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31589-2026 FSC-klagomål.docx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34584-2025 FSC-klagomål.docx", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="AB85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31589-2026 FSC-klagomål mail.docx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34584-2025 FSC-klagomål mail.docx", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="AC85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31589-2026 tillsynsbegäran.docx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34584-2025 tillsynsbegäran.docx", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="AD85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31589-2026 tillsynsbegäran mail.docx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34584-2025 tillsynsbegäran mail.docx", "A 34584-2025")</f>
+        <v/>
+      </c>
+      <c r="AE85">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 34584-2025 prioriterade fågelarter.docx", "A 34584-2025")</f>
         <v/>
       </c>
     </row>
@@ -10575,7 +10575,7 @@
         <v>44509</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>44696</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>44782</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         <v>44550</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>44586</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>44582</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>44694</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>44518</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>44796</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 21509-2024</t>
+          <t>A 48205-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -11264,10 +11264,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45441</v>
+        <v>45205</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11281,11 +11281,11 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.9</v>
+        <v>7.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -11328,7 +11328,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 42832-2022</t>
+          <t>A 15743-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -11338,14 +11338,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44832</v>
+        <v>45021</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -11401,7 +11401,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 42841-2022</t>
+          <t>A 15637-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -11411,14 +11411,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44832</v>
+        <v>44662</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -11474,7 +11474,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 24158-2023</t>
+          <t>A 19786-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -11488,10 +11488,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45079</v>
+        <v>45050</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11505,11 +11505,11 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.1</v>
+        <v>8.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -11552,7 +11552,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 3818-2022</t>
+          <t>A 7787-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -11566,10 +11566,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44587</v>
+        <v>45348</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -11625,7 +11625,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 19782-2023</t>
+          <t>A 72367-2021</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -11639,10 +11639,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45050</v>
+        <v>44545</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11654,13 +11654,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -11703,7 +11698,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 10244-2026</t>
+          <t>A 33931-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -11717,10 +11712,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46076</v>
+        <v>44790</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11732,13 +11727,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>8.699999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -11781,7 +11771,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 10249-2026</t>
+          <t>A 24158-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -11795,10 +11785,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46076</v>
+        <v>45079</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11812,11 +11802,11 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -11859,7 +11849,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 10562-2026</t>
+          <t>A 42714-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -11873,10 +11863,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46077</v>
+        <v>44832</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11888,13 +11878,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -11937,7 +11922,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 14626-2023</t>
+          <t>A 35682-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -11951,10 +11936,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45012</v>
+        <v>44799</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11968,11 +11953,11 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -12015,7 +12000,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 56378-2023</t>
+          <t>A 11728-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -12025,14 +12010,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45236</v>
+        <v>44993</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12050,7 +12035,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>4.6</v>
+        <v>0.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -12093,7 +12078,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 12841-2026</t>
+          <t>A 5567-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -12107,10 +12092,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46091</v>
+        <v>44595</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12122,13 +12107,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -12171,7 +12151,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 11728-2023</t>
+          <t>A 42832-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -12181,14 +12161,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44993</v>
+        <v>44832</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12200,13 +12180,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -12249,7 +12224,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 20904-2023</t>
+          <t>A 24665-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -12259,14 +12234,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45060</v>
+        <v>45084</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12278,13 +12253,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -12327,7 +12297,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 42829-2022</t>
+          <t>A 42841-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -12344,7 +12314,7 @@
         <v>44832</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12357,7 +12327,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -12400,7 +12370,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 37954-2025</t>
+          <t>A 42829-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -12410,14 +12380,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45881</v>
+        <v>44832</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12430,7 +12400,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>9.5</v>
+        <v>1.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -12473,7 +12443,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 19246-2026</t>
+          <t>A 49058-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -12483,14 +12453,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46132</v>
+        <v>45594</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12508,7 +12478,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.5</v>
+        <v>11.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -12551,7 +12521,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 48205-2023</t>
+          <t>A 20535-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -12561,14 +12531,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45205</v>
+        <v>46140</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12582,11 +12552,11 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>7.6</v>
+        <v>2.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -12629,7 +12599,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 33931-2022</t>
+          <t>A 2867-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -12643,10 +12613,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44790</v>
+        <v>45315</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12658,8 +12628,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -12702,7 +12677,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 22662-2023</t>
+          <t>A 3085-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -12712,14 +12687,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45071</v>
+        <v>44946</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12733,11 +12708,11 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.6</v>
+        <v>13</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -12780,7 +12755,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 32808-2024</t>
+          <t>A 20904-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -12790,14 +12765,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45516</v>
+        <v>45060</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12811,11 +12786,11 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -12858,7 +12833,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 20535-2026</t>
+          <t>A 55873-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -12868,14 +12843,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46140</v>
+        <v>45973</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12889,11 +12864,11 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -12936,7 +12911,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 49058-2024</t>
+          <t>A 2660-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -12950,10 +12925,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45594</v>
+        <v>45310</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12965,13 +12940,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>11.4</v>
+        <v>2.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -13014,7 +12984,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 25450-2024</t>
+          <t>A 14626-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -13028,10 +12998,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45463</v>
+        <v>45012</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13049,7 +13019,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -13109,7 +13079,7 @@
         <v>46168</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13165,7 +13135,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 24665-2023</t>
+          <t>A 25450-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -13179,10 +13149,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45084</v>
+        <v>45463</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13194,8 +13164,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -13238,7 +13213,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 72367-2021</t>
+          <t>A 4724-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -13252,10 +13227,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44545</v>
+        <v>46048</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13268,7 +13243,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -13311,7 +13286,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 42714-2022</t>
+          <t>A 4734-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -13325,10 +13300,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44832</v>
+        <v>46048</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13341,7 +13316,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -13384,7 +13359,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 22628-2026</t>
+          <t>A 19782-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -13398,10 +13373,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46155</v>
+        <v>45050</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13415,11 +13390,11 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -13462,7 +13437,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 19099-2022</t>
+          <t>A 7848-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -13476,10 +13451,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44691</v>
+        <v>44608</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13491,13 +13466,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -13540,7 +13510,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 55873-2025</t>
+          <t>A 10249-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -13554,10 +13524,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45973</v>
+        <v>46076</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13571,11 +13541,11 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -13618,7 +13588,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 25780-2023</t>
+          <t>A 10244-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -13632,10 +13602,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45090</v>
+        <v>46076</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13647,8 +13617,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>2.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -13691,7 +13666,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 33933-2026</t>
+          <t>A 10562-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -13705,10 +13680,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46248</v>
+        <v>46077</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13722,11 +13697,11 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -13769,7 +13744,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 35682-2022</t>
+          <t>A 56378-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -13783,10 +13758,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44799</v>
+        <v>45236</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13800,11 +13775,11 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.5</v>
+        <v>4.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -13847,7 +13822,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 2867-2024</t>
+          <t>A 19099-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -13861,10 +13836,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45315</v>
+        <v>44691</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13878,11 +13853,11 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -13925,7 +13900,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 2660-2024</t>
+          <t>A 12841-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -13939,10 +13914,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45310</v>
+        <v>46091</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13954,8 +13929,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -13998,7 +13978,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 31061-2026</t>
+          <t>A 22628-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -14012,10 +13992,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46215</v>
+        <v>46155</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14033,7 +14013,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -14076,7 +14056,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 5567-2022</t>
+          <t>A 3818-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -14090,10 +14070,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44595</v>
+        <v>44587</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14106,7 +14086,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -14149,7 +14129,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 3085-2023</t>
+          <t>A 19246-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -14159,14 +14139,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44946</v>
+        <v>46132</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14180,11 +14160,11 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>13</v>
+        <v>1.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -14227,7 +14207,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 32223-2026</t>
+          <t>A 32808-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -14241,10 +14221,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46237</v>
+        <v>45516</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14258,11 +14238,11 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>8.199999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -14305,7 +14285,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 32501-2026</t>
+          <t>A 33933-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -14315,14 +14295,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46239</v>
+        <v>46248</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14334,8 +14314,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -14378,7 +14363,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 7848-2022</t>
+          <t>A 21509-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -14392,10 +14377,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44608</v>
+        <v>45441</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14407,8 +14392,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -14451,7 +14441,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 15743-2023</t>
+          <t>A 22662-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -14461,14 +14451,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45021</v>
+        <v>45071</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14480,8 +14470,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -14524,7 +14519,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 4724-2026</t>
+          <t>A 31061-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -14538,10 +14533,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46048</v>
+        <v>46215</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14553,8 +14548,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -14597,7 +14597,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 4734-2026</t>
+          <t>A 25780-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -14611,10 +14611,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46048</v>
+        <v>45090</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -14670,7 +14670,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 15637-2022</t>
+          <t>A 32501-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -14680,14 +14680,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44662</v>
+        <v>46239</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -14743,7 +14743,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 19786-2023</t>
+          <t>A 32223-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -14757,10 +14757,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45050</v>
+        <v>46237</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14774,11 +14774,11 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -14821,7 +14821,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 7787-2024</t>
+          <t>A 15739-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -14835,10 +14835,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45348</v>
+        <v>45021</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -14894,7 +14894,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 15739-2023</t>
+          <t>A 37954-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -14908,10 +14908,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45021</v>
+        <v>45881</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.3</v>
+        <v>9.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -14984,7 +14984,7 @@
         <v>44734</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>44734</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>46251</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>

--- a/Översikt SURAHAMMAR.xlsx
+++ b/Översikt SURAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45470</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>45684</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>45890</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>45504</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>45582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45169</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45139</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45782</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>45282</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>46216</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>46216</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>46237</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>44613</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>46085</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>45435</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>46215</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>46111</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>44832</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>45890</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45523</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>45070</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>44565</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>45574</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>46215</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>45435</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>44518</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>44477</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>45203</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>45072</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>46268</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>45545</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>45945</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>44518</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>46009</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>46076</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>44832</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>44832</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>45369</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>45503</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>45463</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>44518</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>45212</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>44832</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>45890</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>44532</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>45684</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
         <v>45205</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>46009</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>46248</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         <v>46268</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>46239</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>44635</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>45708</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>45708</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>45110</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>45236</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>45587</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
         <v>45895</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>46009</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>45174</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>44991</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>45007</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>45007</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>46268</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>45737</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>45874</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>45720</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8717,7 +8717,7 @@
         <v>44696</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>44739</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>44524</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>44696</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>45110</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         <v>44977</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>45156</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>44817</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>44680</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>44796</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>44991</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
         <v>45573</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10031,7 +10031,7 @@
         <v>45518</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         <v>45456</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>45026</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>46224</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10461,7 +10461,7 @@
         <v>45846</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10575,7 +10575,7 @@
         <v>44509</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>44696</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>44782</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         <v>44550</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>44586</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>44582</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>44694</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>44518</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>44796</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>45205</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>45021</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>44662</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>45050</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>45348</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>44545</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>44790</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>45079</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>44832</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>44799</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>44993</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>44595</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>44832</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>45084</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>44832</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>44832</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>45594</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>46140</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>45315</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>44946</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>45060</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>45973</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>45310</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>45012</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>46168</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>45463</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>46048</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>46048</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>45050</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>44608</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>46076</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>46076</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13683,7 +13683,7 @@
         <v>46077</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>45236</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13839,7 +13839,7 @@
         <v>44691</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>46091</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13995,7 +13995,7 @@
         <v>46155</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>44587</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
         <v>46132</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14224,7 +14224,7 @@
         <v>45516</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         <v>46248</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>45441</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>45071</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14536,7 +14536,7 @@
         <v>46215</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>45090</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14687,7 +14687,7 @@
         <v>46239</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>46237</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         <v>45021</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>45881</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>44734</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>44734</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>46251</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>

--- a/Översikt SURAHAMMAR.xlsx
+++ b/Översikt SURAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45470</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>45684</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,10 +834,10 @@
         <v>50</v>
       </c>
       <c r="T3" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="U3" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>45890</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>45504</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>45582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45169</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45139</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45782</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>45282</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>46216</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>46216</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>46237</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>44613</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>46085</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>45435</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>46215</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>46111</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 42853-2022</t>
+          <t>A 39594-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2953,14 +2953,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44832</v>
+        <v>45890</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2972,23 +2972,28 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J19" t="n">
+        <v>6</v>
+      </c>
+      <c r="K19" t="n">
         <v>3</v>
       </c>
-      <c r="K19" t="n">
-        <v>7</v>
-      </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2997,21 +3002,140 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>11</v>
       </c>
       <c r="T19" t="n">
+        <v>14</v>
+      </c>
+      <c r="U19" t="n">
+        <v>10</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Brunlångöra
+Dropptaggsvamp
+Gropticka
+Nordfladdermus
+Talltita
+Bronshjon
+Gullgröppa
+Vedticka
+Järpe
+Tjäder
+Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39594-2025 artfynd.xlsx", "A 39594-2025")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39594-2025 karta.png", "A 39594-2025")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39594-2025 georefererad karta.tif", "A 39594-2025")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39594-2025 FSC-klagomål.docx", "A 39594-2025")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39594-2025 FSC-klagomål mail.docx", "A 39594-2025")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39594-2025 tillsynsbegäran.docx", "A 39594-2025")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39594-2025 tillsynsbegäran mail.docx", "A 39594-2025")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39594-2025 prioriterade fågelarter.docx", "A 39594-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 42853-2022</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>44832</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>7</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>11</v>
+      </c>
+      <c r="T20" t="n">
         <v>15</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U20" t="n">
         <v>2</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Ask
 Kandelabersvamp
@@ -3026,160 +3150,36 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 42853-2022 artfynd.xlsx", "A 42853-2022")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 42853-2022 karta.png", "A 42853-2022")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 42853-2022 georefererad karta.tif", "A 42853-2022")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 42853-2022 FSC-klagomål.docx", "A 42853-2022")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 42853-2022 FSC-klagomål mail.docx", "A 42853-2022")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 42853-2022 tillsynsbegäran.docx", "A 42853-2022")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 42853-2022 tillsynsbegäran mail.docx", "A 42853-2022")</f>
         <v/>
       </c>
-      <c r="AE19">
+      <c r="AE20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 42853-2022 prioriterade fågelarter.docx", "A 42853-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 39594-2025</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45890</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>7</v>
-      </c>
-      <c r="J20" t="n">
-        <v>6</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3</v>
-      </c>
-      <c r="L20" t="n">
-        <v>5</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>5</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>11</v>
-      </c>
-      <c r="T20" t="n">
-        <v>14</v>
-      </c>
-      <c r="U20" t="n">
-        <v>10</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Brunlångöra
-Dropptaggsvamp
-Gropticka
-Nordfladdermus
-Talltita
-Bronshjon
-Gullgröppa
-Vedticka
-Järpe
-Tjäder
-Dvärgpipistrell</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39594-2025 artfynd.xlsx", "A 39594-2025")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39594-2025 karta.png", "A 39594-2025")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39594-2025 georefererad karta.tif", "A 39594-2025")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39594-2025 FSC-klagomål.docx", "A 39594-2025")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39594-2025 FSC-klagomål mail.docx", "A 39594-2025")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39594-2025 tillsynsbegäran.docx", "A 39594-2025")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39594-2025 tillsynsbegäran mail.docx", "A 39594-2025")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39594-2025 prioriterade fågelarter.docx", "A 39594-2025")</f>
         <v/>
       </c>
     </row>
@@ -3203,7 +3203,7 @@
         <v>45523</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>45070</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>44565</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 44798-2024</t>
+          <t>A 31060-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45574</v>
+        <v>46215</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3591,26 +3591,26 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3619,7 +3619,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -3628,12 +3628,134 @@
         <v>9</v>
       </c>
       <c r="T24" t="n">
+        <v>9</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Bombmurkla
+Brunlångöra
+Nordfladdermus
+Springkorn
+Vedticka
+Spillkråka
+Dvärgpipistrell
+Åkergroda
+Vanlig groda</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31060-2026 artfynd.xlsx", "A 31060-2026")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31060-2026 karta.png", "A 31060-2026")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31060-2026 georefererad karta.tif", "A 31060-2026")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31060-2026 FSC-klagomål.docx", "A 31060-2026")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31060-2026 FSC-klagomål mail.docx", "A 31060-2026")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31060-2026 tillsynsbegäran.docx", "A 31060-2026")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31060-2026 tillsynsbegäran mail.docx", "A 31060-2026")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 31060-2026 prioriterade fågelarter.docx", "A 31060-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 44798-2024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>45574</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>7</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>8</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>9</v>
+      </c>
+      <c r="T25" t="n">
         <v>26</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U25" t="n">
         <v>10</v>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Rosetticka
 Brunklöver
@@ -3646,154 +3768,32 @@
 Brandticka</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 44798-2024 artfynd.xlsx", "A 44798-2024")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 44798-2024 karta.png", "A 44798-2024")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 44798-2024 georefererad karta.tif", "A 44798-2024")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 44798-2024 FSC-klagomål.docx", "A 44798-2024")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 44798-2024 FSC-klagomål mail.docx", "A 44798-2024")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 44798-2024 tillsynsbegäran.docx", "A 44798-2024")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 44798-2024 tillsynsbegäran mail.docx", "A 44798-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 31060-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>46215</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J25" t="n">
-        <v>7</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2</v>
-      </c>
-      <c r="L25" t="n">
-        <v>2</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S25" t="n">
-        <v>9</v>
-      </c>
-      <c r="T25" t="n">
-        <v>9</v>
-      </c>
-      <c r="U25" t="n">
-        <v>3</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Bombmurkla
-Brunlångöra
-Nordfladdermus
-Springkorn
-Vedticka
-Spillkråka
-Dvärgpipistrell
-Åkergroda
-Vanlig groda</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31060-2026 artfynd.xlsx", "A 31060-2026")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31060-2026 karta.png", "A 31060-2026")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31060-2026 georefererad karta.tif", "A 31060-2026")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31060-2026 FSC-klagomål.docx", "A 31060-2026")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31060-2026 FSC-klagomål mail.docx", "A 31060-2026")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31060-2026 tillsynsbegäran.docx", "A 31060-2026")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31060-2026 tillsynsbegäran mail.docx", "A 31060-2026")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 31060-2026 prioriterade fågelarter.docx", "A 31060-2026")</f>
         <v/>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
         <v>45435</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>44518</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>44477</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>45203</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>45072</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>46268</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>45545</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>45945</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>44518</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>46009</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>46076</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>44832</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>44832</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>45369</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>45503</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>45463</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>44518</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>45212</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 42765-2022</t>
+          <t>A 39694-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5908,14 +5908,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44832</v>
+        <v>45890</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5927,8 +5927,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
@@ -5961,167 +5966,162 @@
         <v>3</v>
       </c>
       <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Mindre märgborre
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39694-2025 artfynd.xlsx", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="X44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39694-2025 karta.png", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="Y44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39694-2025 georefererad karta.tif", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="AA44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39694-2025 FSC-klagomål.docx", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="AB44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39694-2025 FSC-klagomål mail.docx", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="AC44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39694-2025 tillsynsbegäran.docx", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="AD44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39694-2025 tillsynsbegäran mail.docx", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="AE44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39694-2025 prioriterade fågelarter.docx", "A 39694-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>A 42765-2022</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>44832</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3</v>
+      </c>
+      <c r="T45" t="n">
         <v>4</v>
       </c>
-      <c r="U44" t="n">
-        <v>1</v>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
+      <c r="U45" t="n">
+        <v>1</v>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
         <is>
           <t>Krusfrö
 Barkticka
 Blåsippa</t>
         </is>
       </c>
-      <c r="W44">
+      <c r="W45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 42765-2022 artfynd.xlsx", "A 42765-2022")</f>
         <v/>
       </c>
-      <c r="X44">
+      <c r="X45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 42765-2022 karta.png", "A 42765-2022")</f>
         <v/>
       </c>
-      <c r="Y44">
+      <c r="Y45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 42765-2022 georefererad karta.tif", "A 42765-2022")</f>
         <v/>
       </c>
-      <c r="AA44">
+      <c r="AA45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 42765-2022 FSC-klagomål.docx", "A 42765-2022")</f>
         <v/>
       </c>
-      <c r="AB44">
+      <c r="AB45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 42765-2022 FSC-klagomål mail.docx", "A 42765-2022")</f>
         <v/>
       </c>
-      <c r="AC44">
+      <c r="AC45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 42765-2022 tillsynsbegäran.docx", "A 42765-2022")</f>
         <v/>
       </c>
-      <c r="AD44">
+      <c r="AD45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 42765-2022 tillsynsbegäran mail.docx", "A 42765-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>A 39694-2025</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="n">
-        <v>45890</v>
-      </c>
-      <c r="E45" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J45" t="n">
-        <v>1</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1</v>
-      </c>
-      <c r="L45" t="n">
-        <v>1</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>1</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>3</v>
-      </c>
-      <c r="T45" t="n">
-        <v>3</v>
-      </c>
-      <c r="U45" t="n">
-        <v>2</v>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Mindre märgborre
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39694-2025 artfynd.xlsx", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39694-2025 karta.png", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39694-2025 georefererad karta.tif", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39694-2025 FSC-klagomål.docx", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39694-2025 FSC-klagomål mail.docx", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39694-2025 tillsynsbegäran.docx", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39694-2025 tillsynsbegäran mail.docx", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="AE45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39694-2025 prioriterade fågelarter.docx", "A 39694-2025")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 69777-2021</t>
+          <t>A 4082-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6135,10 +6135,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44532</v>
+        <v>45684</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6150,11 +6150,16 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>2.3</v>
+        <v>11.6</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K46" t="n">
         <v>2</v>
@@ -6166,7 +6171,7 @@
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6175,277 +6180,272 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>3</v>
       </c>
       <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>Grönpyrola
+Plattlummer
+Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="W46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 4082-2025 artfynd.xlsx", "A 4082-2025")</f>
+        <v/>
+      </c>
+      <c r="X46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 4082-2025 karta.png", "A 4082-2025")</f>
+        <v/>
+      </c>
+      <c r="Y46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 4082-2025 georefererad karta.tif", "A 4082-2025")</f>
+        <v/>
+      </c>
+      <c r="AA46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 4082-2025 FSC-klagomål.docx", "A 4082-2025")</f>
+        <v/>
+      </c>
+      <c r="AB46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 4082-2025 FSC-klagomål mail.docx", "A 4082-2025")</f>
+        <v/>
+      </c>
+      <c r="AC46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 4082-2025 tillsynsbegäran.docx", "A 4082-2025")</f>
+        <v/>
+      </c>
+      <c r="AD46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 4082-2025 tillsynsbegäran mail.docx", "A 4082-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>A 48128-2023</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>45205</v>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" t="n">
+        <v>2</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>2</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>Jungfrulin
+Svinrot
+Vedticka</t>
+        </is>
+      </c>
+      <c r="W47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 48128-2023 artfynd.xlsx", "A 48128-2023")</f>
+        <v/>
+      </c>
+      <c r="X47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 48128-2023 karta.png", "A 48128-2023")</f>
+        <v/>
+      </c>
+      <c r="Y47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 48128-2023 georefererad karta.tif", "A 48128-2023")</f>
+        <v/>
+      </c>
+      <c r="AA47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 48128-2023 FSC-klagomål.docx", "A 48128-2023")</f>
+        <v/>
+      </c>
+      <c r="AB47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 48128-2023 FSC-klagomål mail.docx", "A 48128-2023")</f>
+        <v/>
+      </c>
+      <c r="AC47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 48128-2023 tillsynsbegäran.docx", "A 48128-2023")</f>
+        <v/>
+      </c>
+      <c r="AD47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 48128-2023 tillsynsbegäran mail.docx", "A 48128-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>A 69777-2021</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D48" s="1" t="n">
+        <v>44532</v>
+      </c>
+      <c r="E48" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
+        <v>2</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1</v>
+      </c>
+      <c r="S48" t="n">
+        <v>3</v>
+      </c>
+      <c r="T48" t="n">
         <v>5</v>
       </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
         <is>
           <t>Bombmurkla
 Rävticka
 Vedticka</t>
         </is>
       </c>
-      <c r="W46">
+      <c r="W48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 69777-2021 artfynd.xlsx", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="X46">
+      <c r="X48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 69777-2021 karta.png", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="Y46">
+      <c r="Y48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 69777-2021 georefererad karta.tif", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="AA46">
+      <c r="AA48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 69777-2021 FSC-klagomål.docx", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="AB46">
+      <c r="AB48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 69777-2021 FSC-klagomål mail.docx", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="AC46">
+      <c r="AC48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 69777-2021 tillsynsbegäran.docx", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="AD46">
+      <c r="AD48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 69777-2021 tillsynsbegäran mail.docx", "A 69777-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>A 4082-2025</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="n">
-        <v>45684</v>
-      </c>
-      <c r="E47" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="J47" t="n">
-        <v>2</v>
-      </c>
-      <c r="K47" t="n">
-        <v>2</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>3</v>
-      </c>
-      <c r="T47" t="n">
-        <v>3</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1</v>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>Grönpyrola
-Plattlummer
-Lopplummer (aggregat)</t>
-        </is>
-      </c>
-      <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 4082-2025 artfynd.xlsx", "A 4082-2025")</f>
-        <v/>
-      </c>
-      <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 4082-2025 karta.png", "A 4082-2025")</f>
-        <v/>
-      </c>
-      <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 4082-2025 georefererad karta.tif", "A 4082-2025")</f>
-        <v/>
-      </c>
-      <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 4082-2025 FSC-klagomål.docx", "A 4082-2025")</f>
-        <v/>
-      </c>
-      <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 4082-2025 FSC-klagomål mail.docx", "A 4082-2025")</f>
-        <v/>
-      </c>
-      <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 4082-2025 tillsynsbegäran.docx", "A 4082-2025")</f>
-        <v/>
-      </c>
-      <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 4082-2025 tillsynsbegäran mail.docx", "A 4082-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>A 48128-2023</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="n">
-        <v>45205</v>
-      </c>
-      <c r="E48" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>1</v>
-      </c>
-      <c r="L48" t="n">
-        <v>2</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>2</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>3</v>
-      </c>
-      <c r="T48" t="n">
-        <v>3</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>Jungfrulin
-Svinrot
-Vedticka</t>
-        </is>
-      </c>
-      <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 48128-2023 artfynd.xlsx", "A 48128-2023")</f>
-        <v/>
-      </c>
-      <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 48128-2023 karta.png", "A 48128-2023")</f>
-        <v/>
-      </c>
-      <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 48128-2023 georefererad karta.tif", "A 48128-2023")</f>
-        <v/>
-      </c>
-      <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 48128-2023 FSC-klagomål.docx", "A 48128-2023")</f>
-        <v/>
-      </c>
-      <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 48128-2023 FSC-klagomål mail.docx", "A 48128-2023")</f>
-        <v/>
-      </c>
-      <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 48128-2023 tillsynsbegäran.docx", "A 48128-2023")</f>
-        <v/>
-      </c>
-      <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 48128-2023 tillsynsbegäran mail.docx", "A 48128-2023")</f>
         <v/>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
         <v>46009</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>46248</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         <v>46268</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>46239</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>44635</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>45708</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>45708</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>45110</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 56362-2023</t>
+          <t>A 47453-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45236</v>
+        <v>45587</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7396,25 +7396,20 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>15.2</v>
+        <v>5.1</v>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
         <v>0</v>
@@ -7429,7 +7424,7 @@
         <v>1</v>
       </c>
       <c r="R57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>2</v>
@@ -7442,43 +7437,47 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>Väddnätfjäril
-Grönpyrola</t>
+          <t>Göktyta
+Gröngöling</t>
         </is>
       </c>
       <c r="W57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 56362-2023 artfynd.xlsx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 47453-2024 artfynd.xlsx", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="X57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 56362-2023 karta.png", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 47453-2024 karta.png", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="Y57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 56362-2023 georefererad karta.tif", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 47453-2024 georefererad karta.tif", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="AA57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 56362-2023 FSC-klagomål.docx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 47453-2024 FSC-klagomål.docx", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="AB57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 56362-2023 FSC-klagomål mail.docx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 47453-2024 FSC-klagomål mail.docx", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="AC57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 56362-2023 tillsynsbegäran.docx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 47453-2024 tillsynsbegäran.docx", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="AD57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 56362-2023 tillsynsbegäran mail.docx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 47453-2024 tillsynsbegäran mail.docx", "A 47453-2024")</f>
+        <v/>
+      </c>
+      <c r="AE57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 47453-2024 prioriterade fågelarter.docx", "A 47453-2024")</f>
         <v/>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 47453-2024</t>
+          <t>A 56362-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7492,10 +7491,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45587</v>
+        <v>45236</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7507,20 +7506,25 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>5.1</v>
+        <v>15.2</v>
       </c>
       <c r="J58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N58" t="n">
         <v>0</v>
@@ -7535,7 +7539,7 @@
         <v>1</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S58" t="n">
         <v>2</v>
@@ -7548,47 +7552,43 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>Göktyta
-Gröngöling</t>
+          <t>Väddnätfjäril
+Grönpyrola</t>
         </is>
       </c>
       <c r="W58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 47453-2024 artfynd.xlsx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 56362-2023 artfynd.xlsx", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="X58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 47453-2024 karta.png", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 56362-2023 karta.png", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="Y58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 47453-2024 georefererad karta.tif", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 56362-2023 georefererad karta.tif", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="AA58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 47453-2024 FSC-klagomål.docx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 56362-2023 FSC-klagomål.docx", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="AB58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 47453-2024 FSC-klagomål mail.docx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 56362-2023 FSC-klagomål mail.docx", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="AC58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 47453-2024 tillsynsbegäran.docx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 56362-2023 tillsynsbegäran.docx", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="AD58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 47453-2024 tillsynsbegäran mail.docx", "A 47453-2024")</f>
-        <v/>
-      </c>
-      <c r="AE58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 47453-2024 prioriterade fågelarter.docx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 56362-2023 tillsynsbegäran mail.docx", "A 56362-2023")</f>
         <v/>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 40403-2025</t>
+          <t>A 37013-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45895</v>
+        <v>45874</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7619,14 +7619,14 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.9</v>
+        <v>10.7</v>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -7635,7 +7635,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
@@ -7647,59 +7647,59 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S59" t="n">
         <v>2</v>
       </c>
       <c r="T59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>Igelkott
-Gröngöling</t>
+          <t>Brunfläckig pärlemorfjäril
+Fältgentiana</t>
         </is>
       </c>
       <c r="W59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 40403-2025 artfynd.xlsx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37013-2025 artfynd.xlsx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="X59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 40403-2025 karta.png", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37013-2025 karta.png", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="Y59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 40403-2025 georefererad karta.tif", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37013-2025 georefererad karta.tif", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AA59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 40403-2025 FSC-klagomål.docx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37013-2025 FSC-klagomål.docx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AB59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 40403-2025 FSC-klagomål mail.docx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37013-2025 FSC-klagomål mail.docx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AC59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 40403-2025 tillsynsbegäran.docx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37013-2025 tillsynsbegäran.docx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AD59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 40403-2025 tillsynsbegäran mail.docx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37013-2025 tillsynsbegäran mail.docx", "A 37013-2025")</f>
         <v/>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 63138-2025</t>
+          <t>A 40403-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7713,10 +7713,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46009</v>
+        <v>45895</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7730,23 +7730,23 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="J60" t="n">
         <v>1</v>
       </c>
       <c r="K60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N60" t="n">
         <v>0</v>
@@ -7758,10 +7758,10 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S60" t="n">
         <v>2</v>
@@ -7770,51 +7770,47 @@
         <v>3</v>
       </c>
       <c r="U60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>Mindre märgborre
-Tjäder</t>
+          <t>Igelkott
+Gröngöling</t>
         </is>
       </c>
       <c r="W60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63138-2025 artfynd.xlsx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 40403-2025 artfynd.xlsx", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="X60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63138-2025 karta.png", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 40403-2025 karta.png", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="Y60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63138-2025 georefererad karta.tif", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 40403-2025 georefererad karta.tif", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="AA60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63138-2025 FSC-klagomål.docx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 40403-2025 FSC-klagomål.docx", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="AB60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63138-2025 FSC-klagomål mail.docx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 40403-2025 FSC-klagomål mail.docx", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="AC60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63138-2025 tillsynsbegäran.docx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 40403-2025 tillsynsbegäran.docx", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="AD60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63138-2025 tillsynsbegäran mail.docx", "A 63138-2025")</f>
-        <v/>
-      </c>
-      <c r="AE60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 63138-2025 prioriterade fågelarter.docx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 40403-2025 tillsynsbegäran mail.docx", "A 40403-2025")</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 41204-2023</t>
+          <t>A 63138-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7828,10 +7824,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45174</v>
+        <v>46009</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7843,20 +7839,25 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J61" t="n">
         <v>1</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
@@ -7868,63 +7869,63 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>2</v>
       </c>
       <c r="T61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>Knärot
-Vedtrappmossa</t>
+          <t>Mindre märgborre
+Tjäder</t>
         </is>
       </c>
       <c r="W61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 41204-2023 artfynd.xlsx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63138-2025 artfynd.xlsx", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="X61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 41204-2023 karta.png", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63138-2025 karta.png", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="Y61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 41204-2023 georefererad karta.tif", "A 41204-2023")</f>
-        <v/>
-      </c>
-      <c r="Z61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 41204-2023 karta knärot.png", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63138-2025 georefererad karta.tif", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="AA61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 41204-2023 FSC-klagomål.docx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63138-2025 FSC-klagomål.docx", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="AB61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 41204-2023 FSC-klagomål mail.docx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63138-2025 FSC-klagomål mail.docx", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="AC61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 41204-2023 tillsynsbegäran.docx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63138-2025 tillsynsbegäran.docx", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="AD61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 41204-2023 tillsynsbegäran mail.docx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63138-2025 tillsynsbegäran mail.docx", "A 63138-2025")</f>
+        <v/>
+      </c>
+      <c r="AE61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 63138-2025 prioriterade fågelarter.docx", "A 63138-2025")</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 11501-2023</t>
+          <t>A 41204-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7938,10 +7939,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44991</v>
+        <v>45174</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7953,25 +7954,20 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>1</v>
       </c>
       <c r="K62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N62" t="n">
         <v>0</v>
@@ -7983,59 +7979,63 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S62" t="n">
         <v>2</v>
       </c>
       <c r="T62" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva
-Nattviol</t>
+          <t>Knärot
+Vedtrappmossa</t>
         </is>
       </c>
       <c r="W62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 11501-2023 artfynd.xlsx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 41204-2023 artfynd.xlsx", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="X62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 11501-2023 karta.png", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 41204-2023 karta.png", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="Y62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 11501-2023 georefererad karta.tif", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 41204-2023 georefererad karta.tif", "A 41204-2023")</f>
+        <v/>
+      </c>
+      <c r="Z62">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 41204-2023 karta knärot.png", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="AA62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 11501-2023 FSC-klagomål.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 41204-2023 FSC-klagomål.docx", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="AB62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 11501-2023 FSC-klagomål mail.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 41204-2023 FSC-klagomål mail.docx", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="AC62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 11501-2023 tillsynsbegäran.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 41204-2023 tillsynsbegäran.docx", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="AD62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 11501-2023 tillsynsbegäran mail.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 41204-2023 tillsynsbegäran mail.docx", "A 41204-2023")</f>
         <v/>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 14001-2023</t>
+          <t>A 11501-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -8049,10 +8049,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45007</v>
+        <v>44991</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8070,19 +8070,19 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
@@ -8094,10 +8094,10 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>2</v>
@@ -8106,47 +8106,47 @@
         <v>2</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>Garnlav
-Motaggsvamp</t>
+          <t>Svart trolldruva
+Nattviol</t>
         </is>
       </c>
       <c r="W63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 14001-2023 artfynd.xlsx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 11501-2023 artfynd.xlsx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="X63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 14001-2023 karta.png", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 11501-2023 karta.png", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="Y63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 14001-2023 georefererad karta.tif", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 11501-2023 georefererad karta.tif", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AA63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 14001-2023 FSC-klagomål.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 11501-2023 FSC-klagomål.docx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AB63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 14001-2023 FSC-klagomål mail.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 11501-2023 FSC-klagomål mail.docx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AC63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 14001-2023 tillsynsbegäran.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 11501-2023 tillsynsbegäran.docx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AD63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 14001-2023 tillsynsbegäran mail.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 11501-2023 tillsynsbegäran mail.docx", "A 11501-2023")</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 13971-2023</t>
+          <t>A 14001-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -8163,7 +8163,7 @@
         <v>45007</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8181,76 +8181,76 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>1</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
         <v>2</v>
       </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S64" t="n">
         <v>2</v>
       </c>
       <c r="T64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U64" t="n">
         <v>0</v>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>Dubbelnycklar
-Fläcknycklar</t>
+          <t>Garnlav
+Motaggsvamp</t>
         </is>
       </c>
       <c r="W64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 13971-2023 artfynd.xlsx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 14001-2023 artfynd.xlsx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="X64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 13971-2023 karta.png", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 14001-2023 karta.png", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="Y64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 13971-2023 georefererad karta.tif", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 14001-2023 georefererad karta.tif", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AA64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 13971-2023 FSC-klagomål.docx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 14001-2023 FSC-klagomål.docx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AB64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 13971-2023 FSC-klagomål mail.docx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 14001-2023 FSC-klagomål mail.docx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AC64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 13971-2023 tillsynsbegäran.docx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 14001-2023 tillsynsbegäran.docx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AD64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 13971-2023 tillsynsbegäran mail.docx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 14001-2023 tillsynsbegäran mail.docx", "A 14001-2023")</f>
         <v/>
       </c>
     </row>
@@ -8274,7 +8274,7 @@
         <v>46268</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 13788-2025</t>
+          <t>A 13971-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -8382,10 +8382,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45737</v>
+        <v>45007</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8397,8 +8397,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>9.699999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="J66" t="n">
         <v>2</v>
@@ -8407,7 +8412,7 @@
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -8422,7 +8427,7 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
@@ -8431,54 +8436,50 @@
         <v>2</v>
       </c>
       <c r="T66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>Sparvuggla
-Nattskärra</t>
+          <t>Dubbelnycklar
+Fläcknycklar</t>
         </is>
       </c>
       <c r="W66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 13788-2025 artfynd.xlsx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 13971-2023 artfynd.xlsx", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="X66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 13788-2025 karta.png", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 13971-2023 karta.png", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="Y66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 13788-2025 georefererad karta.tif", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 13971-2023 georefererad karta.tif", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="AA66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 13788-2025 FSC-klagomål.docx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 13971-2023 FSC-klagomål.docx", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="AB66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 13788-2025 FSC-klagomål mail.docx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 13971-2023 FSC-klagomål mail.docx", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="AC66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 13788-2025 tillsynsbegäran.docx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 13971-2023 tillsynsbegäran.docx", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="AD66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 13788-2025 tillsynsbegäran mail.docx", "A 13788-2025")</f>
-        <v/>
-      </c>
-      <c r="AE66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 13788-2025 prioriterade fågelarter.docx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 13971-2023 tillsynsbegäran mail.docx", "A 13971-2023")</f>
         <v/>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 37013-2025</t>
+          <t>A 13788-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -8492,10 +8493,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45874</v>
+        <v>45737</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8507,25 +8508,20 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>10.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
         <v>0</v>
@@ -8537,10 +8533,10 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>2</v>
@@ -8549,40 +8545,44 @@
         <v>2</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril
-Fältgentiana</t>
+          <t>Sparvuggla
+Nattskärra</t>
         </is>
       </c>
       <c r="W67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37013-2025 artfynd.xlsx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 13788-2025 artfynd.xlsx", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="X67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37013-2025 karta.png", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 13788-2025 karta.png", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="Y67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37013-2025 georefererad karta.tif", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 13788-2025 georefererad karta.tif", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="AA67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37013-2025 FSC-klagomål.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 13788-2025 FSC-klagomål.docx", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="AB67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37013-2025 FSC-klagomål mail.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 13788-2025 FSC-klagomål mail.docx", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="AC67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37013-2025 tillsynsbegäran.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 13788-2025 tillsynsbegäran.docx", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="AD67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37013-2025 tillsynsbegäran mail.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 13788-2025 tillsynsbegäran mail.docx", "A 13788-2025")</f>
+        <v/>
+      </c>
+      <c r="AE67">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 13788-2025 prioriterade fågelarter.docx", "A 13788-2025")</f>
         <v/>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
         <v>45720</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8717,7 +8717,7 @@
         <v>44696</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>44739</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>44524</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>44696</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>45110</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         <v>44977</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>45156</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>44817</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>44680</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>44796</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>44991</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
         <v>45573</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10031,7 +10031,7 @@
         <v>45518</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         <v>45456</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 16013-2023</t>
+          <t>A 31589-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -10243,10 +10243,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45026</v>
+        <v>46224</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10258,20 +10258,25 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
         <v>0</v>
@@ -10283,10 +10288,10 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>1</v>
@@ -10299,42 +10304,42 @@
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 16013-2023 artfynd.xlsx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31589-2026 artfynd.xlsx", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="X83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 16013-2023 karta.png", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31589-2026 karta.png", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="Y83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 16013-2023 georefererad karta.tif", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31589-2026 georefererad karta.tif", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="AA83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 16013-2023 FSC-klagomål.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31589-2026 FSC-klagomål.docx", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="AB83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 16013-2023 FSC-klagomål mail.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31589-2026 FSC-klagomål mail.docx", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="AC83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 16013-2023 tillsynsbegäran.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31589-2026 tillsynsbegäran.docx", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="AD83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 16013-2023 tillsynsbegäran mail.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31589-2026 tillsynsbegäran mail.docx", "A 31589-2026")</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 31589-2026</t>
+          <t>A 16013-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -10348,10 +10353,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46224</v>
+        <v>45026</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10363,25 +10368,20 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>7</v>
+        <v>3.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N84" t="n">
         <v>0</v>
@@ -10393,10 +10393,10 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S84" t="n">
         <v>1</v>
@@ -10409,35 +10409,35 @@
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="W84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31589-2026 artfynd.xlsx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 16013-2023 artfynd.xlsx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="X84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31589-2026 karta.png", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 16013-2023 karta.png", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="Y84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31589-2026 georefererad karta.tif", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 16013-2023 georefererad karta.tif", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AA84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31589-2026 FSC-klagomål.docx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 16013-2023 FSC-klagomål.docx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AB84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31589-2026 FSC-klagomål mail.docx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 16013-2023 FSC-klagomål mail.docx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AC84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31589-2026 tillsynsbegäran.docx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 16013-2023 tillsynsbegäran.docx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AD84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31589-2026 tillsynsbegäran mail.docx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 16013-2023 tillsynsbegäran mail.docx", "A 16013-2023")</f>
         <v/>
       </c>
     </row>
@@ -10461,7 +10461,7 @@
         <v>45846</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10575,7 +10575,7 @@
         <v>44509</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>44696</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>44782</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         <v>44550</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>44586</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>44582</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>44694</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>44518</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>44796</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>45205</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>45021</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>44662</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>45050</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>45348</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>44545</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>44790</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>45079</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 42714-2022</t>
+          <t>A 37954-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -11863,10 +11863,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44832</v>
+        <v>45881</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.1</v>
+        <v>9.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -11922,7 +11922,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 35682-2022</t>
+          <t>A 32808-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -11936,10 +11936,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44799</v>
+        <v>45516</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11953,11 +11953,11 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -12000,7 +12000,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 11728-2023</t>
+          <t>A 42714-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -12010,14 +12010,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44993</v>
+        <v>44832</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12029,13 +12029,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -12078,7 +12073,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 5567-2022</t>
+          <t>A 35682-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -12092,10 +12087,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44595</v>
+        <v>44799</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12107,8 +12102,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -12151,7 +12151,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 42832-2022</t>
+          <t>A 11728-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -12161,14 +12161,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44832</v>
+        <v>44993</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12180,8 +12180,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -12224,7 +12229,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 24665-2023</t>
+          <t>A 5567-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -12238,10 +12243,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45084</v>
+        <v>44595</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12254,7 +12259,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -12297,7 +12302,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 42841-2022</t>
+          <t>A 42832-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -12314,7 +12319,7 @@
         <v>44832</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12327,7 +12332,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -12370,7 +12375,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 42829-2022</t>
+          <t>A 49058-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -12380,14 +12385,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44832</v>
+        <v>45594</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12399,8 +12404,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>1.6</v>
+        <v>11.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -12443,7 +12453,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 49058-2024</t>
+          <t>A 24665-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -12457,10 +12467,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45594</v>
+        <v>45084</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12472,13 +12482,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>11.4</v>
+        <v>0.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -12538,7 +12543,7 @@
         <v>46140</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12599,7 +12604,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 2867-2024</t>
+          <t>A 42841-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -12609,14 +12614,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45315</v>
+        <v>44832</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12628,13 +12633,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -12677,7 +12677,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 3085-2023</t>
+          <t>A 42829-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -12687,14 +12687,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44946</v>
+        <v>44832</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12706,13 +12706,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>13</v>
+        <v>1.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -12755,7 +12750,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 20904-2023</t>
+          <t>A 2867-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -12765,14 +12760,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45060</v>
+        <v>45315</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12786,11 +12781,11 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -12833,7 +12828,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 55873-2025</t>
+          <t>A 3085-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -12847,10 +12842,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45973</v>
+        <v>44946</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12864,11 +12859,11 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.5</v>
+        <v>13</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -12911,7 +12906,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 2660-2024</t>
+          <t>A 55873-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -12925,10 +12920,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45310</v>
+        <v>45973</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12940,8 +12935,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -12984,7 +12984,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 14626-2023</t>
+          <t>A 24201-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -12998,10 +12998,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45012</v>
+        <v>46168</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13013,13 +13013,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -13062,7 +13057,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 24201-2026</t>
+          <t>A 20904-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -13072,14 +13067,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46168</v>
+        <v>45060</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13091,8 +13086,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -13135,7 +13135,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 25450-2024</t>
+          <t>A 2660-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -13149,10 +13149,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45463</v>
+        <v>45310</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13164,13 +13164,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -13230,7 +13225,7 @@
         <v>46048</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13303,7 +13298,7 @@
         <v>46048</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13359,7 +13354,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 19782-2023</t>
+          <t>A 22628-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -13373,10 +13368,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45050</v>
+        <v>46155</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13390,11 +13385,11 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -13437,7 +13432,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 7848-2022</t>
+          <t>A 14626-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -13451,10 +13446,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44608</v>
+        <v>45012</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13466,8 +13461,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -13527,7 +13527,7 @@
         <v>46076</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>46076</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13683,7 +13683,7 @@
         <v>46077</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 56378-2023</t>
+          <t>A 12841-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -13758,10 +13758,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45236</v>
+        <v>46091</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -13822,7 +13822,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 19099-2022</t>
+          <t>A 25450-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -13836,10 +13836,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44691</v>
+        <v>45463</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13853,11 +13853,11 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -13900,7 +13900,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 12841-2026</t>
+          <t>A 19782-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -13914,10 +13914,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46091</v>
+        <v>45050</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13935,7 +13935,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -13978,7 +13978,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 22628-2026</t>
+          <t>A 19246-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -13988,14 +13988,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46155</v>
+        <v>46132</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -14056,7 +14056,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 3818-2022</t>
+          <t>A 7848-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -14070,10 +14070,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44587</v>
+        <v>44608</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14086,7 +14086,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -14129,7 +14129,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 19246-2026</t>
+          <t>A 56378-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -14139,14 +14139,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46132</v>
+        <v>45236</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14160,11 +14160,11 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.5</v>
+        <v>4.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -14207,7 +14207,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 32808-2024</t>
+          <t>A 19099-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -14221,10 +14221,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45516</v>
+        <v>44691</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -14302,7 +14302,7 @@
         <v>46248</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 21509-2024</t>
+          <t>A 31061-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -14377,10 +14377,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45441</v>
+        <v>46215</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14394,11 +14394,11 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -14441,7 +14441,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 22662-2023</t>
+          <t>A 3818-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -14451,14 +14451,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45071</v>
+        <v>44587</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14470,13 +14470,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -14519,7 +14514,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 31061-2026</t>
+          <t>A 21509-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -14533,10 +14528,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46215</v>
+        <v>45441</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14550,11 +14545,11 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -14597,7 +14592,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 25780-2023</t>
+          <t>A 32501-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -14607,14 +14602,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45090</v>
+        <v>46239</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14627,7 +14622,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -14670,7 +14665,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 32501-2026</t>
+          <t>A 32223-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -14680,14 +14675,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46239</v>
+        <v>46237</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14699,8 +14694,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>1.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -14743,7 +14743,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 32223-2026</t>
+          <t>A 22662-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -14753,14 +14753,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46237</v>
+        <v>45071</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14774,11 +14774,11 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>8.199999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -14821,7 +14821,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 15739-2023</t>
+          <t>A 25780-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -14835,10 +14835,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45021</v>
+        <v>45090</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -14894,7 +14894,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 37954-2025</t>
+          <t>A 15739-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -14908,10 +14908,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45881</v>
+        <v>45021</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>9.5</v>
+        <v>1.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -14984,7 +14984,7 @@
         <v>44734</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>44734</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>46251</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>

--- a/Översikt SURAHAMMAR.xlsx
+++ b/Översikt SURAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45470</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>45684</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 39697-2025</t>
+          <t>A 31280-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45890</v>
+        <v>45504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,23 +964,23 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>25.7</v>
+        <v>6.9</v>
       </c>
       <c r="J4" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -992,21 +992,182 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S4" t="n">
         <v>44</v>
       </c>
       <c r="T4" t="n">
+        <v>93</v>
+      </c>
+      <c r="U4" t="n">
+        <v>91</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Gränsticka
+Knärot
+Liten hornflikmossa
+Spadskinn
+Torrmusseron
+Apelsinticka
+Fjällig taggsvamp s.str.
+Grantaggsvamp
+Gropticka
+Kattfotslav
+Knölspindel
+Kötticka
+Mjölsvärting
+Nordfladdermus
+Nordtagging
+Persiljespindling
+Rynkskinn
+Skarp dropptaggsvamp
+Svartvit taggsvamp
+Tallkötticka
+Tallticka
+Talltita
+Ullticka
+Vaddporing
+Vedskivlav
+Vedtrappmossa
+Vågticka
+Bollvitmossa
+Bronshjon
+Flagellkvastmossa
+Grönpyrola
+Kornknutmossa
+Mindre märgborre
+Rostfläck
+Rödgul trumpetsvamp
+Smal svampklubba
+Thomsons trägnagare
+Vedticka
+Vågbandad barkbock
+Blåsippa
+Kungsfågel
+Mindre vattensalamander
+Fläcknycklar
+Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31280-2024 artfynd.xlsx", "A 31280-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31280-2024 karta.png", "A 31280-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31280-2024 georefererad karta.tif", "A 31280-2024")</f>
+        <v/>
+      </c>
+      <c r="Z4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 31280-2024 karta knärot.png", "A 31280-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31280-2024 FSC-klagomål.docx", "A 31280-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31280-2024 FSC-klagomål mail.docx", "A 31280-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31280-2024 tillsynsbegäran.docx", "A 31280-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31280-2024 tillsynsbegäran mail.docx", "A 31280-2024")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 31280-2024 prioriterade fågelarter.docx", "A 31280-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 39697-2025</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45890</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>28</v>
+      </c>
+      <c r="K5" t="n">
+        <v>7</v>
+      </c>
+      <c r="L5" t="n">
+        <v>14</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>16</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>44</v>
+      </c>
+      <c r="T5" t="n">
         <v>242</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>106</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Grönfink
 Knärot
@@ -1054,201 +1215,40 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39697-2025 artfynd.xlsx", "A 39697-2025")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39697-2025 karta.png", "A 39697-2025")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39697-2025 georefererad karta.tif", "A 39697-2025")</f>
         <v/>
       </c>
-      <c r="Z4">
+      <c r="Z5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 39697-2025 karta knärot.png", "A 39697-2025")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39697-2025 FSC-klagomål.docx", "A 39697-2025")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39697-2025 FSC-klagomål mail.docx", "A 39697-2025")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39697-2025 tillsynsbegäran.docx", "A 39697-2025")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39697-2025 tillsynsbegäran mail.docx", "A 39697-2025")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39697-2025 prioriterade fågelarter.docx", "A 39697-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 31280-2024</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45504</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J5" t="n">
-        <v>8</v>
-      </c>
-      <c r="K5" t="n">
-        <v>12</v>
-      </c>
-      <c r="L5" t="n">
-        <v>22</v>
-      </c>
-      <c r="M5" t="n">
-        <v>5</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>27</v>
-      </c>
-      <c r="R5" t="n">
-        <v>5</v>
-      </c>
-      <c r="S5" t="n">
-        <v>44</v>
-      </c>
-      <c r="T5" t="n">
-        <v>93</v>
-      </c>
-      <c r="U5" t="n">
-        <v>91</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Gränsticka
-Knärot
-Liten hornflikmossa
-Spadskinn
-Torrmusseron
-Apelsinticka
-Fjällig taggsvamp s.str.
-Grantaggsvamp
-Gropticka
-Kattfotslav
-Knölspindel
-Kötticka
-Mjölsvärting
-Nordfladdermus
-Nordtagging
-Persiljespindling
-Rynkskinn
-Skarp dropptaggsvamp
-Svartvit taggsvamp
-Tallkötticka
-Tallticka
-Talltita
-Ullticka
-Vaddporing
-Vedskivlav
-Vedtrappmossa
-Vågticka
-Bollvitmossa
-Bronshjon
-Flagellkvastmossa
-Grönpyrola
-Kornknutmossa
-Mindre märgborre
-Rostfläck
-Rödgul trumpetsvamp
-Smal svampklubba
-Thomsons trägnagare
-Vedticka
-Vågbandad barkbock
-Blåsippa
-Kungsfågel
-Mindre vattensalamander
-Fläcknycklar
-Lopplummer (aggregat)</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31280-2024 artfynd.xlsx", "A 31280-2024")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31280-2024 karta.png", "A 31280-2024")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31280-2024 georefererad karta.tif", "A 31280-2024")</f>
-        <v/>
-      </c>
-      <c r="Z5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 31280-2024 karta knärot.png", "A 31280-2024")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31280-2024 FSC-klagomål.docx", "A 31280-2024")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31280-2024 FSC-klagomål mail.docx", "A 31280-2024")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31280-2024 tillsynsbegäran.docx", "A 31280-2024")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31280-2024 tillsynsbegäran mail.docx", "A 31280-2024")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 31280-2024 prioriterade fågelarter.docx", "A 31280-2024")</f>
         <v/>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
         <v>45582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45169</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45139</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45782</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>45282</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>46216</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>46216</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>46237</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>44613</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>46085</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>45435</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>46215</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>46111</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 39594-2025</t>
+          <t>A 34040-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45890</v>
+        <v>45523</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2974,23 +2974,23 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="J19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L19" t="n">
         <v>3</v>
       </c>
-      <c r="L19" t="n">
-        <v>5</v>
-      </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -3005,18 +3005,146 @@
         <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
         <v>11</v>
       </c>
       <c r="T19" t="n">
+        <v>28</v>
+      </c>
+      <c r="U19" t="n">
+        <v>28</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Gränsticka
+Knärot
+Talltita
+Ullticka
+Vedtrappmossa
+Bronshjon
+Grönpyrola
+Mindre märgborre
+Vedticka
+Spillkråka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34040-2024 artfynd.xlsx", "A 34040-2024")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34040-2024 karta.png", "A 34040-2024")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34040-2024 georefererad karta.tif", "A 34040-2024")</f>
+        <v/>
+      </c>
+      <c r="Z19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 34040-2024 karta knärot.png", "A 34040-2024")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34040-2024 FSC-klagomål.docx", "A 34040-2024")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34040-2024 FSC-klagomål mail.docx", "A 34040-2024")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34040-2024 tillsynsbegäran.docx", "A 34040-2024")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34040-2024 tillsynsbegäran mail.docx", "A 34040-2024")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 34040-2024 prioriterade fågelarter.docx", "A 34040-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 39594-2025</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45890</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>5</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>5</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>11</v>
+      </c>
+      <c r="T20" t="n">
         <v>14</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U20" t="n">
         <v>10</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Brunlångöra
 Dropptaggsvamp
@@ -3031,111 +3159,111 @@
 Dvärgpipistrell</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39594-2025 artfynd.xlsx", "A 39594-2025")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39594-2025 karta.png", "A 39594-2025")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39594-2025 georefererad karta.tif", "A 39594-2025")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39594-2025 FSC-klagomål.docx", "A 39594-2025")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39594-2025 FSC-klagomål mail.docx", "A 39594-2025")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39594-2025 tillsynsbegäran.docx", "A 39594-2025")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39594-2025 tillsynsbegäran mail.docx", "A 39594-2025")</f>
         <v/>
       </c>
-      <c r="AE19">
+      <c r="AE20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39594-2025 prioriterade fågelarter.docx", "A 39594-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A 42853-2022</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="D21" s="1" t="n">
         <v>44832</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="E21" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>VÄSTMANLANDS LÄN</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="I21" t="n">
         <v>7.4</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J21" t="n">
         <v>3</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K21" t="n">
         <v>7</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L21" t="n">
         <v>2</v>
       </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>3</v>
       </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
         <v>11</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>15</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
         <v>2</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Ask
 Kandelabersvamp
@@ -3150,164 +3278,36 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 42853-2022 artfynd.xlsx", "A 42853-2022")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 42853-2022 karta.png", "A 42853-2022")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 42853-2022 georefererad karta.tif", "A 42853-2022")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 42853-2022 FSC-klagomål.docx", "A 42853-2022")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 42853-2022 FSC-klagomål mail.docx", "A 42853-2022")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 42853-2022 tillsynsbegäran.docx", "A 42853-2022")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 42853-2022 tillsynsbegäran mail.docx", "A 42853-2022")</f>
         <v/>
       </c>
-      <c r="AE20">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 42853-2022 prioriterade fågelarter.docx", "A 42853-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 34040-2024</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45523</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J21" t="n">
-        <v>4</v>
-      </c>
-      <c r="K21" t="n">
-        <v>4</v>
-      </c>
-      <c r="L21" t="n">
-        <v>3</v>
-      </c>
-      <c r="M21" t="n">
-        <v>2</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>5</v>
-      </c>
-      <c r="R21" t="n">
-        <v>2</v>
-      </c>
-      <c r="S21" t="n">
-        <v>11</v>
-      </c>
-      <c r="T21" t="n">
-        <v>28</v>
-      </c>
-      <c r="U21" t="n">
-        <v>28</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Gränsticka
-Knärot
-Talltita
-Ullticka
-Vedtrappmossa
-Bronshjon
-Grönpyrola
-Mindre märgborre
-Vedticka
-Spillkråka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34040-2024 artfynd.xlsx", "A 34040-2024")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34040-2024 karta.png", "A 34040-2024")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34040-2024 georefererad karta.tif", "A 34040-2024")</f>
-        <v/>
-      </c>
-      <c r="Z21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 34040-2024 karta knärot.png", "A 34040-2024")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34040-2024 FSC-klagomål.docx", "A 34040-2024")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34040-2024 FSC-klagomål mail.docx", "A 34040-2024")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34040-2024 tillsynsbegäran.docx", "A 34040-2024")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34040-2024 tillsynsbegäran mail.docx", "A 34040-2024")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 34040-2024 prioriterade fågelarter.docx", "A 34040-2024")</f>
         <v/>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
         <v>45070</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>44565</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31060-2026</t>
+          <t>A 44798-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46215</v>
+        <v>45574</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3591,26 +3591,26 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>7.8</v>
+        <v>4.4</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
         <v>7</v>
       </c>
-      <c r="K24" t="n">
-        <v>2</v>
-      </c>
-      <c r="L24" t="n">
-        <v>2</v>
-      </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3619,7 +3619,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -3628,12 +3628,130 @@
         <v>9</v>
       </c>
       <c r="T24" t="n">
+        <v>26</v>
+      </c>
+      <c r="U24" t="n">
+        <v>10</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Rosetticka
+Brunklöver
+Gropticka
+Persiljespindling
+Scharlakansvaxing
+Svinrot
+Ullticka
+Vågticka
+Brandticka</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 44798-2024 artfynd.xlsx", "A 44798-2024")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 44798-2024 karta.png", "A 44798-2024")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 44798-2024 georefererad karta.tif", "A 44798-2024")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 44798-2024 FSC-klagomål.docx", "A 44798-2024")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 44798-2024 FSC-klagomål mail.docx", "A 44798-2024")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 44798-2024 tillsynsbegäran.docx", "A 44798-2024")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 44798-2024 tillsynsbegäran mail.docx", "A 44798-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 31060-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J25" t="n">
+        <v>7</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
         <v>9</v>
       </c>
-      <c r="U24" t="n">
+      <c r="T25" t="n">
+        <v>9</v>
+      </c>
+      <c r="U25" t="n">
         <v>3</v>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Bombmurkla
 Brunlångöra
@@ -3646,154 +3764,36 @@
 Vanlig groda</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31060-2026 artfynd.xlsx", "A 31060-2026")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31060-2026 karta.png", "A 31060-2026")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31060-2026 georefererad karta.tif", "A 31060-2026")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31060-2026 FSC-klagomål.docx", "A 31060-2026")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31060-2026 FSC-klagomål mail.docx", "A 31060-2026")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31060-2026 tillsynsbegäran.docx", "A 31060-2026")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31060-2026 tillsynsbegäran mail.docx", "A 31060-2026")</f>
         <v/>
       </c>
-      <c r="AE24">
+      <c r="AE25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 31060-2026 prioriterade fågelarter.docx", "A 31060-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 44798-2024</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>45574</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" t="n">
-        <v>7</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>8</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S25" t="n">
-        <v>9</v>
-      </c>
-      <c r="T25" t="n">
-        <v>26</v>
-      </c>
-      <c r="U25" t="n">
-        <v>10</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Rosetticka
-Brunklöver
-Gropticka
-Persiljespindling
-Scharlakansvaxing
-Svinrot
-Ullticka
-Vågticka
-Brandticka</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 44798-2024 artfynd.xlsx", "A 44798-2024")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 44798-2024 karta.png", "A 44798-2024")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 44798-2024 georefererad karta.tif", "A 44798-2024")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 44798-2024 FSC-klagomål.docx", "A 44798-2024")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 44798-2024 FSC-klagomål mail.docx", "A 44798-2024")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 44798-2024 tillsynsbegäran.docx", "A 44798-2024")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 44798-2024 tillsynsbegäran mail.docx", "A 44798-2024")</f>
         <v/>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
         <v>45435</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>44518</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 56299-2021</t>
+          <t>A 38172-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4046,14 +4046,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44477</v>
+        <v>45545</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4067,49 +4067,173 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>8</v>
+        <v>5.2</v>
       </c>
       <c r="J28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>3</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
         <v>4</v>
       </c>
-      <c r="L28" t="n">
-        <v>2</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2</v>
-      </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>7</v>
       </c>
       <c r="T28" t="n">
+        <v>8</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Gropticka
+Sädesärla
+Vedtrappmossa
+Stjärtmes
+Lopplummer (aggregat)
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 38172-2024 artfynd.xlsx", "A 38172-2024")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 38172-2024 karta.png", "A 38172-2024")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 38172-2024 georefererad karta.tif", "A 38172-2024")</f>
+        <v/>
+      </c>
+      <c r="Z28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 38172-2024 karta knärot.png", "A 38172-2024")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 38172-2024 FSC-klagomål.docx", "A 38172-2024")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 38172-2024 FSC-klagomål mail.docx", "A 38172-2024")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 38172-2024 tillsynsbegäran.docx", "A 38172-2024")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 38172-2024 tillsynsbegäran mail.docx", "A 38172-2024")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 38172-2024 prioriterade fågelarter.docx", "A 38172-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A 56299-2021</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>44477</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>8</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4</v>
+      </c>
+      <c r="L29" t="n">
+        <v>2</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
         <v>7</v>
       </c>
-      <c r="U28" t="n">
-        <v>1</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="T29" t="n">
+        <v>7</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>Större flatbagge
 Tretåig hackspett
@@ -4120,116 +4244,116 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W28">
+      <c r="W29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 56299-2021 artfynd.xlsx", "A 56299-2021")</f>
         <v/>
       </c>
-      <c r="X28">
+      <c r="X29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 56299-2021 karta.png", "A 56299-2021")</f>
         <v/>
       </c>
-      <c r="Y28">
+      <c r="Y29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 56299-2021 georefererad karta.tif", "A 56299-2021")</f>
         <v/>
       </c>
-      <c r="AA28">
+      <c r="AA29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 56299-2021 FSC-klagomål.docx", "A 56299-2021")</f>
         <v/>
       </c>
-      <c r="AB28">
+      <c r="AB29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 56299-2021 FSC-klagomål mail.docx", "A 56299-2021")</f>
         <v/>
       </c>
-      <c r="AC28">
+      <c r="AC29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 56299-2021 tillsynsbegäran.docx", "A 56299-2021")</f>
         <v/>
       </c>
-      <c r="AD28">
+      <c r="AD29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 56299-2021 tillsynsbegäran mail.docx", "A 56299-2021")</f>
         <v/>
       </c>
-      <c r="AE28">
+      <c r="AE29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 56299-2021 prioriterade fågelarter.docx", "A 56299-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>A 48891-2023</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D29" s="1" t="n">
+      <c r="D30" s="1" t="n">
         <v>45203</v>
       </c>
-      <c r="E29" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F29" t="inlineStr">
+      <c r="E30" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>VÄSTMANLANDS LÄN</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I29" t="n">
+      <c r="I30" t="n">
         <v>2.9</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J30" t="n">
         <v>3</v>
       </c>
-      <c r="K29" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" t="n">
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
         <v>3</v>
       </c>
-      <c r="M29" t="n">
-        <v>1</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
         <v>4</v>
       </c>
-      <c r="R29" t="n">
-        <v>1</v>
-      </c>
-      <c r="S29" t="n">
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
+      <c r="S30" t="n">
         <v>7</v>
       </c>
-      <c r="T29" t="n">
+      <c r="T30" t="n">
         <v>10</v>
       </c>
-      <c r="U29" t="n">
+      <c r="U30" t="n">
         <v>5</v>
       </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Motaggsvamp
@@ -4240,115 +4364,115 @@
 Gröngöling</t>
         </is>
       </c>
-      <c r="W29">
+      <c r="W30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 48891-2023 artfynd.xlsx", "A 48891-2023")</f>
         <v/>
       </c>
-      <c r="X29">
+      <c r="X30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 48891-2023 karta.png", "A 48891-2023")</f>
         <v/>
       </c>
-      <c r="Y29">
+      <c r="Y30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 48891-2023 georefererad karta.tif", "A 48891-2023")</f>
         <v/>
       </c>
-      <c r="Z29">
+      <c r="Z30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 48891-2023 karta knärot.png", "A 48891-2023")</f>
         <v/>
       </c>
-      <c r="AA29">
+      <c r="AA30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 48891-2023 FSC-klagomål.docx", "A 48891-2023")</f>
         <v/>
       </c>
-      <c r="AB29">
+      <c r="AB30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 48891-2023 FSC-klagomål mail.docx", "A 48891-2023")</f>
         <v/>
       </c>
-      <c r="AC29">
+      <c r="AC30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 48891-2023 tillsynsbegäran.docx", "A 48891-2023")</f>
         <v/>
       </c>
-      <c r="AD29">
+      <c r="AD30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 48891-2023 tillsynsbegäran mail.docx", "A 48891-2023")</f>
         <v/>
       </c>
-      <c r="AE29">
+      <c r="AE30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 48891-2023 prioriterade fågelarter.docx", "A 48891-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>A 22840-2023</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D30" s="1" t="n">
+      <c r="D31" s="1" t="n">
         <v>45072</v>
       </c>
-      <c r="E30" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F30" t="inlineStr">
+      <c r="E31" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>VÄSTMANLANDS LÄN</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="I30" t="n">
+      <c r="I31" t="n">
         <v>4.3</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
         <v>7</v>
       </c>
-      <c r="T30" t="n">
+      <c r="T31" t="n">
         <v>10</v>
       </c>
-      <c r="U30" t="n">
+      <c r="U31" t="n">
         <v>9</v>
       </c>
-      <c r="V30" s="2" t="inlineStr">
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>Hultbräken
 Kärrviol
@@ -4359,112 +4483,112 @@
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W30">
+      <c r="W31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 22840-2023 artfynd.xlsx", "A 22840-2023")</f>
         <v/>
       </c>
-      <c r="X30">
+      <c r="X31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 22840-2023 karta.png", "A 22840-2023")</f>
         <v/>
       </c>
-      <c r="Y30">
+      <c r="Y31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 22840-2023 georefererad karta.tif", "A 22840-2023")</f>
         <v/>
       </c>
-      <c r="AA30">
+      <c r="AA31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 22840-2023 FSC-klagomål.docx", "A 22840-2023")</f>
         <v/>
       </c>
-      <c r="AB30">
+      <c r="AB31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 22840-2023 FSC-klagomål mail.docx", "A 22840-2023")</f>
         <v/>
       </c>
-      <c r="AC30">
+      <c r="AC31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 22840-2023 tillsynsbegäran.docx", "A 22840-2023")</f>
         <v/>
       </c>
-      <c r="AD30">
+      <c r="AD31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 22840-2023 tillsynsbegäran mail.docx", "A 22840-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>A 36260-2026</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D31" s="1" t="n">
+      <c r="D32" s="1" t="n">
         <v>46268</v>
       </c>
-      <c r="E31" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F31" t="inlineStr">
+      <c r="E32" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>VÄSTMANLANDS LÄN</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I31" t="n">
+      <c r="I32" t="n">
         <v>5.7</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J32" t="n">
         <v>4</v>
       </c>
-      <c r="K31" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M31" t="n">
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
         <v>2</v>
       </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
         <v>3</v>
       </c>
-      <c r="R31" t="n">
+      <c r="R32" t="n">
         <v>2</v>
       </c>
-      <c r="S31" t="n">
+      <c r="S32" t="n">
         <v>7</v>
       </c>
-      <c r="T31" t="n">
+      <c r="T32" t="n">
         <v>8</v>
       </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>Mindre bastardsvärmare
 Silverblåvinge
@@ -4475,160 +4599,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W31">
+      <c r="W32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 36260-2026 artfynd.xlsx", "A 36260-2026")</f>
         <v/>
       </c>
-      <c r="X31">
+      <c r="X32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 36260-2026 karta.png", "A 36260-2026")</f>
         <v/>
       </c>
-      <c r="Y31">
+      <c r="Y32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 36260-2026 georefererad karta.tif", "A 36260-2026")</f>
         <v/>
       </c>
-      <c r="AA31">
+      <c r="AA32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 36260-2026 FSC-klagomål.docx", "A 36260-2026")</f>
         <v/>
       </c>
-      <c r="AB31">
+      <c r="AB32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 36260-2026 FSC-klagomål mail.docx", "A 36260-2026")</f>
         <v/>
       </c>
-      <c r="AC31">
+      <c r="AC32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 36260-2026 tillsynsbegäran.docx", "A 36260-2026")</f>
         <v/>
       </c>
-      <c r="AD31">
+      <c r="AD32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 36260-2026 tillsynsbegäran mail.docx", "A 36260-2026")</f>
         <v/>
       </c>
-      <c r="AE31">
+      <c r="AE32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 36260-2026 prioriterade fågelarter.docx", "A 36260-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>A 38172-2024</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>45545</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J32" t="n">
-        <v>5</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>3</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>4</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1</v>
-      </c>
-      <c r="S32" t="n">
-        <v>7</v>
-      </c>
-      <c r="T32" t="n">
-        <v>8</v>
-      </c>
-      <c r="U32" t="n">
-        <v>2</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Gropticka
-Sädesärla
-Vedtrappmossa
-Stjärtmes
-Lopplummer (aggregat)
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 38172-2024 artfynd.xlsx", "A 38172-2024")</f>
-        <v/>
-      </c>
-      <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 38172-2024 karta.png", "A 38172-2024")</f>
-        <v/>
-      </c>
-      <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 38172-2024 georefererad karta.tif", "A 38172-2024")</f>
-        <v/>
-      </c>
-      <c r="Z32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 38172-2024 karta knärot.png", "A 38172-2024")</f>
-        <v/>
-      </c>
-      <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 38172-2024 FSC-klagomål.docx", "A 38172-2024")</f>
-        <v/>
-      </c>
-      <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 38172-2024 FSC-klagomål mail.docx", "A 38172-2024")</f>
-        <v/>
-      </c>
-      <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 38172-2024 tillsynsbegäran.docx", "A 38172-2024")</f>
-        <v/>
-      </c>
-      <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 38172-2024 tillsynsbegäran mail.docx", "A 38172-2024")</f>
-        <v/>
-      </c>
-      <c r="AE32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 38172-2024 prioriterade fågelarter.docx", "A 38172-2024")</f>
         <v/>
       </c>
     </row>
@@ -4652,7 +4652,7 @@
         <v>45945</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>44518</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>46009</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>46076</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>44832</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>44832</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 10819-2024</t>
+          <t>A 25548-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5339,10 +5339,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45369</v>
+        <v>45463</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5354,17 +5354,22 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>5.1</v>
       </c>
       <c r="J39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K39" t="n">
         <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>1</v>
@@ -5379,7 +5384,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -5388,12 +5393,241 @@
         <v>4</v>
       </c>
       <c r="T39" t="n">
+        <v>9</v>
+      </c>
+      <c r="U39" t="n">
+        <v>6</v>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Vedticka
+Fläcknycklar
+Nattviol</t>
+        </is>
+      </c>
+      <c r="W39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 25548-2024 artfynd.xlsx", "A 25548-2024")</f>
+        <v/>
+      </c>
+      <c r="X39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 25548-2024 karta.png", "A 25548-2024")</f>
+        <v/>
+      </c>
+      <c r="Y39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 25548-2024 georefererad karta.tif", "A 25548-2024")</f>
+        <v/>
+      </c>
+      <c r="Z39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 25548-2024 karta knärot.png", "A 25548-2024")</f>
+        <v/>
+      </c>
+      <c r="AA39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 25548-2024 FSC-klagomål.docx", "A 25548-2024")</f>
+        <v/>
+      </c>
+      <c r="AB39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 25548-2024 FSC-klagomål mail.docx", "A 25548-2024")</f>
+        <v/>
+      </c>
+      <c r="AC39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 25548-2024 tillsynsbegäran.docx", "A 25548-2024")</f>
+        <v/>
+      </c>
+      <c r="AD39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 25548-2024 tillsynsbegäran mail.docx", "A 25548-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>A 31176-2024</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="n">
+        <v>45503</v>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>2</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>4</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>4</v>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>Doftskinn
+Ullticka
+Tjäder
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31176-2024 artfynd.xlsx", "A 31176-2024")</f>
+        <v/>
+      </c>
+      <c r="X40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31176-2024 karta.png", "A 31176-2024")</f>
+        <v/>
+      </c>
+      <c r="Y40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31176-2024 georefererad karta.tif", "A 31176-2024")</f>
+        <v/>
+      </c>
+      <c r="AA40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31176-2024 FSC-klagomål.docx", "A 31176-2024")</f>
+        <v/>
+      </c>
+      <c r="AB40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31176-2024 FSC-klagomål mail.docx", "A 31176-2024")</f>
+        <v/>
+      </c>
+      <c r="AC40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31176-2024 tillsynsbegäran.docx", "A 31176-2024")</f>
+        <v/>
+      </c>
+      <c r="AD40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31176-2024 tillsynsbegäran mail.docx", "A 31176-2024")</f>
+        <v/>
+      </c>
+      <c r="AE40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 31176-2024 prioriterade fågelarter.docx", "A 31176-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>A 10819-2024</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="n">
+        <v>45369</v>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>2</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1</v>
+      </c>
+      <c r="S41" t="n">
+        <v>4</v>
+      </c>
+      <c r="T41" t="n">
         <v>8</v>
       </c>
-      <c r="U39" t="n">
+      <c r="U41" t="n">
         <v>2</v>
       </c>
-      <c r="V39" s="2" t="inlineStr">
+      <c r="V41" s="2" t="inlineStr">
         <is>
           <t>Igelkott
 Entita
@@ -5401,270 +5635,36 @@
 Näktergal</t>
         </is>
       </c>
-      <c r="W39">
+      <c r="W41">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 10819-2024 artfynd.xlsx", "A 10819-2024")</f>
         <v/>
       </c>
-      <c r="X39">
+      <c r="X41">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 10819-2024 karta.png", "A 10819-2024")</f>
         <v/>
       </c>
-      <c r="Y39">
+      <c r="Y41">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 10819-2024 georefererad karta.tif", "A 10819-2024")</f>
         <v/>
       </c>
-      <c r="AA39">
+      <c r="AA41">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 10819-2024 FSC-klagomål.docx", "A 10819-2024")</f>
         <v/>
       </c>
-      <c r="AB39">
+      <c r="AB41">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 10819-2024 FSC-klagomål mail.docx", "A 10819-2024")</f>
         <v/>
       </c>
-      <c r="AC39">
+      <c r="AC41">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 10819-2024 tillsynsbegäran.docx", "A 10819-2024")</f>
         <v/>
       </c>
-      <c r="AD39">
+      <c r="AD41">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 10819-2024 tillsynsbegäran mail.docx", "A 10819-2024")</f>
         <v/>
       </c>
-      <c r="AE39">
+      <c r="AE41">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 10819-2024 prioriterade fågelarter.docx", "A 10819-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>A 31176-2024</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="n">
-        <v>45503</v>
-      </c>
-      <c r="E40" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="J40" t="n">
-        <v>2</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>2</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>2</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>4</v>
-      </c>
-      <c r="T40" t="n">
-        <v>4</v>
-      </c>
-      <c r="U40" t="n">
-        <v>4</v>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>Doftskinn
-Ullticka
-Tjäder
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31176-2024 artfynd.xlsx", "A 31176-2024")</f>
-        <v/>
-      </c>
-      <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31176-2024 karta.png", "A 31176-2024")</f>
-        <v/>
-      </c>
-      <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31176-2024 georefererad karta.tif", "A 31176-2024")</f>
-        <v/>
-      </c>
-      <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31176-2024 FSC-klagomål.docx", "A 31176-2024")</f>
-        <v/>
-      </c>
-      <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31176-2024 FSC-klagomål mail.docx", "A 31176-2024")</f>
-        <v/>
-      </c>
-      <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31176-2024 tillsynsbegäran.docx", "A 31176-2024")</f>
-        <v/>
-      </c>
-      <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31176-2024 tillsynsbegäran mail.docx", "A 31176-2024")</f>
-        <v/>
-      </c>
-      <c r="AE40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 31176-2024 prioriterade fågelarter.docx", "A 31176-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>A 25548-2024</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="n">
-        <v>45463</v>
-      </c>
-      <c r="E41" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J41" t="n">
-        <v>3</v>
-      </c>
-      <c r="K41" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>1</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>1</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1</v>
-      </c>
-      <c r="S41" t="n">
-        <v>4</v>
-      </c>
-      <c r="T41" t="n">
-        <v>9</v>
-      </c>
-      <c r="U41" t="n">
-        <v>6</v>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Vedticka
-Fläcknycklar
-Nattviol</t>
-        </is>
-      </c>
-      <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 25548-2024 artfynd.xlsx", "A 25548-2024")</f>
-        <v/>
-      </c>
-      <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 25548-2024 karta.png", "A 25548-2024")</f>
-        <v/>
-      </c>
-      <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 25548-2024 georefererad karta.tif", "A 25548-2024")</f>
-        <v/>
-      </c>
-      <c r="Z41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 25548-2024 karta knärot.png", "A 25548-2024")</f>
-        <v/>
-      </c>
-      <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 25548-2024 FSC-klagomål.docx", "A 25548-2024")</f>
-        <v/>
-      </c>
-      <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 25548-2024 FSC-klagomål mail.docx", "A 25548-2024")</f>
-        <v/>
-      </c>
-      <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 25548-2024 tillsynsbegäran.docx", "A 25548-2024")</f>
-        <v/>
-      </c>
-      <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 25548-2024 tillsynsbegäran mail.docx", "A 25548-2024")</f>
         <v/>
       </c>
     </row>
@@ -5688,7 +5688,7 @@
         <v>44518</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 49718-2023</t>
+          <t>A 39694-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5801,10 +5801,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45212</v>
+        <v>45890</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5816,8 +5816,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
@@ -5826,7 +5831,7 @@
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -5841,7 +5846,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -5850,714 +5855,709 @@
         <v>3</v>
       </c>
       <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Mindre märgborre
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39694-2025 artfynd.xlsx", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="X43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39694-2025 karta.png", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="Y43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39694-2025 georefererad karta.tif", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="AA43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39694-2025 FSC-klagomål.docx", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="AB43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39694-2025 FSC-klagomål mail.docx", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="AC43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39694-2025 tillsynsbegäran.docx", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="AD43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39694-2025 tillsynsbegäran mail.docx", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="AE43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39694-2025 prioriterade fågelarter.docx", "A 39694-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>A 69777-2021</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="n">
+        <v>44532</v>
+      </c>
+      <c r="E44" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3</v>
+      </c>
+      <c r="T44" t="n">
+        <v>5</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>Bombmurkla
+Rävticka
+Vedticka</t>
+        </is>
+      </c>
+      <c r="W44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 69777-2021 artfynd.xlsx", "A 69777-2021")</f>
+        <v/>
+      </c>
+      <c r="X44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 69777-2021 karta.png", "A 69777-2021")</f>
+        <v/>
+      </c>
+      <c r="Y44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 69777-2021 georefererad karta.tif", "A 69777-2021")</f>
+        <v/>
+      </c>
+      <c r="AA44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 69777-2021 FSC-klagomål.docx", "A 69777-2021")</f>
+        <v/>
+      </c>
+      <c r="AB44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 69777-2021 FSC-klagomål mail.docx", "A 69777-2021")</f>
+        <v/>
+      </c>
+      <c r="AC44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 69777-2021 tillsynsbegäran.docx", "A 69777-2021")</f>
+        <v/>
+      </c>
+      <c r="AD44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 69777-2021 tillsynsbegäran mail.docx", "A 69777-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>A 49718-2023</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>45212</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>2</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3</v>
+      </c>
+      <c r="T45" t="n">
         <v>6</v>
       </c>
-      <c r="U43" t="n">
+      <c r="U45" t="n">
         <v>6</v>
       </c>
-      <c r="V43" s="2" t="inlineStr">
+      <c r="V45" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Talltita
 Zontaggsvamp</t>
         </is>
       </c>
-      <c r="W43">
+      <c r="W45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 49718-2023 artfynd.xlsx", "A 49718-2023")</f>
         <v/>
       </c>
-      <c r="X43">
+      <c r="X45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 49718-2023 karta.png", "A 49718-2023")</f>
         <v/>
       </c>
-      <c r="Y43">
+      <c r="Y45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 49718-2023 georefererad karta.tif", "A 49718-2023")</f>
         <v/>
       </c>
-      <c r="AA43">
+      <c r="AA45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 49718-2023 FSC-klagomål.docx", "A 49718-2023")</f>
         <v/>
       </c>
-      <c r="AB43">
+      <c r="AB45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 49718-2023 FSC-klagomål mail.docx", "A 49718-2023")</f>
         <v/>
       </c>
-      <c r="AC43">
+      <c r="AC45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 49718-2023 tillsynsbegäran.docx", "A 49718-2023")</f>
         <v/>
       </c>
-      <c r="AD43">
+      <c r="AD45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 49718-2023 tillsynsbegäran mail.docx", "A 49718-2023")</f>
         <v/>
       </c>
-      <c r="AE43">
+      <c r="AE45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 49718-2023 prioriterade fågelarter.docx", "A 49718-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>A 39694-2025</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>A 42765-2022</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="n">
-        <v>45890</v>
-      </c>
-      <c r="E44" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F44" t="inlineStr">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v>44832</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>VÄSTMANLANDS LÄN</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J44" t="n">
-        <v>1</v>
-      </c>
-      <c r="K44" t="n">
-        <v>1</v>
-      </c>
-      <c r="L44" t="n">
-        <v>1</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>1</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
+      <c r="I46" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
         <v>3</v>
       </c>
-      <c r="T44" t="n">
-        <v>3</v>
-      </c>
-      <c r="U44" t="n">
-        <v>2</v>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Mindre märgborre
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39694-2025 artfynd.xlsx", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39694-2025 karta.png", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39694-2025 georefererad karta.tif", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39694-2025 FSC-klagomål.docx", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39694-2025 FSC-klagomål mail.docx", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39694-2025 tillsynsbegäran.docx", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39694-2025 tillsynsbegäran mail.docx", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="AE44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39694-2025 prioriterade fågelarter.docx", "A 39694-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>A 42765-2022</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="n">
-        <v>44832</v>
-      </c>
-      <c r="E45" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J45" t="n">
-        <v>1</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1</v>
-      </c>
-      <c r="L45" t="n">
-        <v>1</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>1</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>3</v>
-      </c>
-      <c r="T45" t="n">
+      <c r="T46" t="n">
         <v>4</v>
       </c>
-      <c r="U45" t="n">
-        <v>1</v>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
+      <c r="U46" t="n">
+        <v>1</v>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
         <is>
           <t>Krusfrö
 Barkticka
 Blåsippa</t>
         </is>
       </c>
-      <c r="W45">
+      <c r="W46">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 42765-2022 artfynd.xlsx", "A 42765-2022")</f>
         <v/>
       </c>
-      <c r="X45">
+      <c r="X46">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 42765-2022 karta.png", "A 42765-2022")</f>
         <v/>
       </c>
-      <c r="Y45">
+      <c r="Y46">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 42765-2022 georefererad karta.tif", "A 42765-2022")</f>
         <v/>
       </c>
-      <c r="AA45">
+      <c r="AA46">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 42765-2022 FSC-klagomål.docx", "A 42765-2022")</f>
         <v/>
       </c>
-      <c r="AB45">
+      <c r="AB46">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 42765-2022 FSC-klagomål mail.docx", "A 42765-2022")</f>
         <v/>
       </c>
-      <c r="AC45">
+      <c r="AC46">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 42765-2022 tillsynsbegäran.docx", "A 42765-2022")</f>
         <v/>
       </c>
-      <c r="AD45">
+      <c r="AD46">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 42765-2022 tillsynsbegäran mail.docx", "A 42765-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>A 63146-2025</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>46009</v>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>2</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3</v>
+      </c>
+      <c r="T47" t="n">
+        <v>12</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>Stor aspticka
+Svart trolldruva
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63146-2025 artfynd.xlsx", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="X47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63146-2025 karta.png", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="Y47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63146-2025 georefererad karta.tif", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="AA47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63146-2025 FSC-klagomål.docx", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="AB47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63146-2025 FSC-klagomål mail.docx", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="AC47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63146-2025 tillsynsbegäran.docx", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="AD47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63146-2025 tillsynsbegäran mail.docx", "A 63146-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>A 4082-2025</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D46" s="1" t="n">
+      <c r="D48" s="1" t="n">
         <v>45684</v>
       </c>
-      <c r="E46" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F46" t="inlineStr">
+      <c r="E48" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>VÄSTMANLANDS LÄN</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I46" t="n">
+      <c r="I48" t="n">
         <v>11.6</v>
       </c>
-      <c r="J46" t="n">
+      <c r="J48" t="n">
         <v>2</v>
       </c>
-      <c r="K46" t="n">
+      <c r="K48" t="n">
         <v>2</v>
       </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
         <v>3</v>
       </c>
-      <c r="T46" t="n">
+      <c r="T48" t="n">
         <v>3</v>
       </c>
-      <c r="U46" t="n">
-        <v>1</v>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
+      <c r="U48" t="n">
+        <v>1</v>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
         <is>
           <t>Grönpyrola
 Plattlummer
 Lopplummer (aggregat)</t>
         </is>
       </c>
-      <c r="W46">
+      <c r="W48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 4082-2025 artfynd.xlsx", "A 4082-2025")</f>
         <v/>
       </c>
-      <c r="X46">
+      <c r="X48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 4082-2025 karta.png", "A 4082-2025")</f>
         <v/>
       </c>
-      <c r="Y46">
+      <c r="Y48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 4082-2025 georefererad karta.tif", "A 4082-2025")</f>
         <v/>
       </c>
-      <c r="AA46">
+      <c r="AA48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 4082-2025 FSC-klagomål.docx", "A 4082-2025")</f>
         <v/>
       </c>
-      <c r="AB46">
+      <c r="AB48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 4082-2025 FSC-klagomål mail.docx", "A 4082-2025")</f>
         <v/>
       </c>
-      <c r="AC46">
+      <c r="AC48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 4082-2025 tillsynsbegäran.docx", "A 4082-2025")</f>
         <v/>
       </c>
-      <c r="AD46">
+      <c r="AD48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 4082-2025 tillsynsbegäran mail.docx", "A 4082-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>A 48128-2023</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D47" s="1" t="n">
+      <c r="D49" s="1" t="n">
         <v>45205</v>
       </c>
-      <c r="E47" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F47" t="inlineStr">
+      <c r="E49" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>VÄSTMANLANDS LÄN</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
-      <c r="I47" t="n">
+      <c r="I49" t="n">
         <v>11.8</v>
       </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
-        <v>1</v>
-      </c>
-      <c r="L47" t="n">
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" t="n">
         <v>2</v>
       </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
         <v>2</v>
       </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
         <v>3</v>
       </c>
-      <c r="T47" t="n">
+      <c r="T49" t="n">
         <v>3</v>
       </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
         <is>
           <t>Jungfrulin
 Svinrot
 Vedticka</t>
         </is>
       </c>
-      <c r="W47">
+      <c r="W49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 48128-2023 artfynd.xlsx", "A 48128-2023")</f>
         <v/>
       </c>
-      <c r="X47">
+      <c r="X49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 48128-2023 karta.png", "A 48128-2023")</f>
         <v/>
       </c>
-      <c r="Y47">
+      <c r="Y49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 48128-2023 georefererad karta.tif", "A 48128-2023")</f>
         <v/>
       </c>
-      <c r="AA47">
+      <c r="AA49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 48128-2023 FSC-klagomål.docx", "A 48128-2023")</f>
         <v/>
       </c>
-      <c r="AB47">
+      <c r="AB49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 48128-2023 FSC-klagomål mail.docx", "A 48128-2023")</f>
         <v/>
       </c>
-      <c r="AC47">
+      <c r="AC49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 48128-2023 tillsynsbegäran.docx", "A 48128-2023")</f>
         <v/>
       </c>
-      <c r="AD47">
+      <c r="AD49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 48128-2023 tillsynsbegäran mail.docx", "A 48128-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>A 69777-2021</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="n">
-        <v>44532</v>
-      </c>
-      <c r="E48" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J48" t="n">
-        <v>1</v>
-      </c>
-      <c r="K48" t="n">
-        <v>2</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>1</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>1</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1</v>
-      </c>
-      <c r="S48" t="n">
-        <v>3</v>
-      </c>
-      <c r="T48" t="n">
-        <v>5</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>Bombmurkla
-Rävticka
-Vedticka</t>
-        </is>
-      </c>
-      <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 69777-2021 artfynd.xlsx", "A 69777-2021")</f>
-        <v/>
-      </c>
-      <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 69777-2021 karta.png", "A 69777-2021")</f>
-        <v/>
-      </c>
-      <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 69777-2021 georefererad karta.tif", "A 69777-2021")</f>
-        <v/>
-      </c>
-      <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 69777-2021 FSC-klagomål.docx", "A 69777-2021")</f>
-        <v/>
-      </c>
-      <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 69777-2021 FSC-klagomål mail.docx", "A 69777-2021")</f>
-        <v/>
-      </c>
-      <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 69777-2021 tillsynsbegäran.docx", "A 69777-2021")</f>
-        <v/>
-      </c>
-      <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 69777-2021 tillsynsbegäran mail.docx", "A 69777-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="15" customHeight="1">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>A 63146-2025</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D49" s="1" t="n">
-        <v>46009</v>
-      </c>
-      <c r="E49" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="J49" t="n">
-        <v>1</v>
-      </c>
-      <c r="K49" t="n">
-        <v>2</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>3</v>
-      </c>
-      <c r="T49" t="n">
-        <v>12</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" s="2" t="inlineStr">
-        <is>
-          <t>Stor aspticka
-Svart trolldruva
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63146-2025 artfynd.xlsx", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63146-2025 karta.png", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63146-2025 georefererad karta.tif", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63146-2025 FSC-klagomål.docx", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63146-2025 FSC-klagomål mail.docx", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63146-2025 tillsynsbegäran.docx", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63146-2025 tillsynsbegäran mail.docx", "A 63146-2025")</f>
         <v/>
       </c>
     </row>
@@ -6581,7 +6581,7 @@
         <v>46248</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         <v>46268</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>46239</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>44635</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>45708</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>45708</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 30074-2023</t>
+          <t>A 41204-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7270,10 +7270,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45110</v>
+        <v>45174</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7285,25 +7285,20 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>1</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
@@ -7315,59 +7310,63 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S56" t="n">
         <v>2</v>
       </c>
       <c r="T56" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U56" t="n">
         <v>0</v>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola
-Revlummer</t>
+          <t>Knärot
+Vedtrappmossa</t>
         </is>
       </c>
       <c r="W56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 30074-2023 artfynd.xlsx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 41204-2023 artfynd.xlsx", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="X56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 30074-2023 karta.png", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 41204-2023 karta.png", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="Y56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 30074-2023 georefererad karta.tif", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 41204-2023 georefererad karta.tif", "A 41204-2023")</f>
+        <v/>
+      </c>
+      <c r="Z56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 41204-2023 karta knärot.png", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="AA56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 30074-2023 FSC-klagomål.docx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 41204-2023 FSC-klagomål.docx", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="AB56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 30074-2023 FSC-klagomål mail.docx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 41204-2023 FSC-klagomål mail.docx", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="AC56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 30074-2023 tillsynsbegäran.docx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 41204-2023 tillsynsbegäran.docx", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="AD56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 30074-2023 tillsynsbegäran mail.docx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 41204-2023 tillsynsbegäran mail.docx", "A 41204-2023")</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 47453-2024</t>
+          <t>A 56362-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7381,10 +7380,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45587</v>
+        <v>45236</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7396,20 +7395,25 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>5.1</v>
+        <v>15.2</v>
       </c>
       <c r="J57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N57" t="n">
         <v>0</v>
@@ -7424,7 +7428,7 @@
         <v>1</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S57" t="n">
         <v>2</v>
@@ -7437,47 +7441,43 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>Göktyta
-Gröngöling</t>
+          <t>Väddnätfjäril
+Grönpyrola</t>
         </is>
       </c>
       <c r="W57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 47453-2024 artfynd.xlsx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 56362-2023 artfynd.xlsx", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="X57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 47453-2024 karta.png", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 56362-2023 karta.png", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="Y57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 47453-2024 georefererad karta.tif", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 56362-2023 georefererad karta.tif", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="AA57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 47453-2024 FSC-klagomål.docx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 56362-2023 FSC-klagomål.docx", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="AB57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 47453-2024 FSC-klagomål mail.docx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 56362-2023 FSC-klagomål mail.docx", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="AC57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 47453-2024 tillsynsbegäran.docx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 56362-2023 tillsynsbegäran.docx", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="AD57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 47453-2024 tillsynsbegäran mail.docx", "A 47453-2024")</f>
-        <v/>
-      </c>
-      <c r="AE57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 47453-2024 prioriterade fågelarter.docx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 56362-2023 tillsynsbegäran mail.docx", "A 56362-2023")</f>
         <v/>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 56362-2023</t>
+          <t>A 30074-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7491,10 +7491,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45236</v>
+        <v>45110</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7508,11 +7508,11 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>15.2</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>1</v>
@@ -7524,7 +7524,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
         <v>0</v>
@@ -7536,10 +7536,10 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>2</v>
@@ -7548,47 +7548,47 @@
         <v>2</v>
       </c>
       <c r="U58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>Väddnätfjäril
-Grönpyrola</t>
+          <t>Grönpyrola
+Revlummer</t>
         </is>
       </c>
       <c r="W58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 56362-2023 artfynd.xlsx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 30074-2023 artfynd.xlsx", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="X58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 56362-2023 karta.png", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 30074-2023 karta.png", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="Y58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 56362-2023 georefererad karta.tif", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 30074-2023 georefererad karta.tif", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="AA58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 56362-2023 FSC-klagomål.docx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 30074-2023 FSC-klagomål.docx", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="AB58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 56362-2023 FSC-klagomål mail.docx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 30074-2023 FSC-klagomål mail.docx", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="AC58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 56362-2023 tillsynsbegäran.docx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 30074-2023 tillsynsbegäran.docx", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="AD58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 56362-2023 tillsynsbegäran mail.docx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 30074-2023 tillsynsbegäran mail.docx", "A 30074-2023")</f>
         <v/>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 37013-2025</t>
+          <t>A 40403-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45874</v>
+        <v>45895</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7619,14 +7619,14 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>10.7</v>
+        <v>3.9</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -7635,7 +7635,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
@@ -7647,59 +7647,59 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S59" t="n">
         <v>2</v>
       </c>
       <c r="T59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril
-Fältgentiana</t>
+          <t>Igelkott
+Gröngöling</t>
         </is>
       </c>
       <c r="W59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37013-2025 artfynd.xlsx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 40403-2025 artfynd.xlsx", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="X59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37013-2025 karta.png", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 40403-2025 karta.png", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="Y59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37013-2025 georefererad karta.tif", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 40403-2025 georefererad karta.tif", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="AA59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37013-2025 FSC-klagomål.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 40403-2025 FSC-klagomål.docx", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="AB59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37013-2025 FSC-klagomål mail.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 40403-2025 FSC-klagomål mail.docx", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="AC59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37013-2025 tillsynsbegäran.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 40403-2025 tillsynsbegäran.docx", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="AD59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37013-2025 tillsynsbegäran mail.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 40403-2025 tillsynsbegäran mail.docx", "A 40403-2025")</f>
         <v/>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 40403-2025</t>
+          <t>A 13788-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7713,10 +7713,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45895</v>
+        <v>45737</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7728,25 +7728,20 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>3.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
         <v>0</v>
@@ -7761,56 +7756,60 @@
         <v>1</v>
       </c>
       <c r="R60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>2</v>
       </c>
       <c r="T60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>Igelkott
-Gröngöling</t>
+          <t>Sparvuggla
+Nattskärra</t>
         </is>
       </c>
       <c r="W60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 40403-2025 artfynd.xlsx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 13788-2025 artfynd.xlsx", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="X60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 40403-2025 karta.png", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 13788-2025 karta.png", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="Y60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 40403-2025 georefererad karta.tif", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 13788-2025 georefererad karta.tif", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="AA60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 40403-2025 FSC-klagomål.docx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 13788-2025 FSC-klagomål.docx", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="AB60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 40403-2025 FSC-klagomål mail.docx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 13788-2025 FSC-klagomål mail.docx", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="AC60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 40403-2025 tillsynsbegäran.docx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 13788-2025 tillsynsbegäran.docx", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="AD60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 40403-2025 tillsynsbegäran mail.docx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 13788-2025 tillsynsbegäran mail.docx", "A 13788-2025")</f>
+        <v/>
+      </c>
+      <c r="AE60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 13788-2025 prioriterade fågelarter.docx", "A 13788-2025")</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 63138-2025</t>
+          <t>A 14001-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7824,10 +7823,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46009</v>
+        <v>45007</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7845,19 +7844,19 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
@@ -7869,63 +7868,59 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S61" t="n">
         <v>2</v>
       </c>
       <c r="T61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>Mindre märgborre
-Tjäder</t>
+          <t>Garnlav
+Motaggsvamp</t>
         </is>
       </c>
       <c r="W61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63138-2025 artfynd.xlsx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 14001-2023 artfynd.xlsx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="X61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63138-2025 karta.png", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 14001-2023 karta.png", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="Y61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63138-2025 georefererad karta.tif", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 14001-2023 georefererad karta.tif", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AA61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63138-2025 FSC-klagomål.docx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 14001-2023 FSC-klagomål.docx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AB61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63138-2025 FSC-klagomål mail.docx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 14001-2023 FSC-klagomål mail.docx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AC61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63138-2025 tillsynsbegäran.docx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 14001-2023 tillsynsbegäran.docx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AD61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63138-2025 tillsynsbegäran mail.docx", "A 63138-2025")</f>
-        <v/>
-      </c>
-      <c r="AE61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 63138-2025 prioriterade fågelarter.docx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 14001-2023 tillsynsbegäran mail.docx", "A 14001-2023")</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 41204-2023</t>
+          <t>A 13971-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7939,10 +7934,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45174</v>
+        <v>45007</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7954,20 +7949,25 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
         <v>0</v>
@@ -7979,63 +7979,59 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>2</v>
       </c>
       <c r="T62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>Knärot
-Vedtrappmossa</t>
+          <t>Dubbelnycklar
+Fläcknycklar</t>
         </is>
       </c>
       <c r="W62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 41204-2023 artfynd.xlsx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 13971-2023 artfynd.xlsx", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="X62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 41204-2023 karta.png", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 13971-2023 karta.png", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="Y62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 41204-2023 georefererad karta.tif", "A 41204-2023")</f>
-        <v/>
-      </c>
-      <c r="Z62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 41204-2023 karta knärot.png", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 13971-2023 georefererad karta.tif", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="AA62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 41204-2023 FSC-klagomål.docx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 13971-2023 FSC-klagomål.docx", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="AB62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 41204-2023 FSC-klagomål mail.docx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 13971-2023 FSC-klagomål mail.docx", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="AC62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 41204-2023 tillsynsbegäran.docx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 13971-2023 tillsynsbegäran.docx", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="AD62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 41204-2023 tillsynsbegäran mail.docx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 13971-2023 tillsynsbegäran mail.docx", "A 13971-2023")</f>
         <v/>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 11501-2023</t>
+          <t>A 47453-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -8049,10 +8045,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44991</v>
+        <v>45587</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8064,22 +8060,17 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="J63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
@@ -8094,7 +8085,7 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
@@ -8106,47 +8097,51 @@
         <v>2</v>
       </c>
       <c r="U63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva
-Nattviol</t>
+          <t>Göktyta
+Gröngöling</t>
         </is>
       </c>
       <c r="W63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 11501-2023 artfynd.xlsx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 47453-2024 artfynd.xlsx", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="X63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 11501-2023 karta.png", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 47453-2024 karta.png", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="Y63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 11501-2023 georefererad karta.tif", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 47453-2024 georefererad karta.tif", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="AA63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 11501-2023 FSC-klagomål.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 47453-2024 FSC-klagomål.docx", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="AB63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 11501-2023 FSC-klagomål mail.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 47453-2024 FSC-klagomål mail.docx", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="AC63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 11501-2023 tillsynsbegäran.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 47453-2024 tillsynsbegäran.docx", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="AD63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 11501-2023 tillsynsbegäran mail.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 47453-2024 tillsynsbegäran mail.docx", "A 47453-2024")</f>
+        <v/>
+      </c>
+      <c r="AE63">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 47453-2024 prioriterade fågelarter.docx", "A 47453-2024")</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 14001-2023</t>
+          <t>A 11501-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -8160,10 +8155,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45007</v>
+        <v>44991</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8181,19 +8176,19 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
@@ -8205,10 +8200,10 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>2</v>
@@ -8217,47 +8212,47 @@
         <v>2</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>Garnlav
-Motaggsvamp</t>
+          <t>Svart trolldruva
+Nattviol</t>
         </is>
       </c>
       <c r="W64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 14001-2023 artfynd.xlsx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 11501-2023 artfynd.xlsx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="X64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 14001-2023 karta.png", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 11501-2023 karta.png", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="Y64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 14001-2023 georefererad karta.tif", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 11501-2023 georefererad karta.tif", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AA64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 14001-2023 FSC-klagomål.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 11501-2023 FSC-klagomål.docx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AB64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 14001-2023 FSC-klagomål mail.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 11501-2023 FSC-klagomål mail.docx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AC64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 14001-2023 tillsynsbegäran.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 11501-2023 tillsynsbegäran.docx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AD64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 14001-2023 tillsynsbegäran mail.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 11501-2023 tillsynsbegäran mail.docx", "A 11501-2023")</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 36261-2026</t>
+          <t>A 63138-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -8271,10 +8266,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46268</v>
+        <v>46009</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8288,20 +8283,20 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>7.9</v>
+        <v>2.5</v>
       </c>
       <c r="J65" t="n">
         <v>1</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
@@ -8316,7 +8311,7 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
@@ -8325,50 +8320,54 @@
         <v>2</v>
       </c>
       <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
         <v>2</v>
       </c>
-      <c r="U65" t="n">
-        <v>0</v>
-      </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>Krusfrö
-Revlummer</t>
+          <t>Mindre märgborre
+Tjäder</t>
         </is>
       </c>
       <c r="W65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 36261-2026 artfynd.xlsx", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63138-2025 artfynd.xlsx", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="X65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 36261-2026 karta.png", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63138-2025 karta.png", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="Y65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 36261-2026 georefererad karta.tif", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63138-2025 georefererad karta.tif", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="AA65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 36261-2026 FSC-klagomål.docx", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63138-2025 FSC-klagomål.docx", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="AB65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 36261-2026 FSC-klagomål mail.docx", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63138-2025 FSC-klagomål mail.docx", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="AC65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 36261-2026 tillsynsbegäran.docx", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63138-2025 tillsynsbegäran.docx", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="AD65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 36261-2026 tillsynsbegäran mail.docx", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63138-2025 tillsynsbegäran mail.docx", "A 63138-2025")</f>
+        <v/>
+      </c>
+      <c r="AE65">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 63138-2025 prioriterade fågelarter.docx", "A 63138-2025")</f>
         <v/>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 13971-2023</t>
+          <t>A 37013-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -8382,10 +8381,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45007</v>
+        <v>45874</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8403,20 +8402,20 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.9</v>
+        <v>10.7</v>
       </c>
       <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
         <v>2</v>
       </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" t="n">
-        <v>0</v>
-      </c>
       <c r="N66" t="n">
         <v>0</v>
       </c>
@@ -8427,59 +8426,59 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S66" t="n">
         <v>2</v>
       </c>
       <c r="T66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>Dubbelnycklar
-Fläcknycklar</t>
+          <t>Brunfläckig pärlemorfjäril
+Fältgentiana</t>
         </is>
       </c>
       <c r="W66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 13971-2023 artfynd.xlsx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37013-2025 artfynd.xlsx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="X66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 13971-2023 karta.png", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37013-2025 karta.png", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="Y66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 13971-2023 georefererad karta.tif", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37013-2025 georefererad karta.tif", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AA66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 13971-2023 FSC-klagomål.docx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37013-2025 FSC-klagomål.docx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AB66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 13971-2023 FSC-klagomål mail.docx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37013-2025 FSC-klagomål mail.docx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AC66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 13971-2023 tillsynsbegäran.docx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37013-2025 tillsynsbegäran.docx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AD66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 13971-2023 tillsynsbegäran mail.docx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37013-2025 tillsynsbegäran mail.docx", "A 37013-2025")</f>
         <v/>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 13788-2025</t>
+          <t>A 36261-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -8493,10 +8492,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45737</v>
+        <v>46268</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8508,11 +8507,16 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>9.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -8545,44 +8549,40 @@
         <v>2</v>
       </c>
       <c r="U67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>Sparvuggla
-Nattskärra</t>
+          <t>Krusfrö
+Revlummer</t>
         </is>
       </c>
       <c r="W67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 13788-2025 artfynd.xlsx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 36261-2026 artfynd.xlsx", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="X67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 13788-2025 karta.png", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 36261-2026 karta.png", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="Y67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 13788-2025 georefererad karta.tif", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 36261-2026 georefererad karta.tif", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="AA67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 13788-2025 FSC-klagomål.docx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 36261-2026 FSC-klagomål.docx", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="AB67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 13788-2025 FSC-klagomål mail.docx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 36261-2026 FSC-klagomål mail.docx", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="AC67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 13788-2025 tillsynsbegäran.docx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 36261-2026 tillsynsbegäran.docx", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="AD67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 13788-2025 tillsynsbegäran mail.docx", "A 13788-2025")</f>
-        <v/>
-      </c>
-      <c r="AE67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 13788-2025 prioriterade fågelarter.docx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 36261-2026 tillsynsbegäran mail.docx", "A 36261-2026")</f>
         <v/>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
         <v>45720</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8717,7 +8717,7 @@
         <v>44696</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>44739</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>44524</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>44696</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 30076-2023</t>
+          <t>A 34955-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -9154,10 +9154,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45110</v>
+        <v>44796</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9175,16 +9175,16 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -9199,7 +9199,7 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R73" t="n">
         <v>0</v>
@@ -9211,46 +9211,46 @@
         <v>1</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 30076-2023 artfynd.xlsx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34955-2022 artfynd.xlsx", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="X73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 30076-2023 karta.png", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34955-2022 karta.png", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="Y73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 30076-2023 georefererad karta.tif", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34955-2022 georefererad karta.tif", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="AA73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 30076-2023 FSC-klagomål.docx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34955-2022 FSC-klagomål.docx", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="AB73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 30076-2023 FSC-klagomål mail.docx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34955-2022 FSC-klagomål mail.docx", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="AC73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 30076-2023 tillsynsbegäran.docx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34955-2022 tillsynsbegäran.docx", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="AD73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 30076-2023 tillsynsbegäran mail.docx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34955-2022 tillsynsbegäran mail.docx", "A 34955-2022")</f>
         <v/>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 8553-2023</t>
+          <t>A 33231-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -9260,14 +9260,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44977</v>
+        <v>45518</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9281,7 +9281,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I74" t="n">
@@ -9297,7 +9297,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
         <v>0</v>
@@ -9309,10 +9309,10 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>1</v>
@@ -9321,46 +9321,46 @@
         <v>1</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>Väddnätfjäril</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="W74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 8553-2023 artfynd.xlsx", "A 8553-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 33231-2024 artfynd.xlsx", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="X74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 8553-2023 karta.png", "A 8553-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 33231-2024 karta.png", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="Y74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 8553-2023 georefererad karta.tif", "A 8553-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 33231-2024 georefererad karta.tif", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="AA74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 8553-2023 FSC-klagomål.docx", "A 8553-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 33231-2024 FSC-klagomål.docx", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="AB74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 8553-2023 FSC-klagomål mail.docx", "A 8553-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 33231-2024 FSC-klagomål mail.docx", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="AC74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 8553-2023 tillsynsbegäran.docx", "A 8553-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 33231-2024 tillsynsbegäran.docx", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="AD74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 8553-2023 tillsynsbegäran mail.docx", "A 8553-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 33231-2024 tillsynsbegäran mail.docx", "A 33231-2024")</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 37287-2023</t>
+          <t>A 30076-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -9374,10 +9374,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45156</v>
+        <v>45110</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9389,17 +9389,22 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -9414,7 +9419,7 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
         <v>0</v>
@@ -9430,35 +9435,35 @@
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>Mindre tåtelsmygare</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37287-2023 artfynd.xlsx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 30076-2023 artfynd.xlsx", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="X75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37287-2023 karta.png", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 30076-2023 karta.png", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="Y75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37287-2023 georefererad karta.tif", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 30076-2023 georefererad karta.tif", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="AA75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37287-2023 FSC-klagomål.docx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 30076-2023 FSC-klagomål.docx", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="AB75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37287-2023 FSC-klagomål mail.docx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 30076-2023 FSC-klagomål mail.docx", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="AC75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37287-2023 tillsynsbegäran.docx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 30076-2023 tillsynsbegäran.docx", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="AD75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37287-2023 tillsynsbegäran mail.docx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 30076-2023 tillsynsbegäran mail.docx", "A 30076-2023")</f>
         <v/>
       </c>
     </row>
@@ -9482,7 +9487,7 @@
         <v>44817</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9575,7 +9580,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 17632-2022</t>
+          <t>A 10883-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -9589,10 +9594,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44680</v>
+        <v>44991</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9604,17 +9609,22 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>5.2</v>
+        <v>12.5</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -9629,7 +9639,7 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R77" t="n">
         <v>0</v>
@@ -9641,46 +9651,50 @@
         <v>1</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="W77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 17632-2022 artfynd.xlsx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 10883-2023 artfynd.xlsx", "A 10883-2023")</f>
         <v/>
       </c>
       <c r="X77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 17632-2022 karta.png", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 10883-2023 karta.png", "A 10883-2023")</f>
         <v/>
       </c>
       <c r="Y77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 17632-2022 georefererad karta.tif", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 10883-2023 georefererad karta.tif", "A 10883-2023")</f>
         <v/>
       </c>
       <c r="AA77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 17632-2022 FSC-klagomål.docx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 10883-2023 FSC-klagomål.docx", "A 10883-2023")</f>
         <v/>
       </c>
       <c r="AB77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 17632-2022 FSC-klagomål mail.docx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 10883-2023 FSC-klagomål mail.docx", "A 10883-2023")</f>
         <v/>
       </c>
       <c r="AC77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 17632-2022 tillsynsbegäran.docx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 10883-2023 tillsynsbegäran.docx", "A 10883-2023")</f>
         <v/>
       </c>
       <c r="AD77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 17632-2022 tillsynsbegäran mail.docx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 10883-2023 tillsynsbegäran mail.docx", "A 10883-2023")</f>
+        <v/>
+      </c>
+      <c r="AE77">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 10883-2023 prioriterade fågelarter.docx", "A 10883-2023")</f>
         <v/>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 34955-2022</t>
+          <t>A 24167-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -9690,14 +9704,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44796</v>
+        <v>45456</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9709,22 +9723,17 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>4.6</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
@@ -9739,7 +9748,7 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
         <v>0</v>
@@ -9751,46 +9760,46 @@
         <v>1</v>
       </c>
       <c r="U78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34955-2022 artfynd.xlsx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 24167-2024 artfynd.xlsx", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="X78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34955-2022 karta.png", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 24167-2024 karta.png", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="Y78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34955-2022 georefererad karta.tif", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 24167-2024 georefererad karta.tif", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="AA78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34955-2022 FSC-klagomål.docx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 24167-2024 FSC-klagomål.docx", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="AB78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34955-2022 FSC-klagomål mail.docx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 24167-2024 FSC-klagomål mail.docx", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="AC78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34955-2022 tillsynsbegäran.docx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 24167-2024 tillsynsbegäran.docx", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="AD78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34955-2022 tillsynsbegäran mail.docx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 24167-2024 tillsynsbegäran mail.docx", "A 24167-2024")</f>
         <v/>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 10883-2023</t>
+          <t>A 37287-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -9804,10 +9813,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44991</v>
+        <v>45156</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9819,16 +9828,11 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>12.5</v>
+        <v>0.6</v>
       </c>
       <c r="J79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -9861,43 +9865,39 @@
         <v>1</v>
       </c>
       <c r="U79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="W79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 10883-2023 artfynd.xlsx", "A 10883-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37287-2023 artfynd.xlsx", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="X79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 10883-2023 karta.png", "A 10883-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37287-2023 karta.png", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="Y79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 10883-2023 georefererad karta.tif", "A 10883-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37287-2023 georefererad karta.tif", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="AA79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 10883-2023 FSC-klagomål.docx", "A 10883-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37287-2023 FSC-klagomål.docx", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="AB79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 10883-2023 FSC-klagomål mail.docx", "A 10883-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37287-2023 FSC-klagomål mail.docx", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="AC79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 10883-2023 tillsynsbegäran.docx", "A 10883-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37287-2023 tillsynsbegäran.docx", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="AD79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 10883-2023 tillsynsbegäran mail.docx", "A 10883-2023")</f>
-        <v/>
-      </c>
-      <c r="AE79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 10883-2023 prioriterade fågelarter.docx", "A 10883-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37287-2023 tillsynsbegäran mail.docx", "A 37287-2023")</f>
         <v/>
       </c>
     </row>
@@ -9921,7 +9921,7 @@
         <v>45573</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 33231-2024</t>
+          <t>A 8553-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -10024,14 +10024,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45518</v>
+        <v>44977</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I81" t="n">
@@ -10061,7 +10061,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N81" t="n">
         <v>0</v>
@@ -10073,10 +10073,10 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S81" t="n">
         <v>1</v>
@@ -10085,46 +10085,46 @@
         <v>1</v>
       </c>
       <c r="U81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="W81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 33231-2024 artfynd.xlsx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 8553-2023 artfynd.xlsx", "A 8553-2023")</f>
         <v/>
       </c>
       <c r="X81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 33231-2024 karta.png", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 8553-2023 karta.png", "A 8553-2023")</f>
         <v/>
       </c>
       <c r="Y81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 33231-2024 georefererad karta.tif", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 8553-2023 georefererad karta.tif", "A 8553-2023")</f>
         <v/>
       </c>
       <c r="AA81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 33231-2024 FSC-klagomål.docx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 8553-2023 FSC-klagomål.docx", "A 8553-2023")</f>
         <v/>
       </c>
       <c r="AB81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 33231-2024 FSC-klagomål mail.docx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 8553-2023 FSC-klagomål mail.docx", "A 8553-2023")</f>
         <v/>
       </c>
       <c r="AC81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 33231-2024 tillsynsbegäran.docx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 8553-2023 tillsynsbegäran.docx", "A 8553-2023")</f>
         <v/>
       </c>
       <c r="AD81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 33231-2024 tillsynsbegäran mail.docx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 8553-2023 tillsynsbegäran mail.docx", "A 8553-2023")</f>
         <v/>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 24167-2024</t>
+          <t>A 16013-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -10134,14 +10134,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45456</v>
+        <v>45026</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10154,10 +10154,10 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
       <c r="J82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -10166,7 +10166,7 @@
         <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N82" t="n">
         <v>0</v>
@@ -10178,10 +10178,10 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S82" t="n">
         <v>1</v>
@@ -10194,42 +10194,42 @@
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="W82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 24167-2024 artfynd.xlsx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 16013-2023 artfynd.xlsx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="X82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 24167-2024 karta.png", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 16013-2023 karta.png", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="Y82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 24167-2024 georefererad karta.tif", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 16013-2023 georefererad karta.tif", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AA82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 24167-2024 FSC-klagomål.docx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 16013-2023 FSC-klagomål.docx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AB82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 24167-2024 FSC-klagomål mail.docx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 16013-2023 FSC-klagomål mail.docx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AC82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 24167-2024 tillsynsbegäran.docx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 16013-2023 tillsynsbegäran.docx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AD82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 24167-2024 tillsynsbegäran mail.docx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 16013-2023 tillsynsbegäran mail.docx", "A 16013-2023")</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 31589-2026</t>
+          <t>A 17632-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -10243,10 +10243,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46224</v>
+        <v>44680</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10258,13 +10258,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -10304,42 +10299,42 @@
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="W83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31589-2026 artfynd.xlsx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 17632-2022 artfynd.xlsx", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="X83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31589-2026 karta.png", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 17632-2022 karta.png", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="Y83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31589-2026 georefererad karta.tif", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 17632-2022 georefererad karta.tif", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="AA83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31589-2026 FSC-klagomål.docx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 17632-2022 FSC-klagomål.docx", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="AB83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31589-2026 FSC-klagomål mail.docx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 17632-2022 FSC-klagomål mail.docx", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="AC83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31589-2026 tillsynsbegäran.docx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 17632-2022 tillsynsbegäran.docx", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="AD83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31589-2026 tillsynsbegäran mail.docx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 17632-2022 tillsynsbegäran mail.docx", "A 17632-2022")</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 16013-2023</t>
+          <t>A 34584-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -10353,10 +10348,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45026</v>
+        <v>45846</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10368,11 +10363,16 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
         <v>0</v>
@@ -10393,10 +10393,10 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>1</v>
@@ -10405,46 +10405,50 @@
         <v>1</v>
       </c>
       <c r="U84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 16013-2023 artfynd.xlsx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34584-2025 artfynd.xlsx", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="X84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 16013-2023 karta.png", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34584-2025 karta.png", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="Y84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 16013-2023 georefererad karta.tif", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34584-2025 georefererad karta.tif", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="AA84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 16013-2023 FSC-klagomål.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34584-2025 FSC-klagomål.docx", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="AB84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 16013-2023 FSC-klagomål mail.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34584-2025 FSC-klagomål mail.docx", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="AC84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 16013-2023 tillsynsbegäran.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34584-2025 tillsynsbegäran.docx", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="AD84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 16013-2023 tillsynsbegäran mail.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34584-2025 tillsynsbegäran mail.docx", "A 34584-2025")</f>
+        <v/>
+      </c>
+      <c r="AE84">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 34584-2025 prioriterade fågelarter.docx", "A 34584-2025")</f>
         <v/>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 34584-2025</t>
+          <t>A 31589-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -10458,10 +10462,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45846</v>
+        <v>46224</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10475,17 +10479,17 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.7</v>
+        <v>7</v>
       </c>
       <c r="J85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -10515,43 +10519,39 @@
         <v>1</v>
       </c>
       <c r="U85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34584-2025 artfynd.xlsx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31589-2026 artfynd.xlsx", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="X85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34584-2025 karta.png", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31589-2026 karta.png", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="Y85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34584-2025 georefererad karta.tif", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31589-2026 georefererad karta.tif", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="AA85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34584-2025 FSC-klagomål.docx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31589-2026 FSC-klagomål.docx", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="AB85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34584-2025 FSC-klagomål mail.docx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31589-2026 FSC-klagomål mail.docx", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="AC85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34584-2025 tillsynsbegäran.docx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31589-2026 tillsynsbegäran.docx", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="AD85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34584-2025 tillsynsbegäran mail.docx", "A 34584-2025")</f>
-        <v/>
-      </c>
-      <c r="AE85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 34584-2025 prioriterade fågelarter.docx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31589-2026 tillsynsbegäran mail.docx", "A 31589-2026")</f>
         <v/>
       </c>
     </row>
@@ -10575,7 +10575,7 @@
         <v>44509</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>44696</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>44782</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         <v>44550</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>44586</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>44582</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>44694</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 66342-2021</t>
+          <t>A 34957-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44518</v>
+        <v>44796</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -11172,7 +11172,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 34957-2022</t>
+          <t>A 66342-2021</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -11186,10 +11186,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44796</v>
+        <v>44518</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -11267,7 +11267,7 @@
         <v>45205</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 15743-2023</t>
+          <t>A 15739-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -11345,7 +11345,7 @@
         <v>45021</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -11401,7 +11401,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 15637-2022</t>
+          <t>A 33931-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -11415,10 +11415,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44662</v>
+        <v>44790</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 19786-2023</t>
+          <t>A 22662-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -11484,14 +11484,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45050</v>
+        <v>45071</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11505,11 +11505,11 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>8.1</v>
+        <v>0.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -11552,7 +11552,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 7787-2024</t>
+          <t>A 21509-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -11566,10 +11566,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45348</v>
+        <v>45441</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11581,8 +11581,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -11625,7 +11630,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 72367-2021</t>
+          <t>A 42832-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -11635,14 +11640,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44545</v>
+        <v>44832</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11655,7 +11660,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -11698,7 +11703,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 33931-2022</t>
+          <t>A 42841-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -11708,14 +11713,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44790</v>
+        <v>44832</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11728,7 +11733,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -11788,7 +11793,7 @@
         <v>45079</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11849,7 +11854,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 37954-2025</t>
+          <t>A 25450-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -11863,10 +11868,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45881</v>
+        <v>45463</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11878,8 +11883,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>9.5</v>
+        <v>2.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -11922,7 +11932,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 32808-2024</t>
+          <t>A 24665-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -11936,10 +11946,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45516</v>
+        <v>45084</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11951,13 +11961,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -12000,7 +12005,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 42714-2022</t>
+          <t>A 3818-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -12014,10 +12019,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44832</v>
+        <v>44587</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12030,7 +12035,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -12073,7 +12078,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 35682-2022</t>
+          <t>A 72367-2021</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -12087,10 +12092,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44799</v>
+        <v>44545</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12102,13 +12107,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -12151,7 +12151,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 11728-2023</t>
+          <t>A 42714-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -12161,14 +12161,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44993</v>
+        <v>44832</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12180,13 +12180,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -12229,7 +12224,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 5567-2022</t>
+          <t>A 19782-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -12243,10 +12238,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44595</v>
+        <v>45050</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12258,8 +12253,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>1.3</v>
+        <v>5.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -12302,7 +12302,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 42832-2022</t>
+          <t>A 14626-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -12312,14 +12312,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44832</v>
+        <v>45012</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12331,8 +12331,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -12375,7 +12380,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 49058-2024</t>
+          <t>A 19099-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -12389,10 +12394,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45594</v>
+        <v>44691</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12406,11 +12411,11 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>11.4</v>
+        <v>3.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -12453,7 +12458,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 24665-2023</t>
+          <t>A 56378-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -12467,10 +12472,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45084</v>
+        <v>45236</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12482,8 +12487,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>0.9</v>
+        <v>4.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -12526,7 +12536,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 20535-2026</t>
+          <t>A 11728-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -12536,14 +12546,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46140</v>
+        <v>44993</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12561,7 +12571,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.7</v>
+        <v>0.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -12604,7 +12614,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 42841-2022</t>
+          <t>A 25780-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -12614,14 +12624,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44832</v>
+        <v>45090</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12634,7 +12644,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -12677,7 +12687,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 42829-2022</t>
+          <t>A 55873-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -12687,14 +12697,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44832</v>
+        <v>45973</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12706,8 +12716,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -12750,7 +12765,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 2867-2024</t>
+          <t>A 20904-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -12760,14 +12775,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45315</v>
+        <v>45060</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12781,11 +12796,11 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -12828,7 +12843,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 3085-2023</t>
+          <t>A 35682-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -12842,10 +12857,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44946</v>
+        <v>44799</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12859,11 +12874,11 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>13</v>
+        <v>1.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -12906,7 +12921,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 55873-2025</t>
+          <t>A 42829-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -12916,14 +12931,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45973</v>
+        <v>44832</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12935,13 +12950,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -12984,7 +12994,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 24201-2026</t>
+          <t>A 2867-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -12998,10 +13008,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46168</v>
+        <v>45315</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13013,8 +13023,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -13057,7 +13072,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 20904-2023</t>
+          <t>A 2660-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -13067,14 +13082,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45060</v>
+        <v>45310</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13086,13 +13101,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -13135,7 +13145,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 2660-2024</t>
+          <t>A 4724-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -13149,10 +13159,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45310</v>
+        <v>46048</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13165,7 +13175,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -13208,7 +13218,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 4724-2026</t>
+          <t>A 4734-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -13225,7 +13235,7 @@
         <v>46048</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13238,7 +13248,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -13281,7 +13291,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 4734-2026</t>
+          <t>A 5567-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -13295,10 +13305,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46048</v>
+        <v>44595</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13311,7 +13321,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -13354,7 +13364,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 22628-2026</t>
+          <t>A 10244-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -13368,10 +13378,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46155</v>
+        <v>46076</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13385,11 +13395,11 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -13432,7 +13442,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 14626-2023</t>
+          <t>A 10249-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -13446,10 +13456,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45012</v>
+        <v>46076</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13463,11 +13473,11 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -13510,7 +13520,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 10249-2026</t>
+          <t>A 10562-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -13524,10 +13534,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13541,11 +13551,11 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -13588,7 +13598,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 10244-2026</t>
+          <t>A 3085-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -13602,10 +13612,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46076</v>
+        <v>44946</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13619,11 +13629,11 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>8.699999999999999</v>
+        <v>13</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -13666,7 +13676,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 10562-2026</t>
+          <t>A 12841-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -13680,10 +13690,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46077</v>
+        <v>46091</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13697,11 +13707,11 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -13744,7 +13754,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 12841-2026</t>
+          <t>A 7848-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -13758,10 +13768,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46091</v>
+        <v>44608</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13773,13 +13783,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -13822,7 +13827,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 25450-2024</t>
+          <t>A 15743-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -13836,10 +13841,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45463</v>
+        <v>45021</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13851,13 +13856,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -13900,7 +13900,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 19782-2023</t>
+          <t>A 19246-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -13910,14 +13910,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45050</v>
+        <v>46132</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13931,11 +13931,11 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>5.2</v>
+        <v>1.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -13978,7 +13978,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 19246-2026</t>
+          <t>A 15637-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -13988,14 +13988,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46132</v>
+        <v>44662</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14007,13 +14007,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -14056,7 +14051,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 7848-2022</t>
+          <t>A 37954-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -14070,10 +14065,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44608</v>
+        <v>45881</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14086,7 +14081,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.1</v>
+        <v>9.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -14129,7 +14124,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 56378-2023</t>
+          <t>A 19786-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -14143,10 +14138,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45236</v>
+        <v>45050</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14164,7 +14159,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4.6</v>
+        <v>8.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -14207,7 +14202,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 19099-2022</t>
+          <t>A 32808-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -14221,10 +14216,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44691</v>
+        <v>45516</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14242,7 +14237,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -14285,7 +14280,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 33933-2026</t>
+          <t>A 20535-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -14295,14 +14290,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46248</v>
+        <v>46140</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14320,7 +14315,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -14363,7 +14358,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 31061-2026</t>
+          <t>A 49058-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -14377,10 +14372,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46215</v>
+        <v>45594</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14398,7 +14393,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>4.4</v>
+        <v>11.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -14441,7 +14436,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 3818-2022</t>
+          <t>A 7787-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -14455,10 +14450,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44587</v>
+        <v>45348</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14471,7 +14466,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -14514,7 +14509,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 21509-2024</t>
+          <t>A 24201-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -14528,10 +14523,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45441</v>
+        <v>46168</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14543,13 +14538,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -14592,7 +14582,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 32501-2026</t>
+          <t>A 22628-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -14602,14 +14592,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46239</v>
+        <v>46155</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14621,8 +14611,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -14665,7 +14660,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 32223-2026</t>
+          <t>A 33933-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -14679,10 +14674,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46237</v>
+        <v>46248</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14696,11 +14691,11 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>8.199999999999999</v>
+        <v>3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -14743,7 +14738,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 22662-2023</t>
+          <t>A 31061-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -14753,14 +14748,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45071</v>
+        <v>46215</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14778,7 +14773,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.6</v>
+        <v>4.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -14821,7 +14816,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 25780-2023</t>
+          <t>A 32223-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -14835,10 +14830,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45090</v>
+        <v>46237</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14850,8 +14845,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>2.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -14894,7 +14894,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 15739-2023</t>
+          <t>A 32501-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -14904,14 +14904,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45021</v>
+        <v>46239</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -14984,7 +14984,7 @@
         <v>44734</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>44734</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>46251</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>

--- a/Översikt SURAHAMMAR.xlsx
+++ b/Översikt SURAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45470</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>45684</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 31280-2024</t>
+          <t>A 39697-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45504</v>
+        <v>45890</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,23 +964,23 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>6.9</v>
+        <v>25.7</v>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="K4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -992,21 +992,182 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="R4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
         <v>44</v>
       </c>
       <c r="T4" t="n">
+        <v>243</v>
+      </c>
+      <c r="U4" t="n">
+        <v>107</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Grönfink
+Knärot
+Bivråk
+Brunlångöra
+Dropptaggsvamp
+Fjällig taggsvamp s.str.
+Järnsparv
+Motaggsvamp
+Nordfladdermus
+Skarp dropptaggsvamp
+Skogshare
+Sotvaxskivling
+Sparvuggla
+Stornopping
+Talltita
+Älg
+Blodvaxing
+Gulgrön kantmusseron
+Honungsvaxing
+Luktvaxing
+Mindre märgborre
+Smal svampklubba
+Vedticka
+Gråspett
+Järpe
+Liljekonvalj
+Mattlummer
+Nattskärra
+Spillkråka
+Tjäder
+Tofsmes
+Dvärgpipistrell
+Gröngöling
+Kungsfågel
+Orre
+Slaguggla
+Större brunfladdermus
+Sångsvan
+Trana
+Trollpipistrell
+Vattenfladdermus
+Vanlig groda
+Fläcknycklar
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39697-2025 artfynd.xlsx", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39697-2025 karta.png", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39697-2025 georefererad karta.tif", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="Z4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 39697-2025 karta knärot.png", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39697-2025 FSC-klagomål.docx", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39697-2025 FSC-klagomål mail.docx", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39697-2025 tillsynsbegäran.docx", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39697-2025 tillsynsbegäran mail.docx", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39697-2025 prioriterade fågelarter.docx", "A 39697-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 31280-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45504</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K5" t="n">
+        <v>12</v>
+      </c>
+      <c r="L5" t="n">
+        <v>22</v>
+      </c>
+      <c r="M5" t="n">
+        <v>5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>27</v>
+      </c>
+      <c r="R5" t="n">
+        <v>5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>44</v>
+      </c>
+      <c r="T5" t="n">
         <v>93</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>91</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Gränsticka
 Knärot
@@ -1054,201 +1215,40 @@
 Lopplummer (aggregat)</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31280-2024 artfynd.xlsx", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31280-2024 karta.png", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31280-2024 georefererad karta.tif", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="Z4">
+      <c r="Z5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 31280-2024 karta knärot.png", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31280-2024 FSC-klagomål.docx", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31280-2024 FSC-klagomål mail.docx", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31280-2024 tillsynsbegäran.docx", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31280-2024 tillsynsbegäran mail.docx", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 31280-2024 prioriterade fågelarter.docx", "A 31280-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 39697-2025</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45890</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>28</v>
-      </c>
-      <c r="K5" t="n">
-        <v>7</v>
-      </c>
-      <c r="L5" t="n">
-        <v>14</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>16</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2</v>
-      </c>
-      <c r="S5" t="n">
-        <v>44</v>
-      </c>
-      <c r="T5" t="n">
-        <v>242</v>
-      </c>
-      <c r="U5" t="n">
-        <v>106</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Grönfink
-Knärot
-Bivråk
-Brunlångöra
-Dropptaggsvamp
-Fjällig taggsvamp s.str.
-Järnsparv
-Motaggsvamp
-Nordfladdermus
-Skarp dropptaggsvamp
-Skogshare
-Sotvaxskivling
-Sparvuggla
-Stornopping
-Talltita
-Älg
-Blodvaxing
-Gulgrön kantmusseron
-Honungsvaxing
-Luktvaxing
-Mindre märgborre
-Smal svampklubba
-Vedticka
-Gråspett
-Järpe
-Liljekonvalj
-Mattlummer
-Nattskärra
-Spillkråka
-Tjäder
-Tofsmes
-Dvärgpipistrell
-Gröngöling
-Kungsfågel
-Orre
-Slaguggla
-Större brunfladdermus
-Sångsvan
-Trana
-Trollpipistrell
-Vattenfladdermus
-Vanlig groda
-Fläcknycklar
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39697-2025 artfynd.xlsx", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39697-2025 karta.png", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39697-2025 georefererad karta.tif", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="Z5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 39697-2025 karta knärot.png", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39697-2025 FSC-klagomål.docx", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39697-2025 FSC-klagomål mail.docx", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39697-2025 tillsynsbegäran.docx", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39697-2025 tillsynsbegäran mail.docx", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39697-2025 prioriterade fågelarter.docx", "A 39697-2025")</f>
         <v/>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
         <v>45582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45169</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45139</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45782</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>45282</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>46216</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>46216</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>46237</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>44613</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>46085</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>45435</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>46215</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>46111</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 34040-2024</t>
+          <t>A 39594-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45523</v>
+        <v>45890</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2974,23 +2974,23 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="J19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -3005,18 +3005,261 @@
         <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>11</v>
       </c>
       <c r="T19" t="n">
+        <v>14</v>
+      </c>
+      <c r="U19" t="n">
+        <v>10</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Brunlångöra
+Dropptaggsvamp
+Gropticka
+Nordfladdermus
+Talltita
+Bronshjon
+Gullgröppa
+Vedticka
+Järpe
+Tjäder
+Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39594-2025 artfynd.xlsx", "A 39594-2025")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39594-2025 karta.png", "A 39594-2025")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39594-2025 georefererad karta.tif", "A 39594-2025")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39594-2025 FSC-klagomål.docx", "A 39594-2025")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39594-2025 FSC-klagomål mail.docx", "A 39594-2025")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39594-2025 tillsynsbegäran.docx", "A 39594-2025")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39594-2025 tillsynsbegäran mail.docx", "A 39594-2025")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39594-2025 prioriterade fågelarter.docx", "A 39594-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 42853-2022</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>44832</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>7</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>11</v>
+      </c>
+      <c r="T20" t="n">
+        <v>15</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Kandelabersvamp
+Mindre hackspett
+Blodvaxing
+Gulvaxing
+Luktvaxing
+Tvåblad
+Vitvaxing agg.
+Ängsfingersvamp
+Ängsvaxing agg.
+Skogsduva</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 42853-2022 artfynd.xlsx", "A 42853-2022")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 42853-2022 karta.png", "A 42853-2022")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 42853-2022 georefererad karta.tif", "A 42853-2022")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 42853-2022 FSC-klagomål.docx", "A 42853-2022")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 42853-2022 FSC-klagomål mail.docx", "A 42853-2022")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 42853-2022 tillsynsbegäran.docx", "A 42853-2022")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 42853-2022 tillsynsbegäran mail.docx", "A 42853-2022")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 42853-2022 prioriterade fågelarter.docx", "A 42853-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 34040-2024</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45523</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L21" t="n">
+        <v>3</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2</v>
+      </c>
+      <c r="S21" t="n">
+        <v>11</v>
+      </c>
+      <c r="T21" t="n">
         <v>28</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U21" t="n">
         <v>28</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Gränsticka
 Knärot
@@ -3031,283 +3274,40 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34040-2024 artfynd.xlsx", "A 34040-2024")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34040-2024 karta.png", "A 34040-2024")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34040-2024 georefererad karta.tif", "A 34040-2024")</f>
         <v/>
       </c>
-      <c r="Z19">
+      <c r="Z21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 34040-2024 karta knärot.png", "A 34040-2024")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34040-2024 FSC-klagomål.docx", "A 34040-2024")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34040-2024 FSC-klagomål mail.docx", "A 34040-2024")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34040-2024 tillsynsbegäran.docx", "A 34040-2024")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34040-2024 tillsynsbegäran mail.docx", "A 34040-2024")</f>
         <v/>
       </c>
-      <c r="AE19">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 34040-2024 prioriterade fågelarter.docx", "A 34040-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 39594-2025</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45890</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>7</v>
-      </c>
-      <c r="J20" t="n">
-        <v>6</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3</v>
-      </c>
-      <c r="L20" t="n">
-        <v>5</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>5</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>11</v>
-      </c>
-      <c r="T20" t="n">
-        <v>14</v>
-      </c>
-      <c r="U20" t="n">
-        <v>10</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Brunlångöra
-Dropptaggsvamp
-Gropticka
-Nordfladdermus
-Talltita
-Bronshjon
-Gullgröppa
-Vedticka
-Järpe
-Tjäder
-Dvärgpipistrell</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39594-2025 artfynd.xlsx", "A 39594-2025")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39594-2025 karta.png", "A 39594-2025")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39594-2025 georefererad karta.tif", "A 39594-2025")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39594-2025 FSC-klagomål.docx", "A 39594-2025")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39594-2025 FSC-klagomål mail.docx", "A 39594-2025")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39594-2025 tillsynsbegäran.docx", "A 39594-2025")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39594-2025 tillsynsbegäran mail.docx", "A 39594-2025")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39594-2025 prioriterade fågelarter.docx", "A 39594-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 42853-2022</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>44832</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3</v>
-      </c>
-      <c r="K21" t="n">
-        <v>7</v>
-      </c>
-      <c r="L21" t="n">
-        <v>2</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>11</v>
-      </c>
-      <c r="T21" t="n">
-        <v>15</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Kandelabersvamp
-Mindre hackspett
-Blodvaxing
-Gulvaxing
-Luktvaxing
-Tvåblad
-Vitvaxing agg.
-Ängsfingersvamp
-Ängsvaxing agg.
-Skogsduva</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 42853-2022 artfynd.xlsx", "A 42853-2022")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 42853-2022 karta.png", "A 42853-2022")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 42853-2022 georefererad karta.tif", "A 42853-2022")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 42853-2022 FSC-klagomål.docx", "A 42853-2022")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 42853-2022 FSC-klagomål mail.docx", "A 42853-2022")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 42853-2022 tillsynsbegäran.docx", "A 42853-2022")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 42853-2022 tillsynsbegäran mail.docx", "A 42853-2022")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 42853-2022 prioriterade fågelarter.docx", "A 42853-2022")</f>
         <v/>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
         <v>45070</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>44565</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 44798-2024</t>
+          <t>A 31060-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45574</v>
+        <v>46215</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3591,26 +3591,26 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3619,7 +3619,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -3628,12 +3628,134 @@
         <v>9</v>
       </c>
       <c r="T24" t="n">
+        <v>9</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Bombmurkla
+Brunlångöra
+Nordfladdermus
+Springkorn
+Vedticka
+Spillkråka
+Dvärgpipistrell
+Åkergroda
+Vanlig groda</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31060-2026 artfynd.xlsx", "A 31060-2026")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31060-2026 karta.png", "A 31060-2026")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31060-2026 georefererad karta.tif", "A 31060-2026")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31060-2026 FSC-klagomål.docx", "A 31060-2026")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31060-2026 FSC-klagomål mail.docx", "A 31060-2026")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31060-2026 tillsynsbegäran.docx", "A 31060-2026")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31060-2026 tillsynsbegäran mail.docx", "A 31060-2026")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 31060-2026 prioriterade fågelarter.docx", "A 31060-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 44798-2024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>45574</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>7</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>8</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>9</v>
+      </c>
+      <c r="T25" t="n">
         <v>26</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U25" t="n">
         <v>10</v>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Rosetticka
 Brunklöver
@@ -3646,154 +3768,32 @@
 Brandticka</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 44798-2024 artfynd.xlsx", "A 44798-2024")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 44798-2024 karta.png", "A 44798-2024")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 44798-2024 georefererad karta.tif", "A 44798-2024")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 44798-2024 FSC-klagomål.docx", "A 44798-2024")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 44798-2024 FSC-klagomål mail.docx", "A 44798-2024")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 44798-2024 tillsynsbegäran.docx", "A 44798-2024")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 44798-2024 tillsynsbegäran mail.docx", "A 44798-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 31060-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>46215</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J25" t="n">
-        <v>7</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2</v>
-      </c>
-      <c r="L25" t="n">
-        <v>2</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S25" t="n">
-        <v>9</v>
-      </c>
-      <c r="T25" t="n">
-        <v>9</v>
-      </c>
-      <c r="U25" t="n">
-        <v>3</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Bombmurkla
-Brunlångöra
-Nordfladdermus
-Springkorn
-Vedticka
-Spillkråka
-Dvärgpipistrell
-Åkergroda
-Vanlig groda</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31060-2026 artfynd.xlsx", "A 31060-2026")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31060-2026 karta.png", "A 31060-2026")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31060-2026 georefererad karta.tif", "A 31060-2026")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31060-2026 FSC-klagomål.docx", "A 31060-2026")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31060-2026 FSC-klagomål mail.docx", "A 31060-2026")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31060-2026 tillsynsbegäran.docx", "A 31060-2026")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31060-2026 tillsynsbegäran mail.docx", "A 31060-2026")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 31060-2026 prioriterade fågelarter.docx", "A 31060-2026")</f>
         <v/>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
         <v>45435</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>44518</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 38172-2024</t>
+          <t>A 56299-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4046,14 +4046,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45545</v>
+        <v>44477</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4067,23 +4067,23 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="J28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -4095,21 +4095,496 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>7</v>
       </c>
       <c r="T28" t="n">
+        <v>7</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Större flatbagge
+Tretåig hackspett
+Björksplintborre
+Blodticka
+Korallblylav
+Skinnlav
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 56299-2021 artfynd.xlsx", "A 56299-2021")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 56299-2021 karta.png", "A 56299-2021")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 56299-2021 georefererad karta.tif", "A 56299-2021")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 56299-2021 FSC-klagomål.docx", "A 56299-2021")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 56299-2021 FSC-klagomål mail.docx", "A 56299-2021")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 56299-2021 tillsynsbegäran.docx", "A 56299-2021")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 56299-2021 tillsynsbegäran mail.docx", "A 56299-2021")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 56299-2021 prioriterade fågelarter.docx", "A 56299-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A 48891-2023</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>45203</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>3</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1</v>
+      </c>
+      <c r="S29" t="n">
+        <v>7</v>
+      </c>
+      <c r="T29" t="n">
+        <v>10</v>
+      </c>
+      <c r="U29" t="n">
+        <v>5</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Motaggsvamp
+Tallticka
+Vintertagging
+Flagellkvastmossa
+Spillkråka
+Gröngöling</t>
+        </is>
+      </c>
+      <c r="W29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 48891-2023 artfynd.xlsx", "A 48891-2023")</f>
+        <v/>
+      </c>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 48891-2023 karta.png", "A 48891-2023")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 48891-2023 georefererad karta.tif", "A 48891-2023")</f>
+        <v/>
+      </c>
+      <c r="Z29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 48891-2023 karta knärot.png", "A 48891-2023")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 48891-2023 FSC-klagomål.docx", "A 48891-2023")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 48891-2023 FSC-klagomål mail.docx", "A 48891-2023")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 48891-2023 tillsynsbegäran.docx", "A 48891-2023")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 48891-2023 tillsynsbegäran mail.docx", "A 48891-2023")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 48891-2023 prioriterade fågelarter.docx", "A 48891-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A 22840-2023</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>45072</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>7</v>
+      </c>
+      <c r="T30" t="n">
+        <v>10</v>
+      </c>
+      <c r="U30" t="n">
+        <v>9</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Hultbräken
+Kärrviol
+Mattlummer
+Skogsstjärna
+Stjärnstarr
+Vitsippa
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 22840-2023 artfynd.xlsx", "A 22840-2023")</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 22840-2023 karta.png", "A 22840-2023")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 22840-2023 georefererad karta.tif", "A 22840-2023")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 22840-2023 FSC-klagomål.docx", "A 22840-2023")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 22840-2023 FSC-klagomål mail.docx", "A 22840-2023")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 22840-2023 tillsynsbegäran.docx", "A 22840-2023")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 22840-2023 tillsynsbegäran mail.docx", "A 22840-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A 36260-2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J31" t="n">
+        <v>4</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="n">
+        <v>2</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2</v>
+      </c>
+      <c r="S31" t="n">
+        <v>7</v>
+      </c>
+      <c r="T31" t="n">
         <v>8</v>
       </c>
-      <c r="U28" t="n">
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare
+Silverblåvinge
+Enkelbeckasin
+Blodticka
+Nattskärra
+Vanlig snok
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 36260-2026 artfynd.xlsx", "A 36260-2026")</f>
+        <v/>
+      </c>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 36260-2026 karta.png", "A 36260-2026")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 36260-2026 georefererad karta.tif", "A 36260-2026")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 36260-2026 FSC-klagomål.docx", "A 36260-2026")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 36260-2026 FSC-klagomål mail.docx", "A 36260-2026")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 36260-2026 tillsynsbegäran.docx", "A 36260-2026")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 36260-2026 tillsynsbegäran mail.docx", "A 36260-2026")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 36260-2026 prioriterade fågelarter.docx", "A 36260-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A 38172-2024</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>45545</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J32" t="n">
+        <v>5</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>3</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>4</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="n">
+        <v>7</v>
+      </c>
+      <c r="T32" t="n">
+        <v>8</v>
+      </c>
+      <c r="U32" t="n">
         <v>2</v>
       </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Gropticka
@@ -4120,515 +4595,40 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W28">
+      <c r="W32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 38172-2024 artfynd.xlsx", "A 38172-2024")</f>
         <v/>
       </c>
-      <c r="X28">
+      <c r="X32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 38172-2024 karta.png", "A 38172-2024")</f>
         <v/>
       </c>
-      <c r="Y28">
+      <c r="Y32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 38172-2024 georefererad karta.tif", "A 38172-2024")</f>
         <v/>
       </c>
-      <c r="Z28">
+      <c r="Z32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 38172-2024 karta knärot.png", "A 38172-2024")</f>
         <v/>
       </c>
-      <c r="AA28">
+      <c r="AA32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 38172-2024 FSC-klagomål.docx", "A 38172-2024")</f>
         <v/>
       </c>
-      <c r="AB28">
+      <c r="AB32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 38172-2024 FSC-klagomål mail.docx", "A 38172-2024")</f>
         <v/>
       </c>
-      <c r="AC28">
+      <c r="AC32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 38172-2024 tillsynsbegäran.docx", "A 38172-2024")</f>
         <v/>
       </c>
-      <c r="AD28">
+      <c r="AD32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 38172-2024 tillsynsbegäran mail.docx", "A 38172-2024")</f>
         <v/>
       </c>
-      <c r="AE28">
+      <c r="AE32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 38172-2024 prioriterade fågelarter.docx", "A 38172-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>A 56299-2021</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>44477</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>8</v>
-      </c>
-      <c r="J29" t="n">
-        <v>2</v>
-      </c>
-      <c r="K29" t="n">
-        <v>4</v>
-      </c>
-      <c r="L29" t="n">
-        <v>2</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>7</v>
-      </c>
-      <c r="T29" t="n">
-        <v>7</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>Större flatbagge
-Tretåig hackspett
-Björksplintborre
-Blodticka
-Korallblylav
-Skinnlav
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 56299-2021 artfynd.xlsx", "A 56299-2021")</f>
-        <v/>
-      </c>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 56299-2021 karta.png", "A 56299-2021")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 56299-2021 georefererad karta.tif", "A 56299-2021")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 56299-2021 FSC-klagomål.docx", "A 56299-2021")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 56299-2021 FSC-klagomål mail.docx", "A 56299-2021")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 56299-2021 tillsynsbegäran.docx", "A 56299-2021")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 56299-2021 tillsynsbegäran mail.docx", "A 56299-2021")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 56299-2021 prioriterade fågelarter.docx", "A 56299-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>A 48891-2023</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>45203</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J30" t="n">
-        <v>3</v>
-      </c>
-      <c r="K30" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" t="n">
-        <v>3</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>4</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1</v>
-      </c>
-      <c r="S30" t="n">
-        <v>7</v>
-      </c>
-      <c r="T30" t="n">
-        <v>10</v>
-      </c>
-      <c r="U30" t="n">
-        <v>5</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Motaggsvamp
-Tallticka
-Vintertagging
-Flagellkvastmossa
-Spillkråka
-Gröngöling</t>
-        </is>
-      </c>
-      <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 48891-2023 artfynd.xlsx", "A 48891-2023")</f>
-        <v/>
-      </c>
-      <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 48891-2023 karta.png", "A 48891-2023")</f>
-        <v/>
-      </c>
-      <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 48891-2023 georefererad karta.tif", "A 48891-2023")</f>
-        <v/>
-      </c>
-      <c r="Z30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 48891-2023 karta knärot.png", "A 48891-2023")</f>
-        <v/>
-      </c>
-      <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 48891-2023 FSC-klagomål.docx", "A 48891-2023")</f>
-        <v/>
-      </c>
-      <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 48891-2023 FSC-klagomål mail.docx", "A 48891-2023")</f>
-        <v/>
-      </c>
-      <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 48891-2023 tillsynsbegäran.docx", "A 48891-2023")</f>
-        <v/>
-      </c>
-      <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 48891-2023 tillsynsbegäran mail.docx", "A 48891-2023")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 48891-2023 prioriterade fågelarter.docx", "A 48891-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A 22840-2023</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>45072</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>7</v>
-      </c>
-      <c r="T31" t="n">
-        <v>10</v>
-      </c>
-      <c r="U31" t="n">
-        <v>9</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Hultbräken
-Kärrviol
-Mattlummer
-Skogsstjärna
-Stjärnstarr
-Vitsippa
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 22840-2023 artfynd.xlsx", "A 22840-2023")</f>
-        <v/>
-      </c>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 22840-2023 karta.png", "A 22840-2023")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 22840-2023 georefererad karta.tif", "A 22840-2023")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 22840-2023 FSC-klagomål.docx", "A 22840-2023")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 22840-2023 FSC-klagomål mail.docx", "A 22840-2023")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 22840-2023 tillsynsbegäran.docx", "A 22840-2023")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 22840-2023 tillsynsbegäran mail.docx", "A 22840-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>A 36260-2026</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>46268</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J32" t="n">
-        <v>4</v>
-      </c>
-      <c r="K32" t="n">
-        <v>1</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1</v>
-      </c>
-      <c r="M32" t="n">
-        <v>2</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>3</v>
-      </c>
-      <c r="R32" t="n">
-        <v>2</v>
-      </c>
-      <c r="S32" t="n">
-        <v>7</v>
-      </c>
-      <c r="T32" t="n">
-        <v>8</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>Mindre bastardsvärmare
-Silverblåvinge
-Enkelbeckasin
-Blodticka
-Nattskärra
-Vanlig snok
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 36260-2026 artfynd.xlsx", "A 36260-2026")</f>
-        <v/>
-      </c>
-      <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 36260-2026 karta.png", "A 36260-2026")</f>
-        <v/>
-      </c>
-      <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 36260-2026 georefererad karta.tif", "A 36260-2026")</f>
-        <v/>
-      </c>
-      <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 36260-2026 FSC-klagomål.docx", "A 36260-2026")</f>
-        <v/>
-      </c>
-      <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 36260-2026 FSC-klagomål mail.docx", "A 36260-2026")</f>
-        <v/>
-      </c>
-      <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 36260-2026 tillsynsbegäran.docx", "A 36260-2026")</f>
-        <v/>
-      </c>
-      <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 36260-2026 tillsynsbegäran mail.docx", "A 36260-2026")</f>
-        <v/>
-      </c>
-      <c r="AE32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 36260-2026 prioriterade fågelarter.docx", "A 36260-2026")</f>
         <v/>
       </c>
     </row>
@@ -4652,7 +4652,7 @@
         <v>45945</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>44518</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>46009</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>46076</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>44832</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>44832</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 25548-2024</t>
+          <t>A 10819-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5339,10 +5339,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45463</v>
+        <v>45369</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5354,22 +5354,17 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>5.1</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K39" t="n">
         <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" t="n">
         <v>1</v>
@@ -5384,7 +5379,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -5393,12 +5388,246 @@
         <v>4</v>
       </c>
       <c r="T39" t="n">
+        <v>8</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott
+Entita
+Tibast
+Näktergal</t>
+        </is>
+      </c>
+      <c r="W39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 10819-2024 artfynd.xlsx", "A 10819-2024")</f>
+        <v/>
+      </c>
+      <c r="X39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 10819-2024 karta.png", "A 10819-2024")</f>
+        <v/>
+      </c>
+      <c r="Y39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 10819-2024 georefererad karta.tif", "A 10819-2024")</f>
+        <v/>
+      </c>
+      <c r="AA39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 10819-2024 FSC-klagomål.docx", "A 10819-2024")</f>
+        <v/>
+      </c>
+      <c r="AB39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 10819-2024 FSC-klagomål mail.docx", "A 10819-2024")</f>
+        <v/>
+      </c>
+      <c r="AC39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 10819-2024 tillsynsbegäran.docx", "A 10819-2024")</f>
+        <v/>
+      </c>
+      <c r="AD39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 10819-2024 tillsynsbegäran mail.docx", "A 10819-2024")</f>
+        <v/>
+      </c>
+      <c r="AE39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 10819-2024 prioriterade fågelarter.docx", "A 10819-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>A 31176-2024</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="n">
+        <v>45503</v>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>2</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>4</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>4</v>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>Doftskinn
+Ullticka
+Tjäder
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31176-2024 artfynd.xlsx", "A 31176-2024")</f>
+        <v/>
+      </c>
+      <c r="X40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31176-2024 karta.png", "A 31176-2024")</f>
+        <v/>
+      </c>
+      <c r="Y40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31176-2024 georefererad karta.tif", "A 31176-2024")</f>
+        <v/>
+      </c>
+      <c r="AA40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31176-2024 FSC-klagomål.docx", "A 31176-2024")</f>
+        <v/>
+      </c>
+      <c r="AB40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31176-2024 FSC-klagomål mail.docx", "A 31176-2024")</f>
+        <v/>
+      </c>
+      <c r="AC40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31176-2024 tillsynsbegäran.docx", "A 31176-2024")</f>
+        <v/>
+      </c>
+      <c r="AD40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31176-2024 tillsynsbegäran mail.docx", "A 31176-2024")</f>
+        <v/>
+      </c>
+      <c r="AE40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 31176-2024 prioriterade fågelarter.docx", "A 31176-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>A 25548-2024</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="n">
+        <v>45463</v>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J41" t="n">
+        <v>3</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1</v>
+      </c>
+      <c r="S41" t="n">
+        <v>4</v>
+      </c>
+      <c r="T41" t="n">
         <v>9</v>
       </c>
-      <c r="U39" t="n">
+      <c r="U41" t="n">
         <v>6</v>
       </c>
-      <c r="V39" s="2" t="inlineStr">
+      <c r="V41" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Vedticka
@@ -5406,265 +5635,36 @@
 Nattviol</t>
         </is>
       </c>
-      <c r="W39">
+      <c r="W41">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 25548-2024 artfynd.xlsx", "A 25548-2024")</f>
         <v/>
       </c>
-      <c r="X39">
+      <c r="X41">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 25548-2024 karta.png", "A 25548-2024")</f>
         <v/>
       </c>
-      <c r="Y39">
+      <c r="Y41">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 25548-2024 georefererad karta.tif", "A 25548-2024")</f>
         <v/>
       </c>
-      <c r="Z39">
+      <c r="Z41">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 25548-2024 karta knärot.png", "A 25548-2024")</f>
         <v/>
       </c>
-      <c r="AA39">
+      <c r="AA41">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 25548-2024 FSC-klagomål.docx", "A 25548-2024")</f>
         <v/>
       </c>
-      <c r="AB39">
+      <c r="AB41">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 25548-2024 FSC-klagomål mail.docx", "A 25548-2024")</f>
         <v/>
       </c>
-      <c r="AC39">
+      <c r="AC41">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 25548-2024 tillsynsbegäran.docx", "A 25548-2024")</f>
         <v/>
       </c>
-      <c r="AD39">
+      <c r="AD41">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 25548-2024 tillsynsbegäran mail.docx", "A 25548-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>A 31176-2024</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="n">
-        <v>45503</v>
-      </c>
-      <c r="E40" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="J40" t="n">
-        <v>2</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>2</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>2</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>4</v>
-      </c>
-      <c r="T40" t="n">
-        <v>4</v>
-      </c>
-      <c r="U40" t="n">
-        <v>4</v>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>Doftskinn
-Ullticka
-Tjäder
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31176-2024 artfynd.xlsx", "A 31176-2024")</f>
-        <v/>
-      </c>
-      <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31176-2024 karta.png", "A 31176-2024")</f>
-        <v/>
-      </c>
-      <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31176-2024 georefererad karta.tif", "A 31176-2024")</f>
-        <v/>
-      </c>
-      <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31176-2024 FSC-klagomål.docx", "A 31176-2024")</f>
-        <v/>
-      </c>
-      <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31176-2024 FSC-klagomål mail.docx", "A 31176-2024")</f>
-        <v/>
-      </c>
-      <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31176-2024 tillsynsbegäran.docx", "A 31176-2024")</f>
-        <v/>
-      </c>
-      <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31176-2024 tillsynsbegäran mail.docx", "A 31176-2024")</f>
-        <v/>
-      </c>
-      <c r="AE40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 31176-2024 prioriterade fågelarter.docx", "A 31176-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>A 10819-2024</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="n">
-        <v>45369</v>
-      </c>
-      <c r="E41" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>2</v>
-      </c>
-      <c r="J41" t="n">
-        <v>2</v>
-      </c>
-      <c r="K41" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" t="n">
-        <v>1</v>
-      </c>
-      <c r="M41" t="n">
-        <v>1</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>2</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1</v>
-      </c>
-      <c r="S41" t="n">
-        <v>4</v>
-      </c>
-      <c r="T41" t="n">
-        <v>8</v>
-      </c>
-      <c r="U41" t="n">
-        <v>2</v>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott
-Entita
-Tibast
-Näktergal</t>
-        </is>
-      </c>
-      <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 10819-2024 artfynd.xlsx", "A 10819-2024")</f>
-        <v/>
-      </c>
-      <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 10819-2024 karta.png", "A 10819-2024")</f>
-        <v/>
-      </c>
-      <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 10819-2024 georefererad karta.tif", "A 10819-2024")</f>
-        <v/>
-      </c>
-      <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 10819-2024 FSC-klagomål.docx", "A 10819-2024")</f>
-        <v/>
-      </c>
-      <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 10819-2024 FSC-klagomål mail.docx", "A 10819-2024")</f>
-        <v/>
-      </c>
-      <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 10819-2024 tillsynsbegäran.docx", "A 10819-2024")</f>
-        <v/>
-      </c>
-      <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 10819-2024 tillsynsbegäran mail.docx", "A 10819-2024")</f>
-        <v/>
-      </c>
-      <c r="AE41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 10819-2024 prioriterade fågelarter.docx", "A 10819-2024")</f>
         <v/>
       </c>
     </row>
@@ -5688,7 +5688,7 @@
         <v>44518</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 39694-2025</t>
+          <t>A 49718-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5801,10 +5801,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45890</v>
+        <v>45212</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5816,13 +5816,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
@@ -5831,7 +5826,7 @@
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -5846,7 +5841,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -5855,380 +5850,385 @@
         <v>3</v>
       </c>
       <c r="T43" t="n">
+        <v>6</v>
+      </c>
+      <c r="U43" t="n">
+        <v>6</v>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Talltita
+Zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="W43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 49718-2023 artfynd.xlsx", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="X43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 49718-2023 karta.png", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="Y43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 49718-2023 georefererad karta.tif", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="AA43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 49718-2023 FSC-klagomål.docx", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="AB43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 49718-2023 FSC-klagomål mail.docx", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="AC43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 49718-2023 tillsynsbegäran.docx", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="AD43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 49718-2023 tillsynsbegäran mail.docx", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="AE43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 49718-2023 prioriterade fågelarter.docx", "A 49718-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>A 39694-2025</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="n">
+        <v>45890</v>
+      </c>
+      <c r="E44" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
         <v>3</v>
       </c>
-      <c r="U43" t="n">
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
         <v>2</v>
       </c>
-      <c r="V43" s="2" t="inlineStr">
+      <c r="V44" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Mindre märgborre
 Tjäder</t>
         </is>
       </c>
-      <c r="W43">
+      <c r="W44">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39694-2025 artfynd.xlsx", "A 39694-2025")</f>
         <v/>
       </c>
-      <c r="X43">
+      <c r="X44">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39694-2025 karta.png", "A 39694-2025")</f>
         <v/>
       </c>
-      <c r="Y43">
+      <c r="Y44">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39694-2025 georefererad karta.tif", "A 39694-2025")</f>
         <v/>
       </c>
-      <c r="AA43">
+      <c r="AA44">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39694-2025 FSC-klagomål.docx", "A 39694-2025")</f>
         <v/>
       </c>
-      <c r="AB43">
+      <c r="AB44">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39694-2025 FSC-klagomål mail.docx", "A 39694-2025")</f>
         <v/>
       </c>
-      <c r="AC43">
+      <c r="AC44">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39694-2025 tillsynsbegäran.docx", "A 39694-2025")</f>
         <v/>
       </c>
-      <c r="AD43">
+      <c r="AD44">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39694-2025 tillsynsbegäran mail.docx", "A 39694-2025")</f>
         <v/>
       </c>
-      <c r="AE43">
+      <c r="AE44">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39694-2025 prioriterade fågelarter.docx", "A 39694-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>A 42765-2022</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>44832</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>Krusfrö
+Barkticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 42765-2022 artfynd.xlsx", "A 42765-2022")</f>
+        <v/>
+      </c>
+      <c r="X45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 42765-2022 karta.png", "A 42765-2022")</f>
+        <v/>
+      </c>
+      <c r="Y45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 42765-2022 georefererad karta.tif", "A 42765-2022")</f>
+        <v/>
+      </c>
+      <c r="AA45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 42765-2022 FSC-klagomål.docx", "A 42765-2022")</f>
+        <v/>
+      </c>
+      <c r="AB45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 42765-2022 FSC-klagomål mail.docx", "A 42765-2022")</f>
+        <v/>
+      </c>
+      <c r="AC45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 42765-2022 tillsynsbegäran.docx", "A 42765-2022")</f>
+        <v/>
+      </c>
+      <c r="AD45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 42765-2022 tillsynsbegäran mail.docx", "A 42765-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>A 69777-2021</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D44" s="1" t="n">
+      <c r="D46" s="1" t="n">
         <v>44532</v>
       </c>
-      <c r="E44" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F44" t="inlineStr">
+      <c r="E46" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>VÄSTMANLANDS LÄN</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="I44" t="n">
+      <c r="I46" t="n">
         <v>2.3</v>
       </c>
-      <c r="J44" t="n">
-        <v>1</v>
-      </c>
-      <c r="K44" t="n">
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
         <v>2</v>
       </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>1</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>1</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1</v>
-      </c>
-      <c r="S44" t="n">
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
+      <c r="S46" t="n">
         <v>3</v>
       </c>
-      <c r="T44" t="n">
+      <c r="T46" t="n">
         <v>5</v>
       </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
         <is>
           <t>Bombmurkla
 Rävticka
 Vedticka</t>
         </is>
       </c>
-      <c r="W44">
+      <c r="W46">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 69777-2021 artfynd.xlsx", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="X44">
+      <c r="X46">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 69777-2021 karta.png", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="Y44">
+      <c r="Y46">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 69777-2021 georefererad karta.tif", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="AA44">
+      <c r="AA46">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 69777-2021 FSC-klagomål.docx", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="AB44">
+      <c r="AB46">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 69777-2021 FSC-klagomål mail.docx", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="AC44">
+      <c r="AC46">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 69777-2021 tillsynsbegäran.docx", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="AD44">
+      <c r="AD46">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 69777-2021 tillsynsbegäran mail.docx", "A 69777-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>A 49718-2023</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="n">
-        <v>45212</v>
-      </c>
-      <c r="E45" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J45" t="n">
-        <v>1</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1</v>
-      </c>
-      <c r="L45" t="n">
-        <v>2</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>2</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>3</v>
-      </c>
-      <c r="T45" t="n">
-        <v>6</v>
-      </c>
-      <c r="U45" t="n">
-        <v>6</v>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Talltita
-Zontaggsvamp</t>
-        </is>
-      </c>
-      <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 49718-2023 artfynd.xlsx", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 49718-2023 karta.png", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 49718-2023 georefererad karta.tif", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 49718-2023 FSC-klagomål.docx", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 49718-2023 FSC-klagomål mail.docx", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 49718-2023 tillsynsbegäran.docx", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 49718-2023 tillsynsbegäran mail.docx", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="AE45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 49718-2023 prioriterade fågelarter.docx", "A 49718-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>A 42765-2022</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="n">
-        <v>44832</v>
-      </c>
-      <c r="E46" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J46" t="n">
-        <v>1</v>
-      </c>
-      <c r="K46" t="n">
-        <v>1</v>
-      </c>
-      <c r="L46" t="n">
-        <v>1</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>1</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>3</v>
-      </c>
-      <c r="T46" t="n">
-        <v>4</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1</v>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>Krusfrö
-Barkticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 42765-2022 artfynd.xlsx", "A 42765-2022")</f>
-        <v/>
-      </c>
-      <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 42765-2022 karta.png", "A 42765-2022")</f>
-        <v/>
-      </c>
-      <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 42765-2022 georefererad karta.tif", "A 42765-2022")</f>
-        <v/>
-      </c>
-      <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 42765-2022 FSC-klagomål.docx", "A 42765-2022")</f>
-        <v/>
-      </c>
-      <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 42765-2022 FSC-klagomål mail.docx", "A 42765-2022")</f>
-        <v/>
-      </c>
-      <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 42765-2022 tillsynsbegäran.docx", "A 42765-2022")</f>
-        <v/>
-      </c>
-      <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 42765-2022 tillsynsbegäran mail.docx", "A 42765-2022")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 63146-2025</t>
+          <t>A 4082-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46009</v>
+        <v>45684</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6263,10 +6263,10 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>10.2</v>
+        <v>11.6</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K47" t="n">
         <v>2</v>
@@ -6296,268 +6296,268 @@
         <v>3</v>
       </c>
       <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>Grönpyrola
+Plattlummer
+Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="W47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 4082-2025 artfynd.xlsx", "A 4082-2025")</f>
+        <v/>
+      </c>
+      <c r="X47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 4082-2025 karta.png", "A 4082-2025")</f>
+        <v/>
+      </c>
+      <c r="Y47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 4082-2025 georefererad karta.tif", "A 4082-2025")</f>
+        <v/>
+      </c>
+      <c r="AA47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 4082-2025 FSC-klagomål.docx", "A 4082-2025")</f>
+        <v/>
+      </c>
+      <c r="AB47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 4082-2025 FSC-klagomål mail.docx", "A 4082-2025")</f>
+        <v/>
+      </c>
+      <c r="AC47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 4082-2025 tillsynsbegäran.docx", "A 4082-2025")</f>
+        <v/>
+      </c>
+      <c r="AD47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 4082-2025 tillsynsbegäran mail.docx", "A 4082-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>A 48128-2023</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D48" s="1" t="n">
+        <v>45205</v>
+      </c>
+      <c r="E48" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" t="n">
+        <v>2</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>2</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>3</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>Jungfrulin
+Svinrot
+Vedticka</t>
+        </is>
+      </c>
+      <c r="W48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 48128-2023 artfynd.xlsx", "A 48128-2023")</f>
+        <v/>
+      </c>
+      <c r="X48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 48128-2023 karta.png", "A 48128-2023")</f>
+        <v/>
+      </c>
+      <c r="Y48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 48128-2023 georefererad karta.tif", "A 48128-2023")</f>
+        <v/>
+      </c>
+      <c r="AA48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 48128-2023 FSC-klagomål.docx", "A 48128-2023")</f>
+        <v/>
+      </c>
+      <c r="AB48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 48128-2023 FSC-klagomål mail.docx", "A 48128-2023")</f>
+        <v/>
+      </c>
+      <c r="AC48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 48128-2023 tillsynsbegäran.docx", "A 48128-2023")</f>
+        <v/>
+      </c>
+      <c r="AD48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 48128-2023 tillsynsbegäran mail.docx", "A 48128-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>A 63146-2025</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D49" s="1" t="n">
+        <v>46009</v>
+      </c>
+      <c r="E49" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
+        <v>2</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>3</v>
+      </c>
+      <c r="T49" t="n">
         <v>12</v>
       </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
         <is>
           <t>Stor aspticka
 Svart trolldruva
 Blåsippa</t>
         </is>
       </c>
-      <c r="W47">
+      <c r="W49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63146-2025 artfynd.xlsx", "A 63146-2025")</f>
         <v/>
       </c>
-      <c r="X47">
+      <c r="X49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63146-2025 karta.png", "A 63146-2025")</f>
         <v/>
       </c>
-      <c r="Y47">
+      <c r="Y49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63146-2025 georefererad karta.tif", "A 63146-2025")</f>
         <v/>
       </c>
-      <c r="AA47">
+      <c r="AA49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63146-2025 FSC-klagomål.docx", "A 63146-2025")</f>
         <v/>
       </c>
-      <c r="AB47">
+      <c r="AB49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63146-2025 FSC-klagomål mail.docx", "A 63146-2025")</f>
         <v/>
       </c>
-      <c r="AC47">
+      <c r="AC49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63146-2025 tillsynsbegäran.docx", "A 63146-2025")</f>
         <v/>
       </c>
-      <c r="AD47">
+      <c r="AD49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63146-2025 tillsynsbegäran mail.docx", "A 63146-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>A 4082-2025</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="n">
-        <v>45684</v>
-      </c>
-      <c r="E48" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="J48" t="n">
-        <v>2</v>
-      </c>
-      <c r="K48" t="n">
-        <v>2</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>3</v>
-      </c>
-      <c r="T48" t="n">
-        <v>3</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1</v>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>Grönpyrola
-Plattlummer
-Lopplummer (aggregat)</t>
-        </is>
-      </c>
-      <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 4082-2025 artfynd.xlsx", "A 4082-2025")</f>
-        <v/>
-      </c>
-      <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 4082-2025 karta.png", "A 4082-2025")</f>
-        <v/>
-      </c>
-      <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 4082-2025 georefererad karta.tif", "A 4082-2025")</f>
-        <v/>
-      </c>
-      <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 4082-2025 FSC-klagomål.docx", "A 4082-2025")</f>
-        <v/>
-      </c>
-      <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 4082-2025 FSC-klagomål mail.docx", "A 4082-2025")</f>
-        <v/>
-      </c>
-      <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 4082-2025 tillsynsbegäran.docx", "A 4082-2025")</f>
-        <v/>
-      </c>
-      <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 4082-2025 tillsynsbegäran mail.docx", "A 4082-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="15" customHeight="1">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>A 48128-2023</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D49" s="1" t="n">
-        <v>45205</v>
-      </c>
-      <c r="E49" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
-        <v>1</v>
-      </c>
-      <c r="L49" t="n">
-        <v>2</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>2</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>3</v>
-      </c>
-      <c r="T49" t="n">
-        <v>3</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" s="2" t="inlineStr">
-        <is>
-          <t>Jungfrulin
-Svinrot
-Vedticka</t>
-        </is>
-      </c>
-      <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 48128-2023 artfynd.xlsx", "A 48128-2023")</f>
-        <v/>
-      </c>
-      <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 48128-2023 karta.png", "A 48128-2023")</f>
-        <v/>
-      </c>
-      <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 48128-2023 georefererad karta.tif", "A 48128-2023")</f>
-        <v/>
-      </c>
-      <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 48128-2023 FSC-klagomål.docx", "A 48128-2023")</f>
-        <v/>
-      </c>
-      <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 48128-2023 FSC-klagomål mail.docx", "A 48128-2023")</f>
-        <v/>
-      </c>
-      <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 48128-2023 tillsynsbegäran.docx", "A 48128-2023")</f>
-        <v/>
-      </c>
-      <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 48128-2023 tillsynsbegäran mail.docx", "A 48128-2023")</f>
         <v/>
       </c>
     </row>
@@ -6581,7 +6581,7 @@
         <v>46248</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         <v>46268</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>46239</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>44635</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>45708</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>45708</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 41204-2023</t>
+          <t>A 30074-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7270,10 +7270,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45174</v>
+        <v>45110</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7285,20 +7285,25 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J56" t="n">
         <v>1</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
@@ -7310,56 +7315,52 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>2</v>
       </c>
       <c r="T56" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U56" t="n">
         <v>0</v>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>Knärot
-Vedtrappmossa</t>
+          <t>Grönpyrola
+Revlummer</t>
         </is>
       </c>
       <c r="W56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 41204-2023 artfynd.xlsx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 30074-2023 artfynd.xlsx", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="X56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 41204-2023 karta.png", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 30074-2023 karta.png", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="Y56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 41204-2023 georefererad karta.tif", "A 41204-2023")</f>
-        <v/>
-      </c>
-      <c r="Z56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 41204-2023 karta knärot.png", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 30074-2023 georefererad karta.tif", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="AA56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 41204-2023 FSC-klagomål.docx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 30074-2023 FSC-klagomål.docx", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="AB56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 41204-2023 FSC-klagomål mail.docx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 30074-2023 FSC-klagomål mail.docx", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="AC56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 41204-2023 tillsynsbegäran.docx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 30074-2023 tillsynsbegäran.docx", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="AD56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 41204-2023 tillsynsbegäran mail.docx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 30074-2023 tillsynsbegäran mail.docx", "A 30074-2023")</f>
         <v/>
       </c>
     </row>
@@ -7383,7 +7384,7 @@
         <v>45236</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7477,7 +7478,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 30074-2023</t>
+          <t>A 47453-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7491,10 +7492,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45110</v>
+        <v>45587</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7506,22 +7507,17 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -7536,7 +7532,7 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -7548,47 +7544,51 @@
         <v>2</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola
-Revlummer</t>
+          <t>Göktyta
+Gröngöling</t>
         </is>
       </c>
       <c r="W58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 30074-2023 artfynd.xlsx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 47453-2024 artfynd.xlsx", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="X58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 30074-2023 karta.png", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 47453-2024 karta.png", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="Y58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 30074-2023 georefererad karta.tif", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 47453-2024 georefererad karta.tif", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="AA58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 30074-2023 FSC-klagomål.docx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 47453-2024 FSC-klagomål.docx", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="AB58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 30074-2023 FSC-klagomål mail.docx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 47453-2024 FSC-klagomål mail.docx", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="AC58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 30074-2023 tillsynsbegäran.docx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 47453-2024 tillsynsbegäran.docx", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="AD58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 30074-2023 tillsynsbegäran mail.docx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 47453-2024 tillsynsbegäran mail.docx", "A 47453-2024")</f>
+        <v/>
+      </c>
+      <c r="AE58">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 47453-2024 prioriterade fågelarter.docx", "A 47453-2024")</f>
         <v/>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 40403-2025</t>
+          <t>A 37013-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45895</v>
+        <v>45874</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7619,14 +7619,14 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.9</v>
+        <v>10.7</v>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -7635,7 +7635,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
@@ -7647,59 +7647,59 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S59" t="n">
         <v>2</v>
       </c>
       <c r="T59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>Igelkott
-Gröngöling</t>
+          <t>Brunfläckig pärlemorfjäril
+Fältgentiana</t>
         </is>
       </c>
       <c r="W59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 40403-2025 artfynd.xlsx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37013-2025 artfynd.xlsx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="X59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 40403-2025 karta.png", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37013-2025 karta.png", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="Y59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 40403-2025 georefererad karta.tif", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37013-2025 georefererad karta.tif", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AA59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 40403-2025 FSC-klagomål.docx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37013-2025 FSC-klagomål.docx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AB59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 40403-2025 FSC-klagomål mail.docx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37013-2025 FSC-klagomål mail.docx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AC59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 40403-2025 tillsynsbegäran.docx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37013-2025 tillsynsbegäran.docx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AD59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 40403-2025 tillsynsbegäran mail.docx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37013-2025 tillsynsbegäran mail.docx", "A 37013-2025")</f>
         <v/>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 13788-2025</t>
+          <t>A 40403-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7713,10 +7713,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45737</v>
+        <v>45895</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7728,20 +7728,25 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>9.699999999999999</v>
+        <v>3.9</v>
       </c>
       <c r="J60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N60" t="n">
         <v>0</v>
@@ -7756,60 +7761,56 @@
         <v>1</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S60" t="n">
         <v>2</v>
       </c>
       <c r="T60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>Sparvuggla
-Nattskärra</t>
+          <t>Igelkott
+Gröngöling</t>
         </is>
       </c>
       <c r="W60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 13788-2025 artfynd.xlsx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 40403-2025 artfynd.xlsx", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="X60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 13788-2025 karta.png", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 40403-2025 karta.png", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="Y60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 13788-2025 georefererad karta.tif", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 40403-2025 georefererad karta.tif", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="AA60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 13788-2025 FSC-klagomål.docx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 40403-2025 FSC-klagomål.docx", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="AB60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 13788-2025 FSC-klagomål mail.docx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 40403-2025 FSC-klagomål mail.docx", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="AC60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 13788-2025 tillsynsbegäran.docx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 40403-2025 tillsynsbegäran.docx", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="AD60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 13788-2025 tillsynsbegäran mail.docx", "A 13788-2025")</f>
-        <v/>
-      </c>
-      <c r="AE60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 13788-2025 prioriterade fågelarter.docx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 40403-2025 tillsynsbegäran mail.docx", "A 40403-2025")</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 14001-2023</t>
+          <t>A 63138-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7823,10 +7824,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45007</v>
+        <v>46009</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7844,19 +7845,19 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
@@ -7868,59 +7869,63 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>2</v>
       </c>
       <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
         <v>2</v>
       </c>
-      <c r="U61" t="n">
-        <v>0</v>
-      </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>Garnlav
-Motaggsvamp</t>
+          <t>Mindre märgborre
+Tjäder</t>
         </is>
       </c>
       <c r="W61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 14001-2023 artfynd.xlsx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63138-2025 artfynd.xlsx", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="X61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 14001-2023 karta.png", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63138-2025 karta.png", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="Y61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 14001-2023 georefererad karta.tif", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63138-2025 georefererad karta.tif", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="AA61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 14001-2023 FSC-klagomål.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63138-2025 FSC-klagomål.docx", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="AB61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 14001-2023 FSC-klagomål mail.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63138-2025 FSC-klagomål mail.docx", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="AC61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 14001-2023 tillsynsbegäran.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63138-2025 tillsynsbegäran.docx", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="AD61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 14001-2023 tillsynsbegäran mail.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63138-2025 tillsynsbegäran mail.docx", "A 63138-2025")</f>
+        <v/>
+      </c>
+      <c r="AE61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 63138-2025 prioriterade fågelarter.docx", "A 63138-2025")</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 13971-2023</t>
+          <t>A 41204-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7934,10 +7939,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45007</v>
+        <v>45174</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7949,89 +7954,88 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>1</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
         <v>2</v>
       </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S62" t="n">
         <v>2</v>
       </c>
       <c r="T62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>Dubbelnycklar
-Fläcknycklar</t>
+          <t>Knärot
+Vedtrappmossa</t>
         </is>
       </c>
       <c r="W62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 13971-2023 artfynd.xlsx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 41204-2023 artfynd.xlsx", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="X62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 13971-2023 karta.png", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 41204-2023 karta.png", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="Y62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 13971-2023 georefererad karta.tif", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 41204-2023 georefererad karta.tif", "A 41204-2023")</f>
+        <v/>
+      </c>
+      <c r="Z62">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 41204-2023 karta knärot.png", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="AA62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 13971-2023 FSC-klagomål.docx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 41204-2023 FSC-klagomål.docx", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="AB62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 13971-2023 FSC-klagomål mail.docx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 41204-2023 FSC-klagomål mail.docx", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="AC62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 13971-2023 tillsynsbegäran.docx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 41204-2023 tillsynsbegäran.docx", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="AD62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 13971-2023 tillsynsbegäran mail.docx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 41204-2023 tillsynsbegäran mail.docx", "A 41204-2023")</f>
         <v/>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 47453-2024</t>
+          <t>A 11501-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -8045,10 +8049,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45587</v>
+        <v>44991</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8060,17 +8064,22 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
@@ -8085,7 +8094,7 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
@@ -8097,51 +8106,47 @@
         <v>2</v>
       </c>
       <c r="U63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>Göktyta
-Gröngöling</t>
+          <t>Svart trolldruva
+Nattviol</t>
         </is>
       </c>
       <c r="W63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 47453-2024 artfynd.xlsx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 11501-2023 artfynd.xlsx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="X63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 47453-2024 karta.png", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 11501-2023 karta.png", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="Y63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 47453-2024 georefererad karta.tif", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 11501-2023 georefererad karta.tif", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AA63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 47453-2024 FSC-klagomål.docx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 11501-2023 FSC-klagomål.docx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AB63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 47453-2024 FSC-klagomål mail.docx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 11501-2023 FSC-klagomål mail.docx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AC63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 47453-2024 tillsynsbegäran.docx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 11501-2023 tillsynsbegäran.docx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AD63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 47453-2024 tillsynsbegäran mail.docx", "A 47453-2024")</f>
-        <v/>
-      </c>
-      <c r="AE63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 47453-2024 prioriterade fågelarter.docx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 11501-2023 tillsynsbegäran mail.docx", "A 11501-2023")</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 11501-2023</t>
+          <t>A 14001-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -8155,10 +8160,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44991</v>
+        <v>45007</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8176,19 +8181,19 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
@@ -8200,10 +8205,10 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S64" t="n">
         <v>2</v>
@@ -8212,47 +8217,47 @@
         <v>2</v>
       </c>
       <c r="U64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva
-Nattviol</t>
+          <t>Garnlav
+Motaggsvamp</t>
         </is>
       </c>
       <c r="W64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 11501-2023 artfynd.xlsx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 14001-2023 artfynd.xlsx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="X64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 11501-2023 karta.png", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 14001-2023 karta.png", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="Y64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 11501-2023 georefererad karta.tif", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 14001-2023 georefererad karta.tif", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AA64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 11501-2023 FSC-klagomål.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 14001-2023 FSC-klagomål.docx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AB64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 11501-2023 FSC-klagomål mail.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 14001-2023 FSC-klagomål mail.docx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AC64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 11501-2023 tillsynsbegäran.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 14001-2023 tillsynsbegäran.docx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AD64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 11501-2023 tillsynsbegäran mail.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 14001-2023 tillsynsbegäran mail.docx", "A 14001-2023")</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 63138-2025</t>
+          <t>A 13971-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -8266,10 +8271,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46009</v>
+        <v>45007</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8287,13 +8292,13 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="J65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -8323,51 +8328,47 @@
         <v>3</v>
       </c>
       <c r="U65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>Mindre märgborre
-Tjäder</t>
+          <t>Dubbelnycklar
+Fläcknycklar</t>
         </is>
       </c>
       <c r="W65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63138-2025 artfynd.xlsx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 13971-2023 artfynd.xlsx", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="X65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63138-2025 karta.png", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 13971-2023 karta.png", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="Y65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63138-2025 georefererad karta.tif", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 13971-2023 georefererad karta.tif", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="AA65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63138-2025 FSC-klagomål.docx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 13971-2023 FSC-klagomål.docx", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="AB65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63138-2025 FSC-klagomål mail.docx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 13971-2023 FSC-klagomål mail.docx", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="AC65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63138-2025 tillsynsbegäran.docx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 13971-2023 tillsynsbegäran.docx", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="AD65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63138-2025 tillsynsbegäran mail.docx", "A 63138-2025")</f>
-        <v/>
-      </c>
-      <c r="AE65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 63138-2025 prioriterade fågelarter.docx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 13971-2023 tillsynsbegäran mail.docx", "A 13971-2023")</f>
         <v/>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 37013-2025</t>
+          <t>A 36261-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -8381,10 +8382,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45874</v>
+        <v>46268</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8398,23 +8399,23 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>10.7</v>
+        <v>7.9</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
         <v>0</v>
@@ -8426,10 +8427,10 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>2</v>
@@ -8442,43 +8443,43 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril
-Fältgentiana</t>
+          <t>Krusfrö
+Revlummer</t>
         </is>
       </c>
       <c r="W66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37013-2025 artfynd.xlsx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 36261-2026 artfynd.xlsx", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="X66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37013-2025 karta.png", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 36261-2026 karta.png", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="Y66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37013-2025 georefererad karta.tif", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 36261-2026 georefererad karta.tif", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="AA66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37013-2025 FSC-klagomål.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 36261-2026 FSC-klagomål.docx", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="AB66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37013-2025 FSC-klagomål mail.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 36261-2026 FSC-klagomål mail.docx", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="AC66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37013-2025 tillsynsbegäran.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 36261-2026 tillsynsbegäran.docx", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="AD66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37013-2025 tillsynsbegäran mail.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 36261-2026 tillsynsbegäran mail.docx", "A 36261-2026")</f>
         <v/>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 36261-2026</t>
+          <t>A 13788-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -8492,10 +8493,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46268</v>
+        <v>45737</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8507,16 +8508,11 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>7.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -8549,40 +8545,44 @@
         <v>2</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>Krusfrö
-Revlummer</t>
+          <t>Sparvuggla
+Nattskärra</t>
         </is>
       </c>
       <c r="W67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 36261-2026 artfynd.xlsx", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 13788-2025 artfynd.xlsx", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="X67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 36261-2026 karta.png", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 13788-2025 karta.png", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="Y67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 36261-2026 georefererad karta.tif", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 13788-2025 georefererad karta.tif", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="AA67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 36261-2026 FSC-klagomål.docx", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 13788-2025 FSC-klagomål.docx", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="AB67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 36261-2026 FSC-klagomål mail.docx", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 13788-2025 FSC-klagomål mail.docx", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="AC67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 36261-2026 tillsynsbegäran.docx", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 13788-2025 tillsynsbegäran.docx", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="AD67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 36261-2026 tillsynsbegäran mail.docx", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 13788-2025 tillsynsbegäran mail.docx", "A 13788-2025")</f>
+        <v/>
+      </c>
+      <c r="AE67">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 13788-2025 prioriterade fågelarter.docx", "A 13788-2025")</f>
         <v/>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
         <v>45720</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8717,7 +8717,7 @@
         <v>44696</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>44739</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>44524</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>44696</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 34955-2022</t>
+          <t>A 30076-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -9154,10 +9154,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44796</v>
+        <v>45110</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9175,16 +9175,16 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -9199,7 +9199,7 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
         <v>0</v>
@@ -9211,46 +9211,46 @@
         <v>1</v>
       </c>
       <c r="U73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34955-2022 artfynd.xlsx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 30076-2023 artfynd.xlsx", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="X73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34955-2022 karta.png", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 30076-2023 karta.png", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="Y73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34955-2022 georefererad karta.tif", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 30076-2023 georefererad karta.tif", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="AA73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34955-2022 FSC-klagomål.docx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 30076-2023 FSC-klagomål.docx", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="AB73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34955-2022 FSC-klagomål mail.docx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 30076-2023 FSC-klagomål mail.docx", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="AC73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34955-2022 tillsynsbegäran.docx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 30076-2023 tillsynsbegäran.docx", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="AD73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34955-2022 tillsynsbegäran mail.docx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 30076-2023 tillsynsbegäran mail.docx", "A 30076-2023")</f>
         <v/>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 33231-2024</t>
+          <t>A 8553-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -9260,14 +9260,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45518</v>
+        <v>44977</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9281,7 +9281,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I74" t="n">
@@ -9297,7 +9297,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N74" t="n">
         <v>0</v>
@@ -9309,10 +9309,10 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S74" t="n">
         <v>1</v>
@@ -9321,46 +9321,46 @@
         <v>1</v>
       </c>
       <c r="U74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="W74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 33231-2024 artfynd.xlsx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 8553-2023 artfynd.xlsx", "A 8553-2023")</f>
         <v/>
       </c>
       <c r="X74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 33231-2024 karta.png", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 8553-2023 karta.png", "A 8553-2023")</f>
         <v/>
       </c>
       <c r="Y74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 33231-2024 georefererad karta.tif", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 8553-2023 georefererad karta.tif", "A 8553-2023")</f>
         <v/>
       </c>
       <c r="AA74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 33231-2024 FSC-klagomål.docx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 8553-2023 FSC-klagomål.docx", "A 8553-2023")</f>
         <v/>
       </c>
       <c r="AB74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 33231-2024 FSC-klagomål mail.docx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 8553-2023 FSC-klagomål mail.docx", "A 8553-2023")</f>
         <v/>
       </c>
       <c r="AC74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 33231-2024 tillsynsbegäran.docx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 8553-2023 tillsynsbegäran.docx", "A 8553-2023")</f>
         <v/>
       </c>
       <c r="AD74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 33231-2024 tillsynsbegäran mail.docx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 8553-2023 tillsynsbegäran mail.docx", "A 8553-2023")</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 30076-2023</t>
+          <t>A 37287-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -9374,10 +9374,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45110</v>
+        <v>45156</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9389,22 +9389,17 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -9419,7 +9414,7 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R75" t="n">
         <v>0</v>
@@ -9435,35 +9430,35 @@
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="W75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 30076-2023 artfynd.xlsx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37287-2023 artfynd.xlsx", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="X75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 30076-2023 karta.png", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37287-2023 karta.png", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="Y75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 30076-2023 georefererad karta.tif", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37287-2023 georefererad karta.tif", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="AA75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 30076-2023 FSC-klagomål.docx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37287-2023 FSC-klagomål.docx", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="AB75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 30076-2023 FSC-klagomål mail.docx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37287-2023 FSC-klagomål mail.docx", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="AC75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 30076-2023 tillsynsbegäran.docx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37287-2023 tillsynsbegäran.docx", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="AD75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 30076-2023 tillsynsbegäran mail.docx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37287-2023 tillsynsbegäran mail.docx", "A 37287-2023")</f>
         <v/>
       </c>
     </row>
@@ -9487,7 +9482,7 @@
         <v>44817</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9580,7 +9575,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 10883-2023</t>
+          <t>A 17632-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -9594,10 +9589,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44991</v>
+        <v>44680</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9609,22 +9604,17 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>12.5</v>
+        <v>5.2</v>
       </c>
       <c r="J77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -9639,7 +9629,7 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
         <v>0</v>
@@ -9651,50 +9641,46 @@
         <v>1</v>
       </c>
       <c r="U77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="W77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 10883-2023 artfynd.xlsx", "A 10883-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 17632-2022 artfynd.xlsx", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="X77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 10883-2023 karta.png", "A 10883-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 17632-2022 karta.png", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="Y77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 10883-2023 georefererad karta.tif", "A 10883-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 17632-2022 georefererad karta.tif", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="AA77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 10883-2023 FSC-klagomål.docx", "A 10883-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 17632-2022 FSC-klagomål.docx", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="AB77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 10883-2023 FSC-klagomål mail.docx", "A 10883-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 17632-2022 FSC-klagomål mail.docx", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="AC77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 10883-2023 tillsynsbegäran.docx", "A 10883-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 17632-2022 tillsynsbegäran.docx", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="AD77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 10883-2023 tillsynsbegäran mail.docx", "A 10883-2023")</f>
-        <v/>
-      </c>
-      <c r="AE77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 10883-2023 prioriterade fågelarter.docx", "A 10883-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 17632-2022 tillsynsbegäran mail.docx", "A 17632-2022")</f>
         <v/>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 24167-2024</t>
+          <t>A 34955-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -9704,14 +9690,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45456</v>
+        <v>44796</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9723,17 +9709,22 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="J78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
@@ -9748,7 +9739,7 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R78" t="n">
         <v>0</v>
@@ -9760,46 +9751,46 @@
         <v>1</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 24167-2024 artfynd.xlsx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34955-2022 artfynd.xlsx", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="X78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 24167-2024 karta.png", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34955-2022 karta.png", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="Y78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 24167-2024 georefererad karta.tif", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34955-2022 georefererad karta.tif", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="AA78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 24167-2024 FSC-klagomål.docx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34955-2022 FSC-klagomål.docx", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="AB78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 24167-2024 FSC-klagomål mail.docx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34955-2022 FSC-klagomål mail.docx", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="AC78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 24167-2024 tillsynsbegäran.docx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34955-2022 tillsynsbegäran.docx", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="AD78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 24167-2024 tillsynsbegäran mail.docx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34955-2022 tillsynsbegäran mail.docx", "A 34955-2022")</f>
         <v/>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 37287-2023</t>
+          <t>A 10883-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -9813,10 +9804,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45156</v>
+        <v>44991</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9828,11 +9819,16 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>0.6</v>
+        <v>12.5</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -9865,39 +9861,43 @@
         <v>1</v>
       </c>
       <c r="U79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>Mindre tåtelsmygare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="W79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37287-2023 artfynd.xlsx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 10883-2023 artfynd.xlsx", "A 10883-2023")</f>
         <v/>
       </c>
       <c r="X79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37287-2023 karta.png", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 10883-2023 karta.png", "A 10883-2023")</f>
         <v/>
       </c>
       <c r="Y79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37287-2023 georefererad karta.tif", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 10883-2023 georefererad karta.tif", "A 10883-2023")</f>
         <v/>
       </c>
       <c r="AA79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37287-2023 FSC-klagomål.docx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 10883-2023 FSC-klagomål.docx", "A 10883-2023")</f>
         <v/>
       </c>
       <c r="AB79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37287-2023 FSC-klagomål mail.docx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 10883-2023 FSC-klagomål mail.docx", "A 10883-2023")</f>
         <v/>
       </c>
       <c r="AC79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37287-2023 tillsynsbegäran.docx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 10883-2023 tillsynsbegäran.docx", "A 10883-2023")</f>
         <v/>
       </c>
       <c r="AD79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37287-2023 tillsynsbegäran mail.docx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 10883-2023 tillsynsbegäran mail.docx", "A 10883-2023")</f>
+        <v/>
+      </c>
+      <c r="AE79">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 10883-2023 prioriterade fågelarter.docx", "A 10883-2023")</f>
         <v/>
       </c>
     </row>
@@ -9921,7 +9921,7 @@
         <v>45573</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 8553-2023</t>
+          <t>A 33231-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -10024,14 +10024,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44977</v>
+        <v>45518</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I81" t="n">
@@ -10061,7 +10061,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
         <v>0</v>
@@ -10073,10 +10073,10 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>1</v>
@@ -10085,46 +10085,46 @@
         <v>1</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>Väddnätfjäril</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="W81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 8553-2023 artfynd.xlsx", "A 8553-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 33231-2024 artfynd.xlsx", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="X81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 8553-2023 karta.png", "A 8553-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 33231-2024 karta.png", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="Y81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 8553-2023 georefererad karta.tif", "A 8553-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 33231-2024 georefererad karta.tif", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="AA81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 8553-2023 FSC-klagomål.docx", "A 8553-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 33231-2024 FSC-klagomål.docx", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="AB81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 8553-2023 FSC-klagomål mail.docx", "A 8553-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 33231-2024 FSC-klagomål mail.docx", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="AC81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 8553-2023 tillsynsbegäran.docx", "A 8553-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 33231-2024 tillsynsbegäran.docx", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="AD81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 8553-2023 tillsynsbegäran mail.docx", "A 8553-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 33231-2024 tillsynsbegäran mail.docx", "A 33231-2024")</f>
         <v/>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 16013-2023</t>
+          <t>A 24167-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -10134,14 +10134,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45026</v>
+        <v>45456</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10154,10 +10154,10 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -10166,7 +10166,7 @@
         <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
         <v>0</v>
@@ -10178,10 +10178,10 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>1</v>
@@ -10194,42 +10194,42 @@
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 16013-2023 artfynd.xlsx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 24167-2024 artfynd.xlsx", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="X82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 16013-2023 karta.png", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 24167-2024 karta.png", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="Y82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 16013-2023 georefererad karta.tif", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 24167-2024 georefererad karta.tif", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="AA82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 16013-2023 FSC-klagomål.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 24167-2024 FSC-klagomål.docx", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="AB82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 16013-2023 FSC-klagomål mail.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 24167-2024 FSC-klagomål mail.docx", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="AC82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 16013-2023 tillsynsbegäran.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 24167-2024 tillsynsbegäran.docx", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="AD82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 16013-2023 tillsynsbegäran mail.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 24167-2024 tillsynsbegäran mail.docx", "A 24167-2024")</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 17632-2022</t>
+          <t>A 31589-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -10243,10 +10243,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44680</v>
+        <v>46224</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10258,8 +10258,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -10299,42 +10304,42 @@
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 17632-2022 artfynd.xlsx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31589-2026 artfynd.xlsx", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="X83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 17632-2022 karta.png", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31589-2026 karta.png", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="Y83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 17632-2022 georefererad karta.tif", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31589-2026 georefererad karta.tif", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="AA83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 17632-2022 FSC-klagomål.docx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31589-2026 FSC-klagomål.docx", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="AB83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 17632-2022 FSC-klagomål mail.docx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31589-2026 FSC-klagomål mail.docx", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="AC83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 17632-2022 tillsynsbegäran.docx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31589-2026 tillsynsbegäran.docx", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="AD83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 17632-2022 tillsynsbegäran mail.docx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31589-2026 tillsynsbegäran mail.docx", "A 31589-2026")</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 34584-2025</t>
+          <t>A 16013-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -10348,10 +10353,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45846</v>
+        <v>45026</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10363,16 +10368,11 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="J84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N84" t="n">
         <v>0</v>
@@ -10393,10 +10393,10 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S84" t="n">
         <v>1</v>
@@ -10405,50 +10405,46 @@
         <v>1</v>
       </c>
       <c r="U84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="W84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34584-2025 artfynd.xlsx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 16013-2023 artfynd.xlsx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="X84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34584-2025 karta.png", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 16013-2023 karta.png", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="Y84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34584-2025 georefererad karta.tif", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 16013-2023 georefererad karta.tif", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AA84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34584-2025 FSC-klagomål.docx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 16013-2023 FSC-klagomål.docx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AB84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34584-2025 FSC-klagomål mail.docx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 16013-2023 FSC-klagomål mail.docx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AC84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34584-2025 tillsynsbegäran.docx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 16013-2023 tillsynsbegäran.docx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AD84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34584-2025 tillsynsbegäran mail.docx", "A 34584-2025")</f>
-        <v/>
-      </c>
-      <c r="AE84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 34584-2025 prioriterade fågelarter.docx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 16013-2023 tillsynsbegäran mail.docx", "A 16013-2023")</f>
         <v/>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 31589-2026</t>
+          <t>A 34584-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -10462,10 +10458,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46224</v>
+        <v>45846</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10479,17 +10475,17 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>7</v>
+        <v>2.7</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -10519,39 +10515,43 @@
         <v>1</v>
       </c>
       <c r="U85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31589-2026 artfynd.xlsx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34584-2025 artfynd.xlsx", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="X85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31589-2026 karta.png", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34584-2025 karta.png", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="Y85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31589-2026 georefererad karta.tif", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34584-2025 georefererad karta.tif", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="AA85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31589-2026 FSC-klagomål.docx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34584-2025 FSC-klagomål.docx", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="AB85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31589-2026 FSC-klagomål mail.docx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34584-2025 FSC-klagomål mail.docx", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="AC85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31589-2026 tillsynsbegäran.docx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34584-2025 tillsynsbegäran.docx", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="AD85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31589-2026 tillsynsbegäran mail.docx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34584-2025 tillsynsbegäran mail.docx", "A 34584-2025")</f>
+        <v/>
+      </c>
+      <c r="AE85">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 34584-2025 prioriterade fågelarter.docx", "A 34584-2025")</f>
         <v/>
       </c>
     </row>
@@ -10575,7 +10575,7 @@
         <v>44509</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>44696</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>44782</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         <v>44550</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>44586</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>44582</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>44694</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 34957-2022</t>
+          <t>A 66342-2021</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44796</v>
+        <v>44518</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -11172,7 +11172,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 66342-2021</t>
+          <t>A 34957-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -11186,10 +11186,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44518</v>
+        <v>44796</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -11267,7 +11267,7 @@
         <v>45205</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 15739-2023</t>
+          <t>A 15743-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -11345,7 +11345,7 @@
         <v>45021</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -11401,7 +11401,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 33931-2022</t>
+          <t>A 15637-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -11415,10 +11415,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44790</v>
+        <v>44662</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 22662-2023</t>
+          <t>A 19786-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -11484,14 +11484,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45071</v>
+        <v>45050</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11505,11 +11505,11 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.6</v>
+        <v>8.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -11552,7 +11552,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 21509-2024</t>
+          <t>A 7787-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -11566,10 +11566,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45441</v>
+        <v>45348</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11581,13 +11581,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -11630,7 +11625,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 42832-2022</t>
+          <t>A 72367-2021</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -11640,14 +11635,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44832</v>
+        <v>44545</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11660,7 +11655,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -11703,7 +11698,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 42841-2022</t>
+          <t>A 33931-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -11713,14 +11708,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44832</v>
+        <v>44790</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11733,7 +11728,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -11793,7 +11788,7 @@
         <v>45079</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11854,7 +11849,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 25450-2024</t>
+          <t>A 32808-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -11868,10 +11863,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45463</v>
+        <v>45516</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11885,11 +11880,11 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -11932,7 +11927,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 24665-2023</t>
+          <t>A 37954-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -11946,10 +11941,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45084</v>
+        <v>45881</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11962,7 +11957,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.9</v>
+        <v>9.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -12005,7 +12000,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 3818-2022</t>
+          <t>A 42714-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -12019,10 +12014,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44587</v>
+        <v>44832</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12035,7 +12030,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -12078,7 +12073,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 72367-2021</t>
+          <t>A 35682-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -12092,10 +12087,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44545</v>
+        <v>44799</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12107,8 +12102,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -12151,7 +12151,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 42714-2022</t>
+          <t>A 11728-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -12161,14 +12161,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44832</v>
+        <v>44993</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12180,8 +12180,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -12224,7 +12229,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 19782-2023</t>
+          <t>A 5567-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -12238,10 +12243,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45050</v>
+        <v>44595</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12253,13 +12258,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>5.2</v>
+        <v>1.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -12302,7 +12302,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 14626-2023</t>
+          <t>A 42832-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -12312,14 +12312,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45012</v>
+        <v>44832</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12331,13 +12331,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -12380,7 +12375,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 19099-2022</t>
+          <t>A 24665-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -12394,10 +12389,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44691</v>
+        <v>45084</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12409,13 +12404,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -12458,7 +12448,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 56378-2023</t>
+          <t>A 42841-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -12468,14 +12458,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45236</v>
+        <v>44832</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12487,13 +12477,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -12536,7 +12521,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 11728-2023</t>
+          <t>A 42829-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -12546,14 +12531,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44993</v>
+        <v>44832</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12565,13 +12550,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -12614,7 +12594,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 25780-2023</t>
+          <t>A 2867-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -12628,10 +12608,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45090</v>
+        <v>45315</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12643,8 +12623,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -12687,7 +12672,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 55873-2025</t>
+          <t>A 49058-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -12701,10 +12686,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45973</v>
+        <v>45594</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12722,7 +12707,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.5</v>
+        <v>11.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -12765,7 +12750,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 20904-2023</t>
+          <t>A 3085-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -12775,14 +12760,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45060</v>
+        <v>44946</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12796,11 +12781,11 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.7</v>
+        <v>13</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -12843,7 +12828,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 35682-2022</t>
+          <t>A 20535-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -12853,14 +12838,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44799</v>
+        <v>46140</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12874,11 +12859,11 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -12921,7 +12906,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 42829-2022</t>
+          <t>A 55873-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -12931,14 +12916,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44832</v>
+        <v>45973</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12950,8 +12935,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -12994,7 +12984,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 2867-2024</t>
+          <t>A 20904-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -13004,14 +12994,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45315</v>
+        <v>45060</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13025,11 +13015,11 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -13089,7 +13079,7 @@
         <v>45310</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13162,7 +13152,7 @@
         <v>46048</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13235,7 +13225,7 @@
         <v>46048</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13291,7 +13281,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 5567-2022</t>
+          <t>A 14626-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -13305,10 +13295,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44595</v>
+        <v>45012</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13320,8 +13310,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -13364,7 +13359,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 10244-2026</t>
+          <t>A 24201-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -13378,10 +13373,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46076</v>
+        <v>46168</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13393,13 +13388,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>8.699999999999999</v>
+        <v>2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -13459,7 +13449,7 @@
         <v>46076</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13520,7 +13510,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 10562-2026</t>
+          <t>A 10244-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -13534,10 +13524,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13551,11 +13541,11 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -13598,7 +13588,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 3085-2023</t>
+          <t>A 10562-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -13612,10 +13602,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44946</v>
+        <v>46077</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13629,11 +13619,11 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>13</v>
+        <v>2.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -13676,7 +13666,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 12841-2026</t>
+          <t>A 25450-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -13690,10 +13680,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46091</v>
+        <v>45463</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13711,7 +13701,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>4.3</v>
+        <v>2.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -13754,7 +13744,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 7848-2022</t>
+          <t>A 12841-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -13768,10 +13758,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44608</v>
+        <v>46091</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13783,8 +13773,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -13827,7 +13822,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 15743-2023</t>
+          <t>A 19782-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -13841,10 +13836,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45021</v>
+        <v>45050</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13856,8 +13851,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>0.5</v>
+        <v>5.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -13900,7 +13900,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 19246-2026</t>
+          <t>A 7848-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -13910,14 +13910,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46132</v>
+        <v>44608</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13929,13 +13929,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -13978,7 +13973,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 15637-2022</t>
+          <t>A 19246-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -13988,14 +13983,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44662</v>
+        <v>46132</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14007,8 +14002,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -14051,7 +14051,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 37954-2025</t>
+          <t>A 56378-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -14065,10 +14065,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45881</v>
+        <v>45236</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14080,8 +14080,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>9.5</v>
+        <v>4.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -14124,7 +14129,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 19786-2023</t>
+          <t>A 19099-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -14138,10 +14143,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45050</v>
+        <v>44691</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14155,11 +14160,11 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>8.1</v>
+        <v>3.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -14202,7 +14207,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 32808-2024</t>
+          <t>A 22628-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -14216,10 +14221,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45516</v>
+        <v>46155</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14233,11 +14238,11 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -14280,7 +14285,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 20535-2026</t>
+          <t>A 3818-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -14290,14 +14295,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46140</v>
+        <v>44587</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14309,13 +14314,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -14358,7 +14358,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 49058-2024</t>
+          <t>A 33933-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -14372,10 +14372,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45594</v>
+        <v>46248</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14389,11 +14389,11 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>11.4</v>
+        <v>3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -14436,7 +14436,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 7787-2024</t>
+          <t>A 31061-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -14450,10 +14450,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45348</v>
+        <v>46215</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14465,8 +14465,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -14509,7 +14514,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 24201-2026</t>
+          <t>A 21509-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -14523,10 +14528,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46168</v>
+        <v>45441</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14538,8 +14543,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -14582,7 +14592,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 22628-2026</t>
+          <t>A 22662-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -14592,14 +14602,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46155</v>
+        <v>45071</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14617,7 +14627,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -14660,7 +14670,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 33933-2026</t>
+          <t>A 25780-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -14674,10 +14684,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46248</v>
+        <v>45090</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14689,13 +14699,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -14738,7 +14743,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 31061-2026</t>
+          <t>A 32501-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -14748,14 +14753,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46215</v>
+        <v>46239</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14767,13 +14772,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -14833,7 +14833,7 @@
         <v>46237</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 32501-2026</t>
+          <t>A 15739-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -14904,14 +14904,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46239</v>
+        <v>45021</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -14984,7 +14984,7 @@
         <v>44734</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>44734</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>46251</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>

--- a/Översikt SURAHAMMAR.xlsx
+++ b/Översikt SURAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45470</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>45684</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 39697-2025</t>
+          <t>A 31280-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45890</v>
+        <v>45504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,23 +964,23 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>25.7</v>
+        <v>6.9</v>
       </c>
       <c r="J4" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -992,21 +992,182 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S4" t="n">
         <v>44</v>
       </c>
       <c r="T4" t="n">
+        <v>93</v>
+      </c>
+      <c r="U4" t="n">
+        <v>91</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Gränsticka
+Knärot
+Liten hornflikmossa
+Spadskinn
+Torrmusseron
+Apelsinticka
+Fjällig taggsvamp s.str.
+Grantaggsvamp
+Gropticka
+Kattfotslav
+Knölspindel
+Kötticka
+Mjölsvärting
+Nordfladdermus
+Nordtagging
+Persiljespindling
+Rynkskinn
+Skarp dropptaggsvamp
+Svartvit taggsvamp
+Tallkötticka
+Tallticka
+Talltita
+Ullticka
+Vaddporing
+Vedskivlav
+Vedtrappmossa
+Vågticka
+Bollvitmossa
+Bronshjon
+Flagellkvastmossa
+Grönpyrola
+Kornknutmossa
+Mindre märgborre
+Rostfläck
+Rödgul trumpetsvamp
+Smal svampklubba
+Thomsons trägnagare
+Vedticka
+Vågbandad barkbock
+Blåsippa
+Kungsfågel
+Mindre vattensalamander
+Fläcknycklar
+Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31280-2024 artfynd.xlsx", "A 31280-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31280-2024 karta.png", "A 31280-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31280-2024 georefererad karta.tif", "A 31280-2024")</f>
+        <v/>
+      </c>
+      <c r="Z4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 31280-2024 karta knärot.png", "A 31280-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31280-2024 FSC-klagomål.docx", "A 31280-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31280-2024 FSC-klagomål mail.docx", "A 31280-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31280-2024 tillsynsbegäran.docx", "A 31280-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31280-2024 tillsynsbegäran mail.docx", "A 31280-2024")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 31280-2024 prioriterade fågelarter.docx", "A 31280-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 39697-2025</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45890</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>28</v>
+      </c>
+      <c r="K5" t="n">
+        <v>7</v>
+      </c>
+      <c r="L5" t="n">
+        <v>14</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>16</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>44</v>
+      </c>
+      <c r="T5" t="n">
         <v>243</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>107</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Grönfink
 Knärot
@@ -1054,201 +1215,40 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39697-2025 artfynd.xlsx", "A 39697-2025")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39697-2025 karta.png", "A 39697-2025")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39697-2025 georefererad karta.tif", "A 39697-2025")</f>
         <v/>
       </c>
-      <c r="Z4">
+      <c r="Z5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 39697-2025 karta knärot.png", "A 39697-2025")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39697-2025 FSC-klagomål.docx", "A 39697-2025")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39697-2025 FSC-klagomål mail.docx", "A 39697-2025")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39697-2025 tillsynsbegäran.docx", "A 39697-2025")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39697-2025 tillsynsbegäran mail.docx", "A 39697-2025")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39697-2025 prioriterade fågelarter.docx", "A 39697-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 31280-2024</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45504</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J5" t="n">
-        <v>8</v>
-      </c>
-      <c r="K5" t="n">
-        <v>12</v>
-      </c>
-      <c r="L5" t="n">
-        <v>22</v>
-      </c>
-      <c r="M5" t="n">
-        <v>5</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>27</v>
-      </c>
-      <c r="R5" t="n">
-        <v>5</v>
-      </c>
-      <c r="S5" t="n">
-        <v>44</v>
-      </c>
-      <c r="T5" t="n">
-        <v>93</v>
-      </c>
-      <c r="U5" t="n">
-        <v>91</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Gränsticka
-Knärot
-Liten hornflikmossa
-Spadskinn
-Torrmusseron
-Apelsinticka
-Fjällig taggsvamp s.str.
-Grantaggsvamp
-Gropticka
-Kattfotslav
-Knölspindel
-Kötticka
-Mjölsvärting
-Nordfladdermus
-Nordtagging
-Persiljespindling
-Rynkskinn
-Skarp dropptaggsvamp
-Svartvit taggsvamp
-Tallkötticka
-Tallticka
-Talltita
-Ullticka
-Vaddporing
-Vedskivlav
-Vedtrappmossa
-Vågticka
-Bollvitmossa
-Bronshjon
-Flagellkvastmossa
-Grönpyrola
-Kornknutmossa
-Mindre märgborre
-Rostfläck
-Rödgul trumpetsvamp
-Smal svampklubba
-Thomsons trägnagare
-Vedticka
-Vågbandad barkbock
-Blåsippa
-Kungsfågel
-Mindre vattensalamander
-Fläcknycklar
-Lopplummer (aggregat)</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31280-2024 artfynd.xlsx", "A 31280-2024")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31280-2024 karta.png", "A 31280-2024")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31280-2024 georefererad karta.tif", "A 31280-2024")</f>
-        <v/>
-      </c>
-      <c r="Z5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 31280-2024 karta knärot.png", "A 31280-2024")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31280-2024 FSC-klagomål.docx", "A 31280-2024")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31280-2024 FSC-klagomål mail.docx", "A 31280-2024")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31280-2024 tillsynsbegäran.docx", "A 31280-2024")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31280-2024 tillsynsbegäran mail.docx", "A 31280-2024")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 31280-2024 prioriterade fågelarter.docx", "A 31280-2024")</f>
         <v/>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
         <v>45582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45169</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45139</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45782</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>45282</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>46216</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>46216</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>46237</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>44613</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>46085</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>45435</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>46215</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>46111</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>45890</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>44832</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45523</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>45070</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>44565</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>46215</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>45574</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>45435</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>44518</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>44477</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>45203</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 22840-2023</t>
+          <t>A 36260-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4294,10 +4294,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45072</v>
+        <v>46268</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4309,21 +4309,26 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="J30" t="n">
+        <v>4</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
         <v>2</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
@@ -4334,21 +4339,136 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S30" t="n">
         <v>7</v>
       </c>
       <c r="T30" t="n">
+        <v>8</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare
+Silverblåvinge
+Enkelbeckasin
+Blodticka
+Nattskärra
+Vanlig snok
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 36260-2026 artfynd.xlsx", "A 36260-2026")</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 36260-2026 karta.png", "A 36260-2026")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 36260-2026 georefererad karta.tif", "A 36260-2026")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 36260-2026 FSC-klagomål.docx", "A 36260-2026")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 36260-2026 FSC-klagomål mail.docx", "A 36260-2026")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 36260-2026 tillsynsbegäran.docx", "A 36260-2026")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 36260-2026 tillsynsbegäran mail.docx", "A 36260-2026")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 36260-2026 prioriterade fågelarter.docx", "A 36260-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A 22840-2023</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>45072</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>7</v>
+      </c>
+      <c r="T31" t="n">
         <v>10</v>
       </c>
-      <c r="U30" t="n">
+      <c r="U31" t="n">
         <v>9</v>
       </c>
-      <c r="V30" s="2" t="inlineStr">
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>Hultbräken
 Kärrviol
@@ -4359,152 +4479,32 @@
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W30">
+      <c r="W31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 22840-2023 artfynd.xlsx", "A 22840-2023")</f>
         <v/>
       </c>
-      <c r="X30">
+      <c r="X31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 22840-2023 karta.png", "A 22840-2023")</f>
         <v/>
       </c>
-      <c r="Y30">
+      <c r="Y31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 22840-2023 georefererad karta.tif", "A 22840-2023")</f>
         <v/>
       </c>
-      <c r="AA30">
+      <c r="AA31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 22840-2023 FSC-klagomål.docx", "A 22840-2023")</f>
         <v/>
       </c>
-      <c r="AB30">
+      <c r="AB31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 22840-2023 FSC-klagomål mail.docx", "A 22840-2023")</f>
         <v/>
       </c>
-      <c r="AC30">
+      <c r="AC31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 22840-2023 tillsynsbegäran.docx", "A 22840-2023")</f>
         <v/>
       </c>
-      <c r="AD30">
+      <c r="AD31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 22840-2023 tillsynsbegäran mail.docx", "A 22840-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A 36260-2026</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>46268</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J31" t="n">
-        <v>4</v>
-      </c>
-      <c r="K31" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M31" t="n">
-        <v>2</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3</v>
-      </c>
-      <c r="R31" t="n">
-        <v>2</v>
-      </c>
-      <c r="S31" t="n">
-        <v>7</v>
-      </c>
-      <c r="T31" t="n">
-        <v>8</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Mindre bastardsvärmare
-Silverblåvinge
-Enkelbeckasin
-Blodticka
-Nattskärra
-Vanlig snok
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 36260-2026 artfynd.xlsx", "A 36260-2026")</f>
-        <v/>
-      </c>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 36260-2026 karta.png", "A 36260-2026")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 36260-2026 georefererad karta.tif", "A 36260-2026")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 36260-2026 FSC-klagomål.docx", "A 36260-2026")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 36260-2026 FSC-klagomål mail.docx", "A 36260-2026")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 36260-2026 tillsynsbegäran.docx", "A 36260-2026")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 36260-2026 tillsynsbegäran mail.docx", "A 36260-2026")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 36260-2026 prioriterade fågelarter.docx", "A 36260-2026")</f>
         <v/>
       </c>
     </row>
@@ -4528,7 +4528,7 @@
         <v>45545</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>45945</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>44518</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 63145-2025</t>
+          <t>A 10236-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46009</v>
+        <v>46076</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4900,23 +4900,23 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>40.5</v>
+        <v>2.8</v>
       </c>
       <c r="J35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L35" t="n">
         <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -4928,10 +4928,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>6</v>
@@ -4943,6 +4943,121 @@
         <v>0</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>Gullpudra
+Vågticka
+Brandticka
+Strutbräken
+Lopplummer (aggregat)
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 10236-2026 artfynd.xlsx", "A 10236-2026")</f>
+        <v/>
+      </c>
+      <c r="X35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 10236-2026 karta.png", "A 10236-2026")</f>
+        <v/>
+      </c>
+      <c r="Y35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 10236-2026 georefererad karta.tif", "A 10236-2026")</f>
+        <v/>
+      </c>
+      <c r="AA35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 10236-2026 FSC-klagomål.docx", "A 10236-2026")</f>
+        <v/>
+      </c>
+      <c r="AB35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 10236-2026 FSC-klagomål mail.docx", "A 10236-2026")</f>
+        <v/>
+      </c>
+      <c r="AC35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 10236-2026 tillsynsbegäran.docx", "A 10236-2026")</f>
+        <v/>
+      </c>
+      <c r="AD35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 10236-2026 tillsynsbegäran mail.docx", "A 10236-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>A 63145-2025</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>46009</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="J36" t="n">
+        <v>5</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" t="n">
+        <v>2</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" t="n">
+        <v>6</v>
+      </c>
+      <c r="T36" t="n">
+        <v>13</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>Väddnätfjäril
 Mindre hackspett
@@ -4952,151 +5067,36 @@
 Nattviol</t>
         </is>
       </c>
-      <c r="W35">
+      <c r="W36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63145-2025 artfynd.xlsx", "A 63145-2025")</f>
         <v/>
       </c>
-      <c r="X35">
+      <c r="X36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63145-2025 karta.png", "A 63145-2025")</f>
         <v/>
       </c>
-      <c r="Y35">
+      <c r="Y36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63145-2025 georefererad karta.tif", "A 63145-2025")</f>
         <v/>
       </c>
-      <c r="AA35">
+      <c r="AA36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63145-2025 FSC-klagomål.docx", "A 63145-2025")</f>
         <v/>
       </c>
-      <c r="AB35">
+      <c r="AB36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63145-2025 FSC-klagomål mail.docx", "A 63145-2025")</f>
         <v/>
       </c>
-      <c r="AC35">
+      <c r="AC36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63145-2025 tillsynsbegäran.docx", "A 63145-2025")</f>
         <v/>
       </c>
-      <c r="AD35">
+      <c r="AD36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63145-2025 tillsynsbegäran mail.docx", "A 63145-2025")</f>
         <v/>
       </c>
-      <c r="AE35">
+      <c r="AE36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 63145-2025 prioriterade fågelarter.docx", "A 63145-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>A 10236-2026</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="n">
-        <v>46076</v>
-      </c>
-      <c r="E36" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J36" t="n">
-        <v>2</v>
-      </c>
-      <c r="K36" t="n">
-        <v>2</v>
-      </c>
-      <c r="L36" t="n">
-        <v>2</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>2</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>6</v>
-      </c>
-      <c r="T36" t="n">
-        <v>13</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>Gullpudra
-Vågticka
-Brandticka
-Strutbräken
-Lopplummer (aggregat)
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 10236-2026 artfynd.xlsx", "A 10236-2026")</f>
-        <v/>
-      </c>
-      <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 10236-2026 karta.png", "A 10236-2026")</f>
-        <v/>
-      </c>
-      <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 10236-2026 georefererad karta.tif", "A 10236-2026")</f>
-        <v/>
-      </c>
-      <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 10236-2026 FSC-klagomål.docx", "A 10236-2026")</f>
-        <v/>
-      </c>
-      <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 10236-2026 FSC-klagomål mail.docx", "A 10236-2026")</f>
-        <v/>
-      </c>
-      <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 10236-2026 tillsynsbegäran.docx", "A 10236-2026")</f>
-        <v/>
-      </c>
-      <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 10236-2026 tillsynsbegäran mail.docx", "A 10236-2026")</f>
         <v/>
       </c>
     </row>
@@ -5120,7 +5120,7 @@
         <v>44832</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>44832</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>45369</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>45503</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>45463</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>44518</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 49718-2023</t>
+          <t>A 39694-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5801,10 +5801,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45212</v>
+        <v>45890</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5816,8 +5816,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
@@ -5826,7 +5831,7 @@
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -5841,7 +5846,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -5850,721 +5855,716 @@
         <v>3</v>
       </c>
       <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Mindre märgborre
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39694-2025 artfynd.xlsx", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="X43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39694-2025 karta.png", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="Y43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39694-2025 georefererad karta.tif", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="AA43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39694-2025 FSC-klagomål.docx", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="AB43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39694-2025 FSC-klagomål mail.docx", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="AC43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39694-2025 tillsynsbegäran.docx", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="AD43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39694-2025 tillsynsbegäran mail.docx", "A 39694-2025")</f>
+        <v/>
+      </c>
+      <c r="AE43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39694-2025 prioriterade fågelarter.docx", "A 39694-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>A 69777-2021</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="n">
+        <v>44532</v>
+      </c>
+      <c r="E44" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3</v>
+      </c>
+      <c r="T44" t="n">
+        <v>5</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>Bombmurkla
+Rävticka
+Vedticka</t>
+        </is>
+      </c>
+      <c r="W44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 69777-2021 artfynd.xlsx", "A 69777-2021")</f>
+        <v/>
+      </c>
+      <c r="X44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 69777-2021 karta.png", "A 69777-2021")</f>
+        <v/>
+      </c>
+      <c r="Y44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 69777-2021 georefererad karta.tif", "A 69777-2021")</f>
+        <v/>
+      </c>
+      <c r="AA44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 69777-2021 FSC-klagomål.docx", "A 69777-2021")</f>
+        <v/>
+      </c>
+      <c r="AB44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 69777-2021 FSC-klagomål mail.docx", "A 69777-2021")</f>
+        <v/>
+      </c>
+      <c r="AC44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 69777-2021 tillsynsbegäran.docx", "A 69777-2021")</f>
+        <v/>
+      </c>
+      <c r="AD44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 69777-2021 tillsynsbegäran mail.docx", "A 69777-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>A 49718-2023</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>45212</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>2</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3</v>
+      </c>
+      <c r="T45" t="n">
         <v>6</v>
       </c>
-      <c r="U43" t="n">
+      <c r="U45" t="n">
         <v>6</v>
       </c>
-      <c r="V43" s="2" t="inlineStr">
+      <c r="V45" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Talltita
 Zontaggsvamp</t>
         </is>
       </c>
-      <c r="W43">
+      <c r="W45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 49718-2023 artfynd.xlsx", "A 49718-2023")</f>
         <v/>
       </c>
-      <c r="X43">
+      <c r="X45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 49718-2023 karta.png", "A 49718-2023")</f>
         <v/>
       </c>
-      <c r="Y43">
+      <c r="Y45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 49718-2023 georefererad karta.tif", "A 49718-2023")</f>
         <v/>
       </c>
-      <c r="AA43">
+      <c r="AA45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 49718-2023 FSC-klagomål.docx", "A 49718-2023")</f>
         <v/>
       </c>
-      <c r="AB43">
+      <c r="AB45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 49718-2023 FSC-klagomål mail.docx", "A 49718-2023")</f>
         <v/>
       </c>
-      <c r="AC43">
+      <c r="AC45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 49718-2023 tillsynsbegäran.docx", "A 49718-2023")</f>
         <v/>
       </c>
-      <c r="AD43">
+      <c r="AD45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 49718-2023 tillsynsbegäran mail.docx", "A 49718-2023")</f>
         <v/>
       </c>
-      <c r="AE43">
+      <c r="AE45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 49718-2023 prioriterade fågelarter.docx", "A 49718-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>A 39694-2025</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>A 63146-2025</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D44" s="1" t="n">
-        <v>45890</v>
-      </c>
-      <c r="E44" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F44" t="inlineStr">
+      <c r="D46" s="1" t="n">
+        <v>46009</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>VÄSTMANLANDS LÄN</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I44" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J44" t="n">
-        <v>1</v>
-      </c>
-      <c r="K44" t="n">
-        <v>1</v>
-      </c>
-      <c r="L44" t="n">
-        <v>1</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>1</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
+      <c r="I46" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
         <v>3</v>
       </c>
-      <c r="T44" t="n">
+      <c r="T46" t="n">
+        <v>12</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>Stor aspticka
+Svart trolldruva
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63146-2025 artfynd.xlsx", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="X46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63146-2025 karta.png", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="Y46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63146-2025 georefererad karta.tif", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="AA46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63146-2025 FSC-klagomål.docx", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="AB46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63146-2025 FSC-klagomål mail.docx", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="AC46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63146-2025 tillsynsbegäran.docx", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="AD46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63146-2025 tillsynsbegäran mail.docx", "A 63146-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>A 4082-2025</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>45684</v>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2</v>
+      </c>
+      <c r="K47" t="n">
+        <v>2</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
         <v>3</v>
       </c>
-      <c r="U44" t="n">
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>Grönpyrola
+Plattlummer
+Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="W47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 4082-2025 artfynd.xlsx", "A 4082-2025")</f>
+        <v/>
+      </c>
+      <c r="X47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 4082-2025 karta.png", "A 4082-2025")</f>
+        <v/>
+      </c>
+      <c r="Y47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 4082-2025 georefererad karta.tif", "A 4082-2025")</f>
+        <v/>
+      </c>
+      <c r="AA47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 4082-2025 FSC-klagomål.docx", "A 4082-2025")</f>
+        <v/>
+      </c>
+      <c r="AB47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 4082-2025 FSC-klagomål mail.docx", "A 4082-2025")</f>
+        <v/>
+      </c>
+      <c r="AC47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 4082-2025 tillsynsbegäran.docx", "A 4082-2025")</f>
+        <v/>
+      </c>
+      <c r="AD47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 4082-2025 tillsynsbegäran mail.docx", "A 4082-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>A 48128-2023</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D48" s="1" t="n">
+        <v>45205</v>
+      </c>
+      <c r="E48" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" t="n">
         <v>2</v>
       </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Mindre märgborre
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39694-2025 artfynd.xlsx", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39694-2025 karta.png", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39694-2025 georefererad karta.tif", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39694-2025 FSC-klagomål.docx", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39694-2025 FSC-klagomål mail.docx", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39694-2025 tillsynsbegäran.docx", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39694-2025 tillsynsbegäran mail.docx", "A 39694-2025")</f>
-        <v/>
-      </c>
-      <c r="AE44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39694-2025 prioriterade fågelarter.docx", "A 39694-2025")</f>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>2</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>3</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>Jungfrulin
+Svinrot
+Vedticka</t>
+        </is>
+      </c>
+      <c r="W48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 48128-2023 artfynd.xlsx", "A 48128-2023")</f>
+        <v/>
+      </c>
+      <c r="X48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 48128-2023 karta.png", "A 48128-2023")</f>
+        <v/>
+      </c>
+      <c r="Y48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 48128-2023 georefererad karta.tif", "A 48128-2023")</f>
+        <v/>
+      </c>
+      <c r="AA48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 48128-2023 FSC-klagomål.docx", "A 48128-2023")</f>
+        <v/>
+      </c>
+      <c r="AB48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 48128-2023 FSC-klagomål mail.docx", "A 48128-2023")</f>
+        <v/>
+      </c>
+      <c r="AC48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 48128-2023 tillsynsbegäran.docx", "A 48128-2023")</f>
+        <v/>
+      </c>
+      <c r="AD48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 48128-2023 tillsynsbegäran mail.docx", "A 48128-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>A 42765-2022</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D45" s="1" t="n">
+      <c r="D49" s="1" t="n">
         <v>44832</v>
       </c>
-      <c r="E45" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F45" t="inlineStr">
+      <c r="E49" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>VÄSTMANLANDS LÄN</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="I45" t="n">
+      <c r="I49" t="n">
         <v>1.8</v>
       </c>
-      <c r="J45" t="n">
-        <v>1</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1</v>
-      </c>
-      <c r="L45" t="n">
-        <v>1</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>1</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
         <v>3</v>
       </c>
-      <c r="T45" t="n">
+      <c r="T49" t="n">
         <v>4</v>
       </c>
-      <c r="U45" t="n">
-        <v>1</v>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
+      <c r="U49" t="n">
+        <v>1</v>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
         <is>
           <t>Krusfrö
 Barkticka
 Blåsippa</t>
         </is>
       </c>
-      <c r="W45">
+      <c r="W49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 42765-2022 artfynd.xlsx", "A 42765-2022")</f>
         <v/>
       </c>
-      <c r="X45">
+      <c r="X49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 42765-2022 karta.png", "A 42765-2022")</f>
         <v/>
       </c>
-      <c r="Y45">
+      <c r="Y49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 42765-2022 georefererad karta.tif", "A 42765-2022")</f>
         <v/>
       </c>
-      <c r="AA45">
+      <c r="AA49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 42765-2022 FSC-klagomål.docx", "A 42765-2022")</f>
         <v/>
       </c>
-      <c r="AB45">
+      <c r="AB49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 42765-2022 FSC-klagomål mail.docx", "A 42765-2022")</f>
         <v/>
       </c>
-      <c r="AC45">
+      <c r="AC49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 42765-2022 tillsynsbegäran.docx", "A 42765-2022")</f>
         <v/>
       </c>
-      <c r="AD45">
+      <c r="AD49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 42765-2022 tillsynsbegäran mail.docx", "A 42765-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>A 69777-2021</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="n">
-        <v>44532</v>
-      </c>
-      <c r="E46" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J46" t="n">
-        <v>1</v>
-      </c>
-      <c r="K46" t="n">
-        <v>2</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>1</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>1</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1</v>
-      </c>
-      <c r="S46" t="n">
-        <v>3</v>
-      </c>
-      <c r="T46" t="n">
-        <v>5</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>Bombmurkla
-Rävticka
-Vedticka</t>
-        </is>
-      </c>
-      <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 69777-2021 artfynd.xlsx", "A 69777-2021")</f>
-        <v/>
-      </c>
-      <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 69777-2021 karta.png", "A 69777-2021")</f>
-        <v/>
-      </c>
-      <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 69777-2021 georefererad karta.tif", "A 69777-2021")</f>
-        <v/>
-      </c>
-      <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 69777-2021 FSC-klagomål.docx", "A 69777-2021")</f>
-        <v/>
-      </c>
-      <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 69777-2021 FSC-klagomål mail.docx", "A 69777-2021")</f>
-        <v/>
-      </c>
-      <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 69777-2021 tillsynsbegäran.docx", "A 69777-2021")</f>
-        <v/>
-      </c>
-      <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 69777-2021 tillsynsbegäran mail.docx", "A 69777-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>A 4082-2025</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="n">
-        <v>45684</v>
-      </c>
-      <c r="E47" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="J47" t="n">
-        <v>2</v>
-      </c>
-      <c r="K47" t="n">
-        <v>2</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>3</v>
-      </c>
-      <c r="T47" t="n">
-        <v>3</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1</v>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>Grönpyrola
-Plattlummer
-Lopplummer (aggregat)</t>
-        </is>
-      </c>
-      <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 4082-2025 artfynd.xlsx", "A 4082-2025")</f>
-        <v/>
-      </c>
-      <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 4082-2025 karta.png", "A 4082-2025")</f>
-        <v/>
-      </c>
-      <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 4082-2025 georefererad karta.tif", "A 4082-2025")</f>
-        <v/>
-      </c>
-      <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 4082-2025 FSC-klagomål.docx", "A 4082-2025")</f>
-        <v/>
-      </c>
-      <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 4082-2025 FSC-klagomål mail.docx", "A 4082-2025")</f>
-        <v/>
-      </c>
-      <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 4082-2025 tillsynsbegäran.docx", "A 4082-2025")</f>
-        <v/>
-      </c>
-      <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 4082-2025 tillsynsbegäran mail.docx", "A 4082-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>A 48128-2023</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="n">
-        <v>45205</v>
-      </c>
-      <c r="E48" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>1</v>
-      </c>
-      <c r="L48" t="n">
-        <v>2</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>2</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>3</v>
-      </c>
-      <c r="T48" t="n">
-        <v>3</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>Jungfrulin
-Svinrot
-Vedticka</t>
-        </is>
-      </c>
-      <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 48128-2023 artfynd.xlsx", "A 48128-2023")</f>
-        <v/>
-      </c>
-      <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 48128-2023 karta.png", "A 48128-2023")</f>
-        <v/>
-      </c>
-      <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 48128-2023 georefererad karta.tif", "A 48128-2023")</f>
-        <v/>
-      </c>
-      <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 48128-2023 FSC-klagomål.docx", "A 48128-2023")</f>
-        <v/>
-      </c>
-      <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 48128-2023 FSC-klagomål mail.docx", "A 48128-2023")</f>
-        <v/>
-      </c>
-      <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 48128-2023 tillsynsbegäran.docx", "A 48128-2023")</f>
-        <v/>
-      </c>
-      <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 48128-2023 tillsynsbegäran mail.docx", "A 48128-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="15" customHeight="1">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>A 63146-2025</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D49" s="1" t="n">
-        <v>46009</v>
-      </c>
-      <c r="E49" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="J49" t="n">
-        <v>1</v>
-      </c>
-      <c r="K49" t="n">
-        <v>2</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>3</v>
-      </c>
-      <c r="T49" t="n">
-        <v>12</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" s="2" t="inlineStr">
-        <is>
-          <t>Stor aspticka
-Svart trolldruva
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63146-2025 artfynd.xlsx", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63146-2025 karta.png", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63146-2025 georefererad karta.tif", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63146-2025 FSC-klagomål.docx", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63146-2025 FSC-klagomål mail.docx", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63146-2025 tillsynsbegäran.docx", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63146-2025 tillsynsbegäran mail.docx", "A 63146-2025")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 33935-2026</t>
+          <t>A 36264-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6578,10 +6578,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46248</v>
+        <v>46268</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6595,309 +6595,309 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
         <v>2</v>
       </c>
-      <c r="K50" t="n">
-        <v>1</v>
-      </c>
-      <c r="L50" t="n">
-        <v>1</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>1</v>
-      </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
       </c>
       <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>Grangråticka
+Fjällig taggsvamp s.str.
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 36264-2026 artfynd.xlsx", "A 36264-2026")</f>
+        <v/>
+      </c>
+      <c r="X50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 36264-2026 karta.png", "A 36264-2026")</f>
+        <v/>
+      </c>
+      <c r="Y50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 36264-2026 georefererad karta.tif", "A 36264-2026")</f>
+        <v/>
+      </c>
+      <c r="AA50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 36264-2026 FSC-klagomål.docx", "A 36264-2026")</f>
+        <v/>
+      </c>
+      <c r="AB50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 36264-2026 FSC-klagomål mail.docx", "A 36264-2026")</f>
+        <v/>
+      </c>
+      <c r="AC50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 36264-2026 tillsynsbegäran.docx", "A 36264-2026")</f>
+        <v/>
+      </c>
+      <c r="AD50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 36264-2026 tillsynsbegäran mail.docx", "A 36264-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>A 32443-2026</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E51" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>3</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>3</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>3</v>
+      </c>
+      <c r="T51" t="n">
         <v>5</v>
       </c>
-      <c r="U50" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" s="2" t="inlineStr">
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Tallticka
+Ullticka</t>
+        </is>
+      </c>
+      <c r="W51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 32443-2026 artfynd.xlsx", "A 32443-2026")</f>
+        <v/>
+      </c>
+      <c r="X51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 32443-2026 karta.png", "A 32443-2026")</f>
+        <v/>
+      </c>
+      <c r="Y51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 32443-2026 georefererad karta.tif", "A 32443-2026")</f>
+        <v/>
+      </c>
+      <c r="AA51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 32443-2026 FSC-klagomål.docx", "A 32443-2026")</f>
+        <v/>
+      </c>
+      <c r="AB51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 32443-2026 FSC-klagomål mail.docx", "A 32443-2026")</f>
+        <v/>
+      </c>
+      <c r="AC51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 32443-2026 tillsynsbegäran.docx", "A 32443-2026")</f>
+        <v/>
+      </c>
+      <c r="AD51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 32443-2026 tillsynsbegäran mail.docx", "A 32443-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>A 33935-2026</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D52" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E52" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" t="n">
+        <v>1</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>3</v>
+      </c>
+      <c r="T52" t="n">
+        <v>5</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Mindre märgborre
 Spillkråka</t>
         </is>
       </c>
-      <c r="W50">
+      <c r="W52">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 33935-2026 artfynd.xlsx", "A 33935-2026")</f>
         <v/>
       </c>
-      <c r="X50">
+      <c r="X52">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 33935-2026 karta.png", "A 33935-2026")</f>
         <v/>
       </c>
-      <c r="Y50">
+      <c r="Y52">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 33935-2026 georefererad karta.tif", "A 33935-2026")</f>
         <v/>
       </c>
-      <c r="AA50">
+      <c r="AA52">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 33935-2026 FSC-klagomål.docx", "A 33935-2026")</f>
         <v/>
       </c>
-      <c r="AB50">
+      <c r="AB52">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 33935-2026 FSC-klagomål mail.docx", "A 33935-2026")</f>
         <v/>
       </c>
-      <c r="AC50">
+      <c r="AC52">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 33935-2026 tillsynsbegäran.docx", "A 33935-2026")</f>
         <v/>
       </c>
-      <c r="AD50">
+      <c r="AD52">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 33935-2026 tillsynsbegäran mail.docx", "A 33935-2026")</f>
         <v/>
       </c>
-      <c r="AE50">
+      <c r="AE52">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 33935-2026 prioriterade fågelarter.docx", "A 33935-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>A 36264-2026</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="n">
-        <v>46268</v>
-      </c>
-      <c r="E51" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J51" t="n">
-        <v>1</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>1</v>
-      </c>
-      <c r="M51" t="n">
-        <v>1</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>2</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1</v>
-      </c>
-      <c r="S51" t="n">
-        <v>3</v>
-      </c>
-      <c r="T51" t="n">
-        <v>3</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" s="2" t="inlineStr">
-        <is>
-          <t>Grangråticka
-Fjällig taggsvamp s.str.
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 36264-2026 artfynd.xlsx", "A 36264-2026")</f>
-        <v/>
-      </c>
-      <c r="X51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 36264-2026 karta.png", "A 36264-2026")</f>
-        <v/>
-      </c>
-      <c r="Y51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 36264-2026 georefererad karta.tif", "A 36264-2026")</f>
-        <v/>
-      </c>
-      <c r="AA51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 36264-2026 FSC-klagomål.docx", "A 36264-2026")</f>
-        <v/>
-      </c>
-      <c r="AB51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 36264-2026 FSC-klagomål mail.docx", "A 36264-2026")</f>
-        <v/>
-      </c>
-      <c r="AC51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 36264-2026 tillsynsbegäran.docx", "A 36264-2026")</f>
-        <v/>
-      </c>
-      <c r="AD51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 36264-2026 tillsynsbegäran mail.docx", "A 36264-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="15" customHeight="1">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>A 32443-2026</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D52" s="1" t="n">
-        <v>46239</v>
-      </c>
-      <c r="E52" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I52" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
-        <v>3</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>3</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" t="n">
-        <v>3</v>
-      </c>
-      <c r="T52" t="n">
-        <v>5</v>
-      </c>
-      <c r="U52" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Tallticka
-Ullticka</t>
-        </is>
-      </c>
-      <c r="W52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 32443-2026 artfynd.xlsx", "A 32443-2026")</f>
-        <v/>
-      </c>
-      <c r="X52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 32443-2026 karta.png", "A 32443-2026")</f>
-        <v/>
-      </c>
-      <c r="Y52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 32443-2026 georefererad karta.tif", "A 32443-2026")</f>
-        <v/>
-      </c>
-      <c r="AA52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 32443-2026 FSC-klagomål.docx", "A 32443-2026")</f>
-        <v/>
-      </c>
-      <c r="AB52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 32443-2026 FSC-klagomål mail.docx", "A 32443-2026")</f>
-        <v/>
-      </c>
-      <c r="AC52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 32443-2026 tillsynsbegäran.docx", "A 32443-2026")</f>
-        <v/>
-      </c>
-      <c r="AD52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 32443-2026 tillsynsbegäran mail.docx", "A 32443-2026")</f>
         <v/>
       </c>
     </row>
@@ -6921,7 +6921,7 @@
         <v>44635</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>45708</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>45708</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 30074-2023</t>
+          <t>A 56362-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7270,10 +7270,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45110</v>
+        <v>45236</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7287,11 +7287,11 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.1</v>
+        <v>15.2</v>
       </c>
       <c r="J56" t="n">
         <v>1</v>
@@ -7303,7 +7303,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
@@ -7315,10 +7315,10 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S56" t="n">
         <v>2</v>
@@ -7327,47 +7327,47 @@
         <v>2</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola
-Revlummer</t>
+          <t>Väddnätfjäril
+Grönpyrola</t>
         </is>
       </c>
       <c r="W56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 30074-2023 artfynd.xlsx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 56362-2023 artfynd.xlsx", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="X56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 30074-2023 karta.png", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 56362-2023 karta.png", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="Y56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 30074-2023 georefererad karta.tif", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 56362-2023 georefererad karta.tif", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="AA56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 30074-2023 FSC-klagomål.docx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 56362-2023 FSC-klagomål.docx", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="AB56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 30074-2023 FSC-klagomål mail.docx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 56362-2023 FSC-klagomål mail.docx", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="AC56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 30074-2023 tillsynsbegäran.docx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 56362-2023 tillsynsbegäran.docx", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="AD56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 30074-2023 tillsynsbegäran mail.docx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 56362-2023 tillsynsbegäran mail.docx", "A 56362-2023")</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 56362-2023</t>
+          <t>A 40403-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45236</v>
+        <v>45895</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7398,17 +7398,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>15.2</v>
+        <v>3.9</v>
       </c>
       <c r="J57" t="n">
         <v>1</v>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -7435,50 +7435,50 @@
         <v>2</v>
       </c>
       <c r="T57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U57" t="n">
         <v>1</v>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>Väddnätfjäril
-Grönpyrola</t>
+          <t>Igelkott
+Gröngöling</t>
         </is>
       </c>
       <c r="W57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 56362-2023 artfynd.xlsx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 40403-2025 artfynd.xlsx", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="X57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 56362-2023 karta.png", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 40403-2025 karta.png", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="Y57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 56362-2023 georefererad karta.tif", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 40403-2025 georefererad karta.tif", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="AA57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 56362-2023 FSC-klagomål.docx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 40403-2025 FSC-klagomål.docx", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="AB57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 56362-2023 FSC-klagomål mail.docx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 40403-2025 FSC-klagomål mail.docx", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="AC57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 56362-2023 tillsynsbegäran.docx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 40403-2025 tillsynsbegäran.docx", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="AD57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 56362-2023 tillsynsbegäran mail.docx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 40403-2025 tillsynsbegäran mail.docx", "A 40403-2025")</f>
         <v/>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 47453-2024</t>
+          <t>A 14001-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7492,10 +7492,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45587</v>
+        <v>45007</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7507,35 +7507,40 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>5.1</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
         <v>2</v>
       </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>1</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>1</v>
-      </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S58" t="n">
         <v>2</v>
@@ -7544,51 +7549,47 @@
         <v>2</v>
       </c>
       <c r="U58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>Göktyta
-Gröngöling</t>
+          <t>Garnlav
+Motaggsvamp</t>
         </is>
       </c>
       <c r="W58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 47453-2024 artfynd.xlsx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 14001-2023 artfynd.xlsx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="X58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 47453-2024 karta.png", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 14001-2023 karta.png", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="Y58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 47453-2024 georefererad karta.tif", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 14001-2023 georefererad karta.tif", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AA58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 47453-2024 FSC-klagomål.docx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 14001-2023 FSC-klagomål.docx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AB58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 47453-2024 FSC-klagomål mail.docx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 14001-2023 FSC-klagomål mail.docx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AC58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 47453-2024 tillsynsbegäran.docx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 14001-2023 tillsynsbegäran.docx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AD58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 47453-2024 tillsynsbegäran mail.docx", "A 47453-2024")</f>
-        <v/>
-      </c>
-      <c r="AE58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 47453-2024 prioriterade fågelarter.docx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 14001-2023 tillsynsbegäran mail.docx", "A 14001-2023")</f>
         <v/>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 37013-2025</t>
+          <t>A 13788-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7602,10 +7603,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45874</v>
+        <v>45737</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7617,25 +7618,20 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>10.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
@@ -7647,10 +7643,10 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>2</v>
@@ -7659,47 +7655,51 @@
         <v>2</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril
-Fältgentiana</t>
+          <t>Sparvuggla
+Nattskärra</t>
         </is>
       </c>
       <c r="W59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37013-2025 artfynd.xlsx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 13788-2025 artfynd.xlsx", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="X59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37013-2025 karta.png", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 13788-2025 karta.png", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="Y59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37013-2025 georefererad karta.tif", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 13788-2025 georefererad karta.tif", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="AA59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37013-2025 FSC-klagomål.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 13788-2025 FSC-klagomål.docx", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="AB59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37013-2025 FSC-klagomål mail.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 13788-2025 FSC-klagomål mail.docx", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="AC59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37013-2025 tillsynsbegäran.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 13788-2025 tillsynsbegäran.docx", "A 13788-2025")</f>
         <v/>
       </c>
       <c r="AD59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37013-2025 tillsynsbegäran mail.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 13788-2025 tillsynsbegäran mail.docx", "A 13788-2025")</f>
+        <v/>
+      </c>
+      <c r="AE59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 13788-2025 prioriterade fågelarter.docx", "A 13788-2025")</f>
         <v/>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 40403-2025</t>
+          <t>A 47453-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7713,10 +7713,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45895</v>
+        <v>45587</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7728,25 +7728,20 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
         <v>0</v>
@@ -7761,56 +7756,60 @@
         <v>1</v>
       </c>
       <c r="R60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>2</v>
       </c>
       <c r="T60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U60" t="n">
         <v>1</v>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>Igelkott
+          <t>Göktyta
 Gröngöling</t>
         </is>
       </c>
       <c r="W60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 40403-2025 artfynd.xlsx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 47453-2024 artfynd.xlsx", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="X60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 40403-2025 karta.png", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 47453-2024 karta.png", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="Y60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 40403-2025 georefererad karta.tif", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 47453-2024 georefererad karta.tif", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="AA60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 40403-2025 FSC-klagomål.docx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 47453-2024 FSC-klagomål.docx", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="AB60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 40403-2025 FSC-klagomål mail.docx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 47453-2024 FSC-klagomål mail.docx", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="AC60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 40403-2025 tillsynsbegäran.docx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 47453-2024 tillsynsbegäran.docx", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="AD60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 40403-2025 tillsynsbegäran mail.docx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 47453-2024 tillsynsbegäran mail.docx", "A 47453-2024")</f>
+        <v/>
+      </c>
+      <c r="AE60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 47453-2024 prioriterade fågelarter.docx", "A 47453-2024")</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 63138-2025</t>
+          <t>A 11501-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7824,10 +7823,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46009</v>
+        <v>44991</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7845,7 +7844,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>1</v>
@@ -7878,47 +7877,43 @@
         <v>2</v>
       </c>
       <c r="T61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U61" t="n">
         <v>2</v>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>Mindre märgborre
-Tjäder</t>
+          <t>Svart trolldruva
+Nattviol</t>
         </is>
       </c>
       <c r="W61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63138-2025 artfynd.xlsx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 11501-2023 artfynd.xlsx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="X61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63138-2025 karta.png", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 11501-2023 karta.png", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="Y61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63138-2025 georefererad karta.tif", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 11501-2023 georefererad karta.tif", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AA61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63138-2025 FSC-klagomål.docx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 11501-2023 FSC-klagomål.docx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AB61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63138-2025 FSC-klagomål mail.docx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 11501-2023 FSC-klagomål mail.docx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AC61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63138-2025 tillsynsbegäran.docx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 11501-2023 tillsynsbegäran.docx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AD61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63138-2025 tillsynsbegäran mail.docx", "A 63138-2025")</f>
-        <v/>
-      </c>
-      <c r="AE61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 63138-2025 prioriterade fågelarter.docx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 11501-2023 tillsynsbegäran mail.docx", "A 11501-2023")</f>
         <v/>
       </c>
     </row>
@@ -7942,7 +7937,7 @@
         <v>45174</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8035,7 +8030,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 11501-2023</t>
+          <t>A 63138-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -8049,10 +8044,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44991</v>
+        <v>46009</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8070,7 +8065,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J63" t="n">
         <v>1</v>
@@ -8103,50 +8098,54 @@
         <v>2</v>
       </c>
       <c r="T63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U63" t="n">
         <v>2</v>
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva
-Nattviol</t>
+          <t>Mindre märgborre
+Tjäder</t>
         </is>
       </c>
       <c r="W63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 11501-2023 artfynd.xlsx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63138-2025 artfynd.xlsx", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="X63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 11501-2023 karta.png", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63138-2025 karta.png", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="Y63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 11501-2023 georefererad karta.tif", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63138-2025 georefererad karta.tif", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="AA63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 11501-2023 FSC-klagomål.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63138-2025 FSC-klagomål.docx", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="AB63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 11501-2023 FSC-klagomål mail.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63138-2025 FSC-klagomål mail.docx", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="AC63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 11501-2023 tillsynsbegäran.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63138-2025 tillsynsbegäran.docx", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="AD63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 11501-2023 tillsynsbegäran mail.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63138-2025 tillsynsbegäran mail.docx", "A 63138-2025")</f>
+        <v/>
+      </c>
+      <c r="AE63">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 63138-2025 prioriterade fågelarter.docx", "A 63138-2025")</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 14001-2023</t>
+          <t>A 30074-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -8160,10 +8159,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45007</v>
+        <v>45110</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8177,23 +8176,23 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
@@ -8205,10 +8204,10 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>2</v>
@@ -8221,43 +8220,43 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>Garnlav
-Motaggsvamp</t>
+          <t>Grönpyrola
+Revlummer</t>
         </is>
       </c>
       <c r="W64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 14001-2023 artfynd.xlsx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 30074-2023 artfynd.xlsx", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="X64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 14001-2023 karta.png", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 30074-2023 karta.png", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="Y64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 14001-2023 georefererad karta.tif", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 30074-2023 georefererad karta.tif", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="AA64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 14001-2023 FSC-klagomål.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 30074-2023 FSC-klagomål.docx", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="AB64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 14001-2023 FSC-klagomål mail.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 30074-2023 FSC-klagomål mail.docx", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="AC64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 14001-2023 tillsynsbegäran.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 30074-2023 tillsynsbegäran.docx", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="AD64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 14001-2023 tillsynsbegäran mail.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 30074-2023 tillsynsbegäran mail.docx", "A 30074-2023")</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 13971-2023</t>
+          <t>A 37013-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -8271,10 +8270,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45007</v>
+        <v>45874</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8292,20 +8291,20 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.9</v>
+        <v>10.7</v>
       </c>
       <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
         <v>2</v>
       </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="n">
-        <v>0</v>
-      </c>
       <c r="N65" t="n">
         <v>0</v>
       </c>
@@ -8316,59 +8315,59 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S65" t="n">
         <v>2</v>
       </c>
       <c r="T65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>Dubbelnycklar
-Fläcknycklar</t>
+          <t>Brunfläckig pärlemorfjäril
+Fältgentiana</t>
         </is>
       </c>
       <c r="W65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 13971-2023 artfynd.xlsx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37013-2025 artfynd.xlsx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="X65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 13971-2023 karta.png", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37013-2025 karta.png", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="Y65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 13971-2023 georefererad karta.tif", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37013-2025 georefererad karta.tif", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AA65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 13971-2023 FSC-klagomål.docx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37013-2025 FSC-klagomål.docx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AB65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 13971-2023 FSC-klagomål mail.docx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37013-2025 FSC-klagomål mail.docx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AC65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 13971-2023 tillsynsbegäran.docx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37013-2025 tillsynsbegäran.docx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AD65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 13971-2023 tillsynsbegäran mail.docx", "A 13971-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37013-2025 tillsynsbegäran mail.docx", "A 37013-2025")</f>
         <v/>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 36261-2026</t>
+          <t>A 13971-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -8382,10 +8381,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46268</v>
+        <v>45007</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8399,20 +8398,20 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>7.9</v>
+        <v>2.9</v>
       </c>
       <c r="J66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -8427,7 +8426,7 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
@@ -8436,50 +8435,50 @@
         <v>2</v>
       </c>
       <c r="T66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>Krusfrö
-Revlummer</t>
+          <t>Dubbelnycklar
+Fläcknycklar</t>
         </is>
       </c>
       <c r="W66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 36261-2026 artfynd.xlsx", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 13971-2023 artfynd.xlsx", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="X66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 36261-2026 karta.png", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 13971-2023 karta.png", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="Y66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 36261-2026 georefererad karta.tif", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 13971-2023 georefererad karta.tif", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="AA66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 36261-2026 FSC-klagomål.docx", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 13971-2023 FSC-klagomål.docx", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="AB66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 36261-2026 FSC-klagomål mail.docx", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 13971-2023 FSC-klagomål mail.docx", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="AC66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 36261-2026 tillsynsbegäran.docx", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 13971-2023 tillsynsbegäran.docx", "A 13971-2023")</f>
         <v/>
       </c>
       <c r="AD66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 36261-2026 tillsynsbegäran mail.docx", "A 36261-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 13971-2023 tillsynsbegäran mail.docx", "A 13971-2023")</f>
         <v/>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 13788-2025</t>
+          <t>A 36261-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -8493,10 +8492,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45737</v>
+        <v>46268</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8508,11 +8507,16 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>9.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -8545,44 +8549,40 @@
         <v>2</v>
       </c>
       <c r="U67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>Sparvuggla
-Nattskärra</t>
+          <t>Krusfrö
+Revlummer</t>
         </is>
       </c>
       <c r="W67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 13788-2025 artfynd.xlsx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 36261-2026 artfynd.xlsx", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="X67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 13788-2025 karta.png", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 36261-2026 karta.png", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="Y67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 13788-2025 georefererad karta.tif", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 36261-2026 georefererad karta.tif", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="AA67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 13788-2025 FSC-klagomål.docx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 36261-2026 FSC-klagomål.docx", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="AB67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 13788-2025 FSC-klagomål mail.docx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 36261-2026 FSC-klagomål mail.docx", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="AC67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 13788-2025 tillsynsbegäran.docx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 36261-2026 tillsynsbegäran.docx", "A 36261-2026")</f>
         <v/>
       </c>
       <c r="AD67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 13788-2025 tillsynsbegäran mail.docx", "A 13788-2025")</f>
-        <v/>
-      </c>
-      <c r="AE67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 13788-2025 prioriterade fågelarter.docx", "A 13788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 36261-2026 tillsynsbegäran mail.docx", "A 36261-2026")</f>
         <v/>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
         <v>45720</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8717,7 +8717,7 @@
         <v>44696</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>44739</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>44524</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>44696</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 30076-2023</t>
+          <t>A 39099-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -9154,10 +9154,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45110</v>
+        <v>44817</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9171,17 +9171,17 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.1</v>
+        <v>7.4</v>
       </c>
       <c r="J73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -9211,39 +9211,39 @@
         <v>1</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="W73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 30076-2023 artfynd.xlsx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39099-2022 artfynd.xlsx", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="X73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 30076-2023 karta.png", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39099-2022 karta.png", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="Y73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 30076-2023 georefererad karta.tif", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39099-2022 georefererad karta.tif", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="AA73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 30076-2023 FSC-klagomål.docx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39099-2022 FSC-klagomål.docx", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="AB73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 30076-2023 FSC-klagomål mail.docx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39099-2022 FSC-klagomål mail.docx", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="AC73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 30076-2023 tillsynsbegäran.docx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39099-2022 tillsynsbegäran.docx", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="AD73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 30076-2023 tillsynsbegäran mail.docx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39099-2022 tillsynsbegäran mail.docx", "A 39099-2022")</f>
         <v/>
       </c>
     </row>
@@ -9267,7 +9267,7 @@
         <v>44977</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 37287-2023</t>
+          <t>A 16013-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -9374,10 +9374,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45156</v>
+        <v>45026</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -9399,10 +9399,10 @@
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N75" t="n">
         <v>0</v>
@@ -9417,7 +9417,7 @@
         <v>1</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S75" t="n">
         <v>1</v>
@@ -9430,42 +9430,42 @@
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>Mindre tåtelsmygare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="W75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37287-2023 artfynd.xlsx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 16013-2023 artfynd.xlsx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="X75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37287-2023 karta.png", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 16013-2023 karta.png", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="Y75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37287-2023 georefererad karta.tif", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 16013-2023 georefererad karta.tif", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AA75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37287-2023 FSC-klagomål.docx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 16013-2023 FSC-klagomål.docx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AB75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37287-2023 FSC-klagomål mail.docx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 16013-2023 FSC-klagomål mail.docx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AC75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37287-2023 tillsynsbegäran.docx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 16013-2023 tillsynsbegäran.docx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AD75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37287-2023 tillsynsbegäran mail.docx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 16013-2023 tillsynsbegäran mail.docx", "A 16013-2023")</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 39099-2022</t>
+          <t>A 34955-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -9479,10 +9479,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44817</v>
+        <v>44796</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9496,20 +9496,20 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -9524,7 +9524,7 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R76" t="n">
         <v>0</v>
@@ -9540,42 +9540,42 @@
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39099-2022 artfynd.xlsx", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34955-2022 artfynd.xlsx", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="X76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39099-2022 karta.png", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34955-2022 karta.png", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="Y76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39099-2022 georefererad karta.tif", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34955-2022 georefererad karta.tif", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="AA76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39099-2022 FSC-klagomål.docx", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34955-2022 FSC-klagomål.docx", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="AB76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39099-2022 FSC-klagomål mail.docx", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34955-2022 FSC-klagomål mail.docx", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="AC76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39099-2022 tillsynsbegäran.docx", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34955-2022 tillsynsbegäran.docx", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="AD76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39099-2022 tillsynsbegäran mail.docx", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34955-2022 tillsynsbegäran mail.docx", "A 34955-2022")</f>
         <v/>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 17632-2022</t>
+          <t>A 33231-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -9589,10 +9589,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44680</v>
+        <v>45518</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9604,14 +9604,19 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>5.2</v>
+        <v>1.5</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -9641,46 +9646,46 @@
         <v>1</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="W77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 17632-2022 artfynd.xlsx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 33231-2024 artfynd.xlsx", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="X77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 17632-2022 karta.png", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 33231-2024 karta.png", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="Y77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 17632-2022 georefererad karta.tif", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 33231-2024 georefererad karta.tif", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="AA77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 17632-2022 FSC-klagomål.docx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 33231-2024 FSC-klagomål.docx", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="AB77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 17632-2022 FSC-klagomål mail.docx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 33231-2024 FSC-klagomål mail.docx", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="AC77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 17632-2022 tillsynsbegäran.docx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 33231-2024 tillsynsbegäran.docx", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="AD77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 17632-2022 tillsynsbegäran mail.docx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 33231-2024 tillsynsbegäran mail.docx", "A 33231-2024")</f>
         <v/>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 34955-2022</t>
+          <t>A 30076-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -9694,10 +9699,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44796</v>
+        <v>45110</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9715,16 +9720,16 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
@@ -9739,7 +9744,7 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
         <v>0</v>
@@ -9751,46 +9756,46 @@
         <v>1</v>
       </c>
       <c r="U78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34955-2022 artfynd.xlsx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 30076-2023 artfynd.xlsx", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="X78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34955-2022 karta.png", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 30076-2023 karta.png", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="Y78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34955-2022 georefererad karta.tif", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 30076-2023 georefererad karta.tif", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="AA78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34955-2022 FSC-klagomål.docx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 30076-2023 FSC-klagomål.docx", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="AB78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34955-2022 FSC-klagomål mail.docx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 30076-2023 FSC-klagomål mail.docx", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="AC78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34955-2022 tillsynsbegäran.docx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 30076-2023 tillsynsbegäran.docx", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="AD78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34955-2022 tillsynsbegäran mail.docx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 30076-2023 tillsynsbegäran mail.docx", "A 30076-2023")</f>
         <v/>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 10883-2023</t>
+          <t>A 34584-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -9804,10 +9809,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44991</v>
+        <v>45846</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9821,11 +9826,11 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>12.5</v>
+        <v>2.7</v>
       </c>
       <c r="J79" t="n">
         <v>1</v>
@@ -9834,7 +9839,7 @@
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -9849,7 +9854,7 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
         <v>0</v>
@@ -9865,46 +9870,46 @@
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 10883-2023 artfynd.xlsx", "A 10883-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34584-2025 artfynd.xlsx", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="X79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 10883-2023 karta.png", "A 10883-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34584-2025 karta.png", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="Y79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 10883-2023 georefererad karta.tif", "A 10883-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34584-2025 georefererad karta.tif", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="AA79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 10883-2023 FSC-klagomål.docx", "A 10883-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34584-2025 FSC-klagomål.docx", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="AB79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 10883-2023 FSC-klagomål mail.docx", "A 10883-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34584-2025 FSC-klagomål mail.docx", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="AC79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 10883-2023 tillsynsbegäran.docx", "A 10883-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34584-2025 tillsynsbegäran.docx", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="AD79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 10883-2023 tillsynsbegäran mail.docx", "A 10883-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34584-2025 tillsynsbegäran mail.docx", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="AE79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 10883-2023 prioriterade fågelarter.docx", "A 10883-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 34584-2025 prioriterade fågelarter.docx", "A 34584-2025")</f>
         <v/>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 44356-2024</t>
+          <t>A 10883-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -9918,10 +9923,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45573</v>
+        <v>44991</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9935,11 +9940,11 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>12.5</v>
       </c>
       <c r="J80" t="n">
         <v>1</v>
@@ -9948,7 +9953,7 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -9963,7 +9968,7 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R80" t="n">
         <v>0</v>
@@ -9979,42 +9984,46 @@
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="W80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 44356-2024 artfynd.xlsx", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 10883-2023 artfynd.xlsx", "A 10883-2023")</f>
         <v/>
       </c>
       <c r="X80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 44356-2024 karta.png", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 10883-2023 karta.png", "A 10883-2023")</f>
         <v/>
       </c>
       <c r="Y80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 44356-2024 georefererad karta.tif", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 10883-2023 georefererad karta.tif", "A 10883-2023")</f>
         <v/>
       </c>
       <c r="AA80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 44356-2024 FSC-klagomål.docx", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 10883-2023 FSC-klagomål.docx", "A 10883-2023")</f>
         <v/>
       </c>
       <c r="AB80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 44356-2024 FSC-klagomål mail.docx", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 10883-2023 FSC-klagomål mail.docx", "A 10883-2023")</f>
         <v/>
       </c>
       <c r="AC80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 44356-2024 tillsynsbegäran.docx", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 10883-2023 tillsynsbegäran.docx", "A 10883-2023")</f>
         <v/>
       </c>
       <c r="AD80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 44356-2024 tillsynsbegäran mail.docx", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 10883-2023 tillsynsbegäran mail.docx", "A 10883-2023")</f>
+        <v/>
+      </c>
+      <c r="AE80">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 10883-2023 prioriterade fågelarter.docx", "A 10883-2023")</f>
         <v/>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 33231-2024</t>
+          <t>A 24167-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -10024,14 +10033,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45518</v>
+        <v>45456</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10043,13 +10052,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J81" t="n">
         <v>1</v>
@@ -10085,46 +10089,46 @@
         <v>1</v>
       </c>
       <c r="U81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 33231-2024 artfynd.xlsx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 24167-2024 artfynd.xlsx", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="X81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 33231-2024 karta.png", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 24167-2024 karta.png", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="Y81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 33231-2024 georefererad karta.tif", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 24167-2024 georefererad karta.tif", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="AA81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 33231-2024 FSC-klagomål.docx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 24167-2024 FSC-klagomål.docx", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="AB81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 33231-2024 FSC-klagomål mail.docx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 24167-2024 FSC-klagomål mail.docx", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="AC81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 33231-2024 tillsynsbegäran.docx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 24167-2024 tillsynsbegäran.docx", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="AD81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 33231-2024 tillsynsbegäran mail.docx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 24167-2024 tillsynsbegäran mail.docx", "A 24167-2024")</f>
         <v/>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 24167-2024</t>
+          <t>A 37287-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -10134,14 +10138,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45456</v>
+        <v>45156</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10157,13 +10161,13 @@
         <v>0.6</v>
       </c>
       <c r="J82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -10178,7 +10182,7 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R82" t="n">
         <v>0</v>
@@ -10194,42 +10198,42 @@
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="W82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 24167-2024 artfynd.xlsx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37287-2023 artfynd.xlsx", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="X82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 24167-2024 karta.png", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37287-2023 karta.png", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="Y82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 24167-2024 georefererad karta.tif", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37287-2023 georefererad karta.tif", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="AA82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 24167-2024 FSC-klagomål.docx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37287-2023 FSC-klagomål.docx", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="AB82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 24167-2024 FSC-klagomål mail.docx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37287-2023 FSC-klagomål mail.docx", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="AC82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 24167-2024 tillsynsbegäran.docx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37287-2023 tillsynsbegäran.docx", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="AD82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 24167-2024 tillsynsbegäran mail.docx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37287-2023 tillsynsbegäran mail.docx", "A 37287-2023")</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 31589-2026</t>
+          <t>A 44356-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -10243,10 +10247,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46224</v>
+        <v>45573</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10260,17 +10264,17 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -10300,46 +10304,46 @@
         <v>1</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31589-2026 artfynd.xlsx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 44356-2024 artfynd.xlsx", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="X83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31589-2026 karta.png", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 44356-2024 karta.png", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="Y83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31589-2026 georefererad karta.tif", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 44356-2024 georefererad karta.tif", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="AA83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31589-2026 FSC-klagomål.docx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 44356-2024 FSC-klagomål.docx", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="AB83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31589-2026 FSC-klagomål mail.docx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 44356-2024 FSC-klagomål mail.docx", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="AC83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31589-2026 tillsynsbegäran.docx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 44356-2024 tillsynsbegäran.docx", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="AD83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31589-2026 tillsynsbegäran mail.docx", "A 31589-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 44356-2024 tillsynsbegäran mail.docx", "A 44356-2024")</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 16013-2023</t>
+          <t>A 31589-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -10353,10 +10357,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45026</v>
+        <v>46224</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10368,20 +10372,25 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
         <v>0</v>
@@ -10393,10 +10402,10 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>1</v>
@@ -10409,42 +10418,42 @@
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 16013-2023 artfynd.xlsx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31589-2026 artfynd.xlsx", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="X84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 16013-2023 karta.png", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31589-2026 karta.png", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="Y84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 16013-2023 georefererad karta.tif", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31589-2026 georefererad karta.tif", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="AA84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 16013-2023 FSC-klagomål.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31589-2026 FSC-klagomål.docx", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="AB84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 16013-2023 FSC-klagomål mail.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31589-2026 FSC-klagomål mail.docx", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="AC84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 16013-2023 tillsynsbegäran.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31589-2026 tillsynsbegäran.docx", "A 31589-2026")</f>
         <v/>
       </c>
       <c r="AD84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 16013-2023 tillsynsbegäran mail.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31589-2026 tillsynsbegäran mail.docx", "A 31589-2026")</f>
         <v/>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 34584-2025</t>
+          <t>A 17632-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -10458,10 +10467,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45846</v>
+        <v>44680</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10473,19 +10482,14 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>2.7</v>
+        <v>5.2</v>
       </c>
       <c r="J85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -10515,43 +10519,39 @@
         <v>1</v>
       </c>
       <c r="U85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="W85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34584-2025 artfynd.xlsx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 17632-2022 artfynd.xlsx", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="X85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34584-2025 karta.png", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 17632-2022 karta.png", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="Y85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34584-2025 georefererad karta.tif", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 17632-2022 georefererad karta.tif", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="AA85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34584-2025 FSC-klagomål.docx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 17632-2022 FSC-klagomål.docx", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="AB85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34584-2025 FSC-klagomål mail.docx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 17632-2022 FSC-klagomål mail.docx", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="AC85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34584-2025 tillsynsbegäran.docx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 17632-2022 tillsynsbegäran.docx", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="AD85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34584-2025 tillsynsbegäran mail.docx", "A 34584-2025")</f>
-        <v/>
-      </c>
-      <c r="AE85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 34584-2025 prioriterade fågelarter.docx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 17632-2022 tillsynsbegäran mail.docx", "A 17632-2022")</f>
         <v/>
       </c>
     </row>
@@ -10575,7 +10575,7 @@
         <v>44509</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>44696</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>44782</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         <v>44550</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>44586</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>44582</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>44694</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>44518</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>44796</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 48205-2023</t>
+          <t>A 24158-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -11264,10 +11264,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45205</v>
+        <v>45079</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11281,11 +11281,11 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>7.6</v>
+        <v>1.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -11328,7 +11328,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 15743-2023</t>
+          <t>A 21509-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -11342,10 +11342,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45021</v>
+        <v>45441</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11357,8 +11357,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -11401,7 +11406,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 15637-2022</t>
+          <t>A 42832-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -11411,14 +11416,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44662</v>
+        <v>44832</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11431,7 +11436,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -11474,7 +11479,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 19786-2023</t>
+          <t>A 42841-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -11484,14 +11489,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45050</v>
+        <v>44832</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11503,13 +11508,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>8.1</v>
+        <v>1.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -11552,7 +11552,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 7787-2024</t>
+          <t>A 4724-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -11566,10 +11566,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45348</v>
+        <v>46048</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -11625,7 +11625,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 72367-2021</t>
+          <t>A 4734-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -11639,10 +11639,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44545</v>
+        <v>46048</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11655,7 +11655,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -11698,7 +11698,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 33931-2022</t>
+          <t>A 3818-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -11712,10 +11712,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44790</v>
+        <v>44587</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11728,7 +11728,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -11771,7 +11771,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 24158-2023</t>
+          <t>A 10244-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -11785,10 +11785,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45079</v>
+        <v>46076</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11802,11 +11802,11 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -11849,7 +11849,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 32808-2024</t>
+          <t>A 10249-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -11863,10 +11863,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45516</v>
+        <v>46076</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11880,11 +11880,11 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.9</v>
+        <v>4.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -11927,7 +11927,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 37954-2025</t>
+          <t>A 10562-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -11941,10 +11941,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45881</v>
+        <v>46077</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11956,8 +11956,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>9.5</v>
+        <v>2.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -12000,7 +12005,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 42714-2022</t>
+          <t>A 19782-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -12014,10 +12019,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44832</v>
+        <v>45050</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12029,8 +12034,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>1.1</v>
+        <v>5.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -12073,7 +12083,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 35682-2022</t>
+          <t>A 14626-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -12087,10 +12097,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44799</v>
+        <v>45012</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12104,11 +12114,11 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -12151,7 +12161,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 11728-2023</t>
+          <t>A 12841-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -12161,14 +12171,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44993</v>
+        <v>46091</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12186,7 +12196,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.4</v>
+        <v>4.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -12229,7 +12239,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 5567-2022</t>
+          <t>A 56378-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -12243,10 +12253,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44595</v>
+        <v>45236</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12258,8 +12268,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>1.3</v>
+        <v>4.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -12302,7 +12317,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 42832-2022</t>
+          <t>A 11728-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -12312,14 +12327,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44832</v>
+        <v>44993</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12331,8 +12346,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -12375,7 +12395,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 24665-2023</t>
+          <t>A 20904-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -12385,14 +12405,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45084</v>
+        <v>45060</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12404,8 +12424,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -12448,7 +12473,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 42841-2022</t>
+          <t>A 55873-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -12458,14 +12483,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44832</v>
+        <v>45973</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12477,8 +12502,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -12521,7 +12551,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 42829-2022</t>
+          <t>A 19246-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -12535,10 +12565,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44832</v>
+        <v>46132</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12550,8 +12580,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -12594,7 +12629,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 2867-2024</t>
+          <t>A 42829-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -12604,14 +12639,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45315</v>
+        <v>44832</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12623,13 +12658,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -12672,7 +12702,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 49058-2024</t>
+          <t>A 48205-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -12686,10 +12716,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45594</v>
+        <v>45205</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12703,11 +12733,11 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>11.4</v>
+        <v>7.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -12750,7 +12780,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 3085-2023</t>
+          <t>A 32808-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -12764,10 +12794,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44946</v>
+        <v>45516</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12781,11 +12811,11 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>13</v>
+        <v>1.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -12845,7 +12875,7 @@
         <v>46140</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12906,7 +12936,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 55873-2025</t>
+          <t>A 33931-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -12920,10 +12950,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45973</v>
+        <v>44790</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12935,13 +12965,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -12984,7 +13009,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 20904-2023</t>
+          <t>A 22662-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -12998,10 +13023,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45060</v>
+        <v>45071</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13019,7 +13044,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -13062,7 +13087,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 2660-2024</t>
+          <t>A 49058-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -13076,10 +13101,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45310</v>
+        <v>45594</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13091,8 +13116,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>2.1</v>
+        <v>11.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -13135,7 +13165,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 4724-2026</t>
+          <t>A 24201-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -13149,10 +13179,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46048</v>
+        <v>46168</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13165,7 +13195,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -13208,7 +13238,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 4734-2026</t>
+          <t>A 25450-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -13222,10 +13252,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46048</v>
+        <v>45463</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13237,8 +13267,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -13281,7 +13316,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 14626-2023</t>
+          <t>A 24665-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -13295,10 +13330,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45012</v>
+        <v>45084</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13310,13 +13345,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -13359,7 +13389,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 24201-2026</t>
+          <t>A 72367-2021</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -13373,10 +13403,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46168</v>
+        <v>44545</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13389,7 +13419,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -13432,7 +13462,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 10249-2026</t>
+          <t>A 22628-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -13446,10 +13476,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46076</v>
+        <v>46155</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13463,11 +13493,11 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -13510,7 +13540,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 10244-2026</t>
+          <t>A 42714-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -13524,10 +13554,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46076</v>
+        <v>44832</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13539,13 +13569,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>8.699999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -13588,7 +13613,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 10562-2026</t>
+          <t>A 37954-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -13602,10 +13627,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46077</v>
+        <v>45881</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13617,13 +13642,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>2.3</v>
+        <v>9.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -13666,7 +13686,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 25450-2024</t>
+          <t>A 19099-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -13680,10 +13700,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45463</v>
+        <v>44691</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13697,11 +13717,11 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -13744,7 +13764,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 12841-2026</t>
+          <t>A 25780-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -13758,10 +13778,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46091</v>
+        <v>45090</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13773,13 +13793,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -13822,7 +13837,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 19782-2023</t>
+          <t>A 31061-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -13836,10 +13851,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45050</v>
+        <v>46215</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13853,11 +13868,11 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -13900,7 +13915,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 7848-2022</t>
+          <t>A 35682-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -13914,10 +13929,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44608</v>
+        <v>44799</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13929,8 +13944,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -13973,7 +13993,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 19246-2026</t>
+          <t>A 2867-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -13983,14 +14003,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46132</v>
+        <v>45315</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14004,11 +14024,11 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -14051,7 +14071,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 56378-2023</t>
+          <t>A 2660-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -14065,10 +14085,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45236</v>
+        <v>45310</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14080,13 +14100,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -14129,7 +14144,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 19099-2022</t>
+          <t>A 5567-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -14143,10 +14158,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44691</v>
+        <v>44595</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14158,13 +14173,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -14207,7 +14217,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 22628-2026</t>
+          <t>A 32223-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -14221,10 +14231,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46155</v>
+        <v>46237</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14238,11 +14248,11 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -14285,7 +14295,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 3818-2022</t>
+          <t>A 32501-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -14295,14 +14305,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44587</v>
+        <v>46239</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14315,7 +14325,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -14358,7 +14368,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 33933-2026</t>
+          <t>A 3085-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -14372,10 +14382,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46248</v>
+        <v>44946</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14389,11 +14399,11 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -14436,7 +14446,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 31061-2026</t>
+          <t>A 7848-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -14450,10 +14460,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46215</v>
+        <v>44608</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14465,13 +14475,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>4.4</v>
+        <v>2.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -14514,7 +14519,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 21509-2024</t>
+          <t>A 33933-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -14528,10 +14533,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45441</v>
+        <v>46248</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14549,7 +14554,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -14592,7 +14597,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 22662-2023</t>
+          <t>A 15743-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -14602,14 +14607,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45071</v>
+        <v>45021</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14621,13 +14626,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -14670,7 +14670,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 25780-2023</t>
+          <t>A 15637-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -14684,10 +14684,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45090</v>
+        <v>44662</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -14743,7 +14743,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 32501-2026</t>
+          <t>A 19786-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -14753,14 +14753,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46239</v>
+        <v>45050</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14772,8 +14772,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>1.5</v>
+        <v>8.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -14816,7 +14821,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 32223-2026</t>
+          <t>A 7787-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -14830,10 +14835,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46237</v>
+        <v>45348</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14845,13 +14850,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>8.199999999999999</v>
+        <v>1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -14911,7 +14911,7 @@
         <v>45021</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>44734</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>44734</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>46251</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>

--- a/Översikt SURAHAMMAR.xlsx
+++ b/Översikt SURAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45470</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>45684</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>45504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>45890</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>45582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45169</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45139</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45782</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>45282</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>46216</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>46216</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>46237</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>44613</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>46085</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>45435</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>46215</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>46111</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>45890</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>44832</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45523</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>45070</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>44565</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>46215</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>45574</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>45435</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>44518</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>44477</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>45203</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>46268</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>45072</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>45545</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>45945</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>44518</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>46076</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>46009</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>44832</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>44832</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>45369</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>45503</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>45463</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>44518</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>45890</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>44532</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>45212</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>46009</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>45684</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>45205</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>44832</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>46268</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>46239</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6805,7 +6805,7 @@
         <v>46248</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>44635</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>45708</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>45708</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>45236</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>45895</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>45007</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         <v>45737</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>45587</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         <v>44991</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>45174</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>46009</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>45110</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>45874</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>45007</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>46268</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>45720</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8717,7 +8717,7 @@
         <v>44696</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>44739</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>44524</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>44696</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>44817</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         <v>44977</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>45026</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>44796</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>45518</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>45110</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>45846</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>44991</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10040,7 +10040,7 @@
         <v>45456</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         <v>45156</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>45573</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>46224</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>44680</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10575,7 +10575,7 @@
         <v>44509</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>44696</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>44782</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         <v>44550</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>44586</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>44582</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>44694</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>44518</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>44796</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>45079</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>45441</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>44832</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>44832</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>46048</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>46048</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>44587</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>46076</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>46076</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>46077</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>45050</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>45012</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12178,7 +12178,7 @@
         <v>46091</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>45236</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>44993</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         <v>45060</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12490,7 +12490,7 @@
         <v>45973</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>46132</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>44832</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>45205</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>45516</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>46140</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12953,7 +12953,7 @@
         <v>44790</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13026,7 +13026,7 @@
         <v>45071</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>45594</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>46168</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>45463</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13333,7 +13333,7 @@
         <v>45084</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>44545</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
         <v>46155</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>44832</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>45881</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>44691</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13781,7 +13781,7 @@
         <v>45090</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13854,7 +13854,7 @@
         <v>46215</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13932,7 +13932,7 @@
         <v>44799</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         <v>45315</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>45310</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>44595</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         <v>46237</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14312,7 +14312,7 @@
         <v>46239</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14385,7 +14385,7 @@
         <v>44946</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14463,7 +14463,7 @@
         <v>44608</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14536,7 +14536,7 @@
         <v>46248</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>45021</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14687,7 +14687,7 @@
         <v>44662</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>45050</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         <v>45348</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>45021</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>44734</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>44734</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>46251</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>

--- a/Översikt SURAHAMMAR.xlsx
+++ b/Översikt SURAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45470</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>45684</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>45504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>45890</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>45582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45169</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45139</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45782</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>45282</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>46216</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>46216</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>46237</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>44613</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>46085</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>45435</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>46215</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>46111</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>45890</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>44832</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45523</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>45070</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>44565</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>46215</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>45574</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>45435</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>44518</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>44477</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>45203</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>46268</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>45072</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>45545</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>45945</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>44518</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>46076</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>46009</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>44832</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>44832</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>45369</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>45503</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>45463</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>44518</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>45890</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>44532</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>45212</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>46009</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>45684</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>45205</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>44832</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>46268</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>46239</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6805,7 +6805,7 @@
         <v>46248</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>44635</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>45708</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>45708</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>45236</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>45895</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>45007</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         <v>45737</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>45587</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         <v>44991</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>45174</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>46009</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>45110</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>45874</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>45007</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>46268</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>45720</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8717,7 +8717,7 @@
         <v>44696</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>44739</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>44524</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>44696</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>44817</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         <v>44977</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>45026</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>44796</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>45518</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>45110</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>45846</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>44991</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10040,7 +10040,7 @@
         <v>45456</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         <v>45156</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>45573</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>46224</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>44680</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10575,7 +10575,7 @@
         <v>44509</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>44696</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>44782</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         <v>44550</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>44586</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>44582</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>44694</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>44518</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>44796</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>45079</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>45441</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>44832</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>44832</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>46048</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>46048</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>44587</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>46076</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>46076</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>46077</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>45050</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>45012</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12178,7 +12178,7 @@
         <v>46091</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>45236</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>44993</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         <v>45060</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12490,7 +12490,7 @@
         <v>45973</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>46132</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>44832</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>45205</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>45516</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>46140</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12953,7 +12953,7 @@
         <v>44790</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13026,7 +13026,7 @@
         <v>45071</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>45594</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>46168</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>45463</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13333,7 +13333,7 @@
         <v>45084</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>44545</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
         <v>46155</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>44832</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>45881</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>44691</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13781,7 +13781,7 @@
         <v>45090</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13854,7 +13854,7 @@
         <v>46215</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13932,7 +13932,7 @@
         <v>44799</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         <v>45315</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>45310</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>44595</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         <v>46237</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14312,7 +14312,7 @@
         <v>46239</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14385,7 +14385,7 @@
         <v>44946</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14463,7 +14463,7 @@
         <v>44608</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14536,7 +14536,7 @@
         <v>46248</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>45021</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14687,7 +14687,7 @@
         <v>44662</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>45050</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         <v>45348</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>45021</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>44734</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>44734</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>46251</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>

--- a/Översikt SURAHAMMAR.xlsx
+++ b/Översikt SURAHAMMAR.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE146"/>
+  <dimension ref="A1:AE145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45470</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>45684</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 31280-2024</t>
+          <t>A 39697-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45504</v>
+        <v>45890</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,23 +964,23 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>6.9</v>
+        <v>25.7</v>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="K4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -992,21 +992,182 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="R4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
         <v>44</v>
       </c>
       <c r="T4" t="n">
+        <v>243</v>
+      </c>
+      <c r="U4" t="n">
+        <v>107</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Grönfink
+Knärot
+Bivråk
+Brunlångöra
+Dropptaggsvamp
+Fjällig taggsvamp s.str.
+Järnsparv
+Motaggsvamp
+Nordfladdermus
+Skarp dropptaggsvamp
+Skogshare
+Sotvaxskivling
+Sparvuggla
+Stornopping
+Talltita
+Älg
+Blodvaxing
+Gulgrön kantmusseron
+Honungsvaxing
+Luktvaxing
+Mindre märgborre
+Smal svampklubba
+Vedticka
+Gråspett
+Järpe
+Liljekonvalj
+Mattlummer
+Nattskärra
+Spillkråka
+Tjäder
+Tofsmes
+Dvärgpipistrell
+Gröngöling
+Kungsfågel
+Orre
+Slaguggla
+Större brunfladdermus
+Sångsvan
+Trana
+Trollpipistrell
+Vattenfladdermus
+Vanlig groda
+Fläcknycklar
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39697-2025 artfynd.xlsx", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39697-2025 karta.png", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39697-2025 georefererad karta.tif", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="Z4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 39697-2025 karta knärot.png", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39697-2025 FSC-klagomål.docx", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39697-2025 FSC-klagomål mail.docx", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39697-2025 tillsynsbegäran.docx", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39697-2025 tillsynsbegäran mail.docx", "A 39697-2025")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39697-2025 prioriterade fågelarter.docx", "A 39697-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 31280-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45504</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K5" t="n">
+        <v>12</v>
+      </c>
+      <c r="L5" t="n">
+        <v>22</v>
+      </c>
+      <c r="M5" t="n">
+        <v>5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>27</v>
+      </c>
+      <c r="R5" t="n">
+        <v>5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>44</v>
+      </c>
+      <c r="T5" t="n">
         <v>93</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>91</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Gränsticka
 Knärot
@@ -1054,201 +1215,40 @@
 Lopplummer (aggregat)</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31280-2024 artfynd.xlsx", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31280-2024 karta.png", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31280-2024 georefererad karta.tif", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="Z4">
+      <c r="Z5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 31280-2024 karta knärot.png", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31280-2024 FSC-klagomål.docx", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31280-2024 FSC-klagomål mail.docx", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31280-2024 tillsynsbegäran.docx", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31280-2024 tillsynsbegäran mail.docx", "A 31280-2024")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 31280-2024 prioriterade fågelarter.docx", "A 31280-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 39697-2025</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45890</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>28</v>
-      </c>
-      <c r="K5" t="n">
-        <v>7</v>
-      </c>
-      <c r="L5" t="n">
-        <v>14</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>16</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2</v>
-      </c>
-      <c r="S5" t="n">
-        <v>44</v>
-      </c>
-      <c r="T5" t="n">
-        <v>243</v>
-      </c>
-      <c r="U5" t="n">
-        <v>107</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Grönfink
-Knärot
-Bivråk
-Brunlångöra
-Dropptaggsvamp
-Fjällig taggsvamp s.str.
-Järnsparv
-Motaggsvamp
-Nordfladdermus
-Skarp dropptaggsvamp
-Skogshare
-Sotvaxskivling
-Sparvuggla
-Stornopping
-Talltita
-Älg
-Blodvaxing
-Gulgrön kantmusseron
-Honungsvaxing
-Luktvaxing
-Mindre märgborre
-Smal svampklubba
-Vedticka
-Gråspett
-Järpe
-Liljekonvalj
-Mattlummer
-Nattskärra
-Spillkråka
-Tjäder
-Tofsmes
-Dvärgpipistrell
-Gröngöling
-Kungsfågel
-Orre
-Slaguggla
-Större brunfladdermus
-Sångsvan
-Trana
-Trollpipistrell
-Vattenfladdermus
-Vanlig groda
-Fläcknycklar
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39697-2025 artfynd.xlsx", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39697-2025 karta.png", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39697-2025 georefererad karta.tif", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="Z5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 39697-2025 karta knärot.png", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39697-2025 FSC-klagomål.docx", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39697-2025 FSC-klagomål mail.docx", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39697-2025 tillsynsbegäran.docx", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39697-2025 tillsynsbegäran mail.docx", "A 39697-2025")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39697-2025 prioriterade fågelarter.docx", "A 39697-2025")</f>
         <v/>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
         <v>45582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45169</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45139</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45782</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>45282</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>46216</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>46216</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>46237</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>44613</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>46085</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>45435</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>46215</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>46111</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>45890</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>44832</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45523</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>45070</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>44565</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>46215</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>45574</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>45435</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>44518</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 56299-2021</t>
+          <t>A 38172-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4046,14 +4046,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44477</v>
+        <v>45545</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4067,49 +4067,173 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>8</v>
+        <v>5.2</v>
       </c>
       <c r="J28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>3</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
         <v>4</v>
       </c>
-      <c r="L28" t="n">
-        <v>2</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2</v>
-      </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>7</v>
       </c>
       <c r="T28" t="n">
+        <v>8</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Gropticka
+Sädesärla
+Vedtrappmossa
+Stjärtmes
+Lopplummer (aggregat)
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 38172-2024 artfynd.xlsx", "A 38172-2024")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 38172-2024 karta.png", "A 38172-2024")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 38172-2024 georefererad karta.tif", "A 38172-2024")</f>
+        <v/>
+      </c>
+      <c r="Z28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 38172-2024 karta knärot.png", "A 38172-2024")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 38172-2024 FSC-klagomål.docx", "A 38172-2024")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 38172-2024 FSC-klagomål mail.docx", "A 38172-2024")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 38172-2024 tillsynsbegäran.docx", "A 38172-2024")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 38172-2024 tillsynsbegäran mail.docx", "A 38172-2024")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 38172-2024 prioriterade fågelarter.docx", "A 38172-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A 56299-2021</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>44477</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>8</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4</v>
+      </c>
+      <c r="L29" t="n">
+        <v>2</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
         <v>7</v>
       </c>
-      <c r="U28" t="n">
-        <v>1</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="T29" t="n">
+        <v>7</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>Större flatbagge
 Tretåig hackspett
@@ -4120,116 +4244,116 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W28">
+      <c r="W29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 56299-2021 artfynd.xlsx", "A 56299-2021")</f>
         <v/>
       </c>
-      <c r="X28">
+      <c r="X29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 56299-2021 karta.png", "A 56299-2021")</f>
         <v/>
       </c>
-      <c r="Y28">
+      <c r="Y29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 56299-2021 georefererad karta.tif", "A 56299-2021")</f>
         <v/>
       </c>
-      <c r="AA28">
+      <c r="AA29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 56299-2021 FSC-klagomål.docx", "A 56299-2021")</f>
         <v/>
       </c>
-      <c r="AB28">
+      <c r="AB29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 56299-2021 FSC-klagomål mail.docx", "A 56299-2021")</f>
         <v/>
       </c>
-      <c r="AC28">
+      <c r="AC29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 56299-2021 tillsynsbegäran.docx", "A 56299-2021")</f>
         <v/>
       </c>
-      <c r="AD28">
+      <c r="AD29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 56299-2021 tillsynsbegäran mail.docx", "A 56299-2021")</f>
         <v/>
       </c>
-      <c r="AE28">
+      <c r="AE29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 56299-2021 prioriterade fågelarter.docx", "A 56299-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>A 48891-2023</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D29" s="1" t="n">
+      <c r="D30" s="1" t="n">
         <v>45203</v>
       </c>
-      <c r="E29" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F29" t="inlineStr">
+      <c r="E30" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>VÄSTMANLANDS LÄN</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I29" t="n">
+      <c r="I30" t="n">
         <v>2.9</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J30" t="n">
         <v>3</v>
       </c>
-      <c r="K29" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" t="n">
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
         <v>3</v>
       </c>
-      <c r="M29" t="n">
-        <v>1</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
         <v>4</v>
       </c>
-      <c r="R29" t="n">
-        <v>1</v>
-      </c>
-      <c r="S29" t="n">
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
+      <c r="S30" t="n">
         <v>7</v>
       </c>
-      <c r="T29" t="n">
+      <c r="T30" t="n">
         <v>10</v>
       </c>
-      <c r="U29" t="n">
+      <c r="U30" t="n">
         <v>5</v>
       </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Motaggsvamp
@@ -4240,120 +4364,231 @@
 Gröngöling</t>
         </is>
       </c>
-      <c r="W29">
+      <c r="W30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 48891-2023 artfynd.xlsx", "A 48891-2023")</f>
         <v/>
       </c>
-      <c r="X29">
+      <c r="X30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 48891-2023 karta.png", "A 48891-2023")</f>
         <v/>
       </c>
-      <c r="Y29">
+      <c r="Y30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 48891-2023 georefererad karta.tif", "A 48891-2023")</f>
         <v/>
       </c>
-      <c r="Z29">
+      <c r="Z30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 48891-2023 karta knärot.png", "A 48891-2023")</f>
         <v/>
       </c>
-      <c r="AA29">
+      <c r="AA30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 48891-2023 FSC-klagomål.docx", "A 48891-2023")</f>
         <v/>
       </c>
-      <c r="AB29">
+      <c r="AB30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 48891-2023 FSC-klagomål mail.docx", "A 48891-2023")</f>
         <v/>
       </c>
-      <c r="AC29">
+      <c r="AC30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 48891-2023 tillsynsbegäran.docx", "A 48891-2023")</f>
         <v/>
       </c>
-      <c r="AD29">
+      <c r="AD30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 48891-2023 tillsynsbegäran mail.docx", "A 48891-2023")</f>
         <v/>
       </c>
-      <c r="AE29">
+      <c r="AE30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 48891-2023 prioriterade fågelarter.docx", "A 48891-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A 22840-2023</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>45072</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>7</v>
+      </c>
+      <c r="T31" t="n">
+        <v>10</v>
+      </c>
+      <c r="U31" t="n">
+        <v>9</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Hultbräken
+Kärrviol
+Mattlummer
+Skogsstjärna
+Stjärnstarr
+Vitsippa
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 22840-2023 artfynd.xlsx", "A 22840-2023")</f>
+        <v/>
+      </c>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 22840-2023 karta.png", "A 22840-2023")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 22840-2023 georefererad karta.tif", "A 22840-2023")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 22840-2023 FSC-klagomål.docx", "A 22840-2023")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 22840-2023 FSC-klagomål mail.docx", "A 22840-2023")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 22840-2023 tillsynsbegäran.docx", "A 22840-2023")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 22840-2023 tillsynsbegäran mail.docx", "A 22840-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>A 36260-2026</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D30" s="1" t="n">
+      <c r="D32" s="1" t="n">
         <v>46268</v>
       </c>
-      <c r="E30" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F30" t="inlineStr">
+      <c r="E32" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>VÄSTMANLANDS LÄN</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I30" t="n">
+      <c r="I32" t="n">
         <v>5.7</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J32" t="n">
         <v>4</v>
       </c>
-      <c r="K30" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" t="n">
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
         <v>2</v>
       </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
         <v>3</v>
       </c>
-      <c r="R30" t="n">
+      <c r="R32" t="n">
         <v>2</v>
       </c>
-      <c r="S30" t="n">
+      <c r="S32" t="n">
         <v>7</v>
       </c>
-      <c r="T30" t="n">
+      <c r="T32" t="n">
         <v>8</v>
       </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>Mindre bastardsvärmare
 Silverblåvinge
@@ -4364,271 +4599,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W30">
+      <c r="W32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 36260-2026 artfynd.xlsx", "A 36260-2026")</f>
         <v/>
       </c>
-      <c r="X30">
+      <c r="X32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 36260-2026 karta.png", "A 36260-2026")</f>
         <v/>
       </c>
-      <c r="Y30">
+      <c r="Y32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 36260-2026 georefererad karta.tif", "A 36260-2026")</f>
         <v/>
       </c>
-      <c r="AA30">
+      <c r="AA32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 36260-2026 FSC-klagomål.docx", "A 36260-2026")</f>
         <v/>
       </c>
-      <c r="AB30">
+      <c r="AB32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 36260-2026 FSC-klagomål mail.docx", "A 36260-2026")</f>
         <v/>
       </c>
-      <c r="AC30">
+      <c r="AC32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 36260-2026 tillsynsbegäran.docx", "A 36260-2026")</f>
         <v/>
       </c>
-      <c r="AD30">
+      <c r="AD32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 36260-2026 tillsynsbegäran mail.docx", "A 36260-2026")</f>
         <v/>
       </c>
-      <c r="AE30">
+      <c r="AE32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 36260-2026 prioriterade fågelarter.docx", "A 36260-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A 22840-2023</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>45072</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>7</v>
-      </c>
-      <c r="T31" t="n">
-        <v>10</v>
-      </c>
-      <c r="U31" t="n">
-        <v>9</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Hultbräken
-Kärrviol
-Mattlummer
-Skogsstjärna
-Stjärnstarr
-Vitsippa
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 22840-2023 artfynd.xlsx", "A 22840-2023")</f>
-        <v/>
-      </c>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 22840-2023 karta.png", "A 22840-2023")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 22840-2023 georefererad karta.tif", "A 22840-2023")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 22840-2023 FSC-klagomål.docx", "A 22840-2023")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 22840-2023 FSC-klagomål mail.docx", "A 22840-2023")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 22840-2023 tillsynsbegäran.docx", "A 22840-2023")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 22840-2023 tillsynsbegäran mail.docx", "A 22840-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>A 38172-2024</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>45545</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J32" t="n">
-        <v>5</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>3</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>4</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1</v>
-      </c>
-      <c r="S32" t="n">
-        <v>7</v>
-      </c>
-      <c r="T32" t="n">
-        <v>8</v>
-      </c>
-      <c r="U32" t="n">
-        <v>2</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Gropticka
-Sädesärla
-Vedtrappmossa
-Stjärtmes
-Lopplummer (aggregat)
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 38172-2024 artfynd.xlsx", "A 38172-2024")</f>
-        <v/>
-      </c>
-      <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 38172-2024 karta.png", "A 38172-2024")</f>
-        <v/>
-      </c>
-      <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 38172-2024 georefererad karta.tif", "A 38172-2024")</f>
-        <v/>
-      </c>
-      <c r="Z32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 38172-2024 karta knärot.png", "A 38172-2024")</f>
-        <v/>
-      </c>
-      <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 38172-2024 FSC-klagomål.docx", "A 38172-2024")</f>
-        <v/>
-      </c>
-      <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 38172-2024 FSC-klagomål mail.docx", "A 38172-2024")</f>
-        <v/>
-      </c>
-      <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 38172-2024 tillsynsbegäran.docx", "A 38172-2024")</f>
-        <v/>
-      </c>
-      <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 38172-2024 tillsynsbegäran mail.docx", "A 38172-2024")</f>
-        <v/>
-      </c>
-      <c r="AE32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 38172-2024 prioriterade fågelarter.docx", "A 38172-2024")</f>
         <v/>
       </c>
     </row>
@@ -4652,7 +4652,7 @@
         <v>45945</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>44518</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10236-2026</t>
+          <t>A 63145-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46076</v>
+        <v>46009</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4900,23 +4900,23 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.8</v>
+        <v>40.5</v>
       </c>
       <c r="J35" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
         <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -4928,10 +4928,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
         <v>6</v>
@@ -4943,6 +4943,125 @@
         <v>0</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril
+Mindre hackspett
+Talltita
+Svart trolldruva
+Kungsfågel
+Nattviol</t>
+        </is>
+      </c>
+      <c r="W35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63145-2025 artfynd.xlsx", "A 63145-2025")</f>
+        <v/>
+      </c>
+      <c r="X35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63145-2025 karta.png", "A 63145-2025")</f>
+        <v/>
+      </c>
+      <c r="Y35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63145-2025 georefererad karta.tif", "A 63145-2025")</f>
+        <v/>
+      </c>
+      <c r="AA35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63145-2025 FSC-klagomål.docx", "A 63145-2025")</f>
+        <v/>
+      </c>
+      <c r="AB35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63145-2025 FSC-klagomål mail.docx", "A 63145-2025")</f>
+        <v/>
+      </c>
+      <c r="AC35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63145-2025 tillsynsbegäran.docx", "A 63145-2025")</f>
+        <v/>
+      </c>
+      <c r="AD35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63145-2025 tillsynsbegäran mail.docx", "A 63145-2025")</f>
+        <v/>
+      </c>
+      <c r="AE35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 63145-2025 prioriterade fågelarter.docx", "A 63145-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>A 10236-2026</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>46076</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2</v>
+      </c>
+      <c r="L36" t="n">
+        <v>2</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>6</v>
+      </c>
+      <c r="T36" t="n">
+        <v>13</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>Gullpudra
 Vågticka
@@ -4952,151 +5071,32 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W35">
+      <c r="W36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 10236-2026 artfynd.xlsx", "A 10236-2026")</f>
         <v/>
       </c>
-      <c r="X35">
+      <c r="X36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 10236-2026 karta.png", "A 10236-2026")</f>
         <v/>
       </c>
-      <c r="Y35">
+      <c r="Y36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 10236-2026 georefererad karta.tif", "A 10236-2026")</f>
         <v/>
       </c>
-      <c r="AA35">
+      <c r="AA36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 10236-2026 FSC-klagomål.docx", "A 10236-2026")</f>
         <v/>
       </c>
-      <c r="AB35">
+      <c r="AB36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 10236-2026 FSC-klagomål mail.docx", "A 10236-2026")</f>
         <v/>
       </c>
-      <c r="AC35">
+      <c r="AC36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 10236-2026 tillsynsbegäran.docx", "A 10236-2026")</f>
         <v/>
       </c>
-      <c r="AD35">
+      <c r="AD36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 10236-2026 tillsynsbegäran mail.docx", "A 10236-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>A 63145-2025</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="n">
-        <v>46009</v>
-      </c>
-      <c r="E36" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="J36" t="n">
-        <v>5</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" t="n">
-        <v>2</v>
-      </c>
-      <c r="M36" t="n">
-        <v>1</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>3</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1</v>
-      </c>
-      <c r="S36" t="n">
-        <v>6</v>
-      </c>
-      <c r="T36" t="n">
-        <v>13</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>Väddnätfjäril
-Mindre hackspett
-Talltita
-Svart trolldruva
-Kungsfågel
-Nattviol</t>
-        </is>
-      </c>
-      <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63145-2025 artfynd.xlsx", "A 63145-2025")</f>
-        <v/>
-      </c>
-      <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63145-2025 karta.png", "A 63145-2025")</f>
-        <v/>
-      </c>
-      <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63145-2025 georefererad karta.tif", "A 63145-2025")</f>
-        <v/>
-      </c>
-      <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63145-2025 FSC-klagomål.docx", "A 63145-2025")</f>
-        <v/>
-      </c>
-      <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63145-2025 FSC-klagomål mail.docx", "A 63145-2025")</f>
-        <v/>
-      </c>
-      <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63145-2025 tillsynsbegäran.docx", "A 63145-2025")</f>
-        <v/>
-      </c>
-      <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63145-2025 tillsynsbegäran mail.docx", "A 63145-2025")</f>
-        <v/>
-      </c>
-      <c r="AE36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 63145-2025 prioriterade fågelarter.docx", "A 63145-2025")</f>
         <v/>
       </c>
     </row>
@@ -5120,7 +5120,7 @@
         <v>44832</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>44832</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>45369</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>45503</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>45463</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>44518</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 39694-2025</t>
+          <t>A 63146-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5801,10 +5801,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45890</v>
+        <v>46009</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5822,16 +5822,16 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.9</v>
+        <v>10.2</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -5846,7 +5846,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -5855,709 +5855,709 @@
         <v>3</v>
       </c>
       <c r="T43" t="n">
+        <v>12</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>Stor aspticka
+Svart trolldruva
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63146-2025 artfynd.xlsx", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="X43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63146-2025 karta.png", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="Y43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63146-2025 georefererad karta.tif", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="AA43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63146-2025 FSC-klagomål.docx", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="AB43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63146-2025 FSC-klagomål mail.docx", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="AC43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63146-2025 tillsynsbegäran.docx", "A 63146-2025")</f>
+        <v/>
+      </c>
+      <c r="AD43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63146-2025 tillsynsbegäran mail.docx", "A 63146-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>A 39694-2025</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="n">
+        <v>45890</v>
+      </c>
+      <c r="E44" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
         <v>3</v>
       </c>
-      <c r="U43" t="n">
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
         <v>2</v>
       </c>
-      <c r="V43" s="2" t="inlineStr">
+      <c r="V44" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Mindre märgborre
 Tjäder</t>
         </is>
       </c>
-      <c r="W43">
+      <c r="W44">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39694-2025 artfynd.xlsx", "A 39694-2025")</f>
         <v/>
       </c>
-      <c r="X43">
+      <c r="X44">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39694-2025 karta.png", "A 39694-2025")</f>
         <v/>
       </c>
-      <c r="Y43">
+      <c r="Y44">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39694-2025 georefererad karta.tif", "A 39694-2025")</f>
         <v/>
       </c>
-      <c r="AA43">
+      <c r="AA44">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39694-2025 FSC-klagomål.docx", "A 39694-2025")</f>
         <v/>
       </c>
-      <c r="AB43">
+      <c r="AB44">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39694-2025 FSC-klagomål mail.docx", "A 39694-2025")</f>
         <v/>
       </c>
-      <c r="AC43">
+      <c r="AC44">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39694-2025 tillsynsbegäran.docx", "A 39694-2025")</f>
         <v/>
       </c>
-      <c r="AD43">
+      <c r="AD44">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39694-2025 tillsynsbegäran mail.docx", "A 39694-2025")</f>
         <v/>
       </c>
-      <c r="AE43">
+      <c r="AE44">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39694-2025 prioriterade fågelarter.docx", "A 39694-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>A 49718-2023</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>45212</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>2</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3</v>
+      </c>
+      <c r="T45" t="n">
+        <v>6</v>
+      </c>
+      <c r="U45" t="n">
+        <v>6</v>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Talltita
+Zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="W45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 49718-2023 artfynd.xlsx", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="X45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 49718-2023 karta.png", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="Y45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 49718-2023 georefererad karta.tif", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="AA45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 49718-2023 FSC-klagomål.docx", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="AB45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 49718-2023 FSC-klagomål mail.docx", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="AC45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 49718-2023 tillsynsbegäran.docx", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="AD45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 49718-2023 tillsynsbegäran mail.docx", "A 49718-2023")</f>
+        <v/>
+      </c>
+      <c r="AE45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 49718-2023 prioriterade fågelarter.docx", "A 49718-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>A 42765-2022</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v>44832</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>Krusfrö
+Barkticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 42765-2022 artfynd.xlsx", "A 42765-2022")</f>
+        <v/>
+      </c>
+      <c r="X46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 42765-2022 karta.png", "A 42765-2022")</f>
+        <v/>
+      </c>
+      <c r="Y46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 42765-2022 georefererad karta.tif", "A 42765-2022")</f>
+        <v/>
+      </c>
+      <c r="AA46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 42765-2022 FSC-klagomål.docx", "A 42765-2022")</f>
+        <v/>
+      </c>
+      <c r="AB46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 42765-2022 FSC-klagomål mail.docx", "A 42765-2022")</f>
+        <v/>
+      </c>
+      <c r="AC46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 42765-2022 tillsynsbegäran.docx", "A 42765-2022")</f>
+        <v/>
+      </c>
+      <c r="AD46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 42765-2022 tillsynsbegäran mail.docx", "A 42765-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>A 69777-2021</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D44" s="1" t="n">
+      <c r="D47" s="1" t="n">
         <v>44532</v>
       </c>
-      <c r="E44" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F44" t="inlineStr">
+      <c r="E47" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>VÄSTMANLANDS LÄN</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="I44" t="n">
+      <c r="I47" t="n">
         <v>2.3</v>
       </c>
-      <c r="J44" t="n">
-        <v>1</v>
-      </c>
-      <c r="K44" t="n">
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
         <v>2</v>
       </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>1</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>1</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1</v>
-      </c>
-      <c r="S44" t="n">
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1</v>
+      </c>
+      <c r="S47" t="n">
         <v>3</v>
       </c>
-      <c r="T44" t="n">
+      <c r="T47" t="n">
         <v>5</v>
       </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
         <is>
           <t>Bombmurkla
 Rävticka
 Vedticka</t>
         </is>
       </c>
-      <c r="W44">
+      <c r="W47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 69777-2021 artfynd.xlsx", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="X44">
+      <c r="X47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 69777-2021 karta.png", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="Y44">
+      <c r="Y47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 69777-2021 georefererad karta.tif", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="AA44">
+      <c r="AA47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 69777-2021 FSC-klagomål.docx", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="AB44">
+      <c r="AB47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 69777-2021 FSC-klagomål mail.docx", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="AC44">
+      <c r="AC47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 69777-2021 tillsynsbegäran.docx", "A 69777-2021")</f>
         <v/>
       </c>
-      <c r="AD44">
+      <c r="AD47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 69777-2021 tillsynsbegäran mail.docx", "A 69777-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>A 49718-2023</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>A 4082-2025</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D45" s="1" t="n">
-        <v>45212</v>
-      </c>
-      <c r="E45" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F45" t="inlineStr">
+      <c r="D48" s="1" t="n">
+        <v>45684</v>
+      </c>
+      <c r="E48" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>VÄSTMANLANDS LÄN</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="I45" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J45" t="n">
-        <v>1</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1</v>
-      </c>
-      <c r="L45" t="n">
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J48" t="n">
         <v>2</v>
       </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
+      <c r="K48" t="n">
         <v>2</v>
       </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
         <v>3</v>
       </c>
-      <c r="T45" t="n">
-        <v>6</v>
-      </c>
-      <c r="U45" t="n">
-        <v>6</v>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Talltita
-Zontaggsvamp</t>
-        </is>
-      </c>
-      <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 49718-2023 artfynd.xlsx", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 49718-2023 karta.png", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 49718-2023 georefererad karta.tif", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 49718-2023 FSC-klagomål.docx", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 49718-2023 FSC-klagomål mail.docx", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 49718-2023 tillsynsbegäran.docx", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 49718-2023 tillsynsbegäran mail.docx", "A 49718-2023")</f>
-        <v/>
-      </c>
-      <c r="AE45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 49718-2023 prioriterade fågelarter.docx", "A 49718-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>A 63146-2025</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="n">
-        <v>46009</v>
-      </c>
-      <c r="E46" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="J46" t="n">
-        <v>1</v>
-      </c>
-      <c r="K46" t="n">
-        <v>2</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
+      <c r="T48" t="n">
         <v>3</v>
       </c>
-      <c r="T46" t="n">
-        <v>12</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>Stor aspticka
-Svart trolldruva
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63146-2025 artfynd.xlsx", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63146-2025 karta.png", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63146-2025 georefererad karta.tif", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63146-2025 FSC-klagomål.docx", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63146-2025 FSC-klagomål mail.docx", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63146-2025 tillsynsbegäran.docx", "A 63146-2025")</f>
-        <v/>
-      </c>
-      <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63146-2025 tillsynsbegäran mail.docx", "A 63146-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>A 4082-2025</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="n">
-        <v>45684</v>
-      </c>
-      <c r="E47" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="J47" t="n">
-        <v>2</v>
-      </c>
-      <c r="K47" t="n">
-        <v>2</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>3</v>
-      </c>
-      <c r="T47" t="n">
-        <v>3</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1</v>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
+      <c r="U48" t="n">
+        <v>1</v>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
         <is>
           <t>Grönpyrola
 Plattlummer
 Lopplummer (aggregat)</t>
         </is>
       </c>
-      <c r="W47">
+      <c r="W48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 4082-2025 artfynd.xlsx", "A 4082-2025")</f>
         <v/>
       </c>
-      <c r="X47">
+      <c r="X48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 4082-2025 karta.png", "A 4082-2025")</f>
         <v/>
       </c>
-      <c r="Y47">
+      <c r="Y48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 4082-2025 georefererad karta.tif", "A 4082-2025")</f>
         <v/>
       </c>
-      <c r="AA47">
+      <c r="AA48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 4082-2025 FSC-klagomål.docx", "A 4082-2025")</f>
         <v/>
       </c>
-      <c r="AB47">
+      <c r="AB48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 4082-2025 FSC-klagomål mail.docx", "A 4082-2025")</f>
         <v/>
       </c>
-      <c r="AC47">
+      <c r="AC48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 4082-2025 tillsynsbegäran.docx", "A 4082-2025")</f>
         <v/>
       </c>
-      <c r="AD47">
+      <c r="AD48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 4082-2025 tillsynsbegäran mail.docx", "A 4082-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>A 48128-2023</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D48" s="1" t="n">
+      <c r="D49" s="1" t="n">
         <v>45205</v>
       </c>
-      <c r="E48" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F48" t="inlineStr">
+      <c r="E49" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>VÄSTMANLANDS LÄN</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
-      <c r="I48" t="n">
+      <c r="I49" t="n">
         <v>11.8</v>
       </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>1</v>
-      </c>
-      <c r="L48" t="n">
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" t="n">
         <v>2</v>
       </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
         <v>2</v>
       </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
         <v>3</v>
       </c>
-      <c r="T48" t="n">
+      <c r="T49" t="n">
         <v>3</v>
       </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
         <is>
           <t>Jungfrulin
 Svinrot
 Vedticka</t>
         </is>
       </c>
-      <c r="W48">
+      <c r="W49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 48128-2023 artfynd.xlsx", "A 48128-2023")</f>
         <v/>
       </c>
-      <c r="X48">
+      <c r="X49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 48128-2023 karta.png", "A 48128-2023")</f>
         <v/>
       </c>
-      <c r="Y48">
+      <c r="Y49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 48128-2023 georefererad karta.tif", "A 48128-2023")</f>
         <v/>
       </c>
-      <c r="AA48">
+      <c r="AA49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 48128-2023 FSC-klagomål.docx", "A 48128-2023")</f>
         <v/>
       </c>
-      <c r="AB48">
+      <c r="AB49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 48128-2023 FSC-klagomål mail.docx", "A 48128-2023")</f>
         <v/>
       </c>
-      <c r="AC48">
+      <c r="AC49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 48128-2023 tillsynsbegäran.docx", "A 48128-2023")</f>
         <v/>
       </c>
-      <c r="AD48">
+      <c r="AD49">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 48128-2023 tillsynsbegäran mail.docx", "A 48128-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="15" customHeight="1">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>A 42765-2022</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D49" s="1" t="n">
-        <v>44832</v>
-      </c>
-      <c r="E49" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J49" t="n">
-        <v>1</v>
-      </c>
-      <c r="K49" t="n">
-        <v>1</v>
-      </c>
-      <c r="L49" t="n">
-        <v>1</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>1</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>3</v>
-      </c>
-      <c r="T49" t="n">
-        <v>4</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1</v>
-      </c>
-      <c r="V49" s="2" t="inlineStr">
-        <is>
-          <t>Krusfrö
-Barkticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 42765-2022 artfynd.xlsx", "A 42765-2022")</f>
-        <v/>
-      </c>
-      <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 42765-2022 karta.png", "A 42765-2022")</f>
-        <v/>
-      </c>
-      <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 42765-2022 georefererad karta.tif", "A 42765-2022")</f>
-        <v/>
-      </c>
-      <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 42765-2022 FSC-klagomål.docx", "A 42765-2022")</f>
-        <v/>
-      </c>
-      <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 42765-2022 FSC-klagomål mail.docx", "A 42765-2022")</f>
-        <v/>
-      </c>
-      <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 42765-2022 tillsynsbegäran.docx", "A 42765-2022")</f>
-        <v/>
-      </c>
-      <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 42765-2022 tillsynsbegäran mail.docx", "A 42765-2022")</f>
         <v/>
       </c>
     </row>
@@ -6581,7 +6581,7 @@
         <v>46268</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>46239</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6805,7 +6805,7 @@
         <v>46248</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>44635</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>45708</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>45708</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 56362-2023</t>
+          <t>A 30074-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7270,10 +7270,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45236</v>
+        <v>45110</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7287,11 +7287,11 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>15.2</v>
+        <v>1.1</v>
       </c>
       <c r="J56" t="n">
         <v>1</v>
@@ -7303,7 +7303,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
@@ -7315,10 +7315,10 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>2</v>
@@ -7327,47 +7327,47 @@
         <v>2</v>
       </c>
       <c r="U56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>Väddnätfjäril
-Grönpyrola</t>
+          <t>Grönpyrola
+Revlummer</t>
         </is>
       </c>
       <c r="W56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 56362-2023 artfynd.xlsx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 30074-2023 artfynd.xlsx", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="X56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 56362-2023 karta.png", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 30074-2023 karta.png", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="Y56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 56362-2023 georefererad karta.tif", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 30074-2023 georefererad karta.tif", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="AA56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 56362-2023 FSC-klagomål.docx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 30074-2023 FSC-klagomål.docx", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="AB56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 56362-2023 FSC-klagomål mail.docx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 30074-2023 FSC-klagomål mail.docx", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="AC56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 56362-2023 tillsynsbegäran.docx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 30074-2023 tillsynsbegäran.docx", "A 30074-2023")</f>
         <v/>
       </c>
       <c r="AD56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 56362-2023 tillsynsbegäran mail.docx", "A 56362-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 30074-2023 tillsynsbegäran mail.docx", "A 30074-2023")</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 40403-2025</t>
+          <t>A 63138-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45895</v>
+        <v>46009</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7398,23 +7398,23 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="J57" t="n">
         <v>1</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
         <v>0</v>
@@ -7426,10 +7426,10 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>2</v>
@@ -7438,47 +7438,51 @@
         <v>3</v>
       </c>
       <c r="U57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>Igelkott
-Gröngöling</t>
+          <t>Mindre märgborre
+Tjäder</t>
         </is>
       </c>
       <c r="W57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 40403-2025 artfynd.xlsx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63138-2025 artfynd.xlsx", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="X57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 40403-2025 karta.png", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63138-2025 karta.png", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="Y57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 40403-2025 georefererad karta.tif", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63138-2025 georefererad karta.tif", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="AA57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 40403-2025 FSC-klagomål.docx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63138-2025 FSC-klagomål.docx", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="AB57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 40403-2025 FSC-klagomål mail.docx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63138-2025 FSC-klagomål mail.docx", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="AC57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 40403-2025 tillsynsbegäran.docx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63138-2025 tillsynsbegäran.docx", "A 63138-2025")</f>
         <v/>
       </c>
       <c r="AD57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 40403-2025 tillsynsbegäran mail.docx", "A 40403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63138-2025 tillsynsbegäran mail.docx", "A 63138-2025")</f>
+        <v/>
+      </c>
+      <c r="AE57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 63138-2025 prioriterade fågelarter.docx", "A 63138-2025")</f>
         <v/>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 14001-2023</t>
+          <t>A 40403-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7492,10 +7496,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45007</v>
+        <v>45895</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7509,20 +7513,20 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
         <v>1</v>
@@ -7537,7 +7541,7 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R58" t="n">
         <v>1</v>
@@ -7546,43 +7550,43 @@
         <v>2</v>
       </c>
       <c r="T58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>Garnlav
-Motaggsvamp</t>
+          <t>Igelkott
+Gröngöling</t>
         </is>
       </c>
       <c r="W58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 14001-2023 artfynd.xlsx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 40403-2025 artfynd.xlsx", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="X58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 14001-2023 karta.png", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 40403-2025 karta.png", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="Y58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 14001-2023 georefererad karta.tif", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 40403-2025 georefererad karta.tif", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="AA58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 14001-2023 FSC-klagomål.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 40403-2025 FSC-klagomål.docx", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="AB58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 14001-2023 FSC-klagomål mail.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 40403-2025 FSC-klagomål mail.docx", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="AC58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 14001-2023 tillsynsbegäran.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 40403-2025 tillsynsbegäran.docx", "A 40403-2025")</f>
         <v/>
       </c>
       <c r="AD58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 14001-2023 tillsynsbegäran mail.docx", "A 14001-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 40403-2025 tillsynsbegäran mail.docx", "A 40403-2025")</f>
         <v/>
       </c>
     </row>
@@ -7606,7 +7610,7 @@
         <v>45737</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7699,7 +7703,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 47453-2024</t>
+          <t>A 56362-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7713,10 +7717,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45587</v>
+        <v>45236</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7728,20 +7732,25 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>5.1</v>
+        <v>15.2</v>
       </c>
       <c r="J60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N60" t="n">
         <v>0</v>
@@ -7756,7 +7765,7 @@
         <v>1</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S60" t="n">
         <v>2</v>
@@ -7769,47 +7778,43 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>Göktyta
-Gröngöling</t>
+          <t>Väddnätfjäril
+Grönpyrola</t>
         </is>
       </c>
       <c r="W60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 47453-2024 artfynd.xlsx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 56362-2023 artfynd.xlsx", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="X60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 47453-2024 karta.png", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 56362-2023 karta.png", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="Y60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 47453-2024 georefererad karta.tif", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 56362-2023 georefererad karta.tif", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="AA60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 47453-2024 FSC-klagomål.docx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 56362-2023 FSC-klagomål.docx", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="AB60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 47453-2024 FSC-klagomål mail.docx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 56362-2023 FSC-klagomål mail.docx", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="AC60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 47453-2024 tillsynsbegäran.docx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 56362-2023 tillsynsbegäran.docx", "A 56362-2023")</f>
         <v/>
       </c>
       <c r="AD60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 47453-2024 tillsynsbegäran mail.docx", "A 47453-2024")</f>
-        <v/>
-      </c>
-      <c r="AE60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 47453-2024 prioriterade fågelarter.docx", "A 47453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 56362-2023 tillsynsbegäran mail.docx", "A 56362-2023")</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 11501-2023</t>
+          <t>A 47453-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7823,10 +7828,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44991</v>
+        <v>45587</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7838,22 +7843,17 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -7868,7 +7868,7 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -7880,47 +7880,51 @@
         <v>2</v>
       </c>
       <c r="U61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva
-Nattviol</t>
+          <t>Göktyta
+Gröngöling</t>
         </is>
       </c>
       <c r="W61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 11501-2023 artfynd.xlsx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 47453-2024 artfynd.xlsx", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="X61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 11501-2023 karta.png", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 47453-2024 karta.png", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="Y61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 11501-2023 georefererad karta.tif", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 47453-2024 georefererad karta.tif", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="AA61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 11501-2023 FSC-klagomål.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 47453-2024 FSC-klagomål.docx", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="AB61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 11501-2023 FSC-klagomål mail.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 47453-2024 FSC-klagomål mail.docx", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="AC61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 11501-2023 tillsynsbegäran.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 47453-2024 tillsynsbegäran.docx", "A 47453-2024")</f>
         <v/>
       </c>
       <c r="AD61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 11501-2023 tillsynsbegäran mail.docx", "A 11501-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 47453-2024 tillsynsbegäran mail.docx", "A 47453-2024")</f>
+        <v/>
+      </c>
+      <c r="AE61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 47453-2024 prioriterade fågelarter.docx", "A 47453-2024")</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 41204-2023</t>
+          <t>A 37013-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7934,10 +7938,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45174</v>
+        <v>45874</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7949,20 +7953,25 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>10.7</v>
       </c>
       <c r="J62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N62" t="n">
         <v>0</v>
@@ -7977,60 +7986,56 @@
         <v>2</v>
       </c>
       <c r="R62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S62" t="n">
         <v>2</v>
       </c>
       <c r="T62" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>Knärot
-Vedtrappmossa</t>
+          <t>Brunfläckig pärlemorfjäril
+Fältgentiana</t>
         </is>
       </c>
       <c r="W62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 41204-2023 artfynd.xlsx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37013-2025 artfynd.xlsx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="X62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 41204-2023 karta.png", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37013-2025 karta.png", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="Y62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 41204-2023 georefererad karta.tif", "A 41204-2023")</f>
-        <v/>
-      </c>
-      <c r="Z62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 41204-2023 karta knärot.png", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37013-2025 georefererad karta.tif", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AA62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 41204-2023 FSC-klagomål.docx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37013-2025 FSC-klagomål.docx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AB62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 41204-2023 FSC-klagomål mail.docx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37013-2025 FSC-klagomål mail.docx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AC62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 41204-2023 tillsynsbegäran.docx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37013-2025 tillsynsbegäran.docx", "A 37013-2025")</f>
         <v/>
       </c>
       <c r="AD62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 41204-2023 tillsynsbegäran mail.docx", "A 41204-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37013-2025 tillsynsbegäran mail.docx", "A 37013-2025")</f>
         <v/>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 63138-2025</t>
+          <t>A 41204-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -8044,10 +8049,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46009</v>
+        <v>45174</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8059,25 +8064,20 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>1</v>
       </c>
       <c r="K63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
@@ -8089,63 +8089,63 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S63" t="n">
         <v>2</v>
       </c>
       <c r="T63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>Mindre märgborre
-Tjäder</t>
+          <t>Knärot
+Vedtrappmossa</t>
         </is>
       </c>
       <c r="W63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 63138-2025 artfynd.xlsx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 41204-2023 artfynd.xlsx", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="X63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 63138-2025 karta.png", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 41204-2023 karta.png", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="Y63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 63138-2025 georefererad karta.tif", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 41204-2023 georefererad karta.tif", "A 41204-2023")</f>
+        <v/>
+      </c>
+      <c r="Z63">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 41204-2023 karta knärot.png", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="AA63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 63138-2025 FSC-klagomål.docx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 41204-2023 FSC-klagomål.docx", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="AB63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 63138-2025 FSC-klagomål mail.docx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 41204-2023 FSC-klagomål mail.docx", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="AC63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 63138-2025 tillsynsbegäran.docx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 41204-2023 tillsynsbegäran.docx", "A 41204-2023")</f>
         <v/>
       </c>
       <c r="AD63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 63138-2025 tillsynsbegäran mail.docx", "A 63138-2025")</f>
-        <v/>
-      </c>
-      <c r="AE63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 63138-2025 prioriterade fågelarter.docx", "A 63138-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 41204-2023 tillsynsbegäran mail.docx", "A 41204-2023")</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 30074-2023</t>
+          <t>A 11501-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -8159,10 +8159,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45110</v>
+        <v>44991</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I64" t="n">
@@ -8216,47 +8216,47 @@
         <v>2</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola
-Revlummer</t>
+          <t>Svart trolldruva
+Nattviol</t>
         </is>
       </c>
       <c r="W64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 30074-2023 artfynd.xlsx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 11501-2023 artfynd.xlsx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="X64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 30074-2023 karta.png", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 11501-2023 karta.png", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="Y64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 30074-2023 georefererad karta.tif", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 11501-2023 georefererad karta.tif", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AA64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 30074-2023 FSC-klagomål.docx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 11501-2023 FSC-klagomål.docx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AB64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 30074-2023 FSC-klagomål mail.docx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 11501-2023 FSC-klagomål mail.docx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AC64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 30074-2023 tillsynsbegäran.docx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 11501-2023 tillsynsbegäran.docx", "A 11501-2023")</f>
         <v/>
       </c>
       <c r="AD64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 30074-2023 tillsynsbegäran mail.docx", "A 30074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 11501-2023 tillsynsbegäran mail.docx", "A 11501-2023")</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 37013-2025</t>
+          <t>A 14001-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -8270,10 +8270,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45874</v>
+        <v>45007</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>10.7</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -8300,10 +8300,10 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
@@ -8318,7 +8318,7 @@
         <v>2</v>
       </c>
       <c r="R65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S65" t="n">
         <v>2</v>
@@ -8331,36 +8331,36 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril
-Fältgentiana</t>
+          <t>Garnlav
+Motaggsvamp</t>
         </is>
       </c>
       <c r="W65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37013-2025 artfynd.xlsx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 14001-2023 artfynd.xlsx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="X65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37013-2025 karta.png", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 14001-2023 karta.png", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="Y65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37013-2025 georefererad karta.tif", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 14001-2023 georefererad karta.tif", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AA65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37013-2025 FSC-klagomål.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 14001-2023 FSC-klagomål.docx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AB65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37013-2025 FSC-klagomål mail.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 14001-2023 FSC-klagomål mail.docx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AC65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37013-2025 tillsynsbegäran.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 14001-2023 tillsynsbegäran.docx", "A 14001-2023")</f>
         <v/>
       </c>
       <c r="AD65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37013-2025 tillsynsbegäran mail.docx", "A 37013-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 14001-2023 tillsynsbegäran mail.docx", "A 14001-2023")</f>
         <v/>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
         <v>45007</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>46268</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>45720</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8717,7 +8717,7 @@
         <v>44696</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>44739</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>44524</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>44696</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 39099-2022</t>
+          <t>A 8553-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -9150,14 +9150,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44817</v>
+        <v>44977</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9171,23 +9171,23 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>7.4</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N73" t="n">
         <v>0</v>
@@ -9199,10 +9199,10 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S73" t="n">
         <v>1</v>
@@ -9211,46 +9211,46 @@
         <v>1</v>
       </c>
       <c r="U73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="W73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39099-2022 artfynd.xlsx", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 8553-2023 artfynd.xlsx", "A 8553-2023")</f>
         <v/>
       </c>
       <c r="X73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39099-2022 karta.png", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 8553-2023 karta.png", "A 8553-2023")</f>
         <v/>
       </c>
       <c r="Y73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39099-2022 georefererad karta.tif", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 8553-2023 georefererad karta.tif", "A 8553-2023")</f>
         <v/>
       </c>
       <c r="AA73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39099-2022 FSC-klagomål.docx", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 8553-2023 FSC-klagomål.docx", "A 8553-2023")</f>
         <v/>
       </c>
       <c r="AB73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39099-2022 FSC-klagomål mail.docx", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 8553-2023 FSC-klagomål mail.docx", "A 8553-2023")</f>
         <v/>
       </c>
       <c r="AC73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39099-2022 tillsynsbegäran.docx", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 8553-2023 tillsynsbegäran.docx", "A 8553-2023")</f>
         <v/>
       </c>
       <c r="AD73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39099-2022 tillsynsbegäran mail.docx", "A 39099-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 8553-2023 tillsynsbegäran mail.docx", "A 8553-2023")</f>
         <v/>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 8553-2023</t>
+          <t>A 30076-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -9260,14 +9260,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44977</v>
+        <v>45110</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J74" t="n">
         <v>1</v>
@@ -9297,7 +9297,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
         <v>0</v>
@@ -9309,10 +9309,10 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>1</v>
@@ -9325,42 +9325,42 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>Väddnätfjäril</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 8553-2023 artfynd.xlsx", "A 8553-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 30076-2023 artfynd.xlsx", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="X74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 8553-2023 karta.png", "A 8553-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 30076-2023 karta.png", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="Y74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 8553-2023 georefererad karta.tif", "A 8553-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 30076-2023 georefererad karta.tif", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="AA74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 8553-2023 FSC-klagomål.docx", "A 8553-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 30076-2023 FSC-klagomål.docx", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="AB74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 8553-2023 FSC-klagomål mail.docx", "A 8553-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 30076-2023 FSC-klagomål mail.docx", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="AC74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 8553-2023 tillsynsbegäran.docx", "A 8553-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 30076-2023 tillsynsbegäran.docx", "A 30076-2023")</f>
         <v/>
       </c>
       <c r="AD74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 8553-2023 tillsynsbegäran mail.docx", "A 8553-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 30076-2023 tillsynsbegäran mail.docx", "A 30076-2023")</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 16013-2023</t>
+          <t>A 37287-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -9374,10 +9374,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45026</v>
+        <v>45156</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -9399,10 +9399,10 @@
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
         <v>0</v>
@@ -9417,7 +9417,7 @@
         <v>1</v>
       </c>
       <c r="R75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>1</v>
@@ -9430,42 +9430,42 @@
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="W75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 16013-2023 artfynd.xlsx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37287-2023 artfynd.xlsx", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="X75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 16013-2023 karta.png", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37287-2023 karta.png", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="Y75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 16013-2023 georefererad karta.tif", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37287-2023 georefererad karta.tif", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="AA75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 16013-2023 FSC-klagomål.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37287-2023 FSC-klagomål.docx", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="AB75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 16013-2023 FSC-klagomål mail.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37287-2023 FSC-klagomål mail.docx", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="AC75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 16013-2023 tillsynsbegäran.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37287-2023 tillsynsbegäran.docx", "A 37287-2023")</f>
         <v/>
       </c>
       <c r="AD75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 16013-2023 tillsynsbegäran mail.docx", "A 16013-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37287-2023 tillsynsbegäran mail.docx", "A 37287-2023")</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 34955-2022</t>
+          <t>A 34584-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -9479,10 +9479,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44796</v>
+        <v>45846</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9496,20 +9496,20 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -9524,7 +9524,7 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
         <v>0</v>
@@ -9540,42 +9540,46 @@
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34955-2022 artfynd.xlsx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34584-2025 artfynd.xlsx", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="X76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34955-2022 karta.png", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34584-2025 karta.png", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="Y76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34955-2022 georefererad karta.tif", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34584-2025 georefererad karta.tif", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="AA76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34955-2022 FSC-klagomål.docx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34584-2025 FSC-klagomål.docx", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="AB76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34955-2022 FSC-klagomål mail.docx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34584-2025 FSC-klagomål mail.docx", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="AC76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34955-2022 tillsynsbegäran.docx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34584-2025 tillsynsbegäran.docx", "A 34584-2025")</f>
         <v/>
       </c>
       <c r="AD76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34955-2022 tillsynsbegäran mail.docx", "A 34955-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34584-2025 tillsynsbegäran mail.docx", "A 34584-2025")</f>
+        <v/>
+      </c>
+      <c r="AE76">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 34584-2025 prioriterade fågelarter.docx", "A 34584-2025")</f>
         <v/>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 33231-2024</t>
+          <t>A 39099-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -9589,10 +9593,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45518</v>
+        <v>44817</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9610,13 +9614,13 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.5</v>
+        <v>7.4</v>
       </c>
       <c r="J77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -9650,42 +9654,42 @@
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="W77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 33231-2024 artfynd.xlsx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39099-2022 artfynd.xlsx", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="X77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 33231-2024 karta.png", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39099-2022 karta.png", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="Y77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 33231-2024 georefererad karta.tif", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39099-2022 georefererad karta.tif", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="AA77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 33231-2024 FSC-klagomål.docx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39099-2022 FSC-klagomål.docx", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="AB77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 33231-2024 FSC-klagomål mail.docx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39099-2022 FSC-klagomål mail.docx", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="AC77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 33231-2024 tillsynsbegäran.docx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39099-2022 tillsynsbegäran.docx", "A 39099-2022")</f>
         <v/>
       </c>
       <c r="AD77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 33231-2024 tillsynsbegäran mail.docx", "A 33231-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39099-2022 tillsynsbegäran mail.docx", "A 39099-2022")</f>
         <v/>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 30076-2023</t>
+          <t>A 17632-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -9699,10 +9703,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45110</v>
+        <v>44680</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9714,19 +9718,14 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>1.1</v>
+        <v>5.2</v>
       </c>
       <c r="J78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -9760,42 +9759,42 @@
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="W78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 30076-2023 artfynd.xlsx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 17632-2022 artfynd.xlsx", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="X78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 30076-2023 karta.png", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 17632-2022 karta.png", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="Y78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 30076-2023 georefererad karta.tif", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 17632-2022 georefererad karta.tif", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="AA78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 30076-2023 FSC-klagomål.docx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 17632-2022 FSC-klagomål.docx", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="AB78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 30076-2023 FSC-klagomål mail.docx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 17632-2022 FSC-klagomål mail.docx", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="AC78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 30076-2023 tillsynsbegäran.docx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 17632-2022 tillsynsbegäran.docx", "A 17632-2022")</f>
         <v/>
       </c>
       <c r="AD78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 30076-2023 tillsynsbegäran mail.docx", "A 30076-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 17632-2022 tillsynsbegäran mail.docx", "A 17632-2022")</f>
         <v/>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 34584-2025</t>
+          <t>A 34955-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -9809,10 +9808,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45846</v>
+        <v>44796</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9826,20 +9825,20 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="J79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -9854,7 +9853,7 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R79" t="n">
         <v>0</v>
@@ -9870,39 +9869,35 @@
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34584-2025 artfynd.xlsx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 34955-2022 artfynd.xlsx", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="X79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34584-2025 karta.png", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 34955-2022 karta.png", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="Y79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34584-2025 georefererad karta.tif", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 34955-2022 georefererad karta.tif", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="AA79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34584-2025 FSC-klagomål.docx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 34955-2022 FSC-klagomål.docx", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="AB79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34584-2025 FSC-klagomål mail.docx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 34955-2022 FSC-klagomål mail.docx", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="AC79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34584-2025 tillsynsbegäran.docx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 34955-2022 tillsynsbegäran.docx", "A 34955-2022")</f>
         <v/>
       </c>
       <c r="AD79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34584-2025 tillsynsbegäran mail.docx", "A 34584-2025")</f>
-        <v/>
-      </c>
-      <c r="AE79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 34584-2025 prioriterade fågelarter.docx", "A 34584-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 34955-2022 tillsynsbegäran mail.docx", "A 34955-2022")</f>
         <v/>
       </c>
     </row>
@@ -9926,7 +9921,7 @@
         <v>44991</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10023,7 +10018,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 24167-2024</t>
+          <t>A 44356-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -10033,14 +10028,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45456</v>
+        <v>45573</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10052,8 +10047,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>1</v>
@@ -10089,46 +10089,46 @@
         <v>1</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 24167-2024 artfynd.xlsx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 44356-2024 artfynd.xlsx", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="X81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 24167-2024 karta.png", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 44356-2024 karta.png", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="Y81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 24167-2024 georefererad karta.tif", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 44356-2024 georefererad karta.tif", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="AA81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 24167-2024 FSC-klagomål.docx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 44356-2024 FSC-klagomål.docx", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="AB81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 24167-2024 FSC-klagomål mail.docx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 44356-2024 FSC-klagomål mail.docx", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="AC81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 24167-2024 tillsynsbegäran.docx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 44356-2024 tillsynsbegäran.docx", "A 44356-2024")</f>
         <v/>
       </c>
       <c r="AD81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 24167-2024 tillsynsbegäran mail.docx", "A 24167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 44356-2024 tillsynsbegäran mail.docx", "A 44356-2024")</f>
         <v/>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 37287-2023</t>
+          <t>A 33231-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -10142,10 +10142,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45156</v>
+        <v>45518</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10157,17 +10157,22 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -10182,7 +10187,7 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
         <v>0</v>
@@ -10194,46 +10199,46 @@
         <v>1</v>
       </c>
       <c r="U82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>Mindre tåtelsmygare</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="W82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 37287-2023 artfynd.xlsx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 33231-2024 artfynd.xlsx", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="X82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 37287-2023 karta.png", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 33231-2024 karta.png", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="Y82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 37287-2023 georefererad karta.tif", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 33231-2024 georefererad karta.tif", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="AA82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 37287-2023 FSC-klagomål.docx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 33231-2024 FSC-klagomål.docx", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="AB82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 37287-2023 FSC-klagomål mail.docx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 33231-2024 FSC-klagomål mail.docx", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="AC82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 37287-2023 tillsynsbegäran.docx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 33231-2024 tillsynsbegäran.docx", "A 33231-2024")</f>
         <v/>
       </c>
       <c r="AD82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 37287-2023 tillsynsbegäran mail.docx", "A 37287-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 33231-2024 tillsynsbegäran mail.docx", "A 33231-2024")</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 44356-2024</t>
+          <t>A 24167-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -10243,14 +10248,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45573</v>
+        <v>45456</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10262,13 +10267,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J83" t="n">
         <v>1</v>
@@ -10304,39 +10304,39 @@
         <v>1</v>
       </c>
       <c r="U83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 44356-2024 artfynd.xlsx", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 24167-2024 artfynd.xlsx", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="X83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 44356-2024 karta.png", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 24167-2024 karta.png", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="Y83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 44356-2024 georefererad karta.tif", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 24167-2024 georefererad karta.tif", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="AA83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 44356-2024 FSC-klagomål.docx", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 24167-2024 FSC-klagomål.docx", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="AB83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 44356-2024 FSC-klagomål mail.docx", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 24167-2024 FSC-klagomål mail.docx", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="AC83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 44356-2024 tillsynsbegäran.docx", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 24167-2024 tillsynsbegäran.docx", "A 24167-2024")</f>
         <v/>
       </c>
       <c r="AD83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 44356-2024 tillsynsbegäran mail.docx", "A 44356-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 24167-2024 tillsynsbegäran mail.docx", "A 24167-2024")</f>
         <v/>
       </c>
     </row>
@@ -10360,7 +10360,7 @@
         <v>46224</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 17632-2022</t>
+          <t>A 16013-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -10467,10 +10467,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44680</v>
+        <v>45026</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10483,19 +10483,19 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N85" t="n">
         <v>0</v>
@@ -10507,10 +10507,10 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S85" t="n">
         <v>1</v>
@@ -10523,35 +10523,35 @@
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="W85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 17632-2022 artfynd.xlsx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 16013-2023 artfynd.xlsx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="X85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 17632-2022 karta.png", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 16013-2023 karta.png", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="Y85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 17632-2022 georefererad karta.tif", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 16013-2023 georefererad karta.tif", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AA85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 17632-2022 FSC-klagomål.docx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 16013-2023 FSC-klagomål.docx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AB85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 17632-2022 FSC-klagomål mail.docx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 16013-2023 FSC-klagomål mail.docx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AC85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 17632-2022 tillsynsbegäran.docx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 16013-2023 tillsynsbegäran.docx", "A 16013-2023")</f>
         <v/>
       </c>
       <c r="AD85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 17632-2022 tillsynsbegäran mail.docx", "A 17632-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 16013-2023 tillsynsbegäran mail.docx", "A 16013-2023")</f>
         <v/>
       </c>
     </row>
@@ -10575,7 +10575,7 @@
         <v>44509</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>44696</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>44782</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         <v>44550</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>44586</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>44582</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>44694</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>44518</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>44796</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 24158-2023</t>
+          <t>A 15637-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -11264,10 +11264,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45079</v>
+        <v>44662</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11279,13 +11279,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -11328,7 +11323,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 21509-2024</t>
+          <t>A 19786-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -11342,10 +11337,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45441</v>
+        <v>45050</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11363,7 +11358,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.9</v>
+        <v>8.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -11406,7 +11401,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 42832-2022</t>
+          <t>A 48205-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -11416,14 +11411,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44832</v>
+        <v>45205</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11435,8 +11430,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>1.1</v>
+        <v>7.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -11479,7 +11479,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 42841-2022</t>
+          <t>A 15743-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -11489,14 +11489,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44832</v>
+        <v>45021</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -11552,7 +11552,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 4724-2026</t>
+          <t>A 15739-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -11566,10 +11566,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46048</v>
+        <v>45021</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -11625,7 +11625,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 4734-2026</t>
+          <t>A 7787-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -11639,10 +11639,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46048</v>
+        <v>45348</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11655,7 +11655,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -11698,7 +11698,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 3818-2022</t>
+          <t>A 72367-2021</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -11712,10 +11712,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44587</v>
+        <v>44545</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11728,7 +11728,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -11771,7 +11771,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 10244-2026</t>
+          <t>A 37954-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -11785,10 +11785,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46076</v>
+        <v>45881</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11800,13 +11800,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>8.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -11849,7 +11844,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 10249-2026</t>
+          <t>A 33931-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -11863,10 +11858,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46076</v>
+        <v>44790</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11878,13 +11873,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -11927,7 +11917,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 10562-2026</t>
+          <t>A 55873-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -11941,10 +11931,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46077</v>
+        <v>45973</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11958,11 +11948,11 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -12005,7 +11995,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 19782-2023</t>
+          <t>A 24158-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -12019,10 +12009,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45050</v>
+        <v>45079</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12036,11 +12026,11 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -12083,7 +12073,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 14626-2023</t>
+          <t>A 4724-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -12097,10 +12087,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45012</v>
+        <v>46048</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12112,13 +12102,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -12161,7 +12146,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 12841-2026</t>
+          <t>A 4734-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -12175,10 +12160,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46091</v>
+        <v>46048</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12190,13 +12175,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -12239,7 +12219,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 56378-2023</t>
+          <t>A 42714-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -12253,10 +12233,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45236</v>
+        <v>44832</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12268,13 +12248,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -12317,7 +12292,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 11728-2023</t>
+          <t>A 35682-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -12327,14 +12302,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44993</v>
+        <v>44799</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12348,11 +12323,11 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -12395,7 +12370,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 20904-2023</t>
+          <t>A 11728-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -12409,10 +12384,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45060</v>
+        <v>44993</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12426,11 +12401,11 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -12473,7 +12448,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 55873-2025</t>
+          <t>A 5567-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -12487,10 +12462,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45973</v>
+        <v>44595</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12502,13 +12477,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -12551,7 +12521,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 19246-2026</t>
+          <t>A 42832-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -12565,10 +12535,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46132</v>
+        <v>44832</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12580,13 +12550,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -12629,7 +12594,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 42829-2022</t>
+          <t>A 24665-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -12639,14 +12604,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44832</v>
+        <v>45084</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12659,7 +12624,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -12702,7 +12667,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 48205-2023</t>
+          <t>A 10244-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -12716,10 +12681,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45205</v>
+        <v>46076</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12737,7 +12702,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>7.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -12780,7 +12745,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 32808-2024</t>
+          <t>A 10562-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -12794,10 +12759,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45516</v>
+        <v>46077</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12815,7 +12780,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -12858,7 +12823,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 20535-2026</t>
+          <t>A 42841-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -12872,10 +12837,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46140</v>
+        <v>44832</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12887,13 +12852,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -12936,7 +12896,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 33931-2022</t>
+          <t>A 42829-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -12946,14 +12906,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44790</v>
+        <v>44832</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12966,7 +12926,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -13009,7 +12969,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 22662-2023</t>
+          <t>A 12841-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -13019,14 +12979,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45071</v>
+        <v>46091</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13040,11 +13000,11 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.6</v>
+        <v>4.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -13087,7 +13047,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 49058-2024</t>
+          <t>A 2867-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -13101,10 +13061,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45594</v>
+        <v>45315</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13118,11 +13078,11 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -13165,7 +13125,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 24201-2026</t>
+          <t>A 3085-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -13179,10 +13139,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46168</v>
+        <v>44946</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13194,8 +13154,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -13238,7 +13203,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 25450-2024</t>
+          <t>A 19246-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -13248,14 +13213,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45463</v>
+        <v>46132</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13269,11 +13234,11 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -13316,7 +13281,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 24665-2023</t>
+          <t>A 32808-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -13330,10 +13295,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45084</v>
+        <v>45516</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13345,8 +13310,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -13389,7 +13359,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 72367-2021</t>
+          <t>A 20904-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -13399,14 +13369,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44545</v>
+        <v>45060</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13418,8 +13388,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -13462,7 +13437,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 22628-2026</t>
+          <t>A 2660-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -13476,10 +13451,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46155</v>
+        <v>45310</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13491,13 +13466,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -13540,7 +13510,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 42714-2022</t>
+          <t>A 49058-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -13554,10 +13524,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44832</v>
+        <v>45594</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13569,8 +13539,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>1.1</v>
+        <v>11.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -13613,7 +13588,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 37954-2025</t>
+          <t>A 20535-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -13623,14 +13598,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45881</v>
+        <v>46140</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13642,8 +13617,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>9.5</v>
+        <v>2.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -13686,7 +13666,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 19099-2022</t>
+          <t>A 14626-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -13700,10 +13680,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44691</v>
+        <v>45012</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13717,11 +13697,11 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -13764,7 +13744,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 25780-2023</t>
+          <t>A 25450-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -13778,10 +13758,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45090</v>
+        <v>45463</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13793,8 +13773,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -13837,7 +13822,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 31061-2026</t>
+          <t>A 24201-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -13851,10 +13836,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46215</v>
+        <v>46168</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13866,13 +13851,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -13915,7 +13895,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 35682-2022</t>
+          <t>A 19782-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -13929,10 +13909,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44799</v>
+        <v>45050</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13946,11 +13926,11 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.5</v>
+        <v>5.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -13993,7 +13973,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 2867-2024</t>
+          <t>A 7848-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -14007,10 +13987,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45315</v>
+        <v>44608</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14022,13 +14002,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -14071,7 +14046,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 2660-2024</t>
+          <t>A 56378-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -14085,10 +14060,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45310</v>
+        <v>45236</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14100,8 +14075,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -14144,7 +14124,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 5567-2022</t>
+          <t>A 19099-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -14158,10 +14138,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44595</v>
+        <v>44691</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14173,8 +14153,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -14217,7 +14202,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 32223-2026</t>
+          <t>A 22628-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -14231,10 +14216,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46237</v>
+        <v>46155</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14248,11 +14233,11 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>8.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -14295,7 +14280,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 32501-2026</t>
+          <t>A 3818-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -14305,14 +14290,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46239</v>
+        <v>44587</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14325,7 +14310,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -14368,7 +14353,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 3085-2023</t>
+          <t>A 31061-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -14382,10 +14367,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44946</v>
+        <v>46215</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14399,11 +14384,11 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>13</v>
+        <v>4.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -14446,7 +14431,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 7848-2022</t>
+          <t>A 21509-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -14460,10 +14445,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44608</v>
+        <v>45441</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14475,8 +14460,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -14519,7 +14509,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 33933-2026</t>
+          <t>A 22662-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -14529,14 +14519,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46248</v>
+        <v>45071</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14550,11 +14540,11 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -14597,7 +14587,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 15743-2023</t>
+          <t>A 25780-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -14611,10 +14601,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45021</v>
+        <v>45090</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14627,7 +14617,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -14670,7 +14660,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 15637-2022</t>
+          <t>A 32501-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -14680,14 +14670,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44662</v>
+        <v>46239</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14700,7 +14690,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -14743,7 +14733,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 19786-2023</t>
+          <t>A 32223-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -14757,10 +14747,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45050</v>
+        <v>46237</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14774,11 +14764,11 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -14821,7 +14811,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 7787-2024</t>
+          <t>A 33933-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -14835,10 +14825,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45348</v>
+        <v>46248</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14850,8 +14840,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -14894,24 +14889,24 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 15739-2023</t>
+          <t>S 3543-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45021</v>
+        <v>44734</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14923,8 +14918,13 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -14967,7 +14967,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S 3543-2022</t>
+          <t>S 3542-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -14984,7 +14984,7 @@
         <v>44734</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15002,7 +15002,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -15042,10 +15042,10 @@
       </c>
       <c r="V144" s="2" t="inlineStr"/>
     </row>
-    <row r="145" ht="15" customHeight="1">
+    <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S 3542-2022</t>
+          <t>S 2172-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -15055,14 +15055,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44734</v>
+        <v>46251</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15074,13 +15074,8 @@
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -15119,79 +15114,6 @@
         <v>0</v>
       </c>
       <c r="V145" s="2" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>S 2172-2026</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D146" s="1" t="n">
-        <v>46251</v>
-      </c>
-      <c r="E146" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="I146" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J146" t="n">
-        <v>0</v>
-      </c>
-      <c r="K146" t="n">
-        <v>0</v>
-      </c>
-      <c r="L146" t="n">
-        <v>0</v>
-      </c>
-      <c r="M146" t="n">
-        <v>0</v>
-      </c>
-      <c r="N146" t="n">
-        <v>0</v>
-      </c>
-      <c r="O146" t="n">
-        <v>0</v>
-      </c>
-      <c r="P146" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
-      <c r="R146" t="n">
-        <v>0</v>
-      </c>
-      <c r="S146" t="n">
-        <v>0</v>
-      </c>
-      <c r="T146" t="n">
-        <v>0</v>
-      </c>
-      <c r="U146" t="n">
-        <v>0</v>
-      </c>
-      <c r="V146" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt SURAHAMMAR.xlsx
+++ b/Översikt SURAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45470</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>45684</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 39697-2025</t>
+          <t>A 31280-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45890</v>
+        <v>45504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,23 +964,23 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>25.7</v>
+        <v>6.9</v>
       </c>
       <c r="J4" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -992,21 +992,182 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S4" t="n">
         <v>44</v>
       </c>
       <c r="T4" t="n">
-        <v>243</v>
+        <v>93</v>
       </c>
       <c r="U4" t="n">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Gränsticka
+Knärot
+Liten hornflikmossa
+Spadskinn
+Torrmusseron
+Apelsinticka
+Fjällig taggsvamp s.str.
+Grantaggsvamp
+Gropticka
+Kattfotslav
+Knölspindel
+Kötticka
+Mjölsvärting
+Nordfladdermus
+Nordtagging
+Persiljespindling
+Rynkskinn
+Skarp dropptaggsvamp
+Svartvit taggsvamp
+Tallkötticka
+Tallticka
+Talltita
+Ullticka
+Vaddporing
+Vedskivlav
+Vedtrappmossa
+Vågticka
+Bollvitmossa
+Bronshjon
+Flagellkvastmossa
+Grönpyrola
+Kornknutmossa
+Mindre märgborre
+Rostfläck
+Rödgul trumpetsvamp
+Smal svampklubba
+Thomsons trägnagare
+Vedticka
+Vågbandad barkbock
+Blåsippa
+Kungsfågel
+Mindre vattensalamander
+Fläcknycklar
+Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31280-2024 artfynd.xlsx", "A 31280-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31280-2024 karta.png", "A 31280-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31280-2024 georefererad karta.tif", "A 31280-2024")</f>
+        <v/>
+      </c>
+      <c r="Z4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 31280-2024 karta knärot.png", "A 31280-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31280-2024 FSC-klagomål.docx", "A 31280-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31280-2024 FSC-klagomål mail.docx", "A 31280-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31280-2024 tillsynsbegäran.docx", "A 31280-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31280-2024 tillsynsbegäran mail.docx", "A 31280-2024")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 31280-2024 prioriterade fågelarter.docx", "A 31280-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 39697-2025</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45890</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>28</v>
+      </c>
+      <c r="K5" t="n">
+        <v>7</v>
+      </c>
+      <c r="L5" t="n">
+        <v>14</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>16</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>44</v>
+      </c>
+      <c r="T5" t="n">
+        <v>245</v>
+      </c>
+      <c r="U5" t="n">
+        <v>109</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Grönfink
 Knärot
@@ -1054,201 +1215,40 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 39697-2025 artfynd.xlsx", "A 39697-2025")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 39697-2025 karta.png", "A 39697-2025")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 39697-2025 georefererad karta.tif", "A 39697-2025")</f>
         <v/>
       </c>
-      <c r="Z4">
+      <c r="Z5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 39697-2025 karta knärot.png", "A 39697-2025")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 39697-2025 FSC-klagomål.docx", "A 39697-2025")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 39697-2025 FSC-klagomål mail.docx", "A 39697-2025")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 39697-2025 tillsynsbegäran.docx", "A 39697-2025")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 39697-2025 tillsynsbegäran mail.docx", "A 39697-2025")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 39697-2025 prioriterade fågelarter.docx", "A 39697-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 31280-2024</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45504</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J5" t="n">
-        <v>8</v>
-      </c>
-      <c r="K5" t="n">
-        <v>12</v>
-      </c>
-      <c r="L5" t="n">
-        <v>22</v>
-      </c>
-      <c r="M5" t="n">
-        <v>5</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>27</v>
-      </c>
-      <c r="R5" t="n">
-        <v>5</v>
-      </c>
-      <c r="S5" t="n">
-        <v>44</v>
-      </c>
-      <c r="T5" t="n">
-        <v>93</v>
-      </c>
-      <c r="U5" t="n">
-        <v>91</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Gränsticka
-Knärot
-Liten hornflikmossa
-Spadskinn
-Torrmusseron
-Apelsinticka
-Fjällig taggsvamp s.str.
-Grantaggsvamp
-Gropticka
-Kattfotslav
-Knölspindel
-Kötticka
-Mjölsvärting
-Nordfladdermus
-Nordtagging
-Persiljespindling
-Rynkskinn
-Skarp dropptaggsvamp
-Svartvit taggsvamp
-Tallkötticka
-Tallticka
-Talltita
-Ullticka
-Vaddporing
-Vedskivlav
-Vedtrappmossa
-Vågticka
-Bollvitmossa
-Bronshjon
-Flagellkvastmossa
-Grönpyrola
-Kornknutmossa
-Mindre märgborre
-Rostfläck
-Rödgul trumpetsvamp
-Smal svampklubba
-Thomsons trägnagare
-Vedticka
-Vågbandad barkbock
-Blåsippa
-Kungsfågel
-Mindre vattensalamander
-Fläcknycklar
-Lopplummer (aggregat)</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31280-2024 artfynd.xlsx", "A 31280-2024")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31280-2024 karta.png", "A 31280-2024")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31280-2024 georefererad karta.tif", "A 31280-2024")</f>
-        <v/>
-      </c>
-      <c r="Z5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 31280-2024 karta knärot.png", "A 31280-2024")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31280-2024 FSC-klagomål.docx", "A 31280-2024")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31280-2024 FSC-klagomål mail.docx", "A 31280-2024")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31280-2024 tillsynsbegäran.docx", "A 31280-2024")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31280-2024 tillsynsbegäran mail.docx", "A 31280-2024")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 31280-2024 prioriterade fågelarter.docx", "A 31280-2024")</f>
         <v/>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
         <v>45582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45169</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45139</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45782</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>45282</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S 2049-2026</t>
+          <t>S 920-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1936,14 +1936,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46216</v>
+        <v>46111</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1957,23 +1957,23 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>11.9</v>
+        <v>66.5</v>
       </c>
       <c r="J11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
         <v>5</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1985,10 +1985,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1997,9 +1997,137 @@
         <v>24</v>
       </c>
       <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp
+Motaggsvamp
+Skogshare
+Tallkötticka
+Talltita
+Bollvitmossa
+Grönpyrola
+Järpe
+Kärrviol
+Linnea
+Mattlummer
+Tjäder
+Orre
+Fläcknycklar
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/S 920-2026 artfynd.xlsx", "S 920-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/S 920-2026 karta.png", "S 920-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/S 920-2026 georefererad karta.tif", "S 920-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/S 920-2026 FSC-klagomål.docx", "S 920-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/S 920-2026 FSC-klagomål mail.docx", "S 920-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/S 920-2026 tillsynsbegäran.docx", "S 920-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/S 920-2026 tillsynsbegäran mail.docx", "S 920-2026")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/S 920-2026 prioriterade fågelarter.docx", "S 920-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>S 2049-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="n">
+        <v>24</v>
+      </c>
+      <c r="U12" t="n">
         <v>9</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Brunlångöra
@@ -2018,120 +2146,120 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/S 2049-2026 artfynd.xlsx", "S 2049-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/S 2049-2026 karta.png", "S 2049-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/S 2049-2026 georefererad karta.tif", "S 2049-2026")</f>
         <v/>
       </c>
-      <c r="Z11">
+      <c r="Z12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/S 2049-2026 karta knärot.png", "S 2049-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/S 2049-2026 FSC-klagomål.docx", "S 2049-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/S 2049-2026 FSC-klagomål mail.docx", "S 2049-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/S 2049-2026 tillsynsbegäran.docx", "S 2049-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/S 2049-2026 tillsynsbegäran mail.docx", "S 2049-2026")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/S 2049-2026 prioriterade fågelarter.docx", "S 2049-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>S 2048-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D13" s="1" t="n">
         <v>46216</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="E13" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>VÄSTMANLANDS LÄN</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="I13" t="n">
         <v>25.7</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J13" t="n">
         <v>9</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K13" t="n">
         <v>3</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L13" t="n">
         <v>6</v>
       </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>7</v>
       </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
         <v>15</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T13" t="n">
         <v>24</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U13" t="n">
         <v>6</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Brunlångöra
@@ -2150,120 +2278,120 @@
 Svartvit flugsnappare</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/S 2048-2026 artfynd.xlsx", "S 2048-2026")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/S 2048-2026 karta.png", "S 2048-2026")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/S 2048-2026 georefererad karta.tif", "S 2048-2026")</f>
         <v/>
       </c>
-      <c r="Z12">
+      <c r="Z13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/S 2048-2026 karta knärot.png", "S 2048-2026")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/S 2048-2026 FSC-klagomål.docx", "S 2048-2026")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/S 2048-2026 FSC-klagomål mail.docx", "S 2048-2026")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/S 2048-2026 tillsynsbegäran.docx", "S 2048-2026")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/S 2048-2026 tillsynsbegäran mail.docx", "S 2048-2026")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/S 2048-2026 prioriterade fågelarter.docx", "S 2048-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 32212-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D14" s="1" t="n">
         <v>46237</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="E14" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>VÄSTMANLANDS LÄN</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="I14" t="n">
         <v>9.6</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J14" t="n">
         <v>14</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>4</v>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>5</v>
       </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
         <v>14</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>15</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Pärluggla
 Björktrast
@@ -2281,116 +2409,116 @@
 Trädlärka</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 32212-2026 artfynd.xlsx", "A 32212-2026")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 32212-2026 karta.png", "A 32212-2026")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 32212-2026 georefererad karta.tif", "A 32212-2026")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 32212-2026 FSC-klagomål.docx", "A 32212-2026")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 32212-2026 FSC-klagomål mail.docx", "A 32212-2026")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 32212-2026 tillsynsbegäran.docx", "A 32212-2026")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 32212-2026 tillsynsbegäran mail.docx", "A 32212-2026")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 32212-2026 prioriterade fågelarter.docx", "A 32212-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>S 1051-2022</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D15" s="1" t="n">
         <v>44613</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="E15" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>VÄSTMANLANDS LÄN</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="I15" t="n">
         <v>12.3</v>
       </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
         <v>3</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L15" t="n">
         <v>9</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M15" t="n">
         <v>2</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>11</v>
       </c>
-      <c r="R14" t="n">
+      <c r="R15" t="n">
         <v>2</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S15" t="n">
         <v>14</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T15" t="n">
         <v>53</v>
       </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Skrovlig taggsvamp
@@ -2408,112 +2536,112 @@
 Vedticka</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/S 1051-2022 artfynd.xlsx", "S 1051-2022")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/S 1051-2022 karta.png", "S 1051-2022")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/S 1051-2022 georefererad karta.tif", "S 1051-2022")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/S 1051-2022 FSC-klagomål.docx", "S 1051-2022")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/S 1051-2022 FSC-klagomål mail.docx", "S 1051-2022")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/S 1051-2022 tillsynsbegäran.docx", "S 1051-2022")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/S 1051-2022 tillsynsbegäran mail.docx", "S 1051-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>S 610-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Skogsgödsling</t>
         </is>
       </c>
-      <c r="D15" s="1" t="n">
+      <c r="D16" s="1" t="n">
         <v>46085</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="E16" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>VÄSTMANLANDS LÄN</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="I16" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J16" t="n">
         <v>7</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K16" t="n">
         <v>2</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L16" t="n">
         <v>6</v>
       </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>7</v>
       </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
         <v>14</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T16" t="n">
         <v>37</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U16" t="n">
         <v>4</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Brunfläckig pärlemorfjäril
 Berggräsfjäril
@@ -2531,111 +2659,111 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/S 610-2026 artfynd.xlsx", "S 610-2026")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/S 610-2026 karta.png", "S 610-2026")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/S 610-2026 georefererad karta.tif", "S 610-2026")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/S 610-2026 FSC-klagomål.docx", "S 610-2026")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/S 610-2026 FSC-klagomål mail.docx", "S 610-2026")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/S 610-2026 tillsynsbegäran.docx", "S 610-2026")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/S 610-2026 tillsynsbegäran mail.docx", "S 610-2026")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/S 610-2026 prioriterade fågelarter.docx", "S 610-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 20389-2024</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D17" s="1" t="n">
         <v>45435</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="E17" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>VÄSTMANLANDS LÄN</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="I17" t="n">
         <v>1.5</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J17" t="n">
         <v>3</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K17" t="n">
         <v>7</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L17" t="n">
         <v>4</v>
       </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>5</v>
       </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
         <v>13</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>32</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>29</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Gropticka
@@ -2652,120 +2780,120 @@
 Havsörn</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 20389-2024 artfynd.xlsx", "A 20389-2024")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 20389-2024 karta.png", "A 20389-2024")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 20389-2024 georefererad karta.tif", "A 20389-2024")</f>
         <v/>
       </c>
-      <c r="Z16">
+      <c r="Z17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/knärot/A 20389-2024 karta knärot.png", "A 20389-2024")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 20389-2024 FSC-klagomål.docx", "A 20389-2024")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 20389-2024 FSC-klagomål mail.docx", "A 20389-2024")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 20389-2024 tillsynsbegäran.docx", "A 20389-2024")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 20389-2024 tillsynsbegäran mail.docx", "A 20389-2024")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 20389-2024 prioriterade fågelarter.docx", "A 20389-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 31059-2026</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D18" s="1" t="n">
         <v>46215</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="E18" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>VÄSTMANLANDS LÄN</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>SURAHAMMAR</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="I18" t="n">
         <v>2</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J18" t="n">
         <v>11</v>
       </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
         <v>5</v>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>6</v>
       </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
         <v>13</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T18" t="n">
         <v>26</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U18" t="n">
         <v>3</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Bombmurkla
 Brunlångöra
@@ -2782,161 +2910,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31059-2026 artfynd.xlsx", "A 31059-2026")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31059-2026 karta.png", "A 31059-2026")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31059-2026 georefererad karta.tif", "A 31059-2026")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31059-2026 FSC-klagomål.docx", "A 31059-2026")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31059-2026 FSC-klagomål mail.docx", "A 31059-2026")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31059-2026 tillsynsbegäran.docx", "A 31059-2026")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31059-2026 tillsynsbegäran mail.docx", "A 31059-2026")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 31059-2026 prioriterade fågelarter.docx", "A 31059-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>S 920-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Skogsgödsling</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46111</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="J18" t="n">
-        <v>7</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>4</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>4</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>12</v>
-      </c>
-      <c r="T18" t="n">
-        <v>21</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Dofttaggsvamp
-Skogshare
-Tallkötticka
-Talltita
-Bollvitmossa
-Grönpyrola
-Järpe
-Mattlummer
-Tjäder
-Orre
-Fläcknycklar
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/S 920-2026 artfynd.xlsx", "S 920-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/S 920-2026 karta.png", "S 920-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/S 920-2026 georefererad karta.tif", "S 920-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/S 920-2026 FSC-klagomål.docx", "S 920-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/S 920-2026 FSC-klagomål mail.docx", "S 920-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/S 920-2026 tillsynsbegäran.docx", "S 920-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/S 920-2026 tillsynsbegäran mail.docx", "S 920-2026")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/S 920-2026 prioriterade fågelarter.docx", "S 920-2026")</f>
         <v/>
       </c>
     </row>
@@ -2960,7 +2963,7 @@
         <v>45890</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3084,7 +3087,7 @@
         <v>44832</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3203,7 +3206,7 @@
         <v>45523</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3331,7 +3334,7 @@
         <v>45070</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3454,7 +3457,7 @@
         <v>44565</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3560,7 +3563,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31060-2026</t>
+          <t>A 44798-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3574,10 +3577,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46215</v>
+        <v>45574</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3591,26 +3594,26 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>7.8</v>
+        <v>4.4</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
         <v>7</v>
       </c>
-      <c r="K24" t="n">
-        <v>2</v>
-      </c>
-      <c r="L24" t="n">
-        <v>2</v>
-      </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3619,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -3628,12 +3631,130 @@
         <v>9</v>
       </c>
       <c r="T24" t="n">
+        <v>26</v>
+      </c>
+      <c r="U24" t="n">
+        <v>10</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Rosetticka
+Brunklöver
+Gropticka
+Persiljespindling
+Scharlakansvaxing
+Svinrot
+Ullticka
+Vågticka
+Brandticka</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 44798-2024 artfynd.xlsx", "A 44798-2024")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 44798-2024 karta.png", "A 44798-2024")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 44798-2024 georefererad karta.tif", "A 44798-2024")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 44798-2024 FSC-klagomål.docx", "A 44798-2024")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 44798-2024 FSC-klagomål mail.docx", "A 44798-2024")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 44798-2024 tillsynsbegäran.docx", "A 44798-2024")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 44798-2024 tillsynsbegäran mail.docx", "A 44798-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 31060-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>SURAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J25" t="n">
+        <v>7</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
         <v>9</v>
       </c>
-      <c r="U24" t="n">
+      <c r="T25" t="n">
+        <v>9</v>
+      </c>
+      <c r="U25" t="n">
         <v>3</v>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Bombmurkla
 Brunlångöra
@@ -3646,154 +3767,36 @@
 Vanlig groda</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 31060-2026 artfynd.xlsx", "A 31060-2026")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 31060-2026 karta.png", "A 31060-2026")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 31060-2026 georefererad karta.tif", "A 31060-2026")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 31060-2026 FSC-klagomål.docx", "A 31060-2026")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 31060-2026 FSC-klagomål mail.docx", "A 31060-2026")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 31060-2026 tillsynsbegäran.docx", "A 31060-2026")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 31060-2026 tillsynsbegäran mail.docx", "A 31060-2026")</f>
         <v/>
       </c>
-      <c r="AE24">
+      <c r="AE25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1907/fåglar/A 31060-2026 prioriterade fågelarter.docx", "A 31060-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 44798-2024</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>45574</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>SURAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" t="n">
-        <v>7</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>8</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S25" t="n">
-        <v>9</v>
-      </c>
-      <c r="T25" t="n">
-        <v>26</v>
-      </c>
-      <c r="U25" t="n">
-        <v>10</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Rosetticka
-Brunklöver
-Gropticka
-Persiljespindling
-Scharlakansvaxing
-Svinrot
-Ullticka
-Vågticka
-Brandticka</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/artfynd/A 44798-2024 artfynd.xlsx", "A 44798-2024")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor/A 44798-2024 karta.png", "A 44798-2024")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/kartor_geotiff/A 44798-2024 georefererad karta.tif", "A 44798-2024")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomål/A 44798-2024 FSC-klagomål.docx", "A 44798-2024")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/klagomålsmail/A 44798-2024 FSC-klagomål mail.docx", "A 44798-2024")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsyn/A 44798-2024 tillsynsbegäran.docx", "A 44798-2024")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1907/tillsynsmail/A 44798-2024 tillsynsbegäran mail.docx", "A 44798-2024")</f>
         <v/>
       </c>
     </row>
@@ -3817,7 +3820,7 @@
         <v>45435</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3933,7 +3936,7 @@
         <v>44518</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4036,7 +4039,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 38172-2024</t>
+          <t>A 56299-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4046,14 +4049,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45545</v>
+        <v>44477</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4067,23 +4070,23 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="J28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="